--- a/insect_analysis_history.xlsx
+++ b/insect_analysis_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>วันที่ตรวจ</t>
   </si>
@@ -52,6 +52,9 @@
     <t>2026-03-08</t>
   </si>
   <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
     <t>11:45:46</t>
   </si>
   <si>
@@ -64,22 +67,37 @@
     <t>15:04:54</t>
   </si>
   <si>
+    <t>16:17:24</t>
+  </si>
+  <si>
     <t>SB</t>
   </si>
   <si>
+    <t>MDC</t>
+  </si>
+  <si>
     <t>บรรจุ</t>
   </si>
   <si>
+    <t>บริการลูกค้า</t>
+  </si>
+  <si>
     <t>ห้องเก็บภาชนะ ชั้น 2</t>
   </si>
   <si>
     <t>ห้องบรรจุ SP</t>
   </si>
   <si>
+    <t>เครื่องที่ 2</t>
+  </si>
+  <si>
     <t>ฺฤฆ</t>
   </si>
   <si>
     <t>Pratchayaw</t>
+  </si>
+  <si>
+    <t>Pratcahyaw</t>
   </si>
   <si>
     <t>หกห</t>
@@ -443,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -483,25 +501,25 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>207</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -509,25 +527,25 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>207</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -535,25 +553,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>207</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -561,25 +579,25 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>152</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -587,30 +605,59 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>207</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>207</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
         <v>202</v>
       </c>
     </row>

--- a/insect_analysis_history.xlsx
+++ b/insect_analysis_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="49">
   <si>
     <t>วันที่ตรวจ</t>
   </si>
@@ -46,6 +46,9 @@
     <t>จำนวนแมลงอื่นๆ</t>
   </si>
   <si>
+    <t>รูปภาพ</t>
+  </si>
+  <si>
     <t>2026-03-09</t>
   </si>
   <si>
@@ -55,6 +58,12 @@
     <t>2026-03-02</t>
   </si>
   <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
     <t>11:45:46</t>
   </si>
   <si>
@@ -70,6 +79,39 @@
     <t>16:17:24</t>
   </si>
   <si>
+    <t>15:16:41</t>
+  </si>
+  <si>
+    <t>15:18:07</t>
+  </si>
+  <si>
+    <t>15:18:50</t>
+  </si>
+  <si>
+    <t>15:30:55</t>
+  </si>
+  <si>
+    <t>16:01:35</t>
+  </si>
+  <si>
+    <t>16:47:34</t>
+  </si>
+  <si>
+    <t>16:51:16</t>
+  </si>
+  <si>
+    <t>08:50:28</t>
+  </si>
+  <si>
+    <t>08:50:52</t>
+  </si>
+  <si>
+    <t>08:51:28</t>
+  </si>
+  <si>
+    <t>08:54:36</t>
+  </si>
+  <si>
     <t>SB</t>
   </si>
   <si>
@@ -91,6 +133,12 @@
     <t>เครื่องที่ 2</t>
   </si>
   <si>
+    <t>ห้อง Mix SP</t>
+  </si>
+  <si>
+    <t>ห้อง Pack SP</t>
+  </si>
+  <si>
     <t>ฺฤฆ</t>
   </si>
   <si>
@@ -100,10 +148,19 @@
     <t>Pratcahyaw</t>
   </si>
   <si>
+    <t>BASS</t>
+  </si>
+  <si>
     <t>หกห</t>
   </si>
   <si>
     <t>ทดสอบ</t>
+  </si>
+  <si>
+    <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAgGBgcGBQgHBwcJCQgKDBQNDAsLDBkSEw8UHRofHh0aHBwgJC4nICIsIxwcKDcpLDAxNDQ0Hyc5PTgyPC4zNDL/2wBDAQkJCQwLDBgNDRgyIRwhMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjL/wAARCAQ0BfEDASIAAhEBAxEB/8QAHwAAAQUBAQEBAQEAAAAAAAAAAAECAwQFBgcICQoL/8QAtRAAAgEDAwIEAwUFBAQAAAF9AQIDAAQRBRIhMUEGE1FhByJxFDKBkaEII0KxwRVS0fAkM2JyggkKFhcYGRolJicoKSo0NTY3ODk6Q0RFRkdISUpTVFVWV1hZWmNkZWZnaGlqc3R1dnd4eXqDhIWGh4iJipKTlJWWl5iZmqKjpKWmp6ipqrKztLW2t7i5usLDxMXGx8jJytLT1NXW19jZ2uHi4+Tl5ufo6erx8vP09fb3+Pn6/8QAHwEAAwEBAQEBAQEBAQAAAAAAAAECAwQFBgcICQoL/8QAtREAAgECBAQDBAcFBAQAAQJ3AAECAxEEBSExBhJBUQdhcRMiMoEIFEKRobHBCSMzUvAVYnLRChYkNOEl8RcYGRomJygpKjU2Nzg5OkNERUZHSElKU1RVVldYWVpjZGVmZ2hpanN0dXZ3eHl6goOEhYaHiImKkpOUlZaXmJmaoqOkpaanqKmqsrO0tba3uLm6wsPExcbHyMnK0tPU1dbX2Nna4uPk5ebn6Onq8vP09fb3+Pn6/9oADAMBAAIRAxEAPwDstchiuvjJosE0EcyfY5SUkUMPrg13R0DRiDnSbE5GD/o6c/pXEakSPjdo+TwbGXH516RU9WZwW5lDwzoQ6aLpw/7dU/wqQeH9GU5Gk2IPtbp/hWlRTsi7Izv7C0jOf7Lss/8AXuv+FL/Yek/9Auy/8B1/wrQoosFjOOh6T0/suy/8B1/wpf7E0sjH9mWeP+uC/wCFaPFFFgsZp0HSHOW0uyP1t1/wpP8AhH9Gzn+ybH/wHT/CtKiiyCyM8aFpA6aVZD/t3X/Cl/sTSf8AoFWP/gOv+FX6KYyh/Ymlf9Ayy/78L/hQdE0s9dNsz9YF/wAK0KSlYDy260fTP+F26fbjTrQQ/wBlySGMQLgnPXGOtehLomlgfLptmB7QL/hXD3bBvjzp645XSpD+tekUrIiKRROj6ZjB060x6eQv+FJ/Ymkn/mGWf/gOv+FX6Kdi7Gf/AGHpP/QLsv8AwHX/AApn/COaJ/0B9P8A/AVP8K1OKKLCsZY8O6KowNH08D0Fsn+FH/CPaLkn+x7DJ7/Zk/wrUpKLBZGb/wAI/ov/AECLD/wGT/Cmnw1oZGDo2nH62qf4Vq0UWCyMb/hFPDv/AEAdL/8AAOP/AAobwn4dbltB0s/Wzj/wrYpaLBZGJ/wiPhw4zoGlcf8ATlH/AIUDwj4bB3Dw/pQPr9ij/wAK26KLBZHksPhzRG+NN3Ztounta/2UkohNqmzcXIJxjGeOtd1/whHhT/oWdG/8AIv8K5m1J/4XxfDr/wASiP8AD5jXotCRMUjn/wDhB/CeMf8ACMaN/wCAMX+FIfAnhMkk+GtI5/6co/8ACuioosVZHN/8IB4P/wChY0j/AMA4/wDCmn4feED/AMyxpP4WiD+ldNRRYLI5Vvhv4MY5PhrTc+0AFN/4Vp4LH/Mtaf8A9+q6uinYLI5A/C7wSf8AmW7L/vk/40w/CnwOevhy0/AsP612VFKwWRxZ+E/gVv8AmXbYfRnH9aY3wi8COOfD0PHpNKP5NXb0U7BZHC/8Kd8Af9C7H/3/AJv/AIqmt8G/AR/5gCD6Ty//ABVd5RQFjwrw98NfC2ofELxTpk9gWsrExCCLzmG3cgJ5znqa7Nvgn4Fb/mFSD6XD/wCNR+EW/wCLueNwOmbf/wBFLXo1JImKVjzv/hSXgfjGmzDHpcP/AI0h+CXgs/8ALpdD/t5avRaWixVkecD4I+DFORbXgPqLlqUfBjwzG26GbV4j6x3pFei0UWDlR52fg5ofbVdfH0vz/hSL8ItOjGE8Q+I1+moMK9GpKLC5Ued/8Klsh08SeJR/3EWoPwpjGPJ8WeJ4sf8AUQavRKKLIOVHnrfDG5JO3xx4pX/uIP8A403/AIVjfA5Xx34n/G9Y/wBa9EoosHIjzs/DfWV/1XxA8QKvo0m79SaRvhvreDs+IWvg+75/rXotFFg5EeJeAtG8U+LfDx1Obx1q1sRcSQhEwwIXvk10zeA/F6keV8RdRI7+ZbpTfgcd3w3hz94XU2frmvSaEtBKKsecHwX4537l+IVx7Zs4/wCWKd/wh/j3/ooL/wDgDF/hXo1JRYfKjzr/AIRDx8M4+IDfjYxf4Ug8JfEMf8z4h+tjH/hXo9JiiwcqPOf+EX+JCj5fHFs3+9Yr/hTF8O/E+M/8jhp0g/2rL/AV6TRQHKjzo6H8Tx/zNWlH/tzpDpHxSVfl8SaM597MivRqKYcp5z9g+KwHGsaET/17t/jSfZviwpH+n+H2/wC2Lf416PRQHKedeV8V8f8AHz4e/wC/T/41ieJfEnxN8K2MF5ef2FNFLcJbgRRvnc3TvXr9eb/GlmHhHTyo5Gq25H5mkDVh+/4rqc+R4fcem5hQbn4rA/8AIO0Aj/ru1ejCiiwcp5yL34qgc6XoR+k7Ug1H4qLndomit9LkivR8UUWDl8zzkav8UEG9/DmkuM/dW8IP8qX/AISH4k5/5E+w/wDA7/61eifjQfrQHL5nnh8R/EcH/kTLIj2v/wD61N/4Sf4jjr4Jtj9L4f4V6NRTDl8zzj/hKviIv3vA0Tf7t6Kd/wAJX8QQP+RFjJ/6/h/hXon40fjSDl8zzo+MPiADj/hAfx+2rigeMPH2/DeAG2+ovVr0aiiwW8zzpvGnjVD83gC6/wCA3aGs+x+K2uancXdvZ+Cb2aa0by51Ey/u29DXqleb/DXd/wAJV455G3+1Bx/wGgTT7jl8feKz1+H+o/8Af9KcfHnisHB+H+o/9/4/8a9EpaB2fc86/wCFgeJkHz+ANUGOuJoz/WgfEfW8c+Adaz7Fa9FooCz7nnZ+I2s8Z8Ba3+af400/EvVQMnwHrnHXha9GophZ9zzkfE3Uf4vA2uj6RigfFC+xn/hB9f4/6ZCvRqKQWfc85HxQu+M+CPEAzz/qaafipcg8+CvEP/fivSKKYWfc87b4oyqMnwf4h/8AAU00/FUgc+EfEQ/7dDXo1FAWfc8um+NFjaSxR3nh7W7ZpW2xiW3wXPoB3NT/APC3I+3hTxCc9P8AQ25o+JKeZ4y+H8eOuqlvy2mvScUtRWfc85/4WwuP+RS8SZ/68moHxZTHzeFPES/WyavR8UYpjs+55yPi1bnj/hF/EOfT7C1B+LloBz4b8QjnvYtXo2KTA9KAs+55yfi7aDGfDfiDn/pyaj/hbtrnnw14hH/bi1ejbR6UbR6UCs+55yfi5bZ/5FjxF7f6C1B+LtqvXwz4hH1sWr0fA9KTaPSgdn3PNz8X7Lt4c8QEev2JuaU/GDTx/wAy/r+fT7E1ej7R6UbR/dH5UBZ9zzhPjBYHk+HtfA/68mNNl+MemQI0kmg66sajLM9mQAPU16TtX+6PyrnvHOE8B+IHIHGnz9v+mZo1FZ9zlLf4zabeQia20HXJ426PFaFgfxFSn4v2QOP+Ec8QZ/68Wrd+G0Qj+HOgjHP2Ra6raPSkOzPOf+Fv2WM/8I54g/8AAFqX/hblt28M+If/AABavRdo9BRgelMLPuedn4tWwJH/AAjPiHj/AKcWpR8V4CP+RX8Q/wDgC1eh49qXFAWfc87/AOFrQ4/5FbxF/wCALUh+K8QJH/CK+I//AABavRcUCgLPuedf8LXT/oVPEWfeyakPxYixk+FfEQ/7cmr0YijAoCzPOh8VozjHhXxEf+3JqRviuqHB8JeIuf8ApzNejYoxQFn3POR8VwWwPCPiL6/YzVeH4x2V1czW1t4c1yaaE4kSO3JKH39K9Nrzn4b/AL3xR44nHRtV25+iigWvcP8Aha2CceEfERx/05tUn/C0yUz/AMIj4h9/9DNeh0UDs+552vxRlf7ng7xCfrbYpT8T7jOF8GeICf8Ar3r0OigLPuedf8LQuySP+EK8QZH/AEwFO/4Wdecf8UV4g5/6YivQ6KAs+556fiZeqT/xRPiDHr5IpU+Jly3Twb4gz7wV6DRQFn3PPT8S77nHgnXzgZ/1Ipn/AAs3UD93wNrx/wC2YFei0d6As+553/wsvU8ZHgXXj/wFaP8AhZWrZ48B67+Sf416JRQFn3PLrj4vXFrqFrYT+C9YS8us+RCSu58dcVf/AOFj6znH/CAa5+cf+NQeJFEnxx8GL3S1u3P/AHwa9JHSkCPPm+Ietj/mQNb/AO+o/wDGmn4g+IVx/wAW/wBY5/6ap/jXodFMdmedH4g+Je3w+1b/AL+p/jR/wnvio8D4e6l+M8f+Nei4ooFZnnX/AAnPjDt8PdQ/8CIv8af/AMJt4yzj/hXl/j/r5i/xr0Kigdjz3/hNvGP/AET2/wD/AAJi/wAaQ+N/GIOB8Pr/AD/18xf416HRQFjzo+NfGYz/AMW+vP8AwKj/AMaT/hOPGudv/Cvbv/wKSvRqKBWfc86/4TXxtnj4e3eP+vqP/Gquq/EnxNoenS6hqPge4t7WPG52u4zjJwOlenVwfxiGfhxfAnG6WEf+RBQDTRUi8c+M54lli+H90UcAqftUfI/OpP8AhNPG/wD0T26/8C4/8a7rT126dar6QqP0FWqBo87/AOEz8cf9E+ufxvI/8acPGPjhv+afzA+94lehUUCt5nn3/CYeOc4/4QCX/wADUpR4u8c7gD4Bk57/AG1OK9A/GigdvM8//wCEw8a5I/4QGf8A8DEph8ZeNh/zT66P0vI/8a9DooCx53/wmfjc/wDNPrr/AMC4/wDGlHjHxv8A9E/uf/AyP/GvQ6KAseenxl42A/5J/cZ/6/EpF8Z+ND1+H13/AOBUf+Neh0UBY84uPHXi+1glnm8A3aRRKXdzdR4AAyT1qtpfxI8T61p8Ooad4Fu7i0mBMcq3MYDYOD1PqK7vxISPC+q/9eU3/oBrnvhIMfC3QsH/AJYsf/IjUhdbFQ+NPGGBj4e3+e/+kxf408eNPF2Ofh9qGf8Ar5i/xrvqKY7Hn/8Awm3i3t8PtQ/G4i/xpD438YA/8k9v/wDwJi/xr0GikFjz0+N/GPb4eX//AIExf40o8beMO/w81D/wJi/xr0GimFjz8+OPFCgZ+H2p5/6+Iv8AGov+E/8AFGMn4fapg9P30f8AjXotFIVjzr/hYHic9Ph7qv8A3+j/AMaUePPFZ6fD3Uv+/wDH/jXomKKYWZ56PHPiw4x8PdSz73EX+NO/4Tbxbnn4e6jj/r5i/wAa9ApDSHY8y0/4paprEVw+neCdTuFt5TDKRLH8rjqvXqKvf8J14lYZj+H+rH/eniH9ag+D2f7H8Q8gj+3rvGP+A16OKFcS1PPD8QPEoOD8PtWz/wBdY/8AGlHj7xIevw+1b2/fRf416FRRqOx5+vjvxMx/5J9q3/f6L/GpG8ceI1GT8PtY/wC/0P8AjXeUUBY4H/hP9cwT/wAK/wBb4H/PSL/Gov8AhZGs/wDQga5+cf8AjXodFAHnn/CxdbJ4+H+t/i0f+NPHj/XyOPh/rOfeSP8Axr0CigLHB/8ACe67tyfAGs/9/Iv8ab/wsHWs/wDIg63/AN9x/wCNd7RQFmcEfiDrIHPgLXP++o/8a1PCXjEeKJtQt30u4064sHRJYbhgWywyOntXU1wHgj/kf/HY/wCnyD/0VR1Fqj0GikopjPNr75/jhpfOQunycY6c16TXmsnzfHi2x0GmMf1r0qkt2TAKWkpaZYlFFFABRRS0AFJS0UAFJS0UAJRRRQB5xK2749Wy/wBzRyfzY16PXmsf7z4/yHH3NHA/8eNelUkTEWkpaSmUFLRSUALRRRQAUlLRQAlLRRQAUUUlAHnNiwf48an/ALOkxD/x416NXm2mjd8eNYYZO3S4v516TSRMRaKSimUFLRSUALRRSUALSUtFACUUUtACUGlpKAPOfB4A+LPjjBz80H/opa9GrzbwUxb4p+Oc9fOh/wDRYr0mkiY7BRS0UygopKWgBKKWigAooooAKSlpKAFpDRSMdqk+goA84+COT8OYpP791M3616RXmvwLH/Fs7b/r4l/nXpXagS2FooooGFFJS0AJRRS0AJS0UUAJS0UlABXnHxmXPhjSj3Gr2vH4mvR685+MDD+x9CQ9G1q1z/31QJno1FFFAxaKSigAooooAKKKWgBKWiigBKWiigBO1eb/AAyYN4j8csBj/ibY/SvSO1eb/C879b8byYxnWWH5DFAup6TRRRQMKKKKACikooAKWkpaACkpaKACkpaSgDzf4gEn4ifD5e326Y/+OivSK838aL53xX8BQ+ktxJ+UZP8ASvSKQhaKKKYxKKWigBKWiigAooooAKSlpKACuY+IvHw48RHOP+JfN/6Ca6euR+J7bfhp4hIP/LmwoE9i34AGPAOhD/pzj/lXR1g+CV2eB9EH/TlF/wCgit6gYUtJS0AFJRRQAUtJS0AFFFJQAtJRRQAV518LPnuPFz9m1qX/ANBWvRa89+FSjyfEsndtam/ktBL3R6FS0lLQUFFJRQAUUUUALSUUtACUUUUAFFFFAHnWs7G+Ofhvj510y4OfzH+NeiDgV51qR3fHvRlHVdFlJ/7+GvRRQTHqLRRRQUFFFHNABmjNFGKACjvRRQAUUUUAFcB8Yv8AkndyB/z8wf8Ao0V39ee/GUgfD6QZ63lv/wCjRQJ7HdWYxZQf7g/lViobT/jzg/3B/KpqBoKWkzRQAUtJS0AFJRRQAUUUUAFFFFAGZ4h/5FrVP+vOb/0A1z3wlBHwv0LP/PFv/RjV0HiQ48MasR1FlN/6Aa5/4TMW+F+gnGP3B/8AQ2oJ6naUtJS0FCUUUUAFLSUUAFFFFABRRRQAUhooNAHnPweA/sTX9vA/t67wP++a9Hrzb4Nsp0TX9pyv9uXRH0+WvSRSWwo7BRzRRTGA60mCe9LRQAUUUUALSGiigApaQUUAHauC8F5/4T/xxwB/pUHT/rlXe9q4DwWT/wALC8cg/wDP1B3/AOmQpdSX0PQKKKKZR5lFlvj03oul/wBTXpleaWmD8drvvjTF6duTXpdJdSIbBRRRTLClpKWgBKKKWgApKWkoAWiiigApKWkNAHm9rz8e7vGPl0iMH/vo16RXm1qP+L93hB/5hMef++jXpNJEx2FopKKZQtFJS0AFJS0UAJRS0lABRS0UAJRS0lAHm2jsf+F66+O39mw/zr0mvOtE+b44eIzj7umwD9a9FpImItJS0lMoKWiigAooooAKKKKAEopaKAEoNFB4oA858Fc/E/xywxjz4R/5DFejV5x4KjMfxP8AHSg5Xz4T+JjB/rXo9JEx2FoooplCUUtFABRRRQAUlLRQAUUlFABTW5U56U+o5QTGwXrjigTPOvgac/DG0PrPL/OvSK83+Box8MrU+s8v869IoQLYWiiigYUUUUAJRS0UAFJRRQAtJRRQAV5r8Zcto2hIM5bWLcD869Krzr4rjefCUR6PrtsD/wB9ihiex6KKWkFLQMSilooAKSiigAopaKAEpaKKACkpaSgANeb/AAqG6bxdJ3OuT/oTXo+a85+EZ3Q+KH/va5cn/wAeNAup6RRRSUDCiiloAKKKKAEpaKKACiiigApKWkPSgDzrxPz8Z/Aw9EvP/RL16LXnHiI7/jh4NX+5a3b/APkNhXo9ISFpKWimMKSlooAKKSloAKKKKAEooooAK434rNt+F+vn/p2x/wCPCuyrifi42z4Wa8cdYUH5yKKBPY3/AAqAvhDRR/04w/8AoArYrK8Nrt8LaOD2soR/44K1aBiUtJS0AFFJ3ooAKWkooAKWkpaAEoqlpWs6brlq91pd7DdwJK0LSQtuAdTgj+o9QQRkEGrtVKMoNxkrNABrzv4RYOka24H3tYuD+orv7ieK1tpbieRIoYkLvI7BVVQMkknoAO9eefBlxN4Vv7lWyk+p3DocYyC2RRyy5ea2hL3R6RRWbr2uWXhvQ7rV9QdxbWyhm8tdzMSQAoHqSQOcDnkgc1zlj8StLTwpYa54iifQxfMwggmzK0qjkOoUbipGOSo6jsVLb0sHXqw9pTi2r206u17JbvTtsNySdmdtSVj+HvFeh+KoJptF1BLpIGCSgKyMhIyMqwBwecHGDg+hpniLxhoPhP7N/bd/9l+07vJ/cu+7bjd91Tj7w6+tSsNWdX2PI+ftZ377b7BzK1zbpa5v/hPfC/8Awjn/AAkH9sQ/2Z5vk+btbd5n9zZjdu74xnHPTmqlv8RdD1fTdSm8OSPrN7ZQGb7DCjRyyDp8ocAkZ67QSMjgkgG1gcS037N2Ts3ZpJ+bei+YuaPc66lrnvBvi2y8Z+H49Vs0eIhjFPC/JikABK56MMEEEdQR0OQOgrGrSnRm6dRWa3Q001dBRRRWYwooooA83uAW/aBtOOE0Jj/5FNekV53Hh/2gZP8Apn4e/L98P8a9EoJiFFFFBQUtJS0AJRRRQAUUUUAFGaMUUAFed/Gc48Dxr/ev7cf+PivRK84+M43eELJfXU7cf+PUCex6DbD/AEWL/cH8qmqOEYhQeiipKAWwUUUUDCiiigAooooAKKWkoAK57xr4mXwl4VvdVMTyyRrthURF18xuE34xhc4ySR6DkgHoe1ZXiezn1HwnrNlax+ZcXFjPDEmQNztGwAyeByR1rfDcntoe0V43V+mlxO9tDzaw+Ken6l8K7qXXroxao0M1mcQMBcy7DtKYyDwV3dApYZChly/wF8RPDeh/C6z+2Xcgm05BBNCkLsxkbzGRQcbTuEbYOcDuRXA6p4e8R3/wx0fzvD19bR+H5rhJxMpSSWOVlfeqEbsLyGOMcgjPzbc3QfB2oXvg++1Y+FbvUIXlt1t5obhkmVQcytFGFPmKwwuSDtzkbtrY+xnlGWTcpuVnzbKUbL3rJa23WvktN1Z83PNHq+rfGPTb/wAD6vf+Hnmg1S32JHDdQZZQ7Kvm4Usu0ZPJOA20EfMobtPBXiVfFvhSy1YRPFLIuyZTEUXzF4fZnOVznBBPoeQQPC/DvgXxDqNn4otLLw/e6fb3FjGIF1RQJGkWaNwgkKITkJJ0AXO3d0Br2P4aalqV74TtrTUtBvNKfToorRDcjHnhEUbwCAw6emORgnnHnZtgsHQw8lh7NqS+0m0nFaeet9r2Lpyk3qY3xh1O9/s3R/DOm3D293r14LYydEMfCsrMMsAWkTOByAwPHBx9Qv8AxRF4utfh/wCBL77LDpFipnuL7bIW4U5LMGO0BkACqMFiMbQMXvjJ/wAS6/8AB/iOb5rPTdTHnInMjZKP8oPB4hbqRyR+FTXo9f8ADPxKl8baFo7+INM1WzjjYWvzEZVcbSm44/dI2/btw2OuDWuBjD6rSVotuM2lK1nO6SvfS/LtcJfE/l9x0Hwt8Watr1rq2meIPm1jSbnyZ3CIoYEsADtOCwZHHAAwF6nJrK8eyfEXQ/7V1y18TaZbaHBhoofswMgBwoXBjfLFiBktjJz8o4HP6EfG/hfw/rHiq20F5dX1zVVL6e9lKxjjAlZpNitvUF2wN3QAHncDXT/EPQte8b6z4d0RLCa20M/6ZfTtImUYcFCQGw6qxAwSGL9whITo0aWY865PZPe9mlypOVk/O6Vgu3C2tyOTxL410/4MRa68SXurzr5pmWJQba3bJWUqvyuQuDwBgMCwO1s27G1uvih8GYBqM+zULqJyskbmJGljdlQuBkFSVBYYI5yACFx1viHTGuPBmq6VptugaTT5ra2gjwigmMqqjoAOg7AVzngmRvBXwgs7jXYXtDZQSzyxOQHw0jsq4JA3EMoCkg5IBwa4liIToe1oRUavtU1bezTsrdk7LsVZ3s9rEnwl8RT+I/AVvNeTTT3lrK9rPNNjLkYZTkdfkZASeSQc56nuK8y+C2mT/wBgah4mvbjzrzXblpnIwBhGcZIAGGLmQ8cY24xzXpuK4s2hThjqsae1/ufVfJ3RVNtxVwpDS0hrzizzb4MkNoGuMAQDrdycf9816UK82+C53eGdXbOd2s3J/wDQa9JpLYmOwUd6KM4plBSUtFABRSYpaACjNFFABRRRQAVwHgjDePPHLA/8vsI/8hV39cB4EU/8Jt46cjrfxD/yHS6iZ39FGKKYHmtiD/wve/3A8aYmM/WvSq83sSf+F6X4Jz/xK48f99GvSKS6k09goopaZYUlFFAC0UlLQAUUlFABS0lLQAlFLTaAPOLNcfHm/Of+YTGf/HjXpArzawz/AML41LBODpUe4f8AAjXpNJEx2DvRQaKZQUUUtABRSUUALRRSUAFFLRQAUlLRQB5xoRP/AAu/xOO32CA/yr0avO9E/wCS3eJf+wfb16JSRMQopaKZQlFLSUALRRRQAUUUUAFFJS0AFIaWkNAHm3gkkfE/x0Mf8t4j/wCOCvSa818DNu+J/jrk5+0Rf+gCvSqRMdhaKKKZQUUUUAFFFFABSUUUAFFM8weZswc4z0p9ABUczeXC7eik1JUU4327jOMqRmgT2PPfgfx8MLH/AK7S/wDoVej15x8Dx/xbCxPrLL/6FXo9CBbC0lLRQMKQgkHBwaWigBB05paSloAKSlpKACiiigArzj4sf67wh6/27b/+hCvR685+KYBvfBn/AGHrf/0MUCex6KDS0CigYUtJRQAtFFFABSUUUALRRRQAUlFLQA09DXm3wf4svEg9NauP/Qq9JPQmvOfhB8+meIJ+0mtXB/8AHqBdT0iiikoGLSUUUAFLRRQAlLRRQAlLSYooAKO1FFAHnOsAH48eGwe2l3BH5mvRq851M7vj1oQ/uaTP/OvRh0oEgpaSgUDFooooASlpKWgApKWkoAPrRR3ooAK4T4xN/wAWr1kevkD85467uuC+Mxx8LtU95Lcf+R46BPY6/RF8vQdOT+7bRD/x0Vfqnpv/ACCbLP8AzwT+Qq5QMKSlooAKKSigBaSiloAKoazYz6no13ZWt/Np888RRLqAAvET3Gf6YPoQcEXq53xZ400rwbYC71Pz23MFjjhTc0hPpkgdATyR09cCtaEKk6sY0leV9Ouona2p4H4Z1rXPCXwzvtb0nVXiN1qqWIt2jV0jIj8xpRuyNxAVemMZzk7StrRvFPxM0qHVdPZtTM8di19/xMQPMt41dN0o84Esu1WXaOMsSBkUW2tfCq2tdUtRpniZ4L/BEbmIi3IJKtH8/wB5dxALbjjI6MwavY6h8KLO1vYH03xLdNdReWJbgQF4Oc7o9rABsgckHpjoWB/R5xjNzlPDuTbT1gnfa3Vba77nGtLai6RrfjGA61oeu6jqcCXmkXMhh1NZGkcJE7Dy/MB252sCeAV3YO4KR6V8C7SSDwM9y91JIlxcuVhYDbFt4OO/OMnnHTAHJPG+Al+HD+J1j06DXpr2S3mjhj1JYmibKEOCE/2C/wB75cZ74rpvgxpOn6Z4av8AXzLOslxLJC6GU+WEjdgML3Puckc4xk58PPcVRVOeH5XCT5ZfCle11306a67NGlNO6Zc+PNxLH4BtkjldEl1CNJFViA67JGwfUZVTj1APas7xfZ6bcfG/wlo+oRw/2PHYjy7SQ7YFfMoRQvA5ZI1x/FhVwRxXb+L9Ch8d+CLixtZYFlmCy200ybgjqQR7rkZUkcgMeD0OBp/hCXx54KsrXxzptzaanpzPbQ3CXB811UqDJyWBLbMEtuzgsuAwrjwGLo08LBylblc4u2650rSS0va3TVFyi3Iw/CtxpHh342eLILW7trDRY7MPIonCQJJuhBzk7QQ7uoH8JYqMdKo/EexuvEfxd0C20WbT3mutKD28t0izQMuZmyQVdWBUHBwecH3ruLH4SeHdP8MapoUM2oeTqbRtcTtKplxGwZVHy7QAc/w5+Y89MS6v8KPDetaNpmnXBvVOnRCGG7SYGdoxn5GZgQVycgYwvRdoyK2hmeDhiVXUm3y8l2r3XKlzNX113V9uouSXLY8KluopPEun+G9atdPt47bWjHqk9ri3huVDrHllUKqhFEmGAXh2OASxb0p7PTdF/aK0i00OOGzinsW+2W9odqb/AC5TtZBwOFibGB2bGTmurg+EvhSHwvJoJtZpIpJfOa5aXE5kCsqsWAAO0OcKRt7kEkk0LTwFafDfStW1rwvaXuq6wbby4YbmUH5dwLYCqu7oGx1OwBSCeeivm2FxCcKTabjKCW0W5W9562SXZ7K21hKnJbmb8NZl0/4keNNC08PNpKzmdXjQxw20gYgxBMYB+YrkYyIcgEdPWK4v4Z+Er3wt4embVnSXV9QnN1dSfecEgYRpOrkHcSemXbGep7Svn82q06uKk6bulZX7tJJv52NaaajqFFFFeaWFBpaQ0AedWK7/AI+6pID/AKvQ40P4yg/0r0QV51pGX+O3iNu0el264+pBr0UUEx6i0UtJQUFFFFAB3paTvRQAUUUUALSUUUAFec/GAeZoGkxDrLq1uoHrzn+lejV5v8XGAtPDaEAh9ahGCOvDGgT2PR1GFAFLSCloGFLSUUAFFFFABS0lFABRRRQAV5X8XtS1SDUfCul6frNxpUOo3TxzzwOUIw0ahiQQSBvY4yAe/QY9UrzD4u+ENb8T/wBh3GjWUN6bGWTzbeSQJuDbD/EVBX5CDgg8jHcj08nlTjjYOo0lrva1+V2vfTexFS/LoeVeKNW1DQpo4LL4gXmvRSiWOePzWZAmAvILsDuBfHptz6Y92+F//JM/D+Bj/Q1rwi/+G3iez08XFz4asdMtLNZJpriO5Viy4Bw37xyfu4GB/Ec8cj3r4aqV+G/h4H/nxiP6V0ZxNSjR5pRlOz5nG1vidvh02Ip/Ezq6KM0V4hsVdT02y1jTJ9P1C3S4tJ12SRP0I/mCDggjkEAjmoNB0Ky8N6Ha6Rp6uLa2UqvmNuZiSSWJ9SSTxgc8ADitGitPaz5PZ39297dL9xWV7h0qOGeK4QvDKkihmQsjAgMpKsOO4III7EEVV1mLUp9Gu4tHuYbbUWiIt5p03oj9iR/XnHXDYwfnnwV4r1zwT8OtQ1e0+xXFnPqa2sNvOjEpN5e95CQRldiqu3PXnjBD+jgcrljKM505LmTiku9/6/BkynyuzPpSsbxL4X0vxbpsdhq0TyQRzpOoSQody9sjsQWU+zHGDgjw/wAP/Gbxj9i1GOW3TVp4oDcRy/Y8+UAybjJ5ZUCMJvOcZ3EZOKg0T4leKvEGn6/o+pXltdRXGlXLiSaOONogkTM20Lt3lhkY5I4borA+jDhzH0JuopqPI1qm7+q06edr9CPbReh9E2X2T7Bb/YPJ+x+UvkeRjy/LwNu3HG3GMY4xUep6nZaPps+oahcJb2kC75JX6AfzJJwABySQBzXCfBOLUk+Hlu93cwyWckshsokTDxIHYMGbvlwxAxx6nICwfHa8ntvh9HDDJtjur6OGYYB3IFd8c9PmRTx6V50cvUsy+p811zWv89fn+pfP7nMdVo/jjQ9X8OQ681z/AGdZTStCraiVgy4zwCTtbofuk9COoIGvYapp+rQNPpt9bXkKtsMltMsihsA4ypIzgjj3rybxjodlq3xZ8H+D7hXGh2+nlo7dGwQFEny7/vYIhjB5zgHBBOal8B6fF4Z+M/ifw7pjOmmfY0nETkMQ37tlG4jOF81wOehGckZrpq5Zh3RdSnJqXLzpPbl5rWv3+X+ZKm72foTfCLWtK0nwbdNqep2dkJ9VuTH9pnWPfjbnG4jOMj8xXpn9taV/ZX9q/wBp2X9nf8/fnr5X3tv384+9x168V8n6Dplxr+o2VtpemDVr5BOZrOQMkIQOxDGRXUj73qoztGTuwPVfhnoHh7U9G13QNcTN1/ae2fSpHKxW0q79ogYMSzFUkBYNuKpg5A3NUspoQwcMTObvo2klezdtr39G9H31JjN3sek3Pjbw7Dpt7e2+q21+LOBriWGwlWeXYMZO1STjJHJwBnJIHNW/D3iLTfFOjQ6ppc3mQScMrcPE46o47MM/yIyCCfFfhrok/gn4rLouv6bC17dW0hsrlGEm3G751O75VZUccru6DgFs9P8ADCaLQvHXi3wdBKj2kU5u7RYGDxxLkKylz8xYBolIOcFG5z1rG5Vh6UKioycnFRknpZxbs9uz/Xtq41G2rnrFFFFfOmwUUGigAooooAKKM0UAH8Nef+AQP+Ey8dN66jH/AOi67+uB8And4s8cN/1E0X8kpdRPc9AooopjPNrBmPx01HngaXHx+Jr0ivN9IJf4461k/d06ID6Zr0gUkRDYKKWimWFJS0UAJRRRQAtFJS0AJR3paSgAooooA8207LfHnVzjhdLiH616TXnGkYPx017J5Gmw4/OvR6SJiIelME8TTvAJUMyKrtGGG5VYkAkdQCVbB74PpUleAWs/iTRvjN4n1Ga8sri40+xlu70LEVS4tlRGWNByUbHlDOTjBJL4Ib0cBgPriqWkk4xuvPVL+vOwpy5bHv8ARXzlpHxs8VzeKLd7mOG5s7iWOJrC2tckAsoPlc7i5wcBmIy3TpiOH4x+NE8WR/bPsyRrOIptMeNYIwfuspd/mQ5ycs2AevAxXqPhbHJtXjor7/htv+HmR7eJ9HRzxSvKkcqO8TbJFVgSjYDYPocMpx6EHvUleMfCyHV/+Fm+NH+2W32SO8kW+QQkGaQySbGQZJQAh+rNwcYJ+ZfUvE95Pp3hPWb61k8u5trGeaJ8A7XWNiDg8HkDrXl4zA/V8SsPGXNfl19Ut/v+4uMrq5m6N4+0DXdS1a0sbh2i0tQ894yYtivOSJOmBg8nGcErkAmtXT/EOi6tO0Gm6xp95Mq72jtrlJGC5AzhSTjJHPvXgd//AMSz9nHS/sf7v+1NTb7Z383DSY69P9TH0x933Od3X/Cmm/D/AOIPgSbw/wCdDJdXItpzI/meYNyIzcjhmWVgcYHTAFevUybDOUoQk025qK3u6a1bfS72tchVJf15nsuoapp+kwLPqV9bWcLNsElzMsalsE4yxAzgHj2qG08Q6LfwXM9nrGn3ENqu+4khuUdYlwTliDhRgHk+hrlfix4avfFfhqx0zT5bZLo6hG6rcS7N42ODt9SAS5A52o2MkYPDeC/Ddr4V8Vz+BvE+l6ffza5Z+Yl1bszbUG4+WxYKQMxFgVAIYL14KcWGy/D1cI6zm+dXfKrfCt3rbpcpzala2h65B4u8NXM8cEHiHSZZpWCRxx3sbM7E4AADZJJ7VV8OeONG8UX+oWFi80d5YysktvcxmKQqDjeFPO3PHOCDjIGRnyZfCfhnUvjPZ6Boeloum6Wpn1FhMZRI687TvdgVDGNCoAOS4PTI6PxFPF4X+O2h6lDKgXW4BaXcMbB5WYnYjMrfdUkRcgjPlvx1z0TyzC/w6bk5Sg5q9la2tmlfdJ+mnfSeeW77mnoYP/C7vEn/AGD7f8a9FrzvQwf+F2+JTj/mHwfzr0SvnEaRFoooplBRWV/wkujf8JJ/wj39ow/2t5Xm/Zsndt64z03Y525zjnGOa1audOcLcytfVencL3CiikqAFoorKsfEujanrN9pFlqMM2oWP/HxApOU7HB6Ng8HGdp4ODVxpzkm4q6W/l6hc1aKKSoAKQ06mmgDznwThvij45Yf894R/wCQxXo/avN/A/HxM8dADA+0xHn/AHBXpFBMdgpaKSgoWiikoAWiiigBKMUUUAFFFFABVe+yLG4I6+U2PyqxUF24js5nPRUJP5UCexwXwRIPwt07HZ5c/wDfZr0TtXnfwRXb8LtOPq8p/wDHzXolALYWikooGLSUtJQAUUUUAFFFFAC0UlLQAlecfFAltb8Dx+utxH8iK9Hrzf4n/Lrvgd1++NaiAHsSoNAnsejiloFLQMKSlooAKKKKACkpaKACkoooAKWikoARvuH6V518GcHwlqDf3tWuv/QhXoj/AOrb6V538FOfAksv/PXUJ3/MigXU9GpaSloGJS0UUAFJS0UAFFFJQAtFFFABSUtIaAPOL1l/4X7pobr/AGPLj67hXo46V5rON/7QVpkA7NFkI9vmH+NelUCQtFFJQMWkopaACkoooAKWiigBKWiigBK87+Nj4+HE6f8APS7t1/8AIgP9K9Erzn42f8iCo9b+3H/j1Amd/ZrssoE/uxqP0qxSAYUAdqWgYUlFFABRS0UAJRS0lABXlPx9Zf8AhB7EDGf7TT/0XLmvVT0968f+O8co8JWbyHg6ggH/AH7k7V6uR/8AIxo+pnV+BnMy+LPHVncJp/hj7N/YYj/0IzRqcoFyRlupHtxXPQ6z8RdIvYCttNBEfmIgVAJTIeSXIOSST9M8Y4rQ+INlqdtr+lIrSEPOyooGAucAAD0wK6678NLpmkSzO88zoQ0EMjZVGOMBfXn1/CvINkc5c2GtS/E/SIr3Zpl9Pp0sgaJi7quybO9iSWc4IJ9MV1nwg8I6dN4NttQvIzeySzPiOf5okAY8hT9O9UNfSaP4zaI04IkbRpmxnp+6uP8ACu1+Dwx8MNH91Y/+PGvWzT4MP/17X/pUjGO79Tsrezt7PctvCqK3UL0/KrIpFBFLXlmgtJRiigAopaKACikzQKACud8V65NpVvFDakpcSnO8x5AUdcE8Z6evHpxXRGsDxdY3OoaTFFawmVxcKSox0wRn8yK48f7T6tP2T963Tc4Mz9r9Un7FtSt03+Rm6d4rmS8ZdRfdbrbRsXSBgQx25J9vn69DgY64PTtfwLqUenneZ3jMvCEgKDjk9s8/l7jPOX+mb9d1m4vh5NhLaACdugb5McA5JBXp9PUZf4NspGgk1S4OZJVEMR9I1AHb/dA5Gfl964cNWxMKvsJa6vV72Td/v0seZg8RjIVlhpe9dvV7qKbu+9noov1Ob02/Sx+LHje9kXcsFlaAe5wcD8TgVqmS90jQG1lp5G1DUXUbiRhF5IO3kHIH4A4GMHOLYWUuqePPiHDbgGYpYKoJxnAc4/8AHa351l17wRarZx7pbRlWSMZydikcccnBBx+HJqswc3Uaje6i3H12fzS+648zdR1Wo3uoNxt/Nezt5pbdVe6LVlqOraf4jg07V7uGZbiPKlMKFJzjnaMnKkY962tWh1SaCMaXcwwSBsuZFzkY7HB/l+I788q6lreuQ382lzQw2UZZYJnKh5BkrtJA5J257cc9hWl9t1i78LXMzWRhvyGVEUEErnlgM5BxnA65Ge+KWHq3pzg3JrVxet7K3X12Hha16VSnJzcdXF+9zWSXXffYxIda19bLUrpr2GWG1xEH8oFWYsBlCAM4HPOeo454tWuq63ZXmltf3ENzb6jgIiqAVB28nCjkbh69/rWjZ6M1l4UkshbRz3EiF3ikbCs57Zz2wBwRyOo61zGi6Jdy63ZsbK6to4SskjzLwSpzxkDqcDHJHXmuOccVRlTV5Nu3V6O+t+j00123PPnHG0JUVzScpJdXo+bW/R6aavTc6Gwln0nxNJpMsxmtroNPBnJMZJJIJJz2b1ycHjJrpa5dXGp+PFmtgTHYRGOZmUgbvmGB+Ld8dDXU16+AfuzS+FSaXp/w9z3ssfuVIp+6pNR9NPwTuhO9Bo60YruPSClpKKACvN/iviSfwlCed+tRnGPRWr0ivN/iaN+v+CI/XVgf/HaCZbHo4pe9AooKDvRR3ooAKKKM0AFFHajNABRRRQAtJS0lAHMfEJmT4fa4VIz9kbFO+H42/D3w+AB/x4Q9P90VB8SWK/DjXSP+fVv6Va8CYHgDQMdtOg/9Fign7R0VFFFBQYoBoooAzdc1/S/DemnUNXvEtbUME3sCSzHoAoBJPU4A6AnoDXglvZ/DqHRtU0mXx5eTWNxKJ7OI2EwFtKMgSH5fnbadpxtBGeM7Svb/AB9P/FDWP/YST/0XLXk/iCa18OaqYre2s5rJWYxn7HG0uewYSKQRn0r6DB16WAwsaspTvUb+Hl+xa26ffoZOLnKy6HR6SnhS/wDtn9sfErUbjUr62+wwzslxGIVL5w7NwyHjKsQoBbPOGXvtI+ELw6+NU8QeJr3XNttLbCOdWUlJFZCC5djt2u/Axyc59fGtTvrrVPAjXF3oGnWRj1KNI7y3s44JJA0cjFDsAyANvb0r6xrfH5jVWHhWw85JVOZNNRurWWjUVa9+hMYK7TWxx/gjwNP4LkvIl8QXt9p0nFtZTKAluNxbPU/NzyV2g8kg8Yf8SvC8vi3wVdWFpEkl9Gyz2oeQoN6nkZ6ZKF1GeMsM46jrqK8T6/XeJWKbvNNO9rbd7W+fc15Vy8p5PB4db4q+GdM1a+OoaH4j0xjam7MIUvIjLufACsQGDYAK7HLjnHM1r8G4oPDuu2M+tvdalq7RmTUJbYFkVZBIRgsWJZhlju5+Xjjn1KkY7VJ9BXS84xMfcovlhe6WjtrdK7V7J9NvIn2cep8+fDr4eXHiHwra63pXiG70O9Dz28z2yn96gkyOVZT165JBwvTHPZj4LWS6G8Y1m5/t97xbw6yUzJvBOABuyB8xJIbJbDEnAAsfA0f8Wytv+vqf/wBDNek0lnOOSSU9vJfjpqvJ6eQKnHseVx+DX8BfbfG2s6rqfii/062ItUYMGjByGJJdjtAY5PRQXOCcY1fhR4d1LSdGv9V1yHy9Y1m5N1Pu4fYeVDqMBW3NI2AONwBwRgd/RSrZpWrUZU6mrla720W0UlZJX182NQSd0GMc0UUV5hYc0UUUAAooooAKKSlFACGuC+Hx3eIvGr9zqxX8lrvj0rgfh2uNZ8Zc5zrMn8qXUl7o76iiimUea6Pg/HLW8A5/s6LP516VXmuisB8cteX1sIq9KpImGwUUd6KZQUtJRQAUtJRQAtFFFACUUUUALSUtJQB5zpRA+OuuA9TpkOPzr0avONNOfjvrHtpcX869HpImIyeeK2gknnlSKGJS8kkjBVRQMkkngADvXiV5f+AdZ+Ib67H42mgi1CIWt5ZG0lRJ0KeWUMpUBEIC5yOMEhlOCvqnjX/kRPEP/YMuf/RTV8qXGt28/hS10YaTZR3EE3mfb40AmkGXyrnGT99e5GEH4fU8P4P2kZVE5Jt8nu20TTbbunpou3qZVZW0Pc7D4MPaX9mk3i3U59Fs7n7RBpw3R7CCSuHD4VsnllUE5ONpORBdfBO7vpBBd+NtTuNKFy04tJkLnliSdxfbvO5svt6sTjnFet0V5v8AbmP5ubn19I/ftv57l+yj2OIg+HP9n+PZPEmla7e2Ntcy+fe6fGNyXEh3ZyScbSWJwVJGW2lcjb2N7ZwajYXFjdR+ZbXMTQypkjcjAgjI5HBPSpqK4a2KrVnGVSV3FJJ9dNtevq9S1FLY8Z8IeHbrUNH1T4ZeLLC5RbFhd21/AqlFRnyNjleCx8wgnJIMinbtxWz4a+EP9j+JLDV9V8QTax/Z8QjtYJoMLHjhMFnbCrkkAYwcEHjn02iu+tnOJm5+zfKp7pd2rNq+qv1sQqa6nldr8FktvC50seIZheRXy3tpex2qobd9oU453c7QThxyiEAYO7V8LfDJ9F8SLr+s+Ib3XdQhiMVrJcbl8kHcG6uxbhiAMgDJOCSCO/pazqZxjakZQlPSV76Lrvra6v1S/UapxXQ5jwd4JsvByag8N1c3l3fzmW4url9zuMsVB7EgMct1YkngYA8cHiXX9f8Ajlpup2ekvHMGaCztNQ/c4gUSJIWIGQQfOJ+8VYFfm24P0VXkvjOC3uPiPpXiLSvGXh2yutOT7Ncw3lyhZAGfcNufmJDupUlSMcEE5HdlOL9pWrSrrmlOLV3ey02suj0XktFuRUjZKxwifFxrL4iah4ks9KElrdxC3aCaXa5Rc7WDAEKc4JGG7jPetzVvj9fRa6yaVpdlLpcUpXdKz+ZOgY/Mp42blxgFTg9c9K47/hFNNfxhqeh2HijRo9JHlsL+9eM5jLA4jbGC69DtK7sc4BIHR+J/Ds2s6rqUiePfBt3bXcquLi8mt0ucBVABdIyVwFA+UgHBOBuIr34YTJ+eNqatbrz+W+m+/X/gYqU7bnQ6FrviK9+PF8ILZ1tZ7OI3FpdTsv2a38uNlO3HEgL/AHMHDSOM4JevZq8uX4a6/onifTdY8M67bROLO3sr/wC1wZDpEsaEooB4YRgldykEcPzx6hXy2bVKFSVOVBqyilpe+mmt/wAPLc6Kaavc+ffDeoS2/wANfHHjmFUj1u9vGgMiAgQrIyFjGQdynMxP3jyienObqPhT/hAvCfhXxzpmozPqMssMkkTjEZ8yMyBRtIO3aCjDJ3Bj93pXSeGtLgsrrxN8KdXimtotQlkuNKnkQsZABlXLKQDgRIwHAyrqSD8tW4/hP4svZ9K0rXfENte+GNOn3R24ZxI8YPCkADkj5RlzsDHaex+neMpUasueajFvms18VPksku+t1bQx5W1ov+HPTfFPiSy8KeHrrVr10AiUiKJm2maTB2xjgnJI9DgZJ4Brxn4T+JJ7j4oard6zqUMUmq23meWboGOSVnjMaLljllViqrksoyvGCK7+y8B6jqGqeIY/Ft3DquiX1z59laPNK72+HYrtYkeVhW2kLnPTIAw1Gw+C+g2njK41KSCGbR/KjNrp7l28uUEbixLHcvy5wcg7yCAFGfGwlXL8Nh61CpJuUlulddGktd779NNzSSm2mjH+z6vpv7SVkL3VHuY76CWSIKSoW3KSlYivTCsme+SAx5Jxe+I8EXhb4geGPG8cSRwmf7HqErKCoUqVDbV+Zm8syc8/6tRjsep1DwbLe/E7SfFgvEWGxs3ga3KEszHeAQc4xiVifTaOu75eO1uSH4i/F3TtKitHuNG8OtIb6UxgL52eUbdkMpaNFxjJ/eYyORpQxEa1anVv7kaTU7K38yt0V3pbz7iasmvPQ9fpaSlr5Y3EoPalpDQB5z4JJHxM8dRkH/j4hbP/AGzFejV5t4Kfd8UvHI7edD/6ABXpNImOwUUUUyhaSlpM0AFFFFABRQKDQAUUYoxQAVXvEEtnOh6NGwP5VYqpqLFdOuWXkiFiB+FAnscL8EM/8Ku0/J/5aS4/77NejV538FBj4WaXyDlpenb94a9EoBCUUGkoGLRR9aKAClpKM0ALRSUUAFLSUUAFec/Eog+KfAaHodWz+QFejV5x8ShnxX4D/wCwt/QUCex6OKWkHeigYUtFFABRRSUAFFFHagAoo5ooAM0tJRQAyT7jfSvPPgmwb4cxAD7tzMP1r0OT7jfSvPfgoP8Ai3kbf37qZh+dAup6NRSUtAwooooASlpKWgAooooATNLSUtABSGlpDQB5yuD+0B9NCf8A9GR16NXnER3ftATY/g0Mg/jJHXo+KBIKKDRzQMKKAKKAFpKWigBKKKWgApKKKACvNPjcvmeD9OQHltWtwP8Ax6vS681+M3zaJ4ej/v69bD/x2SgUtj0oUUCigYtJS0lABRS0negAooooAK5jx34Ni8ceH10yS8ezeOdZ45VQOAwBXBXIyMM3cc4PbB6elrWjWnQqKrTdpLVCaTVmeQSfB3X5XjeX4h6k7RkFC0Tkqfb99xTpPg/4hnKNL8RdTcxtuQvFIdp9RmbivXKK9D+2sb/Mv/AIf/Ik+zieTx/DG60W8ufEmreKrzWLi0sZ0hE8ZBG5GXlmdjtAZuBjk5z1B6L4TRmP4ZaJg53QZ/U1veK22+EtXPpZy/8AoJrK+GKbPhroA/6dFNceKxdbFTU6zu0rbJaeisgjFReh1o6UUUGuYs4Dxp8ULDwl4k0rSv3M/mSg6i25t1rEcYOAD83O7HXC9PnBG3qPj/wrpV1a211rtkstztMYR94AYKVZiuQikMpBYgEHOcVwPxsjtbLXvCGs3mn+fZw3LLeMIQ3mRho2EbE8HIEmFJx973ry7xlp0Vv4v1+XVv7QspbmeS8sU+xgidJGZlLbnUoOgPDEHcCAVIr6/AZNg8ZQoyd4txle2t2pW7dPTa3qc8qkotn0Zq/xE8JaG8SX2u2waVQ6rDumO0gMCfLDYBDAgnGQcjNY+r/FHTdJ8e6ZojzWTaZdWwllvxPuETvkx5xkBSADk9pFbIA+bwfxHpNjps0EWpHX7PUP7Mt38q9tkk8yXYRgNvUpEAEUcMwwwIBXFdHZSf8ACNXPgLxTrGiTDR4LF48Rxbsy+ZOyNh24Y70kBJAPJXgYG6yDB06cZpubkpK2iu+Vtcv3ea79he1k2fSleVjxBqWt/FLVrhdams/DHhaJmufs6cSuF+dZFOS3KychTgR/LgsGPqEEy3EEcyBwsihwJEKMARnlWAIPsQCK8d8M6fLJ4r+KXhqRkh1LU1kkt0kJKlH83DFlBAGJ4zjr83Tg48HK4Q5K05LVRS72TklJ28k3r0NZvYq/8Lb8c/2V/wAJJ/wjFl/wjv2ny/Mw+7buxjdu/wCA+Zs27uMZ+Wuv1LWX1C5v9Qt9VuotMttOF/GbcEF4hGr8KSvJDZ5+n08pm8XS2/wvHw7m0PUI9bM6xhXQglWlEy/IRu3EkKFxyCDntXW2FxcNq+teCIrYT3sfhoWkc0Dlkll+zRDGSoCqSSAzEDoOpArqz3JlXVNU6SilNt2la9JW95692ttfI8zGUp11CCu1zK+ttLP062OZ0Hxp4r8R3cNuwju7aSZIZLeK6AnYEjlI3lBYDOc42gA5KgEib/hLfGM1tq194bgluPD+mysv2lfMUFM/e27genzEAfKD83rXLJHpsmj6ZpOlaTqNv41gvT9ouCxjChS5wMv8hX5CSVXbsJJGDW7pfitvAvgvxJ4O1PSrj7deGUQyggRssiCMtkjJUBdykZDZ7da9Wtw7lyrOpSw8XPRKLbXu82src2vk9Ot0Qsvw3NzuOtrXu/uK1t4r1BfE48QWuoT2mmXElrbalMHJwWUnkDDOVAkweT8p5wwFe423g26td32bXJod2N3lxlc46Zw1fMWna7bweEdd0wpDJLdXNq0ZaMsUVBKXZT/C2Si+pDMO9fRnwrv55vDaW+paxZ3upNiZ44rgSyxqRx5hycsepr5jOcrwUqVKaj8LnGNm7uCejut+qu9XbyZr/ZmGqNc8fhWmr0/E3/B15cXmjO1zM8rJOyKznJxgHr35Jroa5fwL/wAgSb/r5b/0Fa6evCy6TlhYNvoa5TJywVNyd3YKKDRiu09Ap6bpNnpMTx2kW0OxZiTkn0GfQdB/jmrtFJUwhGEVGCskRTpwpxUIKyXRC0lFFUWGKKO9FABXnPxBw3jfwHFzk6hI2PYKP8a9FrzzxoQ3xN8Bx4/5aXTfkqf40Ey2PRBRRR3oKCijFFABSY9KWigAooooAKKM0UAFFGAaKAOP+KTbfhjrx/6dv6itXwigi8HaNGDnbZQjP/ARWJ8WW2/C/XfeAD9RXReHE8vw3piYxi0iH/jooJ6mpRRRQUFFJQCM47/SgDyv4+5/4QWyz/0E4/8A0VLXlnii50HWtdvbyHWbfyXlUxjyJlyvccJwPfqTX1DeWVpqNq9re20NzbyY3wzxh0bByMg8HkA/hWV/whXhU/8AMs6P/wCAMX/xNepTxODqYaFDExl7jbXK0t7d0+xFpRk3E+d/EWq6H/wriw0bTtUS6u0vvPkhWGVQi7XGdzqM9VHX0r6kAxWPD4R8NWs8c8Hh7SYpomDxyJZRqyMDkEELkEHvWxU43FUKlGnQw8WlDmerTetuyXYIxabbCiiivNLCo5ziCQ+impKq6icabdnpiFjn8DQBwnwRGPhdp59Zpz/5FavRa8/+C4x8KNHOBy05/wDI8legUCWwUUtJQMKMUUUAGaKKKAAUd6SloAKM+1MzliOeOacM0AL2rgfhp8114ukIxnXbgfkcV31cH8Mh8nip+58Q3g/JqBPc72imbh7/AJUUDPN9I2/8Lz1sjqNOiz+delZrxa813UNC+NOtS2Gh3Wqu9nErRwHBUYBzzXRH4ka+v3vh7rX4MppIiLsj0fNFebj4k68TgfD3W/xI/wAKB8SfEDHA+HutfiQP6UXQ+dHpGaM15wfiN4hAz/wr3WP++lo/4WN4iz/yT7V/++1ouHMj0eivOR8RvEH8Xw+1n8GWl/4WPr3/AET3W/8AvpaY7notFedf8LH17/onmt/99LR/wsfX/wDonmtf99pQFz0WivOh8RPEB6fDzWv+/q0f8LF8Q5x/wr3WP++1oC6PRaM153/wsLxFnA+Hur/9/Upp+IfiXB/4t7q3/f1aBcyE0vB+Ous47aXFn869HBrwLTfGGsx/FLU9TXwjqD3MtnHG9kP9YgHRifSu3/4WPr3/AET7Wv8AvpaSFF6Ho1Y0PhLw1bTxzweHdJimiYPHJHZRqyMDkEEDIIPeuT/4WPrwPPw91vH+8tH/AAsnWeP+Lf67k/StIVJwuotq49D0WivO/wDhZOrquZPAOvr9FBoHxN1Aj/kRfEOf+uH/ANaoDmR6JRXnY+Jmon/mRPEP/fmj/hZepH/mRPEP/fmi4cyPRKK88PxK1TPHgPX/APv2KQ/E2/GQfAviLI6/uM0BzI9EFFee/wDCz7kAFvBPiQeuLQmm/wDC05QefBfib/wBb/Cgd0eiZr57+Gng3w7rvge+1LVdLe7u4bx41ZJpFIQRxkDCsB1Y9u9egj4psevgzxOP+3Bq8Q8PyXyeF7gabP4miuhclv8AiWo727AKvDBT97+mK9nAVqlHAYidKTi7w1Ts/tdjObXMrnWaF4c8Gap8S9S0xrNBpsdqjW8LXEo+fjccht2fbNbHjnwB4W0j4faxqlhpIt722ljSJxcStt/eop4ZiDwT2rx+9OsXmpNJNPeyX0arjzoCJgfw5/Gt208VahB8Pda8P6na6lJcXlwspuJgxVCHjJ3E9/kx+NGW5ljJ4ylGVWTTlH7T7rzCUYcj0PpXwX/yInh7/sGW3/opa3c15H4Y+K+l2HhnSbCbSNbL21nDCXjsyysVQDIPcHFbX/C3dH3Y/sbxF/4Lm/xrzcV/Hn6v8ylJWO9METTpOYkMyKyLIVG5VYgkA9QCVXI74HpUlee/8Lf0IHB0zXlPvp7f40H4xeHwcGw1v/wBP+NY3Kuj0KivPh8ZPCwXMw1GD/rrZsKP+Fz+Dv8An6uv/AZqQcyPQqijgiieV44kRpW3yMqgF2wFyfU4VRn0AHauCHxo8GE8306/W3anD4zeCSedUkXHrbv/AIU7i5kd/RXBf8Ll8DZ/5C5/78P/AIUD4y+Bj/zGMfWF/wDCkO6O9oNcMPjB4Gb/AJjsY+sUn+FPPxb8C/8AQww/9+pP/iaA5kZvg3B+K3jkjH+tgHH/AFzWvSK8T8MfEHwtY/ELxXqNxqkcNnevCbeUo2HwgB7eoNdyPiv4G/6GK2/75f8AwoJi1Y7OiuPX4peCX6eIrTn13D+lSf8ACzfBf/QxWX/fR/woK5kdZQK5VfiT4Mfp4jsPxlxUn/Cw/B//AEMenf8Af8UBdHTUVzP/AAsPwf8A9DHp3/f8U5fH/hFuniTTfxuFFAXR0lFc/H448KSrlfEmk/jeRj+ZqT/hM/C//QyaP/4HRf40BdG5RWMPFvhxl3DX9LKjuLuP/GnjxPoJ6a1px/7ek/xoC6Naq96/l2M8n92Nj+lVP+Ei0U/8xfT/APwJT/Gqmpa/ox0y7A1awJ8l+BcKex96BNqxzfwTj2fC3S2/vNKf/IhH9K9CrzH4Natp8Hwz02Ca+to5Y2lBR5VBH7wnpn3r0Iatp/8Az/Wp/wC2y/40Ami5RVUahZkZF3AR/wBdBTxd27NtE8ZPoGFA7onopu9fUfnRvX1H50BdDqKbvX+8PzoEiHowP40BdDqWm5FG8UDHUlG4UZoAK85+I3/I4+AR/wBRRv8A0EV6LmvOfiCwPjjwEMjA1CQ8/wC7QJs9HpabkVQv9ZsdNurOC8m8uS8l8qDI+82M4/SgZo0lJvFG8UALRRkUmaAFzRRmjNABRRRmgAopKXNADZf9U30rz74Jf8kwsD6vJ/Ou+uWAtpSeyn+VcH8FsD4YaZ9ZP/QqBHoVFJmjPtQMWkozRmgBaKbmlzQAtFJmjNAC0UmaKACg9KKKAPN9OXd8fdYb+5pEQ/Mj/CvSa830rn486+RzjS4B+tej5oEhaSjNGaBi0lJmlz7UAFFGaM0ALSUZooAWim59qXNAAa82+MB/0Lwsvr4gt/8A0GSvSAeTXmvxbPmS+DYf7+vQfyP+NApbHpfNFGaM0DCikzRmgBTRSZozQAtFJkUuRQAtR+cnneVvHmY3be+KdmjjOcDNAC0UZooAwPG7+V4H1x/Syl/9BNQfD5NngDQhjGLRaT4iSCP4ea+xOMWMo/SrHgkbPBOjL6Wkf8qCepv0UZpCaCj558TfEnxnFr/iD7DrVva2un35tYrUWyMzAFwCNyNnAjLMSR1444HsHw81y98R+BdL1XUGRruZHWRkXaGKSMm7HQEhcnHGScADiue1n4LeGNa1m71OS51KCW7lM0iQzJsDnliNyE8nJ69+MDiu20DRLLw3odrpGnq4tbZSq+Y25mJJJYn1JJPGBzwAOK97MsVgauGjDDxSldfZSslGzTfW71MoRkpamlS0maK8E1CuW1fwFpuqeLtM8TRSzWWo2coaWS2O37SgBAV/0BPdcqexXqaM1rRr1KMnKm7Npr5PdCaT3I5oUuIHhkGUdSrDOODXCo8HhjX9Q+x2bGzsrWNPKjBJSIeUCQOScDn8K77Nee67cfZPE2oNIZo1nhVFaMckYXkZ7fKR+FeVmE4w9lOTslJfkzy80qRp+xnN2Smr/dIdrPxN8BS6dPZ3XiG38u5jaJxHG7MMjB4CnH41806p4m1GSN9Fk1L+0NKilATqA6qTt5OD09a9Z1bw5p17A628YSU5+ZlxuPqSMmuCuPhbfvITDe2wBP8AEW/wqv7Swn/PxF/2xgf+fiOINxGbN0ClHLDAUcY75/Su8+DOlajceP8AT9QhVo7S33tLITgMNpG0f3jnHFVYPhbqokzPdWRX0V35/wDHa9N+HmlWfhK6ku9QaSaYrtVYFBVRx6kela1c5oVeXnqp8qsvJISzbAL/AJeI9L8C/wDIEm/6+W/9BWunrlfBUscOiS+Y6pmdmG4gZG1Rn9DXRfbrUdbmHjr84rLLf90p+g8ossDSv2LFFUzq2nDOb6146/vl/wAab/bOmdtRtP8Av+v+Ndx6N0XqKof23pf/AEErP/v+v+NNOu6QnLapZD63C/40BdGjRWZ/wkGjAZ/tewx/18L/AI01vEugr97WdOH1uk/xoC6NWg1jHxb4cQZbXtLH1u4/8aY3jPwun3vEWkj/ALfY/wDGgLo3K858XHd8XPA8fol2f0X/AArpG8d+E1/5mPSvwu0/xrzzxF4x8O3PxZ8LXkes2j2dpbz+bMsoKqW6An8KRMmj2UUVy/8Awsbwd/0Men/9/hSj4ieDyOPEenf9/wAUyro6eiuWPxI8HD/mY9P/AO/tMPxM8GDr4jsP+/lAXR1lFcgfif4KUZPiOy/Bif6U0/FTwP8A9DFaf+Pf4UBdHY0Vxh+LHgYcf8JFa/k3+FMHxc8CH/mYYOP9h/8ACgLo7b60Vw//AAt7wGP+Zih/79Sf/E0f8Lf8B/8AQxQ/9+pP/iaAujuMiiuGHxh8BkZ/4SCIfWGX/wCJpF+MPgMk/wDFQRD/ALYyf/E0Bcb8Y3K/C/V8dwg/8eFdfpXGj2QHTyI+n0FeP/FH4k+Ftc8EXWm6Xqq3VzMy4VI3HAPOcgV1dl8XfA8Wn26vrkassSgr5MmRx9KCb6noVFcEfjL4EA/5DYP/AGxf/Cm/8Ln8Cb8f2z+Pkvj+VBV0d/RXn5+NHgUDjWM/SB/8KQfGrwKTj+1nH1gf/CgLo9Borz7/AIXV4FP/ADFz/wB+W/wpW+NHgUDI1gn2ED/4UBc9BpK88/4XZ4Fz/wAhST/vy1P/AOF0eBduf7YP08lv8KAuegUVwI+MvgQjP9tj6eS/+FM/4XT4Gzj+1mPv5D/4UBc9BqjrL+Xol++cbbeQ/wDjprjH+NPgdf8AmKO30gb/AArO1n4x+DbrQNRgt76VppbaSNF8huSVIFAXRq/Bnj4T6L/23/8AR8ld7Xifw6+KPhTw/wCAtL0vUL6SK6gRxIoiJxmRj1H1rqv+F1eCP+glL/34agSeh6FRXnf/AAu3wN/0Epf+/DUh+N3gb/oJS/8AfhqCj0XtRXnX/C7vA2f+QnL/AN+GoHxu8DE4/tKX/vw1AHogpa88/wCF1+Bhx/aj/hA/+FP/AOFz+Bsf8hZv+/D/AOFArnfnPbFFefj40+CD/wAxOT/wHb/Cj/hc/gfdxqj/APfhv8KAuj0ClFefH4z+CFOP7Tlyf+ndv8KUfGfwQempyf8AgO3+FAXR35rgfhQ/m6Rr83/PTXrx/wA2FI3xn8D7sDVWb6QP/hR8IZVufCV3eIpVLnU7iYZ64Ld6XUV9T0DAoooplHm2hn/i+HiH/rwhr0jFeb6G5Hxw8Qoe9hDXpIpIiGwUUUUywooooAMUUUUAHWijFFABQKKKACk6UtIaAPNtLwPjxrOeM6ZER7816VXm1iMfHrU8NkHSos8dOTXpI5pExCiiimUGPeiiloATHuaMUUUAGKMUtJQAYo7UtJQA3JrxL4Na1oll4Nu7TVdV0+1Lag8nk3VykZZfLjAOGIOMg/lXt+K4e4+E3gee5llfQkV5GLkR3EqKCTnhVcAD2AAFengcRhoUKtDEc1pcrvFJ7X7tdyJJ3TRxVn4j0i2+LWuXf9qWP2KSxj8qX7QnlM46gNnBNUPHGs6TfeFNWFtqlpLPIIsRJcoxfEqHgA5PAz+FTWvw+8OT/FrUdE/s/Omw2McyQ+fJ8rE8nduz+tdxD8HvBIXMmiEn/r6m/wDi66MNUyuhWhWTqPlae0ejv/MRabTWhueC0P8Awg3h88g/2bb/APota6EdKZBBFbQRwQRJFDEoSOONQqooGAABwAB2qWvIqz56kprq2zVKyEopaKzGJijFFBoACAeophiRuqKfqKfS0AQfZrc9YIz/AMBFRtYWjnLWsDE+sYq1RQKyKTaPpj/e060b/egX/Cm/2HpH/QLsv/Adf8Kv0UBY8r8H6Npx+JvjW1k061aKOSEohhUquUB4GOOtegf8I1oWSf7G07J7/ZU/wri/B24fFrxxn+9B/wCi1r0igmKVjIPhXw8xy2haYT6m0j/wph8IeGj18PaSf+3KP/CtqigqyMI+C/CxHPhvSP8AwCj/AMKjPgTwkTk+GdI/8Ao/8K6GigLI54eBPCQ/5lnSP/AKP/Cmv4B8ISDnwzpI/wB20QfyFdHRQFkcs3w58Guct4a04fSAD+VNPwz8Fnr4csP+/ddXRQFkcgfhd4Ibr4csvyP+NRv8KPAzHJ8O2v4Mw/rXZ0UBZHF/8Kn8C/8AQu23/fT/AONUdS+E/geHS7uWLw/CrpC7KRLJwQD/ALVehVS1T/kEXuenkSfyNAmlY8k+GXw38J6/4A0zU9U0hLi7nEheQyuM4kIHAOOgrrv+FOeAj/zL8f8A3/l/+KqL4MA/8Kq0bPfzcf8Af1q7+gElY4N/gz4CbpoKL9J5f/iqgb4J+BW6aS4+k7/416HRQOyPO/8AhSPgb/oGy/8AgQ1J/wAKQ8D/APQOm/8AAhq9FooCyPOv+FI+Cu1ndD6XLU3/AIUj4MxgW94v0uTXo9LQLlR5v/wpHwf/AM87/wD8CjSH4I+D9uBHfD3F0a9IooDlR5s3wS8KEjbLqif7t2f8KX/hSvhzGBqOuD6Xv/1q9IooDlj2PN1+C+gx/d1XXwPa+x/SuO8X/DfTNN8W+FLGLUdWlW/umjkM11uZABnKnHBr3mvOfGo3/FDwHGennzt+IiNAnFDh8HtGAwNb8RD6agf8KguPgrod06vcaxr0zp9wy3u4r9MivS6KB8qPOh8H9NUYXxH4lX6agf8ACg/CGx7eJvEw/wC4gf8ACvRaKA5Uebj4RWytkeK/EwH/AF/mnN8JVA+Txh4nX0/09jivRqPpQHKjzofCy4UEL468Uj6X7/40f8Ktuu/jzxWf+4g/+Nei0UDsjzv/AIVddf8AQ9+K/wDwYP8A40f8KvvAcr478UD63zH+teiYFFAuVHnZ+GWoEf8AI++Jv/As/wCNH/CstSxx4+8S/wDgUf8AGvRKQnCk9celAcqPN7n4Z3620xbx54lKhDkPdEjp9a5b4a+BbrWPA9jfQ+LdesFl3f6PaXJSNeewzXsmsvs0S/fptt5D/wCOmuT+D8fl/C3RMfxRM3/j5oFyq5WHwz1FTkePfE343ZP9aYfhnrOcr8Q/EQ57zE/1r0aigfKjzZvhjrp6fEbxAOf+eh/+KpR8NfEAGP8AhY2v/n/9evSKWgOVHnI+G/iAf81F1z8h/jR/wrfxAf8AmomufkP8a9GooDlR5x/wrjxCDlfiLrgPuAR/Oj/hXXiPP/JRtbx/uj/Gqnxn8Wa34b03TotIjubYTTiR9QTaUBXkRdzkkBjnAIUj5gWAZr3xttNCjtreTQL3+12ijkubOeQRC33Lu2l8ElsFTjaOG52sCo9Wjk2Lr0oVKK5ue9kmr6dX2/q+6IcoJtM0T8PPEPG34i62Pqqn+tA+HniMf81F1r/v2v8AjWVq/wAeNFs7K0m03Tbm8muF8wxSypF5S7nXDFS5DZQHbj7rA57VjeI/izf3/wDwiWo+HYL1Ee5cXdku0+fKuwGAHBLfLJwduP3iEfMuF0pZBj5tKUOVO+r7pN+vQHOCOs/4V34j/wCij6x/36X/ABqC68Ea1Z+T9q+KOpwedKsMXmhF8yQ9EXLcscHAHNekQSNLBHI8Lws6hjFIQWQkfdO0kZHTgke5ryfU7ODxn8ef7L1GPfYaFYib7NIS8c7na2dvAXmVM9dwiAPBwOPB4WNec+d2jGLk7a7dvVtIqTS2MHR/ButXXxQ16zTxjqMdza20PmXqKPMkDdFPPQYrtf8AhXviX/oo2sf9+l/xryXTp9e8X3/jLxPputXOk3FrD9seGGVk8yIFiIy6Y+6qnGRyeuMk17x4I1m68VfD/TtRnkeC7uIGjkmj2lt6s0ZkAK7QSV3Y2kDOORXTjcqlhIc7mnZ8skr+62r28/VERakzEHw/8S85+Iur8+kKUz/hXniQHI+I2tf9+1/xrgvF2i+JfDOraNpEHxE1a91LVJ1ijiaeSJYlLBQ7kSswBY4Hy84bnjBj+ID+PE8falaaNdeJp7eGK3Km1Mu0gxKN+IwFG5lfoAMhvQ110shjVceSurSTd2mtml1t1f4EuaW6O6l8E61b3VvayfFDU47m43eRDJs3y7RltoLZOBycdKn/AOFeeJe/xG1n/v0v+Ncv4psLLxJ8JtO8UaRqdzqGr6KsZOoGPF0QpG9H2nKlCwfJ3EBc7juLn1vw/rEWv+H9P1aHYFu4FlKJIHCMR8ybh1KnKnpyDwK8/FYH2FJVE76uMtLWa/HVfqXGzdjiz8N/EWMf8LG1z8h/jR/wrnxJgD/hY2tf98D/ABr0eivOL5Uecf8ACuvEv/RR9a/79D/Gl/4V54m/6KPrP/fpf8a9FNGKA5Uec/8ACvPEuf8Ako+sf9+l/wAaUfDvxGP+ai61/wB+1/xr0WigOVHnX/CuNfb73xF1049MD+tcP478Eanp+reFIbjxfqt9Jd6msEcs7c25OPmXnrXvtebfEr954t8AQDvq/mf984NAnFIefhrrX8PxD8QAn1kz/WgfDjX8Y/4WLrv6f416NRigfKjzpfhvrgzn4h68c9eR/jTx8OtbCYPxB18nudwr0KigOVHAD4eaxjH/AAn2v/8AfQpn/CuNXOM+P/ER/wC2tehUUByo88Pw21U/8z/4j/7/AFKnw01HGH8e+JW+l0RXoWKKA5Innv8AwrG97+PPFH/gaab/AMKuu+3jvxSP+35v8a9EooDlR54Phhd4wfHfir/wYN/jS/8ACr7g9fHXiz/wYNXoVFA+VHjfjj4e/wBl+C9XvpPFfiO7EFuzeRc3zPG57AjuK0fD/wAMWfw/p7N4u8TRh4FcxQX7RoMjOAOwroPiqwj+GWu5Gc25H5muj0EY8Pab/wBesX/oIoJ5Vc5Jfhei9fGHi38NVYU0fCyDPPivxUf+4o1d/RQPkRwA+FGn458R+Jzj/qJt/hQPhPpuMHxB4mP/AHE2/wAK7+igORHn3/CotI/6DniT/wAGTf4UjfCHQ2H7zVNeb3bUW4r0KjFAcqPPf+FPaBnJ1HXSw6E6g2RTh8IdAzk3+uE476g1egUUByo8+/4U/wCHSuHu9ZcH+9ftSL8HfDG7cz6ozdyb5+a9BxS0Byo85f4KeCyGaW1u3Pq90xrFb4LeETKxFpdBSeP9IP8AhXrky7l21AluqsWI4AoDlR4V8M/hh4b8RWGsXeqWssvk6jJbQr5xUKigenfk16CPgt4EXn+xyfrcSf40nwijx4Xv5+P3+q3UnH+9j+legUCjqtTg/wDhTXgI/wDMBT/v/L/8VQPg34CXn/hH4z9Z5f8A4qu8ooKsjhR8HfAQ5/4R6I/WeX/4qpB8IfAf/Quwf9/ZP/iq7aigLI4ofCXwKhyPDlt+Luf61IPhT4GGf+Kbs+f97/GuxooCyOQT4XeCIxhfDdif95Sf5mpP+FZ+Cv8AoWdO/wC/Irq6KAsjlB8NPBQGP+EZ07/vyKUfDbwWOnhnTfxgFdVRQFkcwPh34NH/ADLGlfjar/hXB6r4S8On4z6Jp0eh6elm2my</t>
+  </si>
+  <si>
+    <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAgGBgcGBQgHBwcJCQgKDBQNDAsLDBkSEw8UHRofHh0aHBwgJC4nICIsIxwcKDcpLDAxNDQ0Hyc5PTgyPC4zNDL/2wBDAQkJCQwLDBgNDRgyIRwhMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjL/wAARCARDBdwDASIAAhEBAxEB/8QAHwAAAQUBAQEBAQEAAAAAAAAAAAECAwQFBgcICQoL/8QAtRAAAgEDAwIEAwUFBAQAAAF9AQIDAAQRBRIhMUEGE1FhByJxFDKBkaEII0KxwRVS0fAkM2JyggkKFhcYGRolJicoKSo0NTY3ODk6Q0RFRkdISUpTVFVWV1hZWmNkZWZnaGlqc3R1dnd4eXqDhIWGh4iJipKTlJWWl5iZmqKjpKWmp6ipqrKztLW2t7i5usLDxMXGx8jJytLT1NXW19jZ2uHi4+Tl5ufo6erx8vP09fb3+Pn6/8QAHwEAAwEBAQEBAQEBAQAAAAAAAAECAwQFBgcICQoL/8QAtREAAgECBAQDBAcFBAQAAQJ3AAECAxEEBSExBhJBUQdhcRMiMoEIFEKRobHBCSMzUvAVYnLRChYkNOEl8RcYGRomJygpKjU2Nzg5OkNERUZHSElKU1RVVldYWVpjZGVmZ2hpanN0dXZ3eHl6goOEhYaHiImKkpOUlZaXmJmaoqOkpaanqKmqsrO0tba3uLm6wsPExcbHyMnK0tPU1dbX2Nna4uPk5ebn6Onq8vP09fb3+Pn6/9oADAMBAAIRAxEAPwD3KGaMW0ciRSKGUbVKHdjtkdvxrnrLx1a3uGj0bXlgaPzIpzpsnlyjGQFwCfzAra0+SY2wilbdJDmORliaNMj03cnqOckHBrnfhg9zN8PtJkuZ3nmIlEkkj+YxYSsPvZ5Axj8BQDLOp+OtM0eKwlv7a/gN67hEkgw42AE5BPuMAZJJwBmqU/xItEKNZ+HvE2owugkW4tNJk2HOeAWxz+nNdXeypbRvOzoD0HmzlF/rz+FVo7uO4giSG+/eyLxIgzkc9M8Z470BZnEH4iiaa3EngTxdAIGymNJB2jGM89Pwq4/xEa4diPCHjMCMEhRphXzOPXP+FdgbopNsQu5IByVwOQccn1I7Cp4w20NIR5vDMqucE4x+VAWZxFr8SLdYwX8I+L7ePjMsulMc8YGSCSe3NIPizZssuzwr4tcRZ80rpf8Aq/r83H/1q7su5fPCqh+Y/hTROWwyAMDgj5ucH2/z0oFZnERfFKxkuBEPDfisxgbzN/ZZK7cZycHOOfSi4+K2gg8Wuu/K21wumv8AJ9cj6V3vz8EYx3GKYAQo+due5AzQGpwo+KvhZkjG7VyHfC/6BPkt6ZA5+lK3xj8GxkLJeXqE9A1hMD/6DXdbwvDuoP0xinkkEZxigNTgG+NHgfZk6jdAHv8AYpv/AImkHxr8CZx/aswOf+fKb/4mvQAeM9R60EknAH40Bqefj41+ANuTrbgjsbOfP/oFP/4XV8Psc+IP/JKf/wCN13xJHp1rzT43yxx+AoVkgjkMmoQKnmAHack5H4Aj6E0BsXf+F0/D3P8AyMH/AJJXH/xFB+NXw8P/ADMH/klcf/G67iS1tpCplt4mx0LKDg0hsrVnLNbQlmOSSgyaA1OJHxo+HzDP/CQDj1s5/wD4ipT8XvAAZQfEEOTwP3EvH/jvFdZLpenzoFmsLaRR0DQggfpVY+GtBLhjommlvX7Kmf5UBqZFr8TvBN4haLxLp6gf89pfKP5NirX/AAsDwb/0NOj/APgbH/jVtvCnhx/vaDpZ+tnH/hUB8FeFWOT4Z0Y55/48Yv8ACgNSP/hP/Bx5/wCEo0f/AMDo/wDGnf8ACeeD/wDoaNF/8Dov8aX/AIQnwn/0K+i/+AEP+FH/AAhHhIn/AJFbRP8AwAh/wpBqH/CdeETz/wAJTon/AIMIf/iqX/hOvCJ/5mnRP/BhD/8AFUxvAng912t4X0YZ9LGIH+VRv4A8Hyo6t4X0cBuDtsowfzA4/CmGpYHjfwocAeJ9FJ9r+L/GrA8UaAz7F1zTS/XAukzj86xZvhd4JniEbeGrEADHyKVP5gg1Wf4P+ApHLt4eiyf7s0oH5BqQanbCaJhlXU/Q07zE/vD864I/BT4enk+H/wDycn/+Lpv/AApT4e9tA/8AJ2f/AOOUwO+3p/eH50BlPGR7c14N4D+G3hLWdd8YWt/pbTw6bqTW9sPtEi7EBbjhhnp1Nd1/wpP4ff8AQBb/AMDJ/wD4ugNT0AAE54/Clx7V5rcfAvwNKx8qyurfI/5ZXTnH/fRNVm+AXhItlLrV4h3VbkYP5rQB6nz2oxXlSfATw5GpVNa8RIhOSFuowP8A0XVyL4O2cUPlReMPF0ak52pqIAz642UBqek4pa86/wCFUnjHjvxkP+4p/wDY0f8ACqWB/wCR88Zf+DT/AOtQB6LiivOm+Fc+Pk8feMR9dSJ/pVE/CvxBg4+JfiMHnGZW49P+Wn+fagLnqeKK8p/4Vb4uRcR/FLWQe2+Jm/8AatTJ8O/G8Spt+KN8dhyN9gG/PMnP40Bc9Qo59K82Hgbx6rAj4nTfL0zpUZ/9mqT/AIRT4kDhfiTGfrokFAXPRRQTXiiSfEl/iHL4S/4TmLdHY/bftP8AZcOCNwGNuOvPrXQTeGPikBmHx/ZsfR9LiUfyNAXPS+1GOMV5dJoHxeTiHxnpMvvLZKv8ozSrpfxmQ/8AIweG5R/tRMP5RUBc9QxRj8K81jtPjHF97UfCUv8AvLMP5KKlH/C31H3vBr/+BFAXPRaO/SvPTL8XVH+p8Gt9Dc0w3HxeHS08IH6NP/jQFz0WjFebm9+L6/8AML8LN/uyzf1NV21n4xIT/wAUxoMg/wBm4I/nJQFz1GkrzCHxF8WlGZ/AumyH/pnfxpj85DU//CVfE4dfh1Bn/sLQ/wCNAXPSKTFedf8ACYfEVThvhrn0xrEP+FB8a+PgcH4Yy/hq8R/9loC56NniivJ9L+KviTWLu/tLDwBPNcafJ5Vyi6kn7p8kYOUHoelaL+PfGcQ3P8M77/gN+jfyWgLo9H6Vk+J7OfUfCes2VrH5lxcWM8USZA3OyEAZPA5I61w5+JPixT83wy1fn0nz/wCyVw/xE+JHii6h06E6ZrPhaMO7u28q0+AuNrAKTtBORnB3DPQV25dQlXxMIRaT3u9tFfp6EylZFG68MeJNV+HmgxS+GNTWPQrmeOeHaUnuY5nV90aFSwxypO0gZBG7DBatt4F1BtD1a/PgfVmh8+3jt0muWW7hUHMpVBGBIGGF3FPl3AgNtYjl08da/K0ix+KNfJHK5unwenX95x39ew78e06f8W9YGk2O/wAD+Ib+X7NEZbpLYqkzbRl1AUjaTyMdjX1WIzmdDDqrQcZRcntzqzupNa23b37O22hgoJuzOI8O+BvEOo2fii0stAvNPt7ixjEK6moEjSLNG4QSFEJyEk6ALnbu6A17H8NdS1K98J21pqWg3ulSadFFaKbkY88JGo3gEBh09McjBPOMSH4uSHIuPAviuM4HCWG7nv1Iqb/hb9qP+ZN8Y/8AgrH/AMXXg4/OJY2DhOCWqa3utEn11ul1NYQ5Xoyj8ZP+Jdf+D/Ec3zWem6mPOROZGyUf5QeDxC3Ujkj8Kmux694Z+JUvjfQtHfxBpeq2ccTC1+YjKrjaU3HH7pG37duGx1wau6n8T9G1fTZ9O1HwN4tntJ12SRPpgwR/384IOCCOQQCOar6F8RtE8N6Ha6PYeD/GQtrZSq+Zp4ZmJJJYnf1JJPGBzwAOKdDNIUsPGm43aUotPZxk77p3TTBxu7mLoTeNvDHh/WPFVtoLy6vrmqqX097KVjHGBKzSbFbeoLtgbugAPO4Gp/E+mappPxKu/Etx4HfxDYanZoI7UxiU27hYwd4VXAYbCOMghuGOCK6T/hcmmg7f+EX8VZxnH9nD/wCLqKX426FA5SXQ/ESMCAQ1kARnp1bvVf22/auq6a95NPVq60srp6WstRcita55tY+AvEXh2z0LWtS8PXOt2hnklfRU3ExEouxnUAkFioJG0jEaq3J2jsfBjXuja54m8bajob+G9AFmE/s0/ut0ihMbEIQEnDAEgZaXAzlsabfHvwqmd9hra465tV4/8frD8S/Fj4d+K9OhsNYsdaa3WdJ12xBDuXtkP0ILKfZjjBwRvUz54q8MRGylo2r/AA3vZRva/nuJU+XY6L4LaZP/AGBqHia9uPOvNduWmcjAGEZxkgAYYuZDxxjbjHNem968Gn+PdjaeKNNt9NsfL8MxwiGdGg8uSPkgFApICqoXA78+2Ovg+OfgSWMs9/cwnsslq5J/IGvGxuJeKxE6zVrvRdlsl8loaRXKrHpQo6V5yPjf4DMpjOrTAD/lobSXB/8AHc/pTh8bPABcqdacADO42k2D7fcrlKueiGjtXn4+Nfw/Iy2vFcjobOf/AOIpf+F1/D3/AKGH/wAk5/8A4igLnfk4orgf+F0/D4/8zAP/AAEn/wDiKX/hc/gD/oYU/wDAab/4igLne4pK4UfGPwCf+Zij/wC/E3/xNOHxh8BE/wDIxQ/9+Zf/AImgLncjmj6Vw3/C4PAWAf8AhIoeeP8AUy//ABNOHxc8BscDxHb/AIxyD/2WgLnbUuK40fFfwK3TxJafjuH9KX/hangb/oZbL8z/AIUDOx70Vxw+Kfgc9PEtl+JP+FSD4neCSM/8JLp//f2gVzraO9covxK8Ft08T6b+MwFOX4jeDGOF8UaX+NyooC51GOODSKCFAJyfWud/4WB4O/6GjSP/AAMj/wAaUePvCBwR4p0b8b6If1oC6OjqreW63MBVoY5SpDqr9Nw5B/A1kf8ACeeEf+hp0X/wPi/xoPjvwiOD4p0Qf9v8X+NAXHeH/DWn6BLey2dlFby3MimRo1xvAUAf/X98mt/Fc9/wnnhA8f8ACU6L/wCB8X+NH/Cc+ER/zNWif+DGH/4qgZ0Bo71g/wDCd+Ef+hp0T/wYw/8AxVNHjrwhj/katD/8GEP/AMVQB0FH4VgDx14RH/M1aJ/4MIf/AIqg+OPCI4PirRB/3EIv/iqAN+jGawP+E68I/wDQ1aJ/4MYf/iqP+E78If8AQ1aH/wCDGH/4qgDfAwaK5/8A4Tnwh/0NWh/+DCH/AOKo/wCE68If9DVof/gwh/8AiqAOh6jFJjFc/wD8J34P/wChr0T/AMGEX/xVL/wnXhH/AKGrRP8AwYw//FUAb+KOprnf+E98Hscf8JTov430WP50h8e+EFJH/CU6NxzxfRH+tArl7xNq39heGNU1QPCr2ttJJH55wjSBTsU8jOWwMA5OcCvDPDvjPx54is7u4Txxo9gLXBlS/jijbaSAGH7kgjJA65BxnGRn0vxN458Kaj4W1iwtfEelyXVzYzxRJ9rQBmZCANxIA5Pc18wfasWf2fzHCNIH2hwFY4IBIx8xGeDnjLY+8a+t4ew9Gth6l4xcuZatRdl6P+mzCrKzR9B/Cz4iXWrQ63H4n1qwdbJo3iuZNkG5GJVj0UbQdmCQDl8HqAOoHxO8L3Wj6tf6ZqcN0+nWzXDQSboC/ZQC6jOW2rkA4LL6jPzFpM2nxR6kmoz3say2brCtrIi+ZLuUosgY/NHuAJAyeAR0rS0e60bTNZuPJunmt59Nu4FnvoRbmOV4JFXaFkYckhcscfOeBgGvSxuQ4J1KtVtrls7KyirJXv2v8t9LkRqyskfSfgDxpb+NfDkd7mGPUIvkvLaNj+7fnBwedrAZHXuMkqaj+JXiiXwl4Kur+0lSO+kZYLUvGXG9jycdMhA7DPGVGc9DwPwq+IvhHRfCEGk390unXcJeWWWSMBLgs7EEMuckLsB3YPAxkDiD4xeM/DfiPwja2ej6xbXdyl8kzRxsc7Ajgnnrywr5/wCp0Y5yqEo2hz6J9unyfTy03NuZ+zv1KFnZav8AC7VtJ0/Qd+o+JNZs0N1p0wJhhO4nOFIDEYIDbsKEkJ4cbfQ/AHjrVde1nVdA8SafDYazY4kEUKsA0fAPUsOCVIO7DBwQMDJ4DxX4/wBBi+Kvh/xXpt7HqVpb2pgmhh3JKn+sBOGA7S5AzyVIO3rVHTfiTYW3j/xL40EKDzrZLe106WYrLP8ANEu7IUgYWIsfTIAz1r1a1CWPw3tZwTlKPxbP2nPZQ7LTTVfPqZqXK7J/8MexeP8AxnB4K8OSXuYZNQl+SztpGP7x+MnA52qDk9OwyCwrmNU+KOoWfwm0vxVDp9t9uvp/s5jdmMSMDIGbAwSD5ZwM8bhycc+a+O/ENp4uvo9ai8VaasaWPy6VdRyFraRo8SRp+6KMxPSQ7TnHTaprCh8Q3DeFtM0W+8Ro+hi6Hn6VZrtuUTezMSSgVu5ALkZK8ccRgsrwToU+dxc+dcybd9n7iXfT5u+trDlUld9j1nw/468R+LdSu/CmoC2srm8s2e31LQ5UnFrjOTIRI4APAyCrAkYwWDCT4I2cEP8AwkRv493iWC+aG9lkJeQIe2/kHMiyE4PJAJz8tcZ4f8b+FdA+I9pdaEbrRfDc1qY7+G6JfzJAJCrY3OepjAI5HPYnOh4S8f8Ah3T/AIkeKdd1DV47Cxu22W9vDbSbLkbuJioBw2FycjJMrHjkUY+EKVGvThHkjywduvNe1mtbXWtrtaJ9xRbbTep790oz7VwH/C6/h6P+Zg/8k5//AIij/hdXw+/6GD/ySuP/AI3Xxx0nf9Bmlrzx/jX4AC5XXWY+gs5/6pUEfxx8CtGSdSuVIz8rWkmf0GKBXPSKWvLz8evBQTdv1E+gFt1/WmSfH7wcrBY4tUmJ/uWw/qwoC56maK8uX48+FnbbHp+uOf8AZtAf/ZqnT41aE7bE0TxGz/3RYZP/AKFQFz0rFHtXnLfGDTx08LeLG+mm/wD2VM/4XFY/9Cn4t/8ABaP/AIqgLnpVJ3rzkfF60JAXwf4vJPTGmD/4unD4tW7Z2+DPGRxxxpY/+LoC56JRXnb/ABUmwPK8A+Mm9c6Zj+pqA/FXUyfl+HXir23WZH9KAuj0uivM4/ib4gmB8v4b+IBgfxrt5/FaUfEbxY33fhnq/wDwK4A/9loC6PS8ijFeWaj8UPE2lafNf3/w6vbe0gGZZXvlwozj+771NZfETxhqNnDd2fw3uZbeZBJFIdSRdykZB5WgLnpuRQefavOh418eN0+GU346xD/8TR/wmfxAJ4+GMn/g6h/+JoC56LRXncniz4imMmL4bBW7FtbhOPwwKZP4n+JzgfZvh5bRHv52rwvn8iKAuej0ZFeXS6/8X3IMPg7R4hjkS3YfP5SClj1f4xPnPhzw9Hg/xzn+klAXPUKK8yTUPjC3XRfDSfNj5pn6evDdP1qwLj4vMP8Ajy8Irzj5nn/oaAuei0V5153xgzxbeDh9Tcf404SfF8nHleCx/wCBP+NAHoeRRXnUifF+UAibwZFg/wAIuefzBrmvFF98XPCugXeuX+taA1rbbd0dvES3zMFGN0Y7sO9AXPas8Zoz7V5Na6X8Y7q2jn/4SjQkWVQ6j7PkgHn/AJ5Vag8PfFl3X7R430yNcc+VYI/80FAXPT8ijFedHwv8S2OR8RIF9ho8NJ/wivxK6n4jw/8AgmhoC5397eW+nWNxe3Unl21vE0sr4J2ooJJwOTwD0rwTUPG/w21Lxivia407xEbsrtlhUReTN8hT5135IK4BUEKQMEEE56nxN4b8fW3hXVprvx8t1apZzNPbjSYU8xNhyu7ORkZGRyM14nF4w8T2eipotpq7rpJgeN7YRx4Cuzb1yRuOck56jPbivocnhGFGVblk25KHuu2jTb6PsZVG27HtvhX4XeBNYSx8T6f/AGhPZTMZo7K6dTEpBI2Mu3cQrAjBYg7eSwPNo/Anwj9v+0ebqflebv8As3nr5e3Odmdu7b2+9nHfPNYXw78L+LdS8C6ddad45l0yyfzfLtE06OXy8SuD8xOTkgn8a6geCvHORu+JlyfppUI/rWONzPHUMVUpwrStFuO/RN2+fmEYRcU7GrJ8ONAbxrF4qiFzbXyN5jR28vlxSPggswAzk55AIDdwctnqp4IrmCSCeJJYZVKSRyKGV1IwQQeCCO1eat8NfFBkmc/EzWczAhtsWAMnPA34X8MVCPhP4g3Av8TfEhHcLNIM/wDkSvKq4irV5faSb5VZeSNEkth/gfwpq+lJrXgfxDp6aj4cK+db3rMQrBz9wLnKnILYGCjAnJ3K1anhj4S+HvCuuRavZy6hPcxKyx/aZVKoWGC2FVcnBI5yOemcEUB8KdSzz8RvFmPa+b/GrP8Awqqbv4/8Zn/uKH/CuytmuJqObUuVT+JLZu1m7efWwlCKOg8H+CtN8E2FxaabPeSpPL5rG5l3YOAOAAFHTrjJ4yTgYtaN4X0vQdS1a/sInSfVZxPclpCwLc8AHoMszfVj2AA8q8f+EL3wp4ZGo2PjbxXLObmKELPqTFfnbB6AV1Q+FBxz488Z/wDg0/8Asa5KmKrVJSlOTblv527jUUjqrjwtpd34qs/EksT/ANpWcDQROshC7WzyV6EgM4H++c5wMcf4M0DX9T8c6l408TWiWUm1rOxsXPmNAoIBZWJwowGGR9/e7AAEbpx8KR38deND/wBxX/7Gg/CmMgg+OPGpB6/8TXr/AOOVrTx1WFOUN7rlu91G92l6/wDDA4pu56EOfajB9eK8qk+Anh2Zi0mu+I3Y9S13Gf8A2nUZ/Z98LEjfquvN9bmL/wCN1xjPWsd6PevN/wDhSPgkbsWd5zgf8fb8Y64579/rxip/+FLeAhx/Y0v/AIGz/wDxVAHf7h6ijev94V5//wAKS+H566GxP/X5P/8AF0f8KS+H4/5gLH/t8n/+LoDU9A3r6j86TzUHVl/OuA/4Un8Puf8AiQn6fbZ//jlKPgp8Psf8gE/+Bs//AMcpBqd2biL/AJ6oOP71N+1264DXMWT/ALQFcMPgr8Pj/wAy+R/2+z//AByuK8efDXwjouo+FINP0jyV1DWIre4X7TM3mRHqOWOPqOaA1Pbje2wPNzCPq4qGXVtPgjMs19axxjq7zKAPxzXHD4MfD5CSPD4P/b3Of/Z6l/4VD4A6f8I9Dz/03l/+KoDU6P8A4STQzaLdrrOnG3ZiizfaU2kjqAc4zwarv428KRHa/ibRVPob+If1rET4QeAYxtXw7CeO80pP6tTh8I/AXbw5B+Msn/xVMNTXPjnwiD/yNWiD/uIQ/wDxVA8d+Ee/ivQ//BhD/wDFVl/8Kq8CtGU/4Ry0xnr82ePfNXE+Hng1JI3XwvpJKR7Bm1Ugj3BGCfc80DJ/+E78IHj/AISnRP8AwPi/xpT468I4/wCRq0P/AMGEP/xVH/CC+EP+hV0P/wAF8P8A8TQPAvhH/oVdD/8ABfD/APE0CGf8J74PH/M0aN/4HRf40f8ACwPB3QeKdH/8DY/8ak/4Qjwp0HhfRAP+vCL/AOJpf+EJ8Jgf8ivov/gBF/8AE0BqRf8ACwfBv/Q06P8A+Bsf+NH/AAsDwd/0NOj/APgan+NS/wDCF+E8Z/4RfRT/ANuEP+FKPBXhTH/Ir6L/AOAEX/xNAxLu1vJvDN+q+VLqEltLGjhOGJBwOp4yfX8qy/DVinhnwPpmkC6sZp4B5TEP+73GQmTA6nBz+XarfiVCvgLXIorVnf8As64CwheWPlnAGOv4VQ+HkemW/wAPtAOniMQPbhz5shypYkyAZHOGLCjqHU2ZrOztbgX8geWbcZVVcsxOMcc9OfpUhe4W5Mgsl8122BjLwqjkEg9u3Hcj6ifM7XZC2iBY8qkrsMgYB4Azxnjt92n7ZxBJ9oaB+MBiOOvp+XfrQUQQzrGHldgTtGWkbk/h/nrUxREjUAy4c5KjOc5B69qZLJCjyM95Fg8gO44GBkfT6561aCrGRyd7cDIOM0xCMXwwQjO8Ahhng49/enBiFK8EkYAHH/16ajHeQytlBkHsRz39fWnEsAPkAX1zmgQBmWUrs2qehAzk4708kj5Qucdyaqw3kVxqFzaBG8+12lgRgEMDhh6jgj6g1aUBUBVeF7Y5/WkAql+QwU+hHej+LAznqfSgkjnkflS8kkFTx0JPBoAO/wBP1p/4/jUfVcvgcc4bpSqVKAqcrjqO9AAWwRnuccV5v8arb7b4S0qDesXmaxbr5jc7M7hn9a9I4w3HGfTrXmvxqAk8O6BG7mNH163VmHYYk5oE9j0w43e4FHTjH/1qacAgnqadk56UDA/hTehA5P8ASndceuKCMnk/hQAEjufalz7UlGfcZ9KAF4NGQD1o70A0AJz6flRx6Ue9L6AUABzRSYPP+NL+HFAB1oxigdKOvPNAHmHwrx/wlPxCxx/xPJP/AEJ69P4rzH4VZbxJ4/Y4512UfkzV6dgnqaBITP0pfekIGMjFAPH+FAyMTRPcPAkqGZFV2jDDcqsSASOoBKtg+x9KlrwG1n8SaN8ZvE+ozXlncXGn2Mt3ehYiqXFsqIyxoOSjY8oZycYJJfBDUdI+NfiubxPbtcxw3NncSxxNYW1rkgEqD5XO4ucHAZiMt06Y+i/1crzXNQkpLlUu26vZfptoY+2S3PozNMjmileVI5Udom2SKrAlGwGwfQ4ZTj0IPevnKD4x+NI/Fcf2v7MkSziKbTJI1gjB+6yl3+ZDnJyzYB68DFdV8LYdX/4WZ4zf7ZbfZI7yRb1BCQZpDJJsZBklACH6s3Bxgn5ljEcP1sNRnVrTStFNW1vqlb8fRvruNVVJ2R7MDXMaP4+0DXdS1a0sbh2i0tQ894yYtivOSJOmBg8nGcErkAmtLxNd3GneE9ZvbVxHPb2M80T7QdrrGxBweDyB1rwi/wD+JZ+zlpn2P93/AGpqbfbO/m4aTHXp/qY+mPu+5zjluXQxVNub1lKMV5Xu2330Wnmxznys970/xBourztBp2r6feTKu8x29ykjBcgZwpJxkjn3qbUNU0/SIFn1C9trOFm2CS5mWNS2CcZYjnAPHtXjWveFNN8AfEHwJN4f86GS6uRbTmR/M8wbkRm5HDMsrA4wOmAK9U8T+HPD3iGwU+IrSGW3tN0wlkkMflDHzHeCCFwMnnHAJ6Cs8Rg8NSlSnGUnTmn0XNo2tr23XcFJu66otaf4g0XVp2g03V9PvJlXeY7a5SRguQM4Uk4yRz71civbWe8uLWG5hkuLfb58KSAvFuGV3AcjI5GeteOfBvRNN1DxHrniiz077NYRS/ZdNjZt2wHlidxZg+3Zk5x+8cDjgHw/0YeHfjl4i003k135diz+fOcyPveF/mPdvmwT3POBnFdOIyqhCpWhCbvTipWa66XWjtpdL19BKbsnbcs+E9ag1/8AaA1u9tUuFhj0l7bE8RjYMksan5TyOR0IB55Ar2AD3rxG/wBaXQv2k1ZPMEV8sNpcBFDbzIiqvXoA6xk45wO+cH26uHH4aFL2dSlflnFNX6PZr719xUHe6YYpaTvS155YlFHel6UAHWkpe9J1oAWjtQKKACiikzn1pAFFLSEdKYHl/wAJ7YjxD4/v+qT69LEP+Asx/wDagr1DvXmfwpgkGr+PLreTHJ4gnRVPQEMST/48Pyr0ygSA15j8W/CeteJG0K60exgvzYSyNNbTSBQ4bYRnJAK/Jg8g8jHcj07mkHXNdOExU8LWVaCTavvtqrP8GKUeZWPmu6+HvjNlulg8E6fZG8hWBzbXC9A6uMAzEA5Qduma+gfDunT6P4c0vTp5FkltbSKByhJXcqBTjIBxkelamMnJHSjHetsVmEq9JUVCMIp391Pd6dW+wows73FooozXAWGaKMUlABnrRR26UtADea82+M4LaBoCgAhtetQQe/EnFelV5z8YQW0zwuo6t4jtB+klAmejc9hTSoJyVH1Ip3OenFHagZA8NukZZoI8AZ+6Kb9gtGwTa27HsfKFWSMgijGOgoArNp1kxJaytyTySYxz+lN/svTj/wAuNr/35X/CreM0ooApnStOz/x4Wv8A35X/AApDpWmj/mH2n/flf8Ku0c0AUP7I0xs/8S60/wC/C/4U1NC0iMkx6VZAnri3UZ/StDBpaBWMpfD2ix7ymj6epk+/i1QbvrxzTZvDOgzx7J9E06Rf7rWqEfyrW5paAscT4t8KeGrXwdrVzH4e0pGgsJ5VZLKIFSIycg44PFZHw98M+Gpfhlo9/e6Bp9zJ9lMksjWCyyPgsf7pZj7AEmus8dA/8K98S/8AYKuv/RTVW+G8H2X4beHYz3sIpP8Avobv6015hbU8v8HeLPBmq6zrq614b0a206PNzZS/2TH+6hX5SshUH5j8mOuWYqDyi1v6V4n+E2rXl3aR+H9Nh8hZJFebSE2zIis7uu1ScBUJwwU8jAzxXPzeGfE1xqnxC0KLQbnGsT/are8chYcRzmVV3n5SXV8DByGwCANxXm/DngXUL3WLMP4H1aSKCCSS8i1G5a3iuGCYUI/lqUO7ouWzkZIAZq+1nlmV1lOo3y6KyUo/yp31tu7rXqr6Xuc/NNWR32l+JvhLq+svpsXhmxjb5vKml0mLZOR0VAoLFm/hBUE9MbiAYPhTL4b8Z2t/b6n4T0X7fbSmTfDpKLF5TH5V3YIDA7gAcEqAfmIY1xnhHwrrMPjLw5LbeFdZtGhuY2vJr+INEVBBZlDRKEwA5GSxztwdwGfQ/hPa694Tvr7wlqfh+5EInkuf7UjOYD8qKACQAQQM8Etk4KjDEYZhl2BoUKsaGsrRavJXVm02vXTTqEJSbVzW8ceHfCPhzwVq2qx+F9JWaGArCyafCxWRyEQ4IwQGZSfYHg9K8vufD1p4c8B+HIrXSrO+8S+JJUeKe5gjmSKP5SqJ5g2qT5kYOQRy/PC49k+KGny6l8NdcghZFdIBOS5IG2JlkYcDrhDj3x0rzy+tb/xP8PvBPiLwxD9tvPDu1JbMhS26NUySA2TzCuFHzMJARiufKFSWHjz2s5tSvtpG8E/Jy+RVRO+nYq+F9ATSfiMvhPxhoWhXxvbbzbSa3sIQoIDNnKqp2kK4OVzlRjg5PT+MfhZLez2h8J2HhqwhVWE6XGnoWZsjB3GNxjHbAx6nI24tpJ4s8SeO7rxnN4budLOjaVKLO2ngdjcSeXIEj52sxLOx+UdAF6kE9Bq2qeM/EPwkbb4fmh1u/lNnPCEEWyJnKlwjknaVwp3YI3F+FANPE4e2JpVIqmnaKkvd5VJ36baKz06gno1qeT2UqWng3XNYvdL0S+jNymnafcLpcIXziGZnHCEKIxkBkOSycDDA7Fn4YufDfi3QtO8Z6JpF1Ya2vkBbe1iV4pGwuNyBCGVmTJBIwx2kkcdt4i+GF0PhFZeHtJRJdStJ47uVUKj7TMQVf5ztGAHOCedqKKyYpPFnxD8c+F5tU8N3OjW2jt9pmnkgdVdwVZsb9vDFEUKMkZJJYDjtU8FWjOpThBQvPm0Skkorkceur10W5NpLRkXgXwboFp8QPE3hLWNLttSa2C3NnLNErlYuOGbAO4rJFxjGQ2Md/Qb34deDI9PuJF8NaaCsTEHyBkcVyvhl08a/GrVvEUV15lhocQtbTaV+YsGTIKghkJ85gc5+ZO3A9K16b7N4e1OfP+rtZX/JSa8DOV/tClL43GLl/ia1+/RvzZrT2PMvhR4G8Mat8NdJv9S0Kyububzi8sseWbEzgfoBXZn4a+CQP+RY03/vyKofB1cfCfQsf3Jf/Rr13VeSWcoPhr4LU5HhjTfxgBpx+Gngon/kWNN/78Cup6jmjtQOxyw+G/gvkjwzpnP/AE7ilb4c+DGOW8MaX+FsorqKUUCscqnw38GIwYeGdMyDnm3BH61MPh94OHA8L6Rj/rzT/CukowKAscyPh/4PDZHhfSPxsoyP5U5PAPg9OR4W0c/WyjP8xXSUlAWPIvizpmieFfCEV5o/hvQobme8jg81tMhcopVmOAVIz8gHIPBPfBHC/Di7k1bxxpmma34e0aW0vo5CEn0W2jO1VYh1KoD1jI5yMZ46Ee9eK/Cmm+MdH/szUzMIhKsySQPtdHGRkZBHQsOQevrgjA8MfCXw94T1yLWLOa/nuoVZYxcSqVQsMEgKq5OCRzkc9M4I97C4rAwwMqdSK57S+ym7te61Lpb+vPOUZc11sTeJfB3hW08Kaxcx+G9GieGymkWRbCIFCIyQc44xWD8KPCHh+9+Gej3WpaBpl1dSiVnmntI5HYea+MkjPTFdn47bZ8PvEh7/ANl3P/opqZ8P4kg+HfhtIxgHTYGP1MYJ/U14Jp1JP+EF8I9f+EW0P/wXw/8AxNJN4D8JTQywt4Z0lVkUqTHZojAEY4ZQCD7ggiuh6dqWnGTi1KLs0OxxXhn4ZeHfDumS2ctnb6mZJ3l869t43cKeFQHHQAD6nceM4G8vhjw+n3dD00duLRP8K1qWrq1Z1pupUd29WSo20Rljw5og6aNp4B/6dk/wo/4R3RR00fT/APwGT/CtMEEnjpS96zHY5zxB4N0vXtAvNMiiisXuI9i3NvCoaM5B9BkHGCMjIJGRnNT6F4R0Tw9pMOnWNjD5UY5eVFaSRu7M2OSfy7DAAFblLWvt6nsvY39297eYWV7lT7BZ9PsVv/36H+FOWytVPy20A+kYqweKKyGRLbwKciCMH2UVgeOhHH8PvEhAC/8AErueg/6ZMBXSVxXxauWtPhbr8qnloBF+DuqH+dAi/wDD5fL+HfhsY66bAfzjBrpqwvBkRg8DeH4W6x6bbKfqIlrd70Ag70Ue9JxQMWigACigDyvWvis+mfFa10FYZjpcf+jXS/ZGMrzP91kH3mUfJjA+YMxAbKGtW6+M3gy01kaeb2aWMZD3kMJeBGGeMj5m6cFVIO4c9cZXjK01mx+MnhvxDZaHe6lZx232ZzbAHaxMitk9FwJQcttB55GCR5PcfDvX7Ke40iTwzq1zqQnEcN7bPm0Kkrg8x4IIz8xdcZ5A2kV9nhcuy3FU6bm+X3FtKOru0279tPvtbQ55TnFux7bq3xj8KaPrraTM97LJFKYZ5ooP3cLhirBskMcYydoPHTPSqOn/ABNe4+Llx4eb99pE0SR2TwW7Mxk2B95PUowLfMAVwEYYXcx8q8T+Cr631XU7ez8DazBIsqi3azme5tlQKuSCYiz7vmOdy43AEDaQe50/T/FHg74h2esy+G5tRj1PTLazlWwCqLZwkCyZCjYuDGcDKoQRhhg4J5Zl9OjenrKUHZOUd/daatdLr1/zFzzb1Paa8L0PXZZU8XfFO5uLmf7MzWWl27uQEViNiyIpAKjzIuAx53tgtg17pXgng/SG1LwB41+H6TJ/bdrePKqqRtmKMgwm4g4Lw7SxAA3qfavKydU/ZVZT2vBP/A5e9+lzSpe6+ZjeL9T+I7eAbW913UoJtH1lAojWOIMu4bk3bUBG4LuGCemDg8V65rGrXHhL4PrfWyAXVrp0EUWCP3bsEjDcgg7S2cEc4xXjnjfWfFTeA9O0DV/C9zY22juqS3pifZIUUxx4bG0DB5ILBjgjA4r0PUx4t8Y6D4w8MS6J9mjt2RNMuGiaFLhY5s43O3zMyoMFRt9SuRXoYvC0Z1aU5qEbS95RslycyUXpptfztuRFvVK5z/hL4k+JG1CO41DxFpmr2i20k91YLEYJ4o0jMjMhMSK7rtxtDMDk9Bl1gn8Z/Em38K2vjVtZ0w6XcXJC2Plxhhh2GzBUMV+Qj5XLY57EiPQtC1fXfEHg+GHwS+hDRWjlvb6aAxC6CGMlmPlqSxKHAyxy56AE1h6j4J1fX/ED21l4J1DRrue8cO7OfsMKZbOD5eAAMHIcg4O1cFVHqxo4H2zvGC2buoOyTl2aSvo7pNpWTIvKx6BeXK+G/izoOvadf3MujeLlVZYi5cyOQAh2vgqoMkRHOVG8AAYWvX/SvHfiBa2mveKvCnw306fybODElzGrg+XGifIoY7mDiNZMAjB3oTnOR7FmvlM0s6VCb+JxfryptRb87aeiRvDdoKMUUYrxzQKMUUUAFFFGaACvOvje5/4VbqMQ6yzQIB6/vVP9K9Frzz4xn/ijbVdu7dqlqNv975+lAmegRoEjVR0AxT80AUEc0DCkoOc0Y5oAinghuraWCeJJYZVKSRyKCrqRggg9Qa4o/CDwL/0BB/4Fz/8AxddzjFL3rejiq9C6ozcb9m1+QnFPdFXTdNstI02DT9OgS3tIF2RxJ0A/mSTkknkkknmrdIAFGAMAdhSkZrGUnJuUndsYUmBnpRS9aQCHkc80lKBjg/hQDzQB5z8ZQz+G9GtxnFxrdrEcdcfMf6V6NxXnfxWHmDwdBu2iTxLZg4OD/F0/OvQyRkD1oEtxcen60d/akGOSBQNxBzgfSgYvBo4oxwPaigAHBxxQfzpNvpxS55oAOg4oySO1HccUntQAew470cY5NL9KTaCOeec80AJ3xzz7V5j8UXC+L/h3COjawHx9DH/jXqB+vSvNPH0CXHxN+HUTkbRc3cvzHHKrGw/UUhPY9IIUvu5yRj8P8mnZwBxnPpQM7jR+WKYwGOlOyCcelNyOn9KDnrjpQAccYpoK52jsKcBxxgenFIQMg45x6UABYY9MDnNJkdyO3NOx82c9vSm5zkjHpQA+jr7f1pOnOabn5sE/lQA7HQ57UYPr+tKaBjFAHPa5aRSeH9TXz2iQ2bEyy3UkUQ4PUg5UepHaq/hrS9P0zwnpmmtdx3y2luYw44D44bA9M8VV8eiCbwFrxkjikf7BPtGw/KRGec4PccE45xVvwPBDF8PPDqKpjQ6bA+BnqYwST+JoF1NEW6zNl7YpGdgGXDb+hz36dOeuPpVkwQbsSfMxBVM+/NS8B9yBs4PPYmiQZi5XO3BwMc/nQUMdNrCTyt8ioduAP544pQsjffIEeBx+eTnv2p6MoD4ccHnBzig8KCGGQOefb0oAdghRt+XHT0NI8hU/NsCg9+9PBBP97igH5jlB064oEY0mLfxdBtyq3WnyLJyMfunUr/6OkrZPJBPOBng96yNZcQ6hoTsF2m+MbEj+9DKB+ZxWuQByMc/lQAd87SOO/ag5zjHGOTSKVwTwDnB4xzUvU/zoAZuA4JAPpijOD/hScgepPGOlO6g4/Q0AIOOcV558XY45rPwnFIMo/iS0DD2xJmvQzgc/5Nef/FX73gxAeT4ls8f+PUCex6ARk9AcdMinZ9/yprAHIJ4/lTguCfQ0DDjNN6ZyD19aB1J5pfXjmgBenNA6c0fhzRj2oACce1KKaetKDkdMUABznHajJGPf3pcUd8d6AEyaWkx6fpS55x6UAFJjnrQc0cjGaAPMfhOFOu+PpQ2d+vTDHoNzY/nXp/X6V5h8JFDal45lxgtr84z+J/xr04A88igS2FqKaaK1t5J55UihjUvJI7BVVQMkkngADvUhGRisLxru/wCEF8QYIA/s25zkf9MmrSjD2lSMH1aQPRHlOpap8P8AUfHc/iMeNLqG3vIPIvrFLKbFwhj2FN+3hCAuRgnIJBBwVn8IeBNG1+eF9L8eahqOh6ZeCZNOVZIWhbJZOSwKnJPzqgz82CDnHBaJrFla6fpem6V4RtNY1y5B3TXUZdN/mOBHsIwRs2HdkdevGK9J+DEDW3iPxvBJBDbvFdxo0EJzHGQ83yqTztGMD2FfW18T7OlXp4eck6Vo68rVlLl/lTT1dne5gldptbkt18Fbq/lFvd+NdTuNLFyZxaTIXPLEk7i+3edzZfb1YnHOK6SD4df2f49k8R6Vrt5Y29zL595p8Y3JcSHdnJJxtJYnBUkZbaVyNvccUYzXg1M4xtRcsp6WatZWs99LeW+5qqcUV720g1KwuLK6j823uImilTJG5GGCMjkcHtXkXhDw7daho+qfDLxXYXKLYsLu2voFUoqM+RscrwWO8gnJIMinbtxXpnhvxPpfizTJL/SJHkt453gYvGUO5cc4PYgqw9mGcHIF3UtQi0nSr3Up1dobSB55FUAsVRSxAyQM4HrSoYivhebDuPvNpro4yWzX3teYNKWp594a+EP9j+I7DV9V8QTax/Z8QjtYJoMLHjhMFnbCrkkAYwcEHjm3onwvbSPA2seGT4huXXUWLiaKEReUcKDxklg20BgWwV4G3JJg0n4oyx+CpfFXiXT0tbGe8MOnR2bGSWVckYYHABG1vmJXO0/KON2x4P8AiVofjW/uLLTo7yG4hh80pcxqu5cgEgqzDgleuOoxnnHoYmeb2nOpqotXaUbJxd1sujetvRkRVPZG/oGh2PhzQ7XSNPRxbWylV8xtzMSSSSfUkk8YHPAA4rOs/B9rZePdR8WJcTNcX1slu0BxsXG0Eg9eRGnHb5uuRtr+MvH2leBvsX9qW95N9s8zy/syK2Nm3OdzD+8P1qrpvxQ0HUvCupeIlhv4bLT2CSia3+ZmONoUglSSWAxnjIJwCCeCFDHyg8RGLaqaN97vb5tfeW3G9uxw/ge+i8WfHTWNZnsJrVra1byIZ8rJEw2w5YDuR5mVOcE45wDXtmc9K8Q8IeONI1X4ua5qcAMMmq2kUFgl6REHlVQNjMu7buIGDz+eAe8+H3jS98Upqljq1glpq+lT+TdLCcxEksBt5JyCjA8kcAg84G2Y4bFzvUqU+SMFFW7R2Xrru+7Jg47J7naUUdqDgivGNQz+tBzkUyVPMjaPcy5GMqcEfSngCgAPFGf0oo7UAJnmlopM96QC5NFJ1BpRzTAM4+lHeiloA89+E774PGDjgHxNeH9I69BzmvOvhEQbDxWex8SXh/SOvRcDHT8qBLYD6igUUpoGJS80lAPtQAfWijnNHagBaQjvR1ooAXtTe/elooAM84rzv4sNmDweo6nxPZ4Hr9+vROnFeYfFRpG8TfD+3XO1tcjkIHT5WX+hNAmen5oooHIoGFBox70UAL2pKOhoHSgApe9J1HejOO1ABk0ZorP1nU4tF0W91W4DGGzgkmZVxlgozgZ7nFAGgc4oGfWs7Q9Wt9e0Sy1S03iC6iWVA4wwBHQ+9aPNAHM/EOcW/wAOfEbnodPmT/vpSP61zWsaheaN+z3Z3en3D29zHpNkiypwyhvKQ4PY4J5HI6jBrZ+KzAfC/wAQEnH+j4/8eFKnhqPxH8JrHQbid4BNptsnmoASjIqspweoyoyOMjPI6104OdOGJpzq/CpJv0vqRJN3SPAdS8Qa7pjtbv4x8Qtdm0trqNfOdY2EsaORuMufl344U5IPAHNfS/hy7udT8IaPeXE267ubGGaSTAG52RSTgcDknpXlV18A7i7ML3fi+Sd4YlijMtkWKRr0Vcy8ADOAK9i0rT4dJ0mz0+BnaG0gSCNpCCxVFCgnAAzgelevm2KoVqMYxmpy5m7qPLaNlZbK5NOLT2LYzjn9KXPNFJ15r581FzzWHoHhHRvDFzqVxpNr9nbUJVklRWOxcDhUXoq5LHH+0R0AA26K0jVnGMoRdlLdd7a6ishaKKQ9eKzGGQagvbSDUbC4srqPzLe4iaGVMkbkYEEZHI4J6VP9aXjrTTad0BkeHPDum+F9Gi0rTIfLgj5Zjy8rnq7nuxx/IDAAFR+LZfI8G63KSQE0+duOvEZraPIrnvHrhPh74kJ76XcD84mFVUqSqSc5u7e7ElYpfDC0+x/DPw7GRjdZrL/33l//AGauuxWB4GGPh94bH/ULtf8A0Utbwz1NQMXmigUnvigBaOh6Uc0f55oAO9L1pKXIoAKKTPNIQM0ALgA0H2o70UAcz8Q5BH8OfETHPOnzL+akf1qx4IGPh/4cHT/iV23/AKKWsf4sXCwfCzXnyQDCE+X1LquP1rc8IQPb+C9CgkGHi0+BGB9RGBQLqbXNLkUntR0oGLRScDjpRQAuKBSZzzS0AFFFJzQAtFIeaD70AFcF8aTj4Sa79If/AEfHXe4rgPjVx8I9bHqYP/R8dAHb2UYjsLdFAULEoAA4HFWajRdkSr2AAp/agELkUUnWloASgnC55oNBoA+QG8beK7u4up5PEuqo5Hm/JduisxYAqqhgB1JwBwB0x0+q/DF5caj4T0a9upPMubixgmlfAG52jUk4HA5J6Vz83wk8DzzyTPoMYaRi5EdxKigk54VXAA9gABXYwwxW0EcEESRQxKEjjjUKqKBgAAcAAdq97N8yw2LhGNGLTTb1UVZWWitv8zKnCUXqSUZFJRXgmoViS+EtFl8XW/ig2u3VYYmjEiMVD5G3cwH3mC5UE9jznC43MAnNFaU6s6d+R2urP0e6E0nueY/HXMvgCK2XrcajBF+eT/SvTRXnHxj+bRvDkZ6Pr9opH/fdej1mHUU0UnNL9KBmHpHhLRdD1nU9XsbXbfalKZJpXYsRnBZVz91S2WI9T6BQNyjnNGK0qVZ1Zc03d+fkJJLYD04oFFHesxgTRmjvRQAlLR3o70AHavO/jAw/4RzR4e8+t2kY+uSf6V6JXnfxVIkXwdbkf63xLZ/l83+NAmeiUc0Y4pMGgYUUuKTjpQAUUuMDFIaADNLSUvAoAQmilNNGTyDxQAufyoxRRg57UAea/FUbtX8CR88+IIDkdRgivSj04rzX4muG8U+AICeW1kSf984/xr0rjNAuod6QEntijGeMcUvWgYnI460uM46UdaP0oAOhxSYx34pfzoxQAzJ9OtOB5x+lAIPQ0ZHGOfegBTz0pBnGSMH0peoBpMZ6igAwck1574vijl+LPw8SRAwDai2GGeRCpB/MZr0E57/zrz7xTKG+MvgGMHlE1Bvzhx/SkI9CJxnPQUYB5xxR3wef6UE4/pTGGQcgHJHvTSGJGMDGc07I7c031xn1oAcD780jDIwCB9eaTI6ZOaARu5GPT3oAOCOmPXmlXAGDgnqccUvy5/CmhSCfmzznHpQAEDdnHJowcHpk96d1/wA9Kbz2HBH4UAO5Bo4pelLQBznjt9nw98QtxkabP2z/AMszSeCxu+H/AIcwT/yCrcf+QlqPx+zf8K78R/Lx/Z0/f/YOal8GH/igfDjNz/xKrfOR/wBMloF1Nx+QSRgA9zjNKeW5H05pSiOCGAO4d/SlC9CQCQMZxQMTOT2yR09aUgEjpTFXjHJxn5jinjOT8o56880AKAVHJz700jaM8nt1608+3H4U3nJHY/pQBieKWKaXAwPK6hZH/wAmIwf0rb75GMDrmsXxdj+wo+M/6fZcf9vUVbnHP+FACd+eKdkZB6U043Y3de1Ic8nt9KAHcflTeScjA9OadjuaMcUAH481558Uz/pfggeviW05/E16CRuHzCvPvij/AMf/AIHHb/hJLX+tAmegkkE9/ancDt1oIUk5GaOew/OgYAH8c0dCeaX6mgCgBBkjpj8aKWg4HWgAx/nNHGPaigjNABnimkbh3Ge4p3eigBBgnrR3paOAPSgAOaPY0c4oHU0Aea/B7DWniuTHzN4husn14WvSq81+DfOl+KP+xiuufwjr0rNAlsHfn14qC9tINRsbixuo/MtrmJoZUyRuRgQRkcjgnpU/tmjFNNp3Qzyr/hQnhX/n/wBZ+nnRf/G6830+zi8M/wDCwLjTNSubfUNIYWdkVnCu0LXHlSMQMbiAFGeilgcBtpH0L4q8QQ+FPDF7rU0DzrbKCIkIBdmYKoyegywyecDPB6V5Ho/i3QrjxrZXuofDhrGfXn8gXksrOkolAUssbIqENuXcy8kOTzuIP1+V47H16NSdW9SGnWO8WpNWbWjWjsno9jnnGKaS0OE8OT+IbHW45IPENnZSaxFMZLm41UbMmNvnmMbllcbyV3jO/wChp/g5tRsvHOi3Nxqrp/bE4inltLxJppVlI3LJsk3IWLDJbDKfmHzLXZfFHQ9L8BQWMnhvQHtJLhisuou5mj24OYdshYZYdcgZUMvzBnAr3mveA/Bl7p9xbeBrlPEEKxzy2tzdOFtWZdwBLFgWAKsPl43AnawKj21jPrNL2lGk5e0TSso30utfe0Wq77bK6M+Xldm9jZ+AFvpyWGp3K3v/ABNJZfLa1+0f8sVCkP5eefmcjcQcdBjJz2Pxg/5JbrIJ/wCeH/o+OuEvviP4E0jV4fE+jeGHudavlaSRpJVi8oFmRiQC4WQ7M8KCVfJPzEGv43+JF14l0nw//YsV/FbXzz219aQ7d0zlURoFOCWO2Tg7cfvEOCykL41TA4vEZnDGcjim0/eto46taN6aWTaRopRUHG5J4yFvFoPwpvdQh3aXBFCLt3iLxhCsBKsMHOVV+O4B4NT6z4l8Nx/HrStYg1GzNlbWL/bLuEgoZBFN/EPvttMajGT0XqMV1PgjwRf2/hi88OeK7SyvNJjkzp6yIplVWDFydpIVgXIBDEht+GK7SePg8B+GtR+NV14fh037Ppem2Immg8+R/tLkKQdxbcmPOXoT/q/9o4uhiMJJ1KU5NqEamsbWcZO/Xrra2193oJqWj72N/wAazeCPHc/ho6hrlzaWkq3MtvdCPyYZVBCshkkXCtuQEZ7KQQC6E+e63r3/AAj9r4k8GaPJ/bnhoxRPBNJN5v2YkxsXDx4G3zGxjgbtvqwappvgq48U+ENe8R2V0ljpunTzS22mu7yBQFV3G49CE2ANgliozjGa9f8Ahn4f8Pan8LoAdGhSLVIit8rOXM7xsU3FjyOVLADG0njnmt6ksNllFJylUjCSXK7e7K/MnfTVLtdXurpCV5vseP6BcWfhb4r6et/dWGtwQm2hN80+6GEsigOj5IIizgE8YXopwV9HTULfTv2kLlbeVEFzZpb3zXciIN5RCgh5GSSIRjk5L8Y5Hgv7u61D/lhZwyyf7ZjhBP8AwJtoH+8cDuak1KG6t9SnS8iSOctvZY1UId3zAps+XaQQVK/KQQRxivXqZQqsnzz1cJRelt3e9lZaeW7s355qpbofY+o61pejmP8AtLU7Ky83Pl/aZ1j34xnG4jOMj8xWPqXjfT9L8c6b4WuYnWa/gMqXDMqorEkInJySxVh9doGdxx8w6xFZ3EcN3H4ghvJ1sbYPE9tJE6uFEfkrhSreWqLliV3dsnNdPp/9iRa14H1TxBbONGfTnFxLcK0olkikmUAlVywBEQC4O1NinIHPz/8Aq1SpQ55ycnaWii078rasnZvb5+Rt7Ztn06PY15y/i7WdT+KNzpenXVna+H9DiMmp3MiiRJPlBZS/ARlOQBkY2OTuxtr0O3liuYI54JUlhlUPHIjBldSMggjggjvXjPhmznn1n4taOkeNRvfO+z20hCPIG8/awDY+U+YnPT5155FeHllGm41p1ErxSWvS8lFv5J/I0m3okTf8L35+2f8ACJ3n9j/afI+2+f8AjjGzbv287N/445r1+CeG5hjmgmSWGVQ8ckbBldSMggjggjvXzh/wm+i/8KJ/4RbfN/a3m7PK8v5dvn+dv3dNuPl9c9sc16NbeKbu20j/AIQXSIvs/i/T9IgCC6MflNIIoyyIdx3OFZiMjblST8oNelmeUxSXsaXI1KS1bs4q3vu+y11toRCp3dzZj+I+nXHxKPg6G1eRgrKbxJFKiZVLsmB2ABBOchgRt71z+q/GG6tNZ1iz03whe6jb6VK0dxcpMQE25DMwWNgq5VsEnkDPHIHl2jaN4t8IeP8AR7a20S2XXlgkkgt5ZlZZ1KygsxEm0ELuGAV+4OMk50vGXxBj8aapHo8VzDouhSyq99crG7/aJAoBdgqhnUbQEBAJwpbbwE745HhlXiqcFUp8ibfM97u8rRd3zJe6l1v2ZPtZW10Z6Jqvj7VNP8Q+GtbhuLWbwfrapCVdQhtHJG5pJRkBlyeM4wjjAK769QOc8V458TJfDz/CrRtO8PW0NzDeXMa6XFbOdwI3bmCfeduSjA87pMn5q9X0yO9i0qzj1KdJr5IEW5ljGFeQKNxHA4Jyeg+gr5/MKVNYenVjHld5Rs9G0no2u+tn1ujWDd2i39aKP84o/CvHNDzj4OEto3iNyCC2v3RII/3K9I615h8D5Hk8J6tPNw8ms3DN7khM/rXp2eKBLYBR3o7Z4oPrQMWkzRR3oAKBQKXPFABRnmg0lABj2owfp6UUtACYIGK848fjd8Qvh6mM/wCnTn8kWvRyT6V5342Bb4p/Dte3nXpI+kS0CZ6JRmg0ZAwPXigYdeKQjIxnH0paWgBOaB0pTSdTn0oAAaOtGKOtABx2ppAIKkAgjp607FJxmgBECooCgKBwABgU4DHc0UdRigDhfjFkfCjXsf3Iv/RqV1eiRmHQNOiYYKW0Sn8FFch8amx8JNbwcE+QP/I8dd6gAjUKMADgUC6jqSjr1oxQMKQ96XtRmgA4ooFFAC0Uh9KP50AHNGMdKUUUAJ2rlfiScfDXxEen+gy/yrq8VwvxhmNv8KNddepSNP8AvqVB/WgDd8GLs8DeH16bdNtgf+/S1t9c8VleF0KeEdGRhgiwgBHv5YrWzQCAj0z9KMfhRRQAA55HIozRS4oAKKKKAE70Cg8CkJx2zQAjEjpThSUoGKAPPvjWdvwk1rHcwZ/7/wAdd7HEsMSxoMKoAA9hXn/xuP8AxanVOeC8H/o5a9CVgyBlOQehHegXUfSUtJ3oGFLSHrRQAtFJ0pe1AAaSlo5oADiikFFABwa84+NDSy+DbLToAC2parbWoB6HJLD9VFekV558WebfwgB1Piay/wDalAnsehUopKWgYUUY70UAIaKWigAooooAMUUUUAFFFFAHnPxZxIng+2/jl8SWmB7Dd/iK9GrzL4nYk8ZfD63IJB1bzP8Avjaf616aOlAuoUUtFAxKKKKAA0UUDqaACjmjFFACdqXvRRigArzb4lxmbxX4AhHA/tgSf984NeknpXn3jj958Q/AEPc3dzJ/3zEDQJnoFKaBRQMMUCijrQAE4oooNAB3pO/UUY5zS0AJ3pTzRRQAmMcdqOTS0mRigDzX4gfN8Svh3FtDA3Vy2CM9Fj5r0qvO/FwEvxe+HsWfu/b34/64j/Cu/RMO7GRmDEYB6L9KBIlo6dTQfpS9qBiZ4GKB34xQKMc0AHeg/WjpR9KAA59cU08jCtinUe9ABg456UmBjgU6mE5OB2HpQApGex49K858SPu+OXguPj5LW8f84yP6V6PjkcfjXmOvNn9oXwsvZdMnP5iX/CgTPTjz/wDrpu3kjoD6U7nPOMUHrQM5Tx/40g8FeHZbv9zJfS/JZ28jH94/GTgc7VByenYZBYVHZ/Enw1L4WtNfvNTtrWKdQHhLl5EkG3fGFA3MVLDOF6EN0INVfi7ZG9+GWq7bbz5IPLmT93uaPEi7nHphC+T6Z7ZrxDxLDa6jpXhTVPst5ZaImmpYS3MVmG/0mNpC+FLKG3Md27cM5bqysB9PleV4XG4aDndPmabXblvZLz6b9fQxnOUZaH0LN4+8KW2jR6tJr1mLOT7jK+52Py5XYMtuG9cjGVzyBXPeKPitpmk+FLPWtDktdTW5uxAIjIY22rzIdpG4EDA5HHmKeQQD4adJsk8J2t7eHX4rKXU5kt7sWyNbmLyxkiMuMSsyqD823CEAsUIqex0i6v8A4d6/JpthPcWlpqUE7XZjKu8SxzA7l3Ffl3oxC5K+YSSQAR6dPh7A02pyk5JStrorXta/e++vlbqZutJ6H1FpupWmsabb6hp1wlxaTjekqDgj+hByCDyCCDzXA/EjWNXu9f0Hwb4f1F7O71JjLdTQ5WWKEHhlbIGMLISAdx2AcA4PX+Ede03xH4ctr/SbWa1shmGKKWDytgT5cKB8pXjjaSO3UEDhvFf/ABLvjx4R1O8/d2dxbPaRydd0v71duByOZo+SMfN14OPnsvoqGMmpR1gptJ66pOya623+RtN3iQar8QvF0niPU9H8JaTDq8GjxBLq5uImMjyLw5wpQbtwICqCWKkrkcDtPAPi1fGXhaDVGRI7lWMNzFHnaki4zjPYgq3fG7GSQa8zTxJL8LPHPi59W0q5nh1edrizmiyscjAs4XcwGRiYBiM7SOhzSeA/EVx8PvCvh+3vdNeZfEWoSSoUZw8Mf7mMN5YQlyeWAXqNuOvHqYvLY1MNahTV/d5WnrP3W531tpbsvLsRGdnqxutfGjxPYeLNQ0e0stG8u3vpLWJp1deFcqCzGQKOnJOB9K7/AMT/ABR0rwbfW2n6zZXpvJbZbhhZhZI1yWUgMxUnlTztHGPpXnHiHxd4Zto/E+l654NhtvEk0tygnhtkkTey4jlDybWXPytlV5++BliKy9V+HHjfWdI8OyJpU0rwaYIZPOuI1eP99KyIQ7AjEbJx26cYwOt5dgansniIKlHbVpc2l7p3tb/Mnnkr21PaviK3l/DfxEzNj/QJRnHquKt+CiP+ED8Okf8AQLt+P+2S1nfEwM3w01/EYc/Y2+Vu3qfw61o+CxjwJ4fGCD/ZluMHr/qlr4c6Opt88cdOtHvg/gaFAXj0rz/S/itpWqfEK58OrJbLY7Fjs70SHE84+8o4xg5wpzglOC29QOihhK2IU5Uo3UVd+n9fqDkluehcUdO/1rnLXx74UvdaOk22u2cl5xtVX+RycYVH+6zHcOFJPXjg1HD8QvCVzriaPb67bS30rBIwm5o3YjIAkA2EnpjPXjrxT+pYnX93LRX2e3f08xc0e5027n17UvJH9c1wfhL4lWPibxVrOiP9miaCdlsGjl3/AGuNchmBxgn5d3B+63Q7Sx7W9u4dN0+e9upClvbRNNK+CdqKCScDk8A9KWIwlbD1FSqRtJ2/Hb+u+g1JNXRi+Kka4/sWyjGTc6rAS2egizOfzEOPxrfAYZ7jPevnbTfG+tQi88Za1dPdOoLadYs7C3jnfdEhCqTtARbnIO0nZySWBrs9F+Iviy28V6RpfjDRLXTrbVgBbyxxOrb2+6D8zc5IUqcFd4JwOvo1MjxEeblafLfru0ryST1dutiFVR6zxRjjpXEfEzxfqPgvw5balp8NrLNLdrAy3Csy7Sjt/CwOcqO9YvgH4lax4h0nXdW1m0sEsdLgMp+xMRMSFLEeWzHIIHDEqMjAzzt56eV4iphfrUUuW9t9b3sNzSlynqHToeabjOeOa8Y8NfFXxfq9/YtJpGjXdpcShGt7K5RbsjO0lY2mLcfeOVA2gklR8w3PDmqa14e+KuoeFNZ1aa+s7+Jr3T5bkBpCepUbeFUBZBjAGYwVC7sHatk1ejzqclzRV7J3ulvt2316ejEqiZ6Z1OCP61538Uj/AMTLwKPXxHan9a9FJPHFedfFI41fwIM/8zFb8fjXkFs9Fxz3zRx3FBI59utGc+9IYY9KXmjGaT6UwF+lGcjnmjr0xScUALSfWgfWl60AAOelB/WlwAcij3oATkjpQfTg0tIetACHnrQO4psi7kKkkZ7qcGhQQAM5AGMnqaAPOPgyQ2k+JmAwD4hu+Pwjr0oAY/xrzX4M/wDIC8Rt6+ILo/pHXpPpQJC5paToaWgZyPxP0y91b4davZafbPcXLpGyRRjLMFkVjgdzhTwOT0GTXhnhjw/43vvGfh59S07WDbWN1Bsa4tnjjt4o2XPLAKMKgHqdoHJwK+oOtBAYYIyK9bBZq8LR9lyJu7abvo3Hle2+hnKHM73OD+LPhfVfFXg6Gz0mJJ7qG8SfymcIXUK6kAnjPzg8kcA98A8J4o+H3i7U9fTxFN4e0zU7jULaP7VYm6ZEtZVVF4IkQtkLnhiBlhzgM3K/FiWS4+Lt1bzi4uYhJbQJCkmG2tGhKxlshcliRwRkk4616h8Bp5ZPAVykkrukWoSJGrNkRrsjbA9BlmOPUk969mnUq5fgo1KU03FJtOLWlRXtdS/urZJ6b20M2lOVn/Vjj7j4YeKbPR9EhXwxoeqtHBKZ0DmGVHdwwErrKnmFRgKQcDLDBwrG1afDXxlZ+EdDukSGTVtH1OS7t9OmmDDy2MRA3bgow0ZYqDghychuD7uKOorz3xHi2kmo7t7Pre63tbVrSz8y/YxKWjS6lPotpLrFtDbai0QNxDA+9EfuAf6c46ZbGT5jqd3b+DPjyNU1GTZp+u2Ih+0yApHAw2rjdyG5iTPTaJQTwMn1vjvVLVdG03XLVLXVLKG7gSVZljmXcA6nIP8AQ+oJByCRXn4PFwo1Zucfdmmml0T7X7Oxco3Wh4zL4L+InhfTda8NeHba2vtD1JnZZTLH5saNlSpLlPmZAobggfwkHNdVoWg+MvCureGdH04pP4ct7PGolpIgvns0jSFSV8wgFl2gAA4AJHzGvSqT0rprZ1WrQcJwi73vpu7Wu9d0tmuupKppbM+RDpt5Y33ifw7Zw2l75Bk82aYKkipbOxMkYZuGxnIG47SQO9dl4bg8XarpFvf6d4d0PxHZGCO3T+0xBNJZmJdhjGShUHAcLyMODkszE42s+Cdc1v4j+KIdL06LUJre6eSTE4jEYnJZD8zLk4PTkZHOR1ueAtQ1/wAD2vjDUYlttmmLHBeWcw3F5zIY4yGU9EO8nBwRx3DL9fKt7ehOVFwlK8Wtb3cuVO9n7rctFt2fU50rPW5a1zw5aeDvhxDoF9Z2V54u1i5SSKOKIPcWsZK/KrAEtkptwCAS7Y3BST7bpXg7SNP8Kaf4fubK2v7WzUHFzCHVpOS0m1t2CSzHrxuwOK8H0P4ma9f+Mf7SuNKttW1IwTx2Sw2O+WDKOyqmwhiu7GSxZgm/BG5s6fhH4teMNV8ZW1lcXVlLBfymFIZYkjjgLH5WU5Vm29lLEsPlB3EEcOY5dmNalZyScbzk+bdvtpoklbW3UuE4J/gfQUU8VwheGVJEDMhZGBAZSVYcdwQQR2IIrhdd8IxWvjuw8YWWuJpEjNs1FZnGy5hSMsQMnGdsfI6ALvGCnzcz+z/FqQ0LU5muYTpZudqQbP3gmCqWbd2XaUGOckfw4O7D/aAi1JdZ0iW4uYX054pBawom143GzzCx/izlMHjpjAwS3lYTLpUs0lgoVbXTTdr3Vr2s9P00uXKd4czR6No+u+BvFH27xGun2cf2G5VH1O/s0iywwEdZWH+7jJDD5cgZGeg0mbw3qWpXOo6RLpN1fbVS4ubRo3l2noHZecfIMAn+H2r5a1fxjd6n4X0zw3FbQ2ulafh1jTLPJLtO52Y+rNIQBgDfjnANTnXtS8Ka+NT8P2s2h/bLGLbHJBuDIyoXZPN3ko0iMVOTx37V6tThmc01Gbi3flTd1ZW0b897JNL5awq3kfUmp6loukzwT6pfafZzMrpDJdTJGxXKlwpYg4yEyB6LntWO9l4AvrW51l7bw1cW4lP2i9aOB08wkZ3ydNxLDqc/MPWvCPGuo6l4u8TeGL6ezs5rvULGARWcUn7tiZpE2M4f+JgSeVKhtp5Uset8A6Bo2oeINc8KeI/DEdnfrBFO9vBdyNAFUghv9YxEn70fMGPykj5ctv4JZPHC4ZVZVZKSV2o22UrO2qbt32uV7TmdrF/UrjwzdfFjSHm1p9UsLaBW0vTtIhM0Vm6DPzCLJIygYBQT0DbUUbu78OfEXwz4ltYpLbUoLWeWXyVtLuVI5y+cABc/NnIxtz1x1BA8S8L6HbjxX4x1nS1Q2Ph+C8uLCVGSWNZBv8g/Nu3gBWYHnlFOfXhPs1rBZ+ZcT+ZLcW3mW627g+XIJtpWYHp8iuwA5+ZD0Jr1Z5Jh8WlSdSV4KKW2l7vVLyabd7/rmqjjrY+zp5YraCS4nlSKKJS8kkjBVRQMkkngADvWXD4u8N3M8cEHiHSZZpWCRxx3sbM7E4AADZJJ7VBpcMXinwDpya3El4uoafC9yrqAHZkVieMYOeQRjBwRjFeQv4U8Nah8YrbQdC0xF07So2n1FhMZRI687TvdgVDGNCoAOS4PTI+XwWBoVfaxrSacE3olay9Wnq9ErG8pNWt1Nr4K+JNFsPAki6lrWnWl1NfSytHcXSRtzjnBOccV6Bc+N9Fs/GMPhe5eaC+niV4pJYysUjE4CKx6sccYGM/LndxXzNptx4Xg8DXUOo6Pfvrlwxk0+7Rykax5CjOWwQGWQH5TnkZB5HoviL7VL8FfCHiOTybLVtIlj+ytJlWaMEqmxGyHYhIpORghWI44Pp/2FQj7NuTam+VPS12rqS3vG+nQzVV6nu5xxR2qrpmoRatpNnqUCusN3Ak8ayABgrqGAOCRnB9atd6+WlFxbi90dAUYFLmikAh7UHPal70lAC0nvS0dqAEyMZooAAGAKKAAmvPfGZI+LHw7x/f1D/0StehGvO/FQz8ZvAHIOEvyV9P3PX/PpQJnohI+lIACcgAn1pcDOcUtAwxRkUUn1oAOaKXr9KQYHFABz3HNHalo/CgBOfajpRS8GgBKODS0mBQB5r8dXYfDSaJf+W11BGf++s/0r0uvNfjUf+KW0mLGRNrNtGw9R8x/pXpJwMc0CF7UnbBoH1oB9qBi0nGfrR70fjQAopKDntR3oAMij615J8TvG/iHQPGOgWWmWV4tssolITBXUSSFMS4DHgEjHXLg7eEYz678cdK0fWRp0ekXk5hl8u9Z3VDCwxuVQMh2U7geQMrwxBzXrQyTGVYU50o83Om9GtLPr/XluZupFNpnqtHWvI9b+POlafLDFpmkzX++JJJGe4WJU3IrBQV35YbirDjBUjmqt58TdRvfiR4bk0KDULrR7yzH+gKqK05ZnV26nBQpjLEAeW2CFYsahkOOa5pw5VZu7a6K9vJvpe3cPaxPZq82+OWoWtt8MdRs5biJLi6aIRRM4DyBZUZto6nHGcdM16TXzF8Qv+Kk1jxrrFw8i/2XcwafbwM5YL+8KFgcjAPluduMZlPcZPLgsGsQpyk7KK+9tpRXzb3HOVrH0pZ2y2dlBaISVgiWME9cAY/pVjBIr5y2+OP+EB/4WB/wmN5/x8+Z9k859u3zdmdudn3/AODbt29/4a9qvNRutX+G1xqdhFNFeXmkNcQRwMWkSR4SyhSACWBIwQM5roxeVPDuNqiknJxdr6SVrrX1FGd+h0dFfN/gjWvEtj4m0nUPFOteIrLRZmHl3F0ZGtpmZSUVmk+UKwyd2DjqNv31g8T+Mb+bxzr6XnifXNLhgvHggh0wM8e1CUyVMyBThQTjOSSeK7/9WqrrukqiaSvdJvra2m/n26k+2Vr2PpEXtp9v+wfaYftnled9n8weZ5ecb9vXbnjPTNT5rw/xdE9no3hP4kW1zDqGo28sQ1C605GiS7Tplj/BjaYiSozvwQuAg9st5YrmCOeCVJYZVDxyIwZXUjIII4II715OMwSoU4VIu6d09LWlF6r8mti4yu7ElFFFcBYmRRgdaWigBOKOvUGiigDzf43OT8PfsijLXl9bwKPfdn/2WvSK8++KgDr4OjPIfxPZAj1Hz16D3xQJB/KgA0uKKBiHil6UcUhAPUZFAC5zRRQc9qACijmigAFAoooAOled/FRgZPBUWRlvE9mcf99f416J+FeafEndceNPh9p46PqpuT/2yCn+tAmel8UUnfpS9aBnH+I9a1bT/G/hLT7JGexv5LlbweXkYVAV+btj5j74rr+opjozFMNtAOSMdR6U8elAC54o4phRWUq3zA9Qaf2oAKO1FFABRSGlFABR3oooA858dxiX4l/DyM/8/N2/5Rqa9Grzzxfh/i78PUJHH9oHH/bEf4V6FQJbi0UtJ0oGFBpaSgAooFHWgAo+lFFABSc9zS0UAGOK888VzK3xh+H8CsCyrqDsvoDBgH9DXofavNdaiEvx+8MknmDS55B+O5f60CZ6VxR7UcUUDCijNFABRS0lAB9aOM4pCcUvWgA5o75oyKTHtQAvekpTzSGgDzbxCN/x38HLn/VWV2/5owr0nivNdUbf+0HoURHEeiyyD2yzD+lelcUCQdqWkooGGRnjrR9fxpe9IQDQAUUYweKCD1oAAAOPT1oxzmgkZxij+VAC0lBpMZ7GgBfSvM75Ym/aJ00SOVKeHy0a4B3t5sgx7cZPHpXpn4GvPNqyftCAtgmPwxkex+0//XoEz0OkyMjv/Sjv8uMGjjIJHPagZ5d468QeLG+Iek+FfDGo21i11aNP5k0asGb94SGJVsACPjA6k57YzPDPijxpY/FS28L+ItWtr9JUk80RQKAhCM4KkIpz8g9RhvXpD4+1y18M/G3Q9Xu1cwQaad2wDJLeeo/Vhnr361maJqtpr3x90rVLS8guftMUjSCCORUiZYJF2ZkVS3yqp3bRnPQV9fTw/wDsqXsU4eylJy5deb3vtW326nO372/U995JGVoP3cYNQ3FzDZ20tzcypFBGC7uxwFA6kmiCdLm2jniJKSKHXIKnBGRweRXyB0E/0rm/GfgzTvGujGyvVKTxktbXSKC8Dnv7qcDK98diAR0RwT3JHOKTA3k4IJ4JrSjWqUaiqU3aS2Ymk1ZkVlb/AGGxtrUzTXBhiWPzZ33SSYGNzHuxxkn1qwRyOB70n059KUDnJ61Dbbuxh3o4oIGeRRzSA4r4sOY/hdr7Ahf3AXn3dRW14SJPg3QySuTp8HKjAP7sdBWJ8W1D/CzXgQD+5Q4Jx0kU1ueFgP8AhDtEAPH2CAAg5/5ZigXU1+AMk8D1rwjXLWK1+MniewXSnafV9Klh04R24wZ5IFzID2BIlVnHAJbcQNxHs3iDUZdL8NapqECo01rZSzxhwdpZULDIBBxketePaZqPxT1XwrB4iTxRp0Omyh2d7iKJTCqMwLN+66ZTHGTyOK9/JVKlCpXcoqLXL7za1eq2T7GdTWyPN9D0lJdd0uyhOs/2yL5UntLe2WKSEKx3GOQvkOoGfmVQpyScLkwXVlp0OpiCwh1O4vFvjENMvbTaSgchUZkk3FzhQVCryTg8DPufwo8W674gutdsdbvY7yWwkURypD5bNksDxhRj5BjIDc/gPT9vrz6Z7V7WL4krYXESpzheyW0tNdf5VpZrs/MyjRUldM8</t>
   </si>
 </sst>
 </file>
@@ -461,10 +518,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -495,135 +552,138 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>207</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>207</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>207</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>152</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>207</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -632,33 +692,385 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>207</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I7">
         <v>5</v>
       </c>
       <c r="J7">
         <v>202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>58</v>
+      </c>
+      <c r="K8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9">
+        <v>69</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>58</v>
+      </c>
+      <c r="K9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10">
+        <v>69</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10">
+        <v>11</v>
+      </c>
+      <c r="J10">
+        <v>58</v>
+      </c>
+      <c r="K10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11">
+        <v>69</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11">
+        <v>11</v>
+      </c>
+      <c r="J11">
+        <v>58</v>
+      </c>
+      <c r="K11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12">
+        <v>69</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
+      <c r="J12">
+        <v>58</v>
+      </c>
+      <c r="K12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13">
+        <v>69</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13">
+        <v>11</v>
+      </c>
+      <c r="J13">
+        <v>58</v>
+      </c>
+      <c r="K13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14">
+        <v>69</v>
+      </c>
+      <c r="G14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14">
+        <v>11</v>
+      </c>
+      <c r="J14">
+        <v>58</v>
+      </c>
+      <c r="K14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15">
+        <v>207</v>
+      </c>
+      <c r="G15" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15">
+        <v>5</v>
+      </c>
+      <c r="J15">
+        <v>202</v>
+      </c>
+      <c r="K15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16">
+        <v>207</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>202</v>
+      </c>
+      <c r="K16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17">
+        <v>207</v>
+      </c>
+      <c r="G17" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17">
+        <v>5</v>
+      </c>
+      <c r="J17">
+        <v>202</v>
+      </c>
+      <c r="K17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18">
+        <v>207</v>
+      </c>
+      <c r="G18" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>202</v>
+      </c>
+      <c r="K18" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/insect_analysis_history.xlsx
+++ b/insect_analysis_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="65">
   <si>
     <t>วันที่ตรวจ</t>
   </si>
@@ -64,6 +64,12 @@
     <t>2026-04-21</t>
   </si>
   <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
     <t>11:45:46</t>
   </si>
   <si>
@@ -112,6 +118,18 @@
     <t>08:54:36</t>
   </si>
   <si>
+    <t>10:16:11</t>
+  </si>
+  <si>
+    <t>10:59:24</t>
+  </si>
+  <si>
+    <t>11:01:07</t>
+  </si>
+  <si>
+    <t>11:14:48</t>
+  </si>
+  <si>
     <t>SB</t>
   </si>
   <si>
@@ -124,6 +142,12 @@
     <t>บริการลูกค้า</t>
   </si>
   <si>
+    <t>HIT</t>
+  </si>
+  <si>
+    <t>Conditioning Silo</t>
+  </si>
+  <si>
     <t>ห้องเก็บภาชนะ ชั้น 2</t>
   </si>
   <si>
@@ -139,6 +163,12 @@
     <t>ห้อง Pack SP</t>
   </si>
   <si>
+    <t>— เลือกพื้นที่ —</t>
+  </si>
+  <si>
+    <t>เครื่องที่ 3</t>
+  </si>
+  <si>
     <t>ฺฤฆ</t>
   </si>
   <si>
@@ -151,16 +181,34 @@
     <t>BASS</t>
   </si>
   <si>
+    <t>BASSss</t>
+  </si>
+  <si>
+    <t>BASSsss</t>
+  </si>
+  <si>
+    <t>dd</t>
+  </si>
+  <si>
     <t>หกห</t>
   </si>
   <si>
     <t>ทดสอบ</t>
   </si>
   <si>
+    <t>Basss</t>
+  </si>
+  <si>
     <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAgGBgcGBQgHBwcJCQgKDBQNDAsLDBkSEw8UHRofHh0aHBwgJC4nICIsIxwcKDcpLDAxNDQ0Hyc5PTgyPC4zNDL/2wBDAQkJCQwLDBgNDRgyIRwhMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjL/wAARCAQ0BfEDASIAAhEBAxEB/8QAHwAAAQUBAQEBAQEAAAAAAAAAAAECAwQFBgcICQoL/8QAtRAAAgEDAwIEAwUFBAQAAAF9AQIDAAQRBRIhMUEGE1FhByJxFDKBkaEII0KxwRVS0fAkM2JyggkKFhcYGRolJicoKSo0NTY3ODk6Q0RFRkdISUpTVFVWV1hZWmNkZWZnaGlqc3R1dnd4eXqDhIWGh4iJipKTlJWWl5iZmqKjpKWmp6ipqrKztLW2t7i5usLDxMXGx8jJytLT1NXW19jZ2uHi4+Tl5ufo6erx8vP09fb3+Pn6/8QAHwEAAwEBAQEBAQEBAQAAAAAAAAECAwQFBgcICQoL/8QAtREAAgECBAQDBAcFBAQAAQJ3AAECAxEEBSExBhJBUQdhcRMiMoEIFEKRobHBCSMzUvAVYnLRChYkNOEl8RcYGRomJygpKjU2Nzg5OkNERUZHSElKU1RVVldYWVpjZGVmZ2hpanN0dXZ3eHl6goOEhYaHiImKkpOUlZaXmJmaoqOkpaanqKmqsrO0tba3uLm6wsPExcbHyMnK0tPU1dbX2Nna4uPk5ebn6Onq8vP09fb3+Pn6/9oADAMBAAIRAxEAPwDstchiuvjJosE0EcyfY5SUkUMPrg13R0DRiDnSbE5GD/o6c/pXEakSPjdo+TwbGXH516RU9WZwW5lDwzoQ6aLpw/7dU/wqQeH9GU5Gk2IPtbp/hWlRTsi7Izv7C0jOf7Lss/8AXuv+FL/Yek/9Auy/8B1/wrQoosFjOOh6T0/suy/8B1/wpf7E0sjH9mWeP+uC/wCFaPFFFgsZp0HSHOW0uyP1t1/wpP8AhH9Gzn+ybH/wHT/CtKiiyCyM8aFpA6aVZD/t3X/Cl/sTSf8AoFWP/gOv+FX6KYyh/Ymlf9Ayy/78L/hQdE0s9dNsz9YF/wAK0KSlYDy260fTP+F26fbjTrQQ/wBlySGMQLgnPXGOtehLomlgfLptmB7QL/hXD3bBvjzp645XSpD+tekUrIiKRROj6ZjB060x6eQv+FJ/Ymkn/mGWf/gOv+FX6Kdi7Gf/AGHpP/QLsv8AwHX/AApn/COaJ/0B9P8A/AVP8K1OKKLCsZY8O6KowNH08D0Fsn+FH/CPaLkn+x7DJ7/Zk/wrUpKLBZGb/wAI/ov/AECLD/wGT/Cmnw1oZGDo2nH62qf4Vq0UWCyMb/hFPDv/AEAdL/8AAOP/AAobwn4dbltB0s/Wzj/wrYpaLBZGJ/wiPhw4zoGlcf8ATlH/AIUDwj4bB3Dw/pQPr9ij/wAK26KLBZHksPhzRG+NN3Ztounta/2UkohNqmzcXIJxjGeOtd1/whHhT/oWdG/8AIv8K5m1J/4XxfDr/wASiP8AD5jXotCRMUjn/wDhB/CeMf8ACMaN/wCAMX+FIfAnhMkk+GtI5/6co/8ACuioosVZHN/8IB4P/wChY0j/AMA4/wDCmn4feED/AMyxpP4WiD+ldNRRYLI5Vvhv4MY5PhrTc+0AFN/4Vp4LH/Mtaf8A9+q6uinYLI5A/C7wSf8AmW7L/vk/40w/CnwOevhy0/AsP612VFKwWRxZ+E/gVv8AmXbYfRnH9aY3wi8COOfD0PHpNKP5NXb0U7BZHC/8Kd8Af9C7H/3/AJv/AIqmt8G/AR/5gCD6Ty//ABVd5RQFjwrw98NfC2ofELxTpk9gWsrExCCLzmG3cgJ5znqa7Nvgn4Fb/mFSD6XD/wCNR+EW/wCLueNwOmbf/wBFLXo1JImKVjzv/hSXgfjGmzDHpcP/AI0h+CXgs/8ALpdD/t5avRaWixVkecD4I+DFORbXgPqLlqUfBjwzG26GbV4j6x3pFei0UWDlR52fg5ofbVdfH0vz/hSL8ItOjGE8Q+I1+moMK9GpKLC5Ued/8Klsh08SeJR/3EWoPwpjGPJ8WeJ4sf8AUQavRKKLIOVHnrfDG5JO3xx4pX/uIP8A403/AIVjfA5Xx34n/G9Y/wBa9EoosHIjzs/DfWV/1XxA8QKvo0m79SaRvhvreDs+IWvg+75/rXotFFg5EeJeAtG8U+LfDx1Obx1q1sRcSQhEwwIXvk10zeA/F6keV8RdRI7+ZbpTfgcd3w3hz94XU2frmvSaEtBKKsecHwX4537l+IVx7Zs4/wCWKd/wh/j3/ooL/wDgDF/hXo1JRYfKjzr/AIRDx8M4+IDfjYxf4Ug8JfEMf8z4h+tjH/hXo9JiiwcqPOf+EX+JCj5fHFs3+9Yr/hTF8O/E+M/8jhp0g/2rL/AV6TRQHKjzo6H8Tx/zNWlH/tzpDpHxSVfl8SaM597MivRqKYcp5z9g+KwHGsaET/17t/jSfZviwpH+n+H2/wC2Lf416PRQHKedeV8V8f8AHz4e/wC/T/41ieJfEnxN8K2MF5ef2FNFLcJbgRRvnc3TvXr9eb/GlmHhHTyo5Gq25H5mkDVh+/4rqc+R4fcem5hQbn4rA/8AIO0Aj/ru1ejCiiwcp5yL34qgc6XoR+k7Ug1H4qLndomit9LkivR8UUWDl8zzkav8UEG9/DmkuM/dW8IP8qX/AISH4k5/5E+w/wDA7/61eifjQfrQHL5nnh8R/EcH/kTLIj2v/wD61N/4Sf4jjr4Jtj9L4f4V6NRTDl8zzj/hKviIv3vA0Tf7t6Kd/wAJX8QQP+RFjJ/6/h/hXon40fjSDl8zzo+MPiADj/hAfx+2rigeMPH2/DeAG2+ovVr0aiiwW8zzpvGnjVD83gC6/wCA3aGs+x+K2uancXdvZ+Cb2aa0by51Ey/u29DXqleb/DXd/wAJV455G3+1Bx/wGgTT7jl8feKz1+H+o/8Af9KcfHnisHB+H+o/9/4/8a9EpaB2fc86/wCFgeJkHz+ANUGOuJoz/WgfEfW8c+Adaz7Fa9FooCz7nnZ+I2s8Z8Ba3+af400/EvVQMnwHrnHXha9GophZ9zzkfE3Uf4vA2uj6RigfFC+xn/hB9f4/6ZCvRqKQWfc85HxQu+M+CPEAzz/qaafipcg8+CvEP/fivSKKYWfc87b4oyqMnwf4h/8AAU00/FUgc+EfEQ/7dDXo1FAWfc8um+NFjaSxR3nh7W7ZpW2xiW3wXPoB3NT/APC3I+3hTxCc9P8AQ25o+JKeZ4y+H8eOuqlvy2mvScUtRWfc85/4WwuP+RS8SZ/68moHxZTHzeFPES/WyavR8UYpjs+55yPi1bnj/hF/EOfT7C1B+LloBz4b8QjnvYtXo2KTA9KAs+55yfi7aDGfDfiDn/pyaj/hbtrnnw14hH/bi1ejbR6UbR6UCs+55yfi5bZ/5FjxF7f6C1B+LtqvXwz4hH1sWr0fA9KTaPSgdn3PNz8X7Lt4c8QEev2JuaU/GDTx/wAy/r+fT7E1ej7R6UbR/dH5UBZ9zzhPjBYHk+HtfA/68mNNl+MemQI0kmg66sajLM9mQAPU16TtX+6PyrnvHOE8B+IHIHGnz9v+mZo1FZ9zlLf4zabeQia20HXJ426PFaFgfxFSn4v2QOP+Ec8QZ/68Wrd+G0Qj+HOgjHP2Ra6raPSkOzPOf+Fv2WM/8I54g/8AAFqX/hblt28M+If/AABavRdo9BRgelMLPuedn4tWwJH/AAjPiHj/AKcWpR8V4CP+RX8Q/wDgC1eh49qXFAWfc87/AOFrQ4/5FbxF/wCALUh+K8QJH/CK+I//AABavRcUCgLPuedf8LXT/oVPEWfeyakPxYixk+FfEQ/7cmr0YijAoCzPOh8VozjHhXxEf+3JqRviuqHB8JeIuf8ApzNejYoxQFn3POR8VwWwPCPiL6/YzVeH4x2V1czW1t4c1yaaE4kSO3JKH39K9Nrzn4b/AL3xR44nHRtV25+iigWvcP8Aha2CceEfERx/05tUn/C0yUz/AMIj4h9/9DNeh0UDs+552vxRlf7ng7xCfrbYpT8T7jOF8GeICf8Ar3r0OigLPuedf8LQuySP+EK8QZH/AEwFO/4Wdecf8UV4g5/6YivQ6KAs+556fiZeqT/xRPiDHr5IpU+Jly3Twb4gz7wV6DRQFn3PPT8S77nHgnXzgZ/1Ipn/AAs3UD93wNrx/wC2YFei0d6As+553/wsvU8ZHgXXj/wFaP8AhZWrZ48B67+Sf416JRQFn3PLrj4vXFrqFrYT+C9YS8us+RCSu58dcVf/AOFj6znH/CAa5+cf+NQeJFEnxx8GL3S1u3P/AHwa9JHSkCPPm+Ietj/mQNb/AO+o/wDGmn4g+IVx/wAW/wBY5/6ap/jXodFMdmedH4g+Je3w+1b/AL+p/jR/wnvio8D4e6l+M8f+Nei4ooFZnnX/AAnPjDt8PdQ/8CIv8af/AMJt4yzj/hXl/j/r5i/xr0Kigdjz3/hNvGP/AET2/wD/AAJi/wAaQ+N/GIOB8Pr/AD/18xf416HRQFjzo+NfGYz/AMW+vP8AwKj/AMaT/hOPGudv/Cvbv/wKSvRqKBWfc86/4TXxtnj4e3eP+vqP/Gquq/EnxNoenS6hqPge4t7WPG52u4zjJwOlenVwfxiGfhxfAnG6WEf+RBQDTRUi8c+M54lli+H90UcAqftUfI/OpP8AhNPG/wD0T26/8C4/8a7rT126dar6QqP0FWqBo87/AOEz8cf9E+ufxvI/8acPGPjhv+afzA+94lehUUCt5nn3/CYeOc4/4QCX/wADUpR4u8c7gD4Bk57/AG1OK9A/GigdvM8//wCEw8a5I/4QGf8A8DEph8ZeNh/zT66P0vI/8a9DooCx53/wmfjc/wDNPrr/AMC4/wDGlHjHxv8A9E/uf/AyP/GvQ6KAseenxl42A/5J/cZ/6/EpF8Z+ND1+H13/AOBUf+Neh0UBY84uPHXi+1glnm8A3aRRKXdzdR4AAyT1qtpfxI8T61p8Ooad4Fu7i0mBMcq3MYDYOD1PqK7vxISPC+q/9eU3/oBrnvhIMfC3QsH/AJYsf/IjUhdbFQ+NPGGBj4e3+e/+kxf408eNPF2Ofh9qGf8Ar5i/xrvqKY7Hn/8Awm3i3t8PtQ/G4i/xpD438YA/8k9v/wDwJi/xr0GikFjz0+N/GPb4eX//AIExf40o8beMO/w81D/wJi/xr0GimFjz8+OPFCgZ+H2p5/6+Iv8AGov+E/8AFGMn4fapg9P30f8AjXotFIVjzr/hYHic9Ph7qv8A3+j/AMaUePPFZ6fD3Uv+/wDH/jXomKKYWZ56PHPiw4x8PdSz73EX+NO/4Tbxbnn4e6jj/r5i/wAa9ApDSHY8y0/4paprEVw+neCdTuFt5TDKRLH8rjqvXqKvf8J14lYZj+H+rH/eniH9ag+D2f7H8Q8gj+3rvGP+A16OKFcS1PPD8QPEoOD8PtWz/wBdY/8AGlHj7xIevw+1b2/fRf416FRRqOx5+vjvxMx/5J9q3/f6L/GpG8ceI1GT8PtY/wC/0P8AjXeUUBY4H/hP9cwT/wAK/wBb4H/PSL/Gov8AhZGs/wDQga5+cf8AjXodFAHnn/CxdbJ4+H+t/i0f+NPHj/XyOPh/rOfeSP8Axr0CigLHB/8ACe67tyfAGs/9/Iv8ab/wsHWs/wDIg63/AN9x/wCNd7RQFmcEfiDrIHPgLXP++o/8a1PCXjEeKJtQt30u4064sHRJYbhgWywyOntXU1wHgj/kf/HY/wCnyD/0VR1Fqj0GikopjPNr75/jhpfOQunycY6c16TXmsnzfHi2x0GmMf1r0qkt2TAKWkpaZYlFFFABRRS0AFJS0UAFJS0UAJRRRQB5xK2749Wy/wBzRyfzY16PXmsf7z4/yHH3NHA/8eNelUkTEWkpaSmUFLRSUALRRRQAUlLRQAlLRRQAUUUlAHnNiwf48an/ALOkxD/x416NXm2mjd8eNYYZO3S4v516TSRMRaKSimUFLRSUALRRSUALSUtFACUUUtACUGlpKAPOfB4A+LPjjBz80H/opa9GrzbwUxb4p+Oc9fOh/wDRYr0mkiY7BRS0UygopKWgBKKWigAooooAKSlpKAFpDRSMdqk+goA84+COT8OYpP791M3616RXmvwLH/Fs7b/r4l/nXpXagS2FooooGFFJS0AJRRS0AJS0UUAJS0UlABXnHxmXPhjSj3Gr2vH4mvR685+MDD+x9CQ9G1q1z/31QJno1FFFAxaKSigAooooAKKKWgBKWiigBKWiigBO1eb/AAyYN4j8csBj/ibY/SvSO1eb/C879b8byYxnWWH5DFAup6TRRRQMKKKKACikooAKWkpaACkpaKACkpaSgDzf4gEn4ifD5e326Y/+OivSK838aL53xX8BQ+ktxJ+UZP8ASvSKQhaKKKYxKKWigBKWiigAooooAKSlpKACuY+IvHw48RHOP+JfN/6Ca6euR+J7bfhp4hIP/LmwoE9i34AGPAOhD/pzj/lXR1g+CV2eB9EH/TlF/wCgit6gYUtJS0AFJRRQAUtJS0AFFFJQAtJRRQAV518LPnuPFz9m1qX/ANBWvRa89+FSjyfEsndtam/ktBL3R6FS0lLQUFFJRQAUUUUALSUUtACUUUUAFFFFAHnWs7G+Ofhvj510y4OfzH+NeiDgV51qR3fHvRlHVdFlJ/7+GvRRQTHqLRRRQUFFFHNABmjNFGKACjvRRQAUUUUAFcB8Yv8AkndyB/z8wf8Ao0V39ee/GUgfD6QZ63lv/wCjRQJ7HdWYxZQf7g/lViobT/jzg/3B/KpqBoKWkzRQAUtJS0AFJRRQAUUUUAFFFFAGZ4h/5FrVP+vOb/0A1z3wlBHwv0LP/PFv/RjV0HiQ48MasR1FlN/6Aa5/4TMW+F+gnGP3B/8AQ2oJ6naUtJS0FCUUUUAFLSUUAFFFFABRRRQAUhooNAHnPweA/sTX9vA/t67wP++a9Hrzb4Nsp0TX9pyv9uXRH0+WvSRSWwo7BRzRRTGA60mCe9LRQAUUUUALSGiigApaQUUAHauC8F5/4T/xxwB/pUHT/rlXe9q4DwWT/wALC8cg/wDP1B3/AOmQpdSX0PQKKKKZR5lFlvj03oul/wBTXpleaWmD8drvvjTF6duTXpdJdSIbBRRRTLClpKWgBKKKWgApKWkoAWiiigApKWkNAHm9rz8e7vGPl0iMH/vo16RXm1qP+L93hB/5hMef++jXpNJEx2FopKKZQtFJS0AFJS0UAJRS0lABRS0UAJRS0lAHm2jsf+F66+O39mw/zr0mvOtE+b44eIzj7umwD9a9FpImItJS0lMoKWiigAooooAKKKKAEopaKAEoNFB4oA858Fc/E/xywxjz4R/5DFejV5x4KjMfxP8AHSg5Xz4T+JjB/rXo9JEx2FoooplCUUtFABRRRQAUlLRQAUUlFABTW5U56U+o5QTGwXrjigTPOvgac/DG0PrPL/OvSK83+Box8MrU+s8v869IoQLYWiiigYUUUUAJRS0UAFJRRQAtJRRQAV5r8Zcto2hIM5bWLcD869Krzr4rjefCUR6PrtsD/wB9ihiex6KKWkFLQMSilooAKSiigAopaKAEpaKKACkpaSgANeb/AAqG6bxdJ3OuT/oTXo+a85+EZ3Q+KH/va5cn/wAeNAup6RRRSUDCiiloAKKKKAEpaKKACiiigApKWkPSgDzrxPz8Z/Aw9EvP/RL16LXnHiI7/jh4NX+5a3b/APkNhXo9ISFpKWimMKSlooAKKSloAKKKKAEooooAK434rNt+F+vn/p2x/wCPCuyrifi42z4Wa8cdYUH5yKKBPY3/AAqAvhDRR/04w/8AoArYrK8Nrt8LaOD2soR/44K1aBiUtJS0AFFJ3ooAKWkooAKWkpaAEoqlpWs6brlq91pd7DdwJK0LSQtuAdTgj+o9QQRkEGrtVKMoNxkrNABrzv4RYOka24H3tYuD+orv7ieK1tpbieRIoYkLvI7BVVQMkknoAO9eefBlxN4Vv7lWyk+p3DocYyC2RRyy5ea2hL3R6RRWbr2uWXhvQ7rV9QdxbWyhm8tdzMSQAoHqSQOcDnkgc1zlj8StLTwpYa54iifQxfMwggmzK0qjkOoUbipGOSo6jsVLb0sHXqw9pTi2r206u17JbvTtsNySdmdtSVj+HvFeh+KoJptF1BLpIGCSgKyMhIyMqwBwecHGDg+hpniLxhoPhP7N/bd/9l+07vJ/cu+7bjd91Tj7w6+tSsNWdX2PI+ftZ377b7BzK1zbpa5v/hPfC/8Awjn/AAkH9sQ/2Z5vk+btbd5n9zZjdu74xnHPTmqlv8RdD1fTdSm8OSPrN7ZQGb7DCjRyyDp8ocAkZ67QSMjgkgG1gcS037N2Ts3ZpJ+bei+YuaPc66lrnvBvi2y8Z+H49Vs0eIhjFPC/JikABK56MMEEEdQR0OQOgrGrSnRm6dRWa3Q001dBRRRWYwooooA83uAW/aBtOOE0Jj/5FNekV53Hh/2gZP8Apn4e/L98P8a9EoJiFFFFBQUtJS0AJRRRQAUUUUAFGaMUUAFed/Gc48Dxr/ev7cf+PivRK84+M43eELJfXU7cf+PUCex6DbD/AEWL/cH8qmqOEYhQeiipKAWwUUUUDCiiigAooooAKKWkoAK57xr4mXwl4VvdVMTyyRrthURF18xuE34xhc4ySR6DkgHoe1ZXiezn1HwnrNlax+ZcXFjPDEmQNztGwAyeByR1rfDcntoe0V43V+mlxO9tDzaw+Ken6l8K7qXXroxao0M1mcQMBcy7DtKYyDwV3dApYZChly/wF8RPDeh/C6z+2Xcgm05BBNCkLsxkbzGRQcbTuEbYOcDuRXA6p4e8R3/wx0fzvD19bR+H5rhJxMpSSWOVlfeqEbsLyGOMcgjPzbc3QfB2oXvg++1Y+FbvUIXlt1t5obhkmVQcytFGFPmKwwuSDtzkbtrY+xnlGWTcpuVnzbKUbL3rJa23WvktN1Z83PNHq+rfGPTb/wAD6vf+Hnmg1S32JHDdQZZQ7Kvm4Usu0ZPJOA20EfMobtPBXiVfFvhSy1YRPFLIuyZTEUXzF4fZnOVznBBPoeQQPC/DvgXxDqNn4otLLw/e6fb3FjGIF1RQJGkWaNwgkKITkJJ0AXO3d0Br2P4aalqV74TtrTUtBvNKfToorRDcjHnhEUbwCAw6emORgnnHnZtgsHQw8lh7NqS+0m0nFaeet9r2Lpyk3qY3xh1O9/s3R/DOm3D293r14LYydEMfCsrMMsAWkTOByAwPHBx9Qv8AxRF4utfh/wCBL77LDpFipnuL7bIW4U5LMGO0BkACqMFiMbQMXvjJ/wAS6/8AB/iOb5rPTdTHnInMjZKP8oPB4hbqRyR+FTXo9f8ADPxKl8baFo7+INM1WzjjYWvzEZVcbSm44/dI2/btw2OuDWuBjD6rSVotuM2lK1nO6SvfS/LtcJfE/l9x0Hwt8Watr1rq2meIPm1jSbnyZ3CIoYEsADtOCwZHHAAwF6nJrK8eyfEXQ/7V1y18TaZbaHBhoofswMgBwoXBjfLFiBktjJz8o4HP6EfG/hfw/rHiq20F5dX1zVVL6e9lKxjjAlZpNitvUF2wN3QAHncDXT/EPQte8b6z4d0RLCa20M/6ZfTtImUYcFCQGw6qxAwSGL9whITo0aWY865PZPe9mlypOVk/O6Vgu3C2tyOTxL410/4MRa68SXurzr5pmWJQba3bJWUqvyuQuDwBgMCwO1s27G1uvih8GYBqM+zULqJyskbmJGljdlQuBkFSVBYYI5yACFx1viHTGuPBmq6VptugaTT5ra2gjwigmMqqjoAOg7AVzngmRvBXwgs7jXYXtDZQSzyxOQHw0jsq4JA3EMoCkg5IBwa4liIToe1oRUavtU1bezTsrdk7LsVZ3s9rEnwl8RT+I/AVvNeTTT3lrK9rPNNjLkYZTkdfkZASeSQc56nuK8y+C2mT/wBgah4mvbjzrzXblpnIwBhGcZIAGGLmQ8cY24xzXpuK4s2hThjqsae1/ufVfJ3RVNtxVwpDS0hrzizzb4MkNoGuMAQDrdycf9816UK82+C53eGdXbOd2s3J/wDQa9JpLYmOwUd6KM4plBSUtFABRSYpaACjNFFABRRRQAVwHgjDePPHLA/8vsI/8hV39cB4EU/8Jt46cjrfxD/yHS6iZ39FGKKYHmtiD/wve/3A8aYmM/WvSq83sSf+F6X4Jz/xK48f99GvSKS6k09goopaZYUlFFAC0UlLQAUUlFABS0lLQAlFLTaAPOLNcfHm/Of+YTGf/HjXpArzawz/AML41LBODpUe4f8AAjXpNJEx2DvRQaKZQUUUtABRSUUALRRSUAFFLRQAUlLRQB5xoRP/AAu/xOO32CA/yr0avO9E/wCS3eJf+wfb16JSRMQopaKZQlFLSUALRRRQAUUUUAFFJS0AFIaWkNAHm3gkkfE/x0Mf8t4j/wCOCvSa818DNu+J/jrk5+0Rf+gCvSqRMdhaKKKZQUUUUAFFFFABSUUUAFFM8weZswc4z0p9ABUczeXC7eik1JUU4327jOMqRmgT2PPfgfx8MLH/AK7S/wDoVej15x8Dx/xbCxPrLL/6FXo9CBbC0lLRQMKQgkHBwaWigBB05paSloAKSlpKACiiigArzj4sf67wh6/27b/+hCvR685+KYBvfBn/AGHrf/0MUCex6KDS0CigYUtJRQAtFFFABSUUUALRRRQAUlFLQA09DXm3wf4svEg9NauP/Qq9JPQmvOfhB8+meIJ+0mtXB/8AHqBdT0iiikoGLSUUUAFLRRQAlLRRQAlLSYooAKO1FFAHnOsAH48eGwe2l3BH5mvRq851M7vj1oQ/uaTP/OvRh0oEgpaSgUDFooooASlpKWgApKWkoAPrRR3ooAK4T4xN/wAWr1kevkD85467uuC+Mxx8LtU95Lcf+R46BPY6/RF8vQdOT+7bRD/x0Vfqnpv/ACCbLP8AzwT+Qq5QMKSlooAKKSigBaSiloAKoazYz6no13ZWt/Np888RRLqAAvET3Gf6YPoQcEXq53xZ400rwbYC71Pz23MFjjhTc0hPpkgdATyR09cCtaEKk6sY0leV9Ouona2p4H4Z1rXPCXwzvtb0nVXiN1qqWIt2jV0jIj8xpRuyNxAVemMZzk7StrRvFPxM0qHVdPZtTM8di19/xMQPMt41dN0o84Esu1WXaOMsSBkUW2tfCq2tdUtRpniZ4L/BEbmIi3IJKtH8/wB5dxALbjjI6MwavY6h8KLO1vYH03xLdNdReWJbgQF4Oc7o9rABsgckHpjoWB/R5xjNzlPDuTbT1gnfa3Vba77nGtLai6RrfjGA61oeu6jqcCXmkXMhh1NZGkcJE7Dy/MB252sCeAV3YO4KR6V8C7SSDwM9y91JIlxcuVhYDbFt4OO/OMnnHTAHJPG+Al+HD+J1j06DXpr2S3mjhj1JYmibKEOCE/2C/wB75cZ74rpvgxpOn6Z4av8AXzLOslxLJC6GU+WEjdgML3Puckc4xk58PPcVRVOeH5XCT5ZfCle11306a67NGlNO6Zc+PNxLH4BtkjldEl1CNJFViA67JGwfUZVTj1APas7xfZ6bcfG/wlo+oRw/2PHYjy7SQ7YFfMoRQvA5ZI1x/FhVwRxXb+L9Ch8d+CLixtZYFlmCy200ybgjqQR7rkZUkcgMeD0OBp/hCXx54KsrXxzptzaanpzPbQ3CXB811UqDJyWBLbMEtuzgsuAwrjwGLo08LBylblc4u2650rSS0va3TVFyi3Iw/CtxpHh342eLILW7trDRY7MPIonCQJJuhBzk7QQ7uoH8JYqMdKo/EexuvEfxd0C20WbT3mutKD28t0izQMuZmyQVdWBUHBwecH3ruLH4SeHdP8MapoUM2oeTqbRtcTtKplxGwZVHy7QAc/w5+Y89MS6v8KPDetaNpmnXBvVOnRCGG7SYGdoxn5GZgQVycgYwvRdoyK2hmeDhiVXUm3y8l2r3XKlzNX113V9uouSXLY8KluopPEun+G9atdPt47bWjHqk9ri3huVDrHllUKqhFEmGAXh2OASxb0p7PTdF/aK0i00OOGzinsW+2W9odqb/AC5TtZBwOFibGB2bGTmurg+EvhSHwvJoJtZpIpJfOa5aXE5kCsqsWAAO0OcKRt7kEkk0LTwFafDfStW1rwvaXuq6wbby4YbmUH5dwLYCqu7oGx1OwBSCeeivm2FxCcKTabjKCW0W5W9562SXZ7K21hKnJbmb8NZl0/4keNNC08PNpKzmdXjQxw20gYgxBMYB+YrkYyIcgEdPWK4v4Z+Er3wt4embVnSXV9QnN1dSfecEgYRpOrkHcSemXbGep7Svn82q06uKk6bulZX7tJJv52NaaajqFFFFeaWFBpaQ0AedWK7/AI+6pID/AKvQ40P4yg/0r0QV51pGX+O3iNu0el264+pBr0UUEx6i0UtJQUFFFFAB3paTvRQAUUUUALSUUUAFec/GAeZoGkxDrLq1uoHrzn+lejV5v8XGAtPDaEAh9ahGCOvDGgT2PR1GFAFLSCloGFLSUUAFFFFABS0lFABRRRQAV5X8XtS1SDUfCul6frNxpUOo3TxzzwOUIw0ahiQQSBvY4yAe/QY9UrzD4u+ENb8T/wBh3GjWUN6bGWTzbeSQJuDbD/EVBX5CDgg8jHcj08nlTjjYOo0lrva1+V2vfTexFS/LoeVeKNW1DQpo4LL4gXmvRSiWOePzWZAmAvILsDuBfHptz6Y92+F//JM/D+Bj/Q1rwi/+G3iez08XFz4asdMtLNZJpriO5Viy4Bw37xyfu4GB/Ec8cj3r4aqV+G/h4H/nxiP6V0ZxNSjR5pRlOz5nG1vidvh02Ip/Ezq6KM0V4hsVdT02y1jTJ9P1C3S4tJ12SRP0I/mCDggjkEAjmoNB0Ky8N6Ha6Rp6uLa2UqvmNuZiSSWJ9SSTxgc8ADitGitPaz5PZ39297dL9xWV7h0qOGeK4QvDKkihmQsjAgMpKsOO4III7EEVV1mLUp9Gu4tHuYbbUWiIt5p03oj9iR/XnHXDYwfnnwV4r1zwT8OtQ1e0+xXFnPqa2sNvOjEpN5e95CQRldiqu3PXnjBD+jgcrljKM505LmTiku9/6/BkynyuzPpSsbxL4X0vxbpsdhq0TyQRzpOoSQody9sjsQWU+zHGDgjw/wAP/Gbxj9i1GOW3TVp4oDcRy/Y8+UAybjJ5ZUCMJvOcZ3EZOKg0T4leKvEGn6/o+pXltdRXGlXLiSaOONogkTM20Lt3lhkY5I4borA+jDhzH0JuopqPI1qm7+q06edr9CPbReh9E2X2T7Bb/YPJ+x+UvkeRjy/LwNu3HG3GMY4xUep6nZaPps+oahcJb2kC75JX6AfzJJwABySQBzXCfBOLUk+Hlu93cwyWckshsokTDxIHYMGbvlwxAxx6nICwfHa8ntvh9HDDJtjur6OGYYB3IFd8c9PmRTx6V50cvUsy+p811zWv89fn+pfP7nMdVo/jjQ9X8OQ681z/AGdZTStCraiVgy4zwCTtbofuk9COoIGvYapp+rQNPpt9bXkKtsMltMsihsA4ypIzgjj3rybxjodlq3xZ8H+D7hXGh2+nlo7dGwQFEny7/vYIhjB5zgHBBOal8B6fF4Z+M/ifw7pjOmmfY0nETkMQ37tlG4jOF81wOehGckZrpq5Zh3RdSnJqXLzpPbl5rWv3+X+ZKm72foTfCLWtK0nwbdNqep2dkJ9VuTH9pnWPfjbnG4jOMj8xXpn9taV/ZX9q/wBp2X9nf8/fnr5X3tv384+9x168V8n6Dplxr+o2VtpemDVr5BOZrOQMkIQOxDGRXUj73qoztGTuwPVfhnoHh7U9G13QNcTN1/ae2fSpHKxW0q79ogYMSzFUkBYNuKpg5A3NUspoQwcMTObvo2klezdtr39G9H31JjN3sek3Pjbw7Dpt7e2+q21+LOBriWGwlWeXYMZO1STjJHJwBnJIHNW/D3iLTfFOjQ6ppc3mQScMrcPE46o47MM/yIyCCfFfhrok/gn4rLouv6bC17dW0hsrlGEm3G751O75VZUccru6DgFs9P8ADCaLQvHXi3wdBKj2kU5u7RYGDxxLkKylz8xYBolIOcFG5z1rG5Vh6UKioycnFRknpZxbs9uz/Xtq41G2rnrFFFFfOmwUUGigAooooAKKM0UAH8Nef+AQP+Ey8dN66jH/AOi67+uB8And4s8cN/1E0X8kpdRPc9AooopjPNrBmPx01HngaXHx+Jr0ivN9IJf4461k/d06ID6Zr0gUkRDYKKWimWFJS0UAJRRRQAtFJS0AJR3paSgAooooA8207LfHnVzjhdLiH616TXnGkYPx017J5Gmw4/OvR6SJiIelME8TTvAJUMyKrtGGG5VYkAkdQCVbB74PpUleAWs/iTRvjN4n1Ga8sri40+xlu70LEVS4tlRGWNByUbHlDOTjBJL4Ib0cBgPriqWkk4xuvPVL+vOwpy5bHv8ARXzlpHxs8VzeKLd7mOG5s7iWOJrC2tckAsoPlc7i5wcBmIy3TpiOH4x+NE8WR/bPsyRrOIptMeNYIwfuspd/mQ5ycs2AevAxXqPhbHJtXjor7/htv+HmR7eJ9HRzxSvKkcqO8TbJFVgSjYDYPocMpx6EHvUleMfCyHV/+Fm+NH+2W32SO8kW+QQkGaQySbGQZJQAh+rNwcYJ+ZfUvE95Pp3hPWb61k8u5trGeaJ8A7XWNiDg8HkDrXl4zA/V8SsPGXNfl19Ut/v+4uMrq5m6N4+0DXdS1a0sbh2i0tQ894yYtivOSJOmBg8nGcErkAmtXT/EOi6tO0Gm6xp95Mq72jtrlJGC5AzhSTjJHPvXgd//AMSz9nHS/sf7v+1NTb7Z383DSY69P9TH0x933Od3X/Cmm/D/AOIPgSbw/wCdDJdXItpzI/meYNyIzcjhmWVgcYHTAFevUybDOUoQk025qK3u6a1bfS72tchVJf15nsuoapp+kwLPqV9bWcLNsElzMsalsE4yxAzgHj2qG08Q6LfwXM9nrGn3ENqu+4khuUdYlwTliDhRgHk+hrlfix4avfFfhqx0zT5bZLo6hG6rcS7N42ODt9SAS5A52o2MkYPDeC/Ddr4V8Vz+BvE+l6ffza5Z+Yl1bszbUG4+WxYKQMxFgVAIYL14KcWGy/D1cI6zm+dXfKrfCt3rbpcpzala2h65B4u8NXM8cEHiHSZZpWCRxx3sbM7E4AADZJJ7VV8OeONG8UX+oWFi80d5YysktvcxmKQqDjeFPO3PHOCDjIGRnyZfCfhnUvjPZ6Boeloum6Wpn1FhMZRI687TvdgVDGNCoAOS4PTI6PxFPF4X+O2h6lDKgXW4BaXcMbB5WYnYjMrfdUkRcgjPlvx1z0TyzC/w6bk5Sg5q9la2tmlfdJ+mnfSeeW77mnoYP/C7vEn/AGD7f8a9FrzvQwf+F2+JTj/mHwfzr0SvnEaRFoooplBRWV/wkujf8JJ/wj39ow/2t5Xm/Zsndt64z03Y525zjnGOa1audOcLcytfVencL3CiikqAFoorKsfEujanrN9pFlqMM2oWP/HxApOU7HB6Ng8HGdp4ODVxpzkm4q6W/l6hc1aKKSoAKQ06mmgDznwThvij45Yf894R/wCQxXo/avN/A/HxM8dADA+0xHn/AHBXpFBMdgpaKSgoWiikoAWiiigBKMUUUAFFFFABVe+yLG4I6+U2PyqxUF24js5nPRUJP5UCexwXwRIPwt07HZ5c/wDfZr0TtXnfwRXb8LtOPq8p/wDHzXolALYWikooGLSUtJQAUUUUAFFFFAC0UlLQAlecfFAltb8Dx+utxH8iK9Hrzf4n/Lrvgd1++NaiAHsSoNAnsejiloFLQMKSlooAKKKKACkpaKACkoooAKWikoARvuH6V518GcHwlqDf3tWuv/QhXoj/AOrb6V538FOfAksv/PXUJ3/MigXU9GpaSloGJS0UUAFJS0UAFFFJQAtFFFABSUtIaAPOL1l/4X7pobr/AGPLj67hXo46V5rON/7QVpkA7NFkI9vmH+NelUCQtFFJQMWkopaACkoooAKWiigBKWiigBK87+Nj4+HE6f8APS7t1/8AIgP9K9Erzn42f8iCo9b+3H/j1Amd/ZrssoE/uxqP0qxSAYUAdqWgYUlFFABRS0UAJRS0lABXlPx9Zf8AhB7EDGf7TT/0XLmvVT0968f+O8co8JWbyHg6ggH/AH7k7V6uR/8AIxo+pnV+BnMy+LPHVncJp/hj7N/YYj/0IzRqcoFyRlupHtxXPQ6z8RdIvYCttNBEfmIgVAJTIeSXIOSST9M8Y4rQ+INlqdtr+lIrSEPOyooGAucAAD0wK6678NLpmkSzO88zoQ0EMjZVGOMBfXn1/CvINkc5c2GtS/E/SIr3Zpl9Pp0sgaJi7quybO9iSWc4IJ9MV1nwg8I6dN4NttQvIzeySzPiOf5okAY8hT9O9UNfSaP4zaI04IkbRpmxnp+6uP8ACu1+Dwx8MNH91Y/+PGvWzT4MP/17X/pUjGO79Tsrezt7PctvCqK3UL0/KrIpFBFLXlmgtJRiigAopaKACikzQKACud8V65NpVvFDakpcSnO8x5AUdcE8Z6evHpxXRGsDxdY3OoaTFFawmVxcKSox0wRn8yK48f7T6tP2T963Tc4Mz9r9Un7FtSt03+Rm6d4rmS8ZdRfdbrbRsXSBgQx25J9vn69DgY64PTtfwLqUenneZ3jMvCEgKDjk9s8/l7jPOX+mb9d1m4vh5NhLaACdugb5McA5JBXp9PUZf4NspGgk1S4OZJVEMR9I1AHb/dA5Gfl964cNWxMKvsJa6vV72Td/v0seZg8RjIVlhpe9dvV7qKbu+9noov1Ob02/Sx+LHje9kXcsFlaAe5wcD8TgVqmS90jQG1lp5G1DUXUbiRhF5IO3kHIH4A4GMHOLYWUuqePPiHDbgGYpYKoJxnAc4/8AHa351l17wRarZx7pbRlWSMZydikcccnBBx+HJqswc3Uaje6i3H12fzS+648zdR1Wo3uoNxt/Nezt5pbdVe6LVlqOraf4jg07V7uGZbiPKlMKFJzjnaMnKkY962tWh1SaCMaXcwwSBsuZFzkY7HB/l+I788q6lreuQ382lzQw2UZZYJnKh5BkrtJA5J257cc9hWl9t1i78LXMzWRhvyGVEUEErnlgM5BxnA65Ge+KWHq3pzg3JrVxet7K3X12Hha16VSnJzcdXF+9zWSXXffYxIda19bLUrpr2GWG1xEH8oFWYsBlCAM4HPOeo454tWuq63ZXmltf3ENzb6jgIiqAVB28nCjkbh69/rWjZ6M1l4UkshbRz3EiF3ikbCs57Zz2wBwRyOo61zGi6Jdy63ZsbK6to4SskjzLwSpzxkDqcDHJHXmuOccVRlTV5Nu3V6O+t+j00123PPnHG0JUVzScpJdXo+bW/R6aavTc6Gwln0nxNJpMsxmtroNPBnJMZJJIJJz2b1ycHjJrpa5dXGp+PFmtgTHYRGOZmUgbvmGB+Ld8dDXU16+AfuzS+FSaXp/w9z3ssfuVIp+6pNR9NPwTuhO9Bo60YruPSClpKKACvN/iviSfwlCed+tRnGPRWr0ivN/iaN+v+CI/XVgf/HaCZbHo4pe9AooKDvRR3ooAKKKM0AFFHajNABRRRQAtJS0lAHMfEJmT4fa4VIz9kbFO+H42/D3w+AB/x4Q9P90VB8SWK/DjXSP+fVv6Va8CYHgDQMdtOg/9Fign7R0VFFFBQYoBoooAzdc1/S/DemnUNXvEtbUME3sCSzHoAoBJPU4A6AnoDXglvZ/DqHRtU0mXx5eTWNxKJ7OI2EwFtKMgSH5fnbadpxtBGeM7Svb/AB9P/FDWP/YST/0XLXk/iCa18OaqYre2s5rJWYxn7HG0uewYSKQRn0r6DB16WAwsaspTvUb+Hl+xa26ffoZOLnKy6HR6SnhS/wDtn9sfErUbjUr62+wwzslxGIVL5w7NwyHjKsQoBbPOGXvtI+ELw6+NU8QeJr3XNttLbCOdWUlJFZCC5djt2u/Axyc59fGtTvrrVPAjXF3oGnWRj1KNI7y3s44JJA0cjFDsAyANvb0r6xrfH5jVWHhWw85JVOZNNRurWWjUVa9+hMYK7TWxx/gjwNP4LkvIl8QXt9p0nFtZTKAluNxbPU/NzyV2g8kg8Yf8SvC8vi3wVdWFpEkl9Gyz2oeQoN6nkZ6ZKF1GeMsM46jrqK8T6/XeJWKbvNNO9rbd7W+fc15Vy8p5PB4db4q+GdM1a+OoaH4j0xjam7MIUvIjLufACsQGDYAK7HLjnHM1r8G4oPDuu2M+tvdalq7RmTUJbYFkVZBIRgsWJZhlju5+Xjjn1KkY7VJ9BXS84xMfcovlhe6WjtrdK7V7J9NvIn2cep8+fDr4eXHiHwra63pXiG70O9Dz28z2yn96gkyOVZT165JBwvTHPZj4LWS6G8Y1m5/t97xbw6yUzJvBOABuyB8xJIbJbDEnAAsfA0f8Wytv+vqf/wBDNek0lnOOSSU9vJfjpqvJ6eQKnHseVx+DX8BfbfG2s6rqfii/062ItUYMGjByGJJdjtAY5PRQXOCcY1fhR4d1LSdGv9V1yHy9Y1m5N1Pu4fYeVDqMBW3NI2AONwBwRgd/RSrZpWrUZU6mrla720W0UlZJX182NQSd0GMc0UUV5hYc0UUUAAooooAKKSlFACGuC+Hx3eIvGr9zqxX8lrvj0rgfh2uNZ8Zc5zrMn8qXUl7o76iiimUea6Pg/HLW8A5/s6LP516VXmuisB8cteX1sIq9KpImGwUUd6KZQUtJRQAUtJRQAtFFFACUUUUALSUtJQB5zpRA+OuuA9TpkOPzr0avONNOfjvrHtpcX869HpImIyeeK2gknnlSKGJS8kkjBVRQMkkngADvXiV5f+AdZ+Ib67H42mgi1CIWt5ZG0lRJ0KeWUMpUBEIC5yOMEhlOCvqnjX/kRPEP/YMuf/RTV8qXGt28/hS10YaTZR3EE3mfb40AmkGXyrnGT99e5GEH4fU8P4P2kZVE5Jt8nu20TTbbunpou3qZVZW0Pc7D4MPaX9mk3i3U59Fs7n7RBpw3R7CCSuHD4VsnllUE5ONpORBdfBO7vpBBd+NtTuNKFy04tJkLnliSdxfbvO5svt6sTjnFet0V5v8AbmP5ubn19I/ftv57l+yj2OIg+HP9n+PZPEmla7e2Ntcy+fe6fGNyXEh3ZyScbSWJwVJGW2lcjb2N7ZwajYXFjdR+ZbXMTQypkjcjAgjI5HBPSpqK4a2KrVnGVSV3FJJ9dNtevq9S1FLY8Z8IeHbrUNH1T4ZeLLC5RbFhd21/AqlFRnyNjleCx8wgnJIMinbtxWz4a+EP9j+JLDV9V8QTax/Z8QjtYJoMLHjhMFnbCrkkAYwcEHjn02iu+tnOJm5+zfKp7pd2rNq+qv1sQqa6nldr8FktvC50seIZheRXy3tpex2qobd9oU453c7QThxyiEAYO7V8LfDJ9F8SLr+s+Ib3XdQhiMVrJcbl8kHcG6uxbhiAMgDJOCSCO/pazqZxjakZQlPSV76Lrvra6v1S/UapxXQ5jwd4JsvByag8N1c3l3fzmW4url9zuMsVB7EgMct1YkngYA8cHiXX9f8Ajlpup2ekvHMGaCztNQ/c4gUSJIWIGQQfOJ+8VYFfm24P0VXkvjOC3uPiPpXiLSvGXh2yutOT7Ncw3lyhZAGfcNufmJDupUlSMcEE5HdlOL9pWrSrrmlOLV3ey02suj0XktFuRUjZKxwifFxrL4iah4ks9KElrdxC3aCaXa5Rc7WDAEKc4JGG7jPetzVvj9fRa6yaVpdlLpcUpXdKz+ZOgY/Mp42blxgFTg9c9K47/hFNNfxhqeh2HijRo9JHlsL+9eM5jLA4jbGC69DtK7sc4BIHR+J/Ds2s6rqUiePfBt3bXcquLi8mt0ucBVABdIyVwFA+UgHBOBuIr34YTJ+eNqatbrz+W+m+/X/gYqU7bnQ6FrviK9+PF8ILZ1tZ7OI3FpdTsv2a38uNlO3HEgL/AHMHDSOM4JevZq8uX4a6/onifTdY8M67bROLO3sr/wC1wZDpEsaEooB4YRgldykEcPzx6hXy2bVKFSVOVBqyilpe+mmt/wAPLc6Kaavc+ffDeoS2/wANfHHjmFUj1u9vGgMiAgQrIyFjGQdynMxP3jyienObqPhT/hAvCfhXxzpmozPqMssMkkTjEZ8yMyBRtIO3aCjDJ3Bj93pXSeGtLgsrrxN8KdXimtotQlkuNKnkQsZABlXLKQDgRIwHAyrqSD8tW4/hP4svZ9K0rXfENte+GNOn3R24ZxI8YPCkADkj5RlzsDHaex+neMpUasueajFvms18VPksku+t1bQx5W1ov+HPTfFPiSy8KeHrrVr10AiUiKJm2maTB2xjgnJI9DgZJ4Brxn4T+JJ7j4oard6zqUMUmq23meWboGOSVnjMaLljllViqrksoyvGCK7+y8B6jqGqeIY/Ft3DquiX1z59laPNK72+HYrtYkeVhW2kLnPTIAw1Gw+C+g2njK41KSCGbR/KjNrp7l28uUEbixLHcvy5wcg7yCAFGfGwlXL8Nh61CpJuUlulddGktd779NNzSSm2mjH+z6vpv7SVkL3VHuY76CWSIKSoW3KSlYivTCsme+SAx5Jxe+I8EXhb4geGPG8cSRwmf7HqErKCoUqVDbV+Zm8syc8/6tRjsep1DwbLe/E7SfFgvEWGxs3ga3KEszHeAQc4xiVifTaOu75eO1uSH4i/F3TtKitHuNG8OtIb6UxgL52eUbdkMpaNFxjJ/eYyORpQxEa1anVv7kaTU7K38yt0V3pbz7iasmvPQ9fpaSlr5Y3EoPalpDQB5z4JJHxM8dRkH/j4hbP/AGzFejV5t4Kfd8UvHI7edD/6ABXpNImOwUUUUyhaSlpM0AFFFFABRQKDQAUUYoxQAVXvEEtnOh6NGwP5VYqpqLFdOuWXkiFiB+FAnscL8EM/8Ku0/J/5aS4/77NejV538FBj4WaXyDlpenb94a9EoBCUUGkoGLRR9aKAClpKM0ALRSUUAFLSUUAFec/Eog+KfAaHodWz+QFejV5x8ShnxX4D/wCwt/QUCex6OKWkHeigYUtFFABRRSUAFFFHagAoo5ooAM0tJRQAyT7jfSvPPgmwb4cxAD7tzMP1r0OT7jfSvPfgoP8Ai3kbf37qZh+dAup6NRSUtAwooooASlpKWgAooooATNLSUtABSGlpDQB5yuD+0B9NCf8A9GR16NXnER3ftATY/g0Mg/jJHXo+KBIKKDRzQMKKAKKAFpKWigBKKKWgApKKKACvNPjcvmeD9OQHltWtwP8Ax6vS681+M3zaJ4ej/v69bD/x2SgUtj0oUUCigYtJS0lABRS0negAooooAK5jx34Ni8ceH10yS8ezeOdZ45VQOAwBXBXIyMM3cc4PbB6elrWjWnQqKrTdpLVCaTVmeQSfB3X5XjeX4h6k7RkFC0Tkqfb99xTpPg/4hnKNL8RdTcxtuQvFIdp9RmbivXKK9D+2sb/Mv/AIf/Ik+zieTx/DG60W8ufEmreKrzWLi0sZ0hE8ZBG5GXlmdjtAZuBjk5z1B6L4TRmP4ZaJg53QZ/U1veK22+EtXPpZy/8AoJrK+GKbPhroA/6dFNceKxdbFTU6zu0rbJaeisgjFReh1o6UUUGuYs4Dxp8ULDwl4k0rSv3M/mSg6i25t1rEcYOAD83O7HXC9PnBG3qPj/wrpV1a211rtkstztMYR94AYKVZiuQikMpBYgEHOcVwPxsjtbLXvCGs3mn+fZw3LLeMIQ3mRho2EbE8HIEmFJx973ry7xlp0Vv4v1+XVv7QspbmeS8sU+xgidJGZlLbnUoOgPDEHcCAVIr6/AZNg8ZQoyd4txle2t2pW7dPTa3qc8qkotn0Zq/xE8JaG8SX2u2waVQ6rDumO0gMCfLDYBDAgnGQcjNY+r/FHTdJ8e6ZojzWTaZdWwllvxPuETvkx5xkBSADk9pFbIA+bwfxHpNjps0EWpHX7PUP7Mt38q9tkk8yXYRgNvUpEAEUcMwwwIBXFdHZSf8ACNXPgLxTrGiTDR4LF48Rxbsy+ZOyNh24Y70kBJAPJXgYG6yDB06cZpubkpK2iu+Vtcv3ea79he1k2fSleVjxBqWt/FLVrhdams/DHhaJmufs6cSuF+dZFOS3KychTgR/LgsGPqEEy3EEcyBwsihwJEKMARnlWAIPsQCK8d8M6fLJ4r+KXhqRkh1LU1kkt0kJKlH83DFlBAGJ4zjr83Tg48HK4Q5K05LVRS72TklJ28k3r0NZvYq/8Lb8c/2V/wAJJ/wjFl/wjv2ny/Mw+7buxjdu/wCA+Zs27uMZ+Wuv1LWX1C5v9Qt9VuotMttOF/GbcEF4hGr8KSvJDZ5+n08pm8XS2/wvHw7m0PUI9bM6xhXQglWlEy/IRu3EkKFxyCDntXW2FxcNq+teCIrYT3sfhoWkc0Dlkll+zRDGSoCqSSAzEDoOpArqz3JlXVNU6SilNt2la9JW95692ttfI8zGUp11CCu1zK+ttLP062OZ0Hxp4r8R3cNuwju7aSZIZLeK6AnYEjlI3lBYDOc42gA5KgEib/hLfGM1tq194bgluPD+mysv2lfMUFM/e27genzEAfKD83rXLJHpsmj6ZpOlaTqNv41gvT9ouCxjChS5wMv8hX5CSVXbsJJGDW7pfitvAvgvxJ4O1PSrj7deGUQyggRssiCMtkjJUBdykZDZ7da9Wtw7lyrOpSw8XPRKLbXu82src2vk9Ot0Qsvw3NzuOtrXu/uK1t4r1BfE48QWuoT2mmXElrbalMHJwWUnkDDOVAkweT8p5wwFe423g26td32bXJod2N3lxlc46Zw1fMWna7bweEdd0wpDJLdXNq0ZaMsUVBKXZT/C2Si+pDMO9fRnwrv55vDaW+paxZ3upNiZ44rgSyxqRx5hycsepr5jOcrwUqVKaj8LnGNm7uCejut+qu9XbyZr/ZmGqNc8fhWmr0/E3/B15cXmjO1zM8rJOyKznJxgHr35Jroa5fwL/wAgSb/r5b/0Fa6evCy6TlhYNvoa5TJywVNyd3YKKDRiu09Ap6bpNnpMTx2kW0OxZiTkn0GfQdB/jmrtFJUwhGEVGCskRTpwpxUIKyXRC0lFFUWGKKO9FABXnPxBw3jfwHFzk6hI2PYKP8a9FrzzxoQ3xN8Bx4/5aXTfkqf40Ey2PRBRRR3oKCijFFABSY9KWigAooooAKKM0UAFFGAaKAOP+KTbfhjrx/6dv6itXwigi8HaNGDnbZQjP/ARWJ8WW2/C/XfeAD9RXReHE8vw3piYxi0iH/jooJ6mpRRRQUFFJQCM47/SgDyv4+5/4QWyz/0E4/8A0VLXlnii50HWtdvbyHWbfyXlUxjyJlyvccJwPfqTX1DeWVpqNq9re20NzbyY3wzxh0bByMg8HkA/hWV/whXhU/8AMs6P/wCAMX/xNepTxODqYaFDExl7jbXK0t7d0+xFpRk3E+d/EWq6H/wriw0bTtUS6u0vvPkhWGVQi7XGdzqM9VHX0r6kAxWPD4R8NWs8c8Hh7SYpomDxyJZRqyMDkEELkEHvWxU43FUKlGnQw8WlDmerTetuyXYIxabbCiiivNLCo5ziCQ+impKq6icabdnpiFjn8DQBwnwRGPhdp59Zpz/5FavRa8/+C4x8KNHOBy05/wDI8legUCWwUUtJQMKMUUUAGaKKKAAUd6SloAKM+1MzliOeOacM0AL2rgfhp8114ukIxnXbgfkcV31cH8Mh8nip+58Q3g/JqBPc72imbh7/AJUUDPN9I2/8Lz1sjqNOiz+delZrxa813UNC+NOtS2Gh3Wqu9nErRwHBUYBzzXRH4ka+v3vh7rX4MppIiLsj0fNFebj4k68TgfD3W/xI/wAKB8SfEDHA+HutfiQP6UXQ+dHpGaM15wfiN4hAz/wr3WP++lo/4WN4iz/yT7V/++1ouHMj0eivOR8RvEH8Xw+1n8GWl/4WPr3/AET3W/8AvpaY7notFedf8LH17/onmt/99LR/wsfX/wDonmtf99pQFz0WivOh8RPEB6fDzWv+/q0f8LF8Q5x/wr3WP++1oC6PRaM153/wsLxFnA+Hur/9/Upp+IfiXB/4t7q3/f1aBcyE0vB+Ous47aXFn869HBrwLTfGGsx/FLU9TXwjqD3MtnHG9kP9YgHRifSu3/4WPr3/AET7Wv8AvpaSFF6Ho1Y0PhLw1bTxzweHdJimiYPHJHZRqyMDkEEDIIPeuT/4WPrwPPw91vH+8tH/AAsnWeP+Lf67k/StIVJwuotq49D0WivO/wDhZOrquZPAOvr9FBoHxN1Aj/kRfEOf+uH/ANaoDmR6JRXnY+Jmon/mRPEP/fmj/hZepH/mRPEP/fmi4cyPRKK88PxK1TPHgPX/APv2KQ/E2/GQfAviLI6/uM0BzI9EFFee/wDCz7kAFvBPiQeuLQmm/wDC05QefBfib/wBb/Cgd0eiZr57+Gng3w7rvge+1LVdLe7u4bx41ZJpFIQRxkDCsB1Y9u9egj4psevgzxOP+3Bq8Q8PyXyeF7gabP4miuhclv8AiWo727AKvDBT97+mK9nAVqlHAYidKTi7w1Ts/tdjObXMrnWaF4c8Gap8S9S0xrNBpsdqjW8LXEo+fjccht2fbNbHjnwB4W0j4faxqlhpIt722ljSJxcStt/eop4ZiDwT2rx+9OsXmpNJNPeyX0arjzoCJgfw5/Gt208VahB8Pda8P6na6lJcXlwspuJgxVCHjJ3E9/kx+NGW5ljJ4ylGVWTTlH7T7rzCUYcj0PpXwX/yInh7/sGW3/opa3c15H4Y+K+l2HhnSbCbSNbL21nDCXjsyysVQDIPcHFbX/C3dH3Y/sbxF/4Lm/xrzcV/Hn6v8ylJWO9METTpOYkMyKyLIVG5VYgkA9QCVXI74HpUlee/8Lf0IHB0zXlPvp7f40H4xeHwcGw1v/wBP+NY3Kuj0KivPh8ZPCwXMw1GD/rrZsKP+Fz+Dv8An6uv/AZqQcyPQqijgiieV44kRpW3yMqgF2wFyfU4VRn0AHauCHxo8GE8306/W3anD4zeCSedUkXHrbv/AIU7i5kd/RXBf8Ll8DZ/5C5/78P/AIUD4y+Bj/zGMfWF/wDCkO6O9oNcMPjB4Gb/AJjsY+sUn+FPPxb8C/8AQww/9+pP/iaA5kZvg3B+K3jkjH+tgHH/AFzWvSK8T8MfEHwtY/ELxXqNxqkcNnevCbeUo2HwgB7eoNdyPiv4G/6GK2/75f8AwoJi1Y7OiuPX4peCX6eIrTn13D+lSf8ACzfBf/QxWX/fR/woK5kdZQK5VfiT4Mfp4jsPxlxUn/Cw/B//AEMenf8Af8UBdHTUVzP/AAsPwf8A9DHp3/f8U5fH/hFuniTTfxuFFAXR0lFc/H448KSrlfEmk/jeRj+ZqT/hM/C//QyaP/4HRf40BdG5RWMPFvhxl3DX9LKjuLuP/GnjxPoJ6a1px/7ek/xoC6Naq96/l2M8n92Nj+lVP+Ei0U/8xfT/APwJT/Gqmpa/ox0y7A1awJ8l+BcKex96BNqxzfwTj2fC3S2/vNKf/IhH9K9CrzH4Natp8Hwz02Ca+to5Y2lBR5VBH7wnpn3r0Iatp/8Az/Wp/wC2y/40Ami5RVUahZkZF3AR/wBdBTxd27NtE8ZPoGFA7onopu9fUfnRvX1H50BdDqKbvX+8PzoEiHowP40BdDqWm5FG8UDHUlG4UZoAK85+I3/I4+AR/wBRRv8A0EV6LmvOfiCwPjjwEMjA1CQ8/wC7QJs9HpabkVQv9ZsdNurOC8m8uS8l8qDI+82M4/SgZo0lJvFG8UALRRkUmaAFzRRmjNABRRRmgAopKXNADZf9U30rz74Jf8kwsD6vJ/Ou+uWAtpSeyn+VcH8FsD4YaZ9ZP/QqBHoVFJmjPtQMWkozRmgBaKbmlzQAtFJmjNAC0UmaKACg9KKKAPN9OXd8fdYb+5pEQ/Mj/CvSa830rn486+RzjS4B+tej5oEhaSjNGaBi0lJmlz7UAFFGaM0ALSUZooAWim59qXNAAa82+MB/0Lwsvr4gt/8A0GSvSAeTXmvxbPmS+DYf7+vQfyP+NApbHpfNFGaM0DCikzRmgBTRSZozQAtFJkUuRQAtR+cnneVvHmY3be+KdmjjOcDNAC0UZooAwPG7+V4H1x/Syl/9BNQfD5NngDQhjGLRaT4iSCP4ea+xOMWMo/SrHgkbPBOjL6Wkf8qCepv0UZpCaCj558TfEnxnFr/iD7DrVva2un35tYrUWyMzAFwCNyNnAjLMSR1444HsHw81y98R+BdL1XUGRruZHWRkXaGKSMm7HQEhcnHGScADiue1n4LeGNa1m71OS51KCW7lM0iQzJsDnliNyE8nJ69+MDiu20DRLLw3odrpGnq4tbZSq+Y25mJJJYn1JJPGBzwAOK97MsVgauGjDDxSldfZSslGzTfW71MoRkpamlS0maK8E1CuW1fwFpuqeLtM8TRSzWWo2coaWS2O37SgBAV/0BPdcqexXqaM1rRr1KMnKm7Npr5PdCaT3I5oUuIHhkGUdSrDOODXCo8HhjX9Q+x2bGzsrWNPKjBJSIeUCQOScDn8K77Nee67cfZPE2oNIZo1nhVFaMckYXkZ7fKR+FeVmE4w9lOTslJfkzy80qRp+xnN2Smr/dIdrPxN8BS6dPZ3XiG38u5jaJxHG7MMjB4CnH41806p4m1GSN9Fk1L+0NKilATqA6qTt5OD09a9Z1bw5p17A628YSU5+ZlxuPqSMmuCuPhbfvITDe2wBP8AEW/wqv7Swn/PxF/2xgf+fiOINxGbN0ClHLDAUcY75/Su8+DOlajceP8AT9QhVo7S33tLITgMNpG0f3jnHFVYPhbqokzPdWRX0V35/wDHa9N+HmlWfhK6ku9QaSaYrtVYFBVRx6kela1c5oVeXnqp8qsvJISzbAL/AJeI9L8C/wDIEm/6+W/9BWunrlfBUscOiS+Y6pmdmG4gZG1Rn9DXRfbrUdbmHjr84rLLf90p+g8ossDSv2LFFUzq2nDOb6146/vl/wAab/bOmdtRtP8Av+v+Ndx6N0XqKof23pf/AEErP/v+v+NNOu6QnLapZD63C/40BdGjRWZ/wkGjAZ/tewx/18L/AI01vEugr97WdOH1uk/xoC6NWg1jHxb4cQZbXtLH1u4/8aY3jPwun3vEWkj/ALfY/wDGgLo3K858XHd8XPA8fol2f0X/AArpG8d+E1/5mPSvwu0/xrzzxF4x8O3PxZ8LXkes2j2dpbz+bMsoKqW6An8KRMmj2UUVy/8Awsbwd/0Men/9/hSj4ieDyOPEenf9/wAUyro6eiuWPxI8HD/mY9P/AO/tMPxM8GDr4jsP+/lAXR1lFcgfif4KUZPiOy/Bif6U0/FTwP8A9DFaf+Pf4UBdHY0Vxh+LHgYcf8JFa/k3+FMHxc8CH/mYYOP9h/8ACgLo7b60Vw//AAt7wGP+Zih/79Sf/E0f8Lf8B/8AQxQ/9+pP/iaAujuMiiuGHxh8BkZ/4SCIfWGX/wCJpF+MPgMk/wDFQRD/ALYyf/E0Bcb8Y3K/C/V8dwg/8eFdfpXGj2QHTyI+n0FeP/FH4k+Ftc8EXWm6Xqq3VzMy4VI3HAPOcgV1dl8XfA8Wn26vrkassSgr5MmRx9KCb6noVFcEfjL4EA/5DYP/AGxf/Cm/8Ln8Cb8f2z+Pkvj+VBV0d/RXn5+NHgUDjWM/SB/8KQfGrwKTj+1nH1gf/CgLo9Borz7/AIXV4FP/ADFz/wB+W/wpW+NHgUDI1gn2ED/4UBc9BpK88/4XZ4Fz/wAhST/vy1P/AOF0eBduf7YP08lv8KAuegUVwI+MvgQjP9tj6eS/+FM/4XT4Gzj+1mPv5D/4UBc9BqjrL+Xol++cbbeQ/wDjprjH+NPgdf8AmKO30gb/AArO1n4x+DbrQNRgt76VppbaSNF8huSVIFAXRq/Bnj4T6L/23/8AR8ld7Xifw6+KPhTw/wCAtL0vUL6SK6gRxIoiJxmRj1H1rqv+F1eCP+glL/34agSeh6FRXnf/AAu3wN/0Epf+/DUh+N3gb/oJS/8AfhqCj0XtRXnX/C7vA2f+QnL/AN+GoHxu8DE4/tKX/vw1AHogpa88/wCF1+Bhx/aj/hA/+FP/AOFz+Bsf8hZv+/D/AOFArnfnPbFFefj40+CD/wAxOT/wHb/Cj/hc/gfdxqj/APfhv8KAuj0ClFefH4z+CFOP7Tlyf+ndv8KUfGfwQempyf8AgO3+FAXR35rgfhQ/m6Rr83/PTXrx/wA2FI3xn8D7sDVWb6QP/hR8IZVufCV3eIpVLnU7iYZ64Ld6XUV9T0DAoooplHm2hn/i+HiH/rwhr0jFeb6G5Hxw8Qoe9hDXpIpIiGwUUUUywooooAMUUUUAHWijFFABQKKKACk6UtIaAPNtLwPjxrOeM6ZER7816VXm1iMfHrU8NkHSos8dOTXpI5pExCiiimUGPeiiloATHuaMUUUAGKMUtJQAYo7UtJQA3JrxL4Na1oll4Nu7TVdV0+1Lag8nk3VykZZfLjAOGIOMg/lXt+K4e4+E3gee5llfQkV5GLkR3EqKCTnhVcAD2AAFengcRhoUKtDEc1pcrvFJ7X7tdyJJ3TRxVn4j0i2+LWuXf9qWP2KSxj8qX7QnlM46gNnBNUPHGs6TfeFNWFtqlpLPIIsRJcoxfEqHgA5PAz+FTWvw+8OT/FrUdE/s/Omw2McyQ+fJ8rE8nduz+tdxD8HvBIXMmiEn/r6m/wDi66MNUyuhWhWTqPlae0ejv/MRabTWhueC0P8Awg3h88g/2bb/APota6EdKZBBFbQRwQRJFDEoSOONQqooGAABwAB2qWvIqz56kprq2zVKyEopaKzGJijFFBoACAeophiRuqKfqKfS0AQfZrc9YIz/AMBFRtYWjnLWsDE+sYq1RQKyKTaPpj/e060b/egX/Cm/2HpH/QLsv/Adf8Kv0UBY8r8H6Npx+JvjW1k061aKOSEohhUquUB4GOOtegf8I1oWSf7G07J7/ZU/wri/B24fFrxxn+9B/wCi1r0igmKVjIPhXw8xy2haYT6m0j/wph8IeGj18PaSf+3KP/CtqigqyMI+C/CxHPhvSP8AwCj/AMKjPgTwkTk+GdI/8Ao/8K6GigLI54eBPCQ/5lnSP/AKP/Cmv4B8ISDnwzpI/wB20QfyFdHRQFkcs3w58Guct4a04fSAD+VNPwz8Fnr4csP+/ddXRQFkcgfhd4Ibr4csvyP+NRv8KPAzHJ8O2v4Mw/rXZ0UBZHF/8Kn8C/8AQu23/fT/AONUdS+E/geHS7uWLw/CrpC7KRLJwQD/ALVehVS1T/kEXuenkSfyNAmlY8k+GXw38J6/4A0zU9U0hLi7nEheQyuM4kIHAOOgrrv+FOeAj/zL8f8A3/l/+KqL4MA/8Kq0bPfzcf8Af1q7+gElY4N/gz4CbpoKL9J5f/iqgb4J+BW6aS4+k7/416HRQOyPO/8AhSPgb/oGy/8AgQ1J/wAKQ8D/APQOm/8AAhq9FooCyPOv+FI+Cu1ndD6XLU3/AIUj4MxgW94v0uTXo9LQLlR5v/wpHwf/AM87/wD8CjSH4I+D9uBHfD3F0a9IooDlR5s3wS8KEjbLqif7t2f8KX/hSvhzGBqOuD6Xv/1q9IooDlj2PN1+C+gx/d1XXwPa+x/SuO8X/DfTNN8W+FLGLUdWlW/umjkM11uZABnKnHBr3mvOfGo3/FDwHGennzt+IiNAnFDh8HtGAwNb8RD6agf8KguPgrod06vcaxr0zp9wy3u4r9MivS6KB8qPOh8H9NUYXxH4lX6agf8ACg/CGx7eJvEw/wC4gf8ACvRaKA5Uebj4RWytkeK/EwH/AF/mnN8JVA+Txh4nX0/09jivRqPpQHKjzofCy4UEL468Uj6X7/40f8Ktuu/jzxWf+4g/+Nei0UDsjzv/AIVddf8AQ9+K/wDwYP8A40f8KvvAcr478UD63zH+teiYFFAuVHnZ+GWoEf8AI++Jv/As/wCNH/CstSxx4+8S/wDgUf8AGvRKQnCk9celAcqPN7n4Z3620xbx54lKhDkPdEjp9a5b4a+BbrWPA9jfQ+LdesFl3f6PaXJSNeewzXsmsvs0S/fptt5D/wCOmuT+D8fl/C3RMfxRM3/j5oFyq5WHwz1FTkePfE343ZP9aYfhnrOcr8Q/EQ57zE/1r0aigfKjzZvhjrp6fEbxAOf+eh/+KpR8NfEAGP8AhY2v/n/9evSKWgOVHnI+G/iAf81F1z8h/jR/wrfxAf8AmomufkP8a9GooDlR5x/wrjxCDlfiLrgPuAR/Oj/hXXiPP/JRtbx/uj/Gqnxn8Wa34b03TotIjubYTTiR9QTaUBXkRdzkkBjnAIUj5gWAZr3xttNCjtreTQL3+12ijkubOeQRC33Lu2l8ElsFTjaOG52sCo9Wjk2Lr0oVKK5ue9kmr6dX2/q+6IcoJtM0T8PPEPG34i62Pqqn+tA+HniMf81F1r/v2v8AjWVq/wAeNFs7K0m03Tbm8muF8wxSypF5S7nXDFS5DZQHbj7rA57VjeI/izf3/wDwiWo+HYL1Ee5cXdku0+fKuwGAHBLfLJwduP3iEfMuF0pZBj5tKUOVO+r7pN+vQHOCOs/4V34j/wCij6x/36X/ABqC68Ea1Z+T9q+KOpwedKsMXmhF8yQ9EXLcscHAHNekQSNLBHI8Lws6hjFIQWQkfdO0kZHTgke5ryfU7ODxn8ef7L1GPfYaFYib7NIS8c7na2dvAXmVM9dwiAPBwOPB4WNec+d2jGLk7a7dvVtIqTS2MHR/ButXXxQ16zTxjqMdza20PmXqKPMkDdFPPQYrtf8AhXviX/oo2sf9+l/xryXTp9e8X3/jLxPputXOk3FrD9seGGVk8yIFiIy6Y+6qnGRyeuMk17x4I1m68VfD/TtRnkeC7uIGjkmj2lt6s0ZkAK7QSV3Y2kDOORXTjcqlhIc7mnZ8skr+62r28/VERakzEHw/8S85+Iur8+kKUz/hXniQHI+I2tf9+1/xrgvF2i+JfDOraNpEHxE1a91LVJ1ijiaeSJYlLBQ7kSswBY4Hy84bnjBj+ID+PE8falaaNdeJp7eGK3Km1Mu0gxKN+IwFG5lfoAMhvQ110shjVceSurSTd2mtml1t1f4EuaW6O6l8E61b3VvayfFDU47m43eRDJs3y7RltoLZOBycdKn/AOFeeJe/xG1n/v0v+Ncv4psLLxJ8JtO8UaRqdzqGr6KsZOoGPF0QpG9H2nKlCwfJ3EBc7juLn1vw/rEWv+H9P1aHYFu4FlKJIHCMR8ybh1KnKnpyDwK8/FYH2FJVE76uMtLWa/HVfqXGzdjiz8N/EWMf8LG1z8h/jR/wrnxJgD/hY2tf98D/ABr0eivOL5Uecf8ACuvEv/RR9a/79D/Gl/4V54m/6KPrP/fpf8a9FNGKA5Uec/8ACvPEuf8Ako+sf9+l/wAaUfDvxGP+ai61/wB+1/xr0WigOVHnX/CuNfb73xF1049MD+tcP478Eanp+reFIbjxfqt9Jd6msEcs7c25OPmXnrXvtebfEr954t8AQDvq/mf984NAnFIefhrrX8PxD8QAn1kz/WgfDjX8Y/4WLrv6f416NRigfKjzpfhvrgzn4h68c9eR/jTx8OtbCYPxB18nudwr0KigOVHAD4eaxjH/AAn2v/8AfQpn/CuNXOM+P/ER/wC2tehUUByo88Pw21U/8z/4j/7/AFKnw01HGH8e+JW+l0RXoWKKA5Innv8AwrG97+PPFH/gaab/AMKuu+3jvxSP+35v8a9EooDlR54Phhd4wfHfir/wYN/jS/8ACr7g9fHXiz/wYNXoVFA+VHjfjj4e/wBl+C9XvpPFfiO7EFuzeRc3zPG57AjuK0fD/wAMWfw/p7N4u8TRh4FcxQX7RoMjOAOwroPiqwj+GWu5Gc25H5muj0EY8Pab/wBesX/oIoJ5Vc5Jfhei9fGHi38NVYU0fCyDPPivxUf+4o1d/RQPkRwA+FGn458R+Jzj/qJt/hQPhPpuMHxB4mP/AHE2/wAK7+igORHn3/CotI/6DniT/wAGTf4UjfCHQ2H7zVNeb3bUW4r0KjFAcqPPf+FPaBnJ1HXSw6E6g2RTh8IdAzk3+uE476g1egUUByo8+/4U/wCHSuHu9ZcH+9ftSL8HfDG7cz6ozdyb5+a9BxS0Byo85f4KeCyGaW1u3Pq90xrFb4LeETKxFpdBSeP9IP8AhXrky7l21AluqsWI4AoDlR4V8M/hh4b8RWGsXeqWssvk6jJbQr5xUKigenfk16CPgt4EXn+xyfrcSf40nwijx4Xv5+P3+q3UnH+9j+legUCjqtTg/wDhTXgI/wDMBT/v/L/8VQPg34CXn/hH4z9Z5f8A4qu8ooKsjhR8HfAQ5/4R6I/WeX/4qpB8IfAf/Quwf9/ZP/iq7aigLI4ofCXwKhyPDlt+Luf61IPhT4GGf+Kbs+f97/GuxooCyOQT4XeCIxhfDdif95Sf5mpP+FZ+Cv8AoWdO/wC/Irq6KAsjlB8NPBQGP+EZ07/vyKUfDbwWOnhnTfxgFdVRQFkcwPh34NH/ADLGlfjar/hXB6r4S8On4z6Jp0eh6elm2my</t>
   </si>
   <si>
     <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAgGBgcGBQgHBwcJCQgKDBQNDAsLDBkSEw8UHRofHh0aHBwgJC4nICIsIxwcKDcpLDAxNDQ0Hyc5PTgyPC4zNDL/2wBDAQkJCQwLDBgNDRgyIRwhMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjL/wAARCARDBdwDASIAAhEBAxEB/8QAHwAAAQUBAQEBAQEAAAAAAAAAAAECAwQFBgcICQoL/8QAtRAAAgEDAwIEAwUFBAQAAAF9AQIDAAQRBRIhMUEGE1FhByJxFDKBkaEII0KxwRVS0fAkM2JyggkKFhcYGRolJicoKSo0NTY3ODk6Q0RFRkdISUpTVFVWV1hZWmNkZWZnaGlqc3R1dnd4eXqDhIWGh4iJipKTlJWWl5iZmqKjpKWmp6ipqrKztLW2t7i5usLDxMXGx8jJytLT1NXW19jZ2uHi4+Tl5ufo6erx8vP09fb3+Pn6/8QAHwEAAwEBAQEBAQEBAQAAAAAAAAECAwQFBgcICQoL/8QAtREAAgECBAQDBAcFBAQAAQJ3AAECAxEEBSExBhJBUQdhcRMiMoEIFEKRobHBCSMzUvAVYnLRChYkNOEl8RcYGRomJygpKjU2Nzg5OkNERUZHSElKU1RVVldYWVpjZGVmZ2hpanN0dXZ3eHl6goOEhYaHiImKkpOUlZaXmJmaoqOkpaanqKmqsrO0tba3uLm6wsPExcbHyMnK0tPU1dbX2Nna4uPk5ebn6Onq8vP09fb3+Pn6/9oADAMBAAIRAxEAPwD3KGaMW0ciRSKGUbVKHdjtkdvxrnrLx1a3uGj0bXlgaPzIpzpsnlyjGQFwCfzAra0+SY2wilbdJDmORliaNMj03cnqOckHBrnfhg9zN8PtJkuZ3nmIlEkkj+YxYSsPvZ5Axj8BQDLOp+OtM0eKwlv7a/gN67hEkgw42AE5BPuMAZJJwBmqU/xItEKNZ+HvE2owugkW4tNJk2HOeAWxz+nNdXeypbRvOzoD0HmzlF/rz+FVo7uO4giSG+/eyLxIgzkc9M8Z470BZnEH4iiaa3EngTxdAIGymNJB2jGM89Pwq4/xEa4diPCHjMCMEhRphXzOPXP+FdgbopNsQu5IByVwOQccn1I7Cp4w20NIR5vDMqucE4x+VAWZxFr8SLdYwX8I+L7ePjMsulMc8YGSCSe3NIPizZssuzwr4tcRZ80rpf8Aq/r83H/1q7su5fPCqh+Y/hTROWwyAMDgj5ucH2/z0oFZnERfFKxkuBEPDfisxgbzN/ZZK7cZycHOOfSi4+K2gg8Wuu/K21wumv8AJ9cj6V3vz8EYx3GKYAQo+due5AzQGpwo+KvhZkjG7VyHfC/6BPkt6ZA5+lK3xj8GxkLJeXqE9A1hMD/6DXdbwvDuoP0xinkkEZxigNTgG+NHgfZk6jdAHv8AYpv/AImkHxr8CZx/aswOf+fKb/4mvQAeM9R60EknAH40Bqefj41+ANuTrbgjsbOfP/oFP/4XV8Psc+IP/JKf/wCN13xJHp1rzT43yxx+AoVkgjkMmoQKnmAHack5H4Aj6E0BsXf+F0/D3P8AyMH/AJJXH/xFB+NXw8P/ADMH/klcf/G67iS1tpCplt4mx0LKDg0hsrVnLNbQlmOSSgyaA1OJHxo+HzDP/CQDj1s5/wD4ipT8XvAAZQfEEOTwP3EvH/jvFdZLpenzoFmsLaRR0DQggfpVY+GtBLhjommlvX7Kmf5UBqZFr8TvBN4haLxLp6gf89pfKP5NirX/AAsDwb/0NOj/APgbH/jVtvCnhx/vaDpZ+tnH/hUB8FeFWOT4Z0Y55/48Yv8ACgNSP/hP/Bx5/wCEo0f/AMDo/wDGnf8ACeeD/wDoaNF/8Dov8aX/AIQnwn/0K+i/+AEP+FH/AAhHhIn/AJFbRP8AwAh/wpBqH/CdeETz/wAJTon/AIMIf/iqX/hOvCJ/5mnRP/BhD/8AFUxvAng912t4X0YZ9LGIH+VRv4A8Hyo6t4X0cBuDtsowfzA4/CmGpYHjfwocAeJ9FJ9r+L/GrA8UaAz7F1zTS/XAukzj86xZvhd4JniEbeGrEADHyKVP5gg1Wf4P+ApHLt4eiyf7s0oH5BqQanbCaJhlXU/Q07zE/vD864I/BT4enk+H/wDycn/+Lpv/AApT4e9tA/8AJ2f/AOOUwO+3p/eH50BlPGR7c14N4D+G3hLWdd8YWt/pbTw6bqTW9sPtEi7EBbjhhnp1Nd1/wpP4ff8AQBb/AMDJ/wD4ugNT0AAE54/Clx7V5rcfAvwNKx8qyurfI/5ZXTnH/fRNVm+AXhItlLrV4h3VbkYP5rQB6nz2oxXlSfATw5GpVNa8RIhOSFuowP8A0XVyL4O2cUPlReMPF0ak52pqIAz642UBqek4pa86/wCFUnjHjvxkP+4p/wDY0f8ACqWB/wCR88Zf+DT/AOtQB6LiivOm+Fc+Pk8feMR9dSJ/pVE/CvxBg4+JfiMHnGZW49P+Wn+fagLnqeKK8p/4Vb4uRcR/FLWQe2+Jm/8AatTJ8O/G8Spt+KN8dhyN9gG/PMnP40Bc9Qo59K82Hgbx6rAj4nTfL0zpUZ/9mqT/AIRT4kDhfiTGfrokFAXPRRQTXiiSfEl/iHL4S/4TmLdHY/bftP8AZcOCNwGNuOvPrXQTeGPikBmHx/ZsfR9LiUfyNAXPS+1GOMV5dJoHxeTiHxnpMvvLZKv8ozSrpfxmQ/8AIweG5R/tRMP5RUBc9QxRj8K81jtPjHF97UfCUv8AvLMP5KKlH/C31H3vBr/+BFAXPRaO/SvPTL8XVH+p8Gt9Dc0w3HxeHS08IH6NP/jQFz0WjFebm9+L6/8AML8LN/uyzf1NV21n4xIT/wAUxoMg/wBm4I/nJQFz1GkrzCHxF8WlGZ/AumyH/pnfxpj85DU//CVfE4dfh1Bn/sLQ/wCNAXPSKTFedf8ACYfEVThvhrn0xrEP+FB8a+PgcH4Yy/hq8R/9loC56NniivJ9L+KviTWLu/tLDwBPNcafJ5Vyi6kn7p8kYOUHoelaL+PfGcQ3P8M77/gN+jfyWgLo9H6Vk+J7OfUfCes2VrH5lxcWM8USZA3OyEAZPA5I61w5+JPixT83wy1fn0nz/wCyVw/xE+JHii6h06E6ZrPhaMO7u28q0+AuNrAKTtBORnB3DPQV25dQlXxMIRaT3u9tFfp6EylZFG68MeJNV+HmgxS+GNTWPQrmeOeHaUnuY5nV90aFSwxypO0gZBG7DBatt4F1BtD1a/PgfVmh8+3jt0muWW7hUHMpVBGBIGGF3FPl3AgNtYjl08da/K0ix+KNfJHK5unwenX95x39ew78e06f8W9YGk2O/wAD+Ib+X7NEZbpLYqkzbRl1AUjaTyMdjX1WIzmdDDqrQcZRcntzqzupNa23b37O22hgoJuzOI8O+BvEOo2fii0stAvNPt7ixjEK6moEjSLNG4QSFEJyEk6ALnbu6A17H8NdS1K98J21pqWg3ulSadFFaKbkY88JGo3gEBh09McjBPOMSH4uSHIuPAviuM4HCWG7nv1Iqb/hb9qP+ZN8Y/8AgrH/AMXXg4/OJY2DhOCWqa3utEn11ul1NYQ5Xoyj8ZP+Jdf+D/Ec3zWem6mPOROZGyUf5QeDxC3Ujkj8Kmux694Z+JUvjfQtHfxBpeq2ccTC1+YjKrjaU3HH7pG37duGx1wau6n8T9G1fTZ9O1HwN4tntJ12SRPpgwR/384IOCCOQQCOar6F8RtE8N6Ha6PYeD/GQtrZSq+Zp4ZmJJJYnf1JJPGBzwAOKdDNIUsPGm43aUotPZxk77p3TTBxu7mLoTeNvDHh/WPFVtoLy6vrmqqX097KVjHGBKzSbFbeoLtgbugAPO4Gp/E+mappPxKu/Etx4HfxDYanZoI7UxiU27hYwd4VXAYbCOMghuGOCK6T/hcmmg7f+EX8VZxnH9nD/wCLqKX426FA5SXQ/ESMCAQ1kARnp1bvVf22/auq6a95NPVq60srp6WstRcita55tY+AvEXh2z0LWtS8PXOt2hnklfRU3ExEouxnUAkFioJG0jEaq3J2jsfBjXuja54m8bajob+G9AFmE/s0/ut0ihMbEIQEnDAEgZaXAzlsabfHvwqmd9hra465tV4/8frD8S/Fj4d+K9OhsNYsdaa3WdJ12xBDuXtkP0ILKfZjjBwRvUz54q8MRGylo2r/AA3vZRva/nuJU+XY6L4LaZP/AGBqHia9uPOvNduWmcjAGEZxkgAYYuZDxxjbjHNem968Gn+PdjaeKNNt9NsfL8MxwiGdGg8uSPkgFApICqoXA78+2Ovg+OfgSWMs9/cwnsslq5J/IGvGxuJeKxE6zVrvRdlsl8loaRXKrHpQo6V5yPjf4DMpjOrTAD/lobSXB/8AHc/pTh8bPABcqdacADO42k2D7fcrlKueiGjtXn4+Nfw/Iy2vFcjobOf/AOIpf+F1/D3/AKGH/wAk5/8A4igLnfk4orgf+F0/D4/8zAP/AAEn/wDiKX/hc/gD/oYU/wDAab/4igLne4pK4UfGPwCf+Zij/wC/E3/xNOHxh8BE/wDIxQ/9+Zf/AImgLncjmj6Vw3/C4PAWAf8AhIoeeP8AUy//ABNOHxc8BscDxHb/AIxyD/2WgLnbUuK40fFfwK3TxJafjuH9KX/hangb/oZbL8z/AIUDOx70Vxw+Kfgc9PEtl+JP+FSD4neCSM/8JLp//f2gVzraO9covxK8Ft08T6b+MwFOX4jeDGOF8UaX+NyooC51GOODSKCFAJyfWud/4WB4O/6GjSP/AAMj/wAaUePvCBwR4p0b8b6If1oC6OjqreW63MBVoY5SpDqr9Nw5B/A1kf8ACeeEf+hp0X/wPi/xoPjvwiOD4p0Qf9v8X+NAXHeH/DWn6BLey2dlFby3MimRo1xvAUAf/X98mt/Fc9/wnnhA8f8ACU6L/wCB8X+NH/Cc+ER/zNWif+DGH/4qgZ0Bo71g/wDCd+Ef+hp0T/wYw/8AxVNHjrwhj/katD/8GEP/AMVQB0FH4VgDx14RH/M1aJ/4MIf/AIqg+OPCI4PirRB/3EIv/iqAN+jGawP+E68I/wDQ1aJ/4MYf/iqP+E78If8AQ1aH/wCDGH/4qgDfAwaK5/8A4Tnwh/0NWh/+DCH/AOKo/wCE68If9DVof/gwh/8AiqAOh6jFJjFc/wD8J34P/wChr0T/AMGEX/xVL/wnXhH/AKGrRP8AwYw//FUAb+KOprnf+E98Hscf8JTov430WP50h8e+EFJH/CU6NxzxfRH+tArl7xNq39heGNU1QPCr2ttJJH55wjSBTsU8jOWwMA5OcCvDPDvjPx54is7u4Txxo9gLXBlS/jijbaSAGH7kgjJA65BxnGRn0vxN458Kaj4W1iwtfEelyXVzYzxRJ9rQBmZCANxIA5Pc18wfasWf2fzHCNIH2hwFY4IBIx8xGeDnjLY+8a+t4ew9Gth6l4xcuZatRdl6P+mzCrKzR9B/Cz4iXWrQ63H4n1qwdbJo3iuZNkG5GJVj0UbQdmCQDl8HqAOoHxO8L3Wj6tf6ZqcN0+nWzXDQSboC/ZQC6jOW2rkA4LL6jPzFpM2nxR6kmoz3say2brCtrIi+ZLuUosgY/NHuAJAyeAR0rS0e60bTNZuPJunmt59Nu4FnvoRbmOV4JFXaFkYckhcscfOeBgGvSxuQ4J1KtVtrls7KyirJXv2v8t9LkRqyskfSfgDxpb+NfDkd7mGPUIvkvLaNj+7fnBwedrAZHXuMkqaj+JXiiXwl4Kur+0lSO+kZYLUvGXG9jycdMhA7DPGVGc9DwPwq+IvhHRfCEGk390unXcJeWWWSMBLgs7EEMuckLsB3YPAxkDiD4xeM/DfiPwja2ej6xbXdyl8kzRxsc7Ajgnnrywr5/wCp0Y5yqEo2hz6J9unyfTy03NuZ+zv1KFnZav8AC7VtJ0/Qd+o+JNZs0N1p0wJhhO4nOFIDEYIDbsKEkJ4cbfQ/AHjrVde1nVdA8SafDYazY4kEUKsA0fAPUsOCVIO7DBwQMDJ4DxX4/wBBi+Kvh/xXpt7HqVpb2pgmhh3JKn+sBOGA7S5AzyVIO3rVHTfiTYW3j/xL40EKDzrZLe106WYrLP8ANEu7IUgYWIsfTIAz1r1a1CWPw3tZwTlKPxbP2nPZQ7LTTVfPqZqXK7J/8MexeP8AxnB4K8OSXuYZNQl+SztpGP7x+MnA52qDk9OwyCwrmNU+KOoWfwm0vxVDp9t9uvp/s5jdmMSMDIGbAwSD5ZwM8bhycc+a+O/ENp4uvo9ai8VaasaWPy6VdRyFraRo8SRp+6KMxPSQ7TnHTaprCh8Q3DeFtM0W+8Ro+hi6Hn6VZrtuUTezMSSgVu5ALkZK8ccRgsrwToU+dxc+dcybd9n7iXfT5u+trDlUld9j1nw/468R+LdSu/CmoC2srm8s2e31LQ5UnFrjOTIRI4APAyCrAkYwWDCT4I2cEP8AwkRv493iWC+aG9lkJeQIe2/kHMiyE4PJAJz8tcZ4f8b+FdA+I9pdaEbrRfDc1qY7+G6JfzJAJCrY3OepjAI5HPYnOh4S8f8Ah3T/AIkeKdd1DV47Cxu22W9vDbSbLkbuJioBw2FycjJMrHjkUY+EKVGvThHkjywduvNe1mtbXWtrtaJ9xRbbTep790oz7VwH/C6/h6P+Zg/8k5//AIij/hdXw+/6GD/ySuP/AI3Xxx0nf9Bmlrzx/jX4AC5XXWY+gs5/6pUEfxx8CtGSdSuVIz8rWkmf0GKBXPSKWvLz8evBQTdv1E+gFt1/WmSfH7wcrBY4tUmJ/uWw/qwoC56maK8uX48+FnbbHp+uOf8AZtAf/ZqnT41aE7bE0TxGz/3RYZP/AKFQFz0rFHtXnLfGDTx08LeLG+mm/wD2VM/4XFY/9Cn4t/8ABaP/AIqgLnpVJ3rzkfF60JAXwf4vJPTGmD/4unD4tW7Z2+DPGRxxxpY/+LoC56JRXnb/ABUmwPK8A+Mm9c6Zj+pqA/FXUyfl+HXir23WZH9KAuj0uivM4/ib4gmB8v4b+IBgfxrt5/FaUfEbxY33fhnq/wDwK4A/9loC6PS8ijFeWaj8UPE2lafNf3/w6vbe0gGZZXvlwozj+771NZfETxhqNnDd2fw3uZbeZBJFIdSRdykZB5WgLnpuRQefavOh418eN0+GU346xD/8TR/wmfxAJ4+GMn/g6h/+JoC56LRXncniz4imMmL4bBW7FtbhOPwwKZP4n+JzgfZvh5bRHv52rwvn8iKAuej0ZFeXS6/8X3IMPg7R4hjkS3YfP5SClj1f4xPnPhzw9Hg/xzn+klAXPUKK8yTUPjC3XRfDSfNj5pn6evDdP1qwLj4vMP8Ajy8Irzj5nn/oaAuei0V5153xgzxbeDh9Tcf404SfF8nHleCx/wCBP+NAHoeRRXnUifF+UAibwZFg/wAIuefzBrmvFF98XPCugXeuX+taA1rbbd0dvES3zMFGN0Y7sO9AXPas8Zoz7V5Na6X8Y7q2jn/4SjQkWVQ6j7PkgHn/AJ5Vag8PfFl3X7R430yNcc+VYI/80FAXPT8ijFedHwv8S2OR8RIF9ho8NJ/wivxK6n4jw/8AgmhoC5397eW+nWNxe3Unl21vE0sr4J2ooJJwOTwD0rwTUPG/w21Lxivia407xEbsrtlhUReTN8hT5135IK4BUEKQMEEE56nxN4b8fW3hXVprvx8t1apZzNPbjSYU8xNhyu7ORkZGRyM14nF4w8T2eipotpq7rpJgeN7YRx4Cuzb1yRuOck56jPbivocnhGFGVblk25KHuu2jTb6PsZVG27HtvhX4XeBNYSx8T6f/AGhPZTMZo7K6dTEpBI2Mu3cQrAjBYg7eSwPNo/Anwj9v+0ebqflebv8As3nr5e3Odmdu7b2+9nHfPNYXw78L+LdS8C6ddad45l0yyfzfLtE06OXy8SuD8xOTkgn8a6geCvHORu+JlyfppUI/rWONzPHUMVUpwrStFuO/RN2+fmEYRcU7GrJ8ONAbxrF4qiFzbXyN5jR28vlxSPggswAzk55AIDdwctnqp4IrmCSCeJJYZVKSRyKGV1IwQQeCCO1eat8NfFBkmc/EzWczAhtsWAMnPA34X8MVCPhP4g3Av8TfEhHcLNIM/wDkSvKq4irV5faSb5VZeSNEkth/gfwpq+lJrXgfxDp6aj4cK+db3rMQrBz9wLnKnILYGCjAnJ3K1anhj4S+HvCuuRavZy6hPcxKyx/aZVKoWGC2FVcnBI5yOemcEUB8KdSzz8RvFmPa+b/GrP8Awqqbv4/8Zn/uKH/CuytmuJqObUuVT+JLZu1m7efWwlCKOg8H+CtN8E2FxaabPeSpPL5rG5l3YOAOAAFHTrjJ4yTgYtaN4X0vQdS1a/sInSfVZxPclpCwLc8AHoMszfVj2AA8q8f+EL3wp4ZGo2PjbxXLObmKELPqTFfnbB6AV1Q+FBxz488Z/wDg0/8Asa5KmKrVJSlOTblv527jUUjqrjwtpd34qs/EksT/ANpWcDQROshC7WzyV6EgM4H++c5wMcf4M0DX9T8c6l408TWiWUm1rOxsXPmNAoIBZWJwowGGR9/e7AAEbpx8KR38deND/wBxX/7Gg/CmMgg+OPGpB6/8TXr/AOOVrTx1WFOUN7rlu91G92l6/wDDA4pu56EOfajB9eK8qk+Anh2Zi0mu+I3Y9S13Gf8A2nUZ/Z98LEjfquvN9bmL/wCN1xjPWsd6PevN/wDhSPgkbsWd5zgf8fb8Y64579/rxip/+FLeAhx/Y0v/AIGz/wDxVAHf7h6ijev94V5//wAKS+H566GxP/X5P/8AF0f8KS+H4/5gLH/t8n/+LoDU9A3r6j86TzUHVl/OuA/4Un8Puf8AiQn6fbZ//jlKPgp8Psf8gE/+Bs//AMcpBqd2biL/AJ6oOP71N+1264DXMWT/ALQFcMPgr8Pj/wAy+R/2+z//AByuK8efDXwjouo+FINP0jyV1DWIre4X7TM3mRHqOWOPqOaA1Pbje2wPNzCPq4qGXVtPgjMs19axxjq7zKAPxzXHD4MfD5CSPD4P/b3Of/Z6l/4VD4A6f8I9Dz/03l/+KoDU6P8A4STQzaLdrrOnG3ZiizfaU2kjqAc4zwarv428KRHa/ibRVPob+If1rET4QeAYxtXw7CeO80pP6tTh8I/AXbw5B+Msn/xVMNTXPjnwiD/yNWiD/uIQ/wDxVA8d+Ee/ivQ//BhD/wDFVl/8Kq8CtGU/4Ry0xnr82ePfNXE+Hng1JI3XwvpJKR7Bm1Ugj3BGCfc80DJ/+E78IHj/AISnRP8AwPi/xpT468I4/wCRq0P/AMGEP/xVH/CC+EP+hV0P/wAF8P8A8TQPAvhH/oVdD/8ABfD/APE0CGf8J74PH/M0aN/4HRf40f8ACwPB3QeKdH/8DY/8ak/4Qjwp0HhfRAP+vCL/AOJpf+EJ8Jgf8ivov/gBF/8AE0BqRf8ACwfBv/Q06P8A+Bsf+NH/AAsDwd/0NOj/APgan+NS/wDCF+E8Z/4RfRT/ANuEP+FKPBXhTH/Ir6L/AOAEX/xNAxLu1vJvDN+q+VLqEltLGjhOGJBwOp4yfX8qy/DVinhnwPpmkC6sZp4B5TEP+73GQmTA6nBz+XarfiVCvgLXIorVnf8As64CwheWPlnAGOv4VQ+HkemW/wAPtAOniMQPbhz5shypYkyAZHOGLCjqHU2ZrOztbgX8geWbcZVVcsxOMcc9OfpUhe4W5Mgsl8122BjLwqjkEg9u3Hcj6ifM7XZC2iBY8qkrsMgYB4Azxnjt92n7ZxBJ9oaB+MBiOOvp+XfrQUQQzrGHldgTtGWkbk/h/nrUxREjUAy4c5KjOc5B69qZLJCjyM95Fg8gO44GBkfT6561aCrGRyd7cDIOM0xCMXwwQjO8Ahhng49/enBiFK8EkYAHH/16ajHeQytlBkHsRz39fWnEsAPkAX1zmgQBmWUrs2qehAzk4708kj5Qucdyaqw3kVxqFzaBG8+12lgRgEMDhh6jgj6g1aUBUBVeF7Y5/WkAql+QwU+hHej+LAznqfSgkjnkflS8kkFTx0JPBoAO/wBP1p/4/jUfVcvgcc4bpSqVKAqcrjqO9AAWwRnuccV5v8arb7b4S0qDesXmaxbr5jc7M7hn9a9I4w3HGfTrXmvxqAk8O6BG7mNH163VmHYYk5oE9j0w43e4FHTjH/1qacAgnqadk56UDA/hTehA5P8ASndceuKCMnk/hQAEjufalz7UlGfcZ9KAF4NGQD1o70A0AJz6flRx6Ue9L6AUABzRSYPP+NL+HFAB1oxigdKOvPNAHmHwrx/wlPxCxx/xPJP/AEJ69P4rzH4VZbxJ4/Y4512UfkzV6dgnqaBITP0pfekIGMjFAPH+FAyMTRPcPAkqGZFV2jDDcqsSASOoBKtg+x9KlrwG1n8SaN8ZvE+ozXlncXGn2Mt3ehYiqXFsqIyxoOSjY8oZycYJJfBDUdI+NfiubxPbtcxw3NncSxxNYW1rkgEqD5XO4ucHAZiMt06Y+i/1crzXNQkpLlUu26vZfptoY+2S3PozNMjmileVI5Udom2SKrAlGwGwfQ4ZTj0IPevnKD4x+NI/Fcf2v7MkSziKbTJI1gjB+6yl3+ZDnJyzYB68DFdV8LYdX/4WZ4zf7ZbfZI7yRb1BCQZpDJJsZBklACH6s3Bxgn5ljEcP1sNRnVrTStFNW1vqlb8fRvruNVVJ2R7MDXMaP4+0DXdS1a0sbh2i0tQ894yYtivOSJOmBg8nGcErkAmtLxNd3GneE9ZvbVxHPb2M80T7QdrrGxBweDyB1rwi/wD+JZ+zlpn2P93/AGpqbfbO/m4aTHXp/qY+mPu+5zjluXQxVNub1lKMV5Xu2330Wnmxznys970/xBourztBp2r6feTKu8x29ykjBcgZwpJxkjn3qbUNU0/SIFn1C9trOFm2CS5mWNS2CcZYjnAPHtXjWveFNN8AfEHwJN4f86GS6uRbTmR/M8wbkRm5HDMsrA4wOmAK9U8T+HPD3iGwU+IrSGW3tN0wlkkMflDHzHeCCFwMnnHAJ6Cs8Rg8NSlSnGUnTmn0XNo2tr23XcFJu66otaf4g0XVp2g03V9PvJlXeY7a5SRguQM4Uk4yRz71civbWe8uLWG5hkuLfb58KSAvFuGV3AcjI5GeteOfBvRNN1DxHrniiz077NYRS/ZdNjZt2wHlidxZg+3Zk5x+8cDjgHw/0YeHfjl4i003k135diz+fOcyPveF/mPdvmwT3POBnFdOIyqhCpWhCbvTipWa66XWjtpdL19BKbsnbcs+E9ag1/8AaA1u9tUuFhj0l7bE8RjYMksan5TyOR0IB55Ar2AD3rxG/wBaXQv2k1ZPMEV8sNpcBFDbzIiqvXoA6xk45wO+cH26uHH4aFL2dSlflnFNX6PZr719xUHe6YYpaTvS155YlFHel6UAHWkpe9J1oAWjtQKKACiikzn1pAFFLSEdKYHl/wAJ7YjxD4/v+qT69LEP+Asx/wDagr1DvXmfwpgkGr+PLreTHJ4gnRVPQEMST/48Pyr0ygSA15j8W/CeteJG0K60exgvzYSyNNbTSBQ4bYRnJAK/Jg8g8jHcj07mkHXNdOExU8LWVaCTavvtqrP8GKUeZWPmu6+HvjNlulg8E6fZG8hWBzbXC9A6uMAzEA5Qduma+gfDunT6P4c0vTp5FkltbSKByhJXcqBTjIBxkelamMnJHSjHetsVmEq9JUVCMIp391Pd6dW+wows73FooozXAWGaKMUlABnrRR26UtADea82+M4LaBoCgAhtetQQe/EnFelV5z8YQW0zwuo6t4jtB+klAmejc9hTSoJyVH1Ip3OenFHagZA8NukZZoI8AZ+6Kb9gtGwTa27HsfKFWSMgijGOgoArNp1kxJaytyTySYxz+lN/svTj/wAuNr/35X/CreM0ooApnStOz/x4Wv8A35X/AApDpWmj/mH2n/flf8Ku0c0AUP7I0xs/8S60/wC/C/4U1NC0iMkx6VZAnri3UZ/StDBpaBWMpfD2ix7ymj6epk+/i1QbvrxzTZvDOgzx7J9E06Rf7rWqEfyrW5paAscT4t8KeGrXwdrVzH4e0pGgsJ5VZLKIFSIycg44PFZHw98M+Gpfhlo9/e6Bp9zJ9lMksjWCyyPgsf7pZj7AEmus8dA/8K98S/8AYKuv/RTVW+G8H2X4beHYz3sIpP8Avobv6015hbU8v8HeLPBmq6zrq614b0a206PNzZS/2TH+6hX5SshUH5j8mOuWYqDyi1v6V4n+E2rXl3aR+H9Nh8hZJFebSE2zIis7uu1ScBUJwwU8jAzxXPzeGfE1xqnxC0KLQbnGsT/are8chYcRzmVV3n5SXV8DByGwCANxXm/DngXUL3WLMP4H1aSKCCSS8i1G5a3iuGCYUI/lqUO7ouWzkZIAZq+1nlmV1lOo3y6KyUo/yp31tu7rXqr6Xuc/NNWR32l+JvhLq+svpsXhmxjb5vKml0mLZOR0VAoLFm/hBUE9MbiAYPhTL4b8Z2t/b6n4T0X7fbSmTfDpKLF5TH5V3YIDA7gAcEqAfmIY1xnhHwrrMPjLw5LbeFdZtGhuY2vJr+INEVBBZlDRKEwA5GSxztwdwGfQ/hPa694Tvr7wlqfh+5EInkuf7UjOYD8qKACQAQQM8Etk4KjDEYZhl2BoUKsaGsrRavJXVm02vXTTqEJSbVzW8ceHfCPhzwVq2qx+F9JWaGArCyafCxWRyEQ4IwQGZSfYHg9K8vufD1p4c8B+HIrXSrO+8S+JJUeKe5gjmSKP5SqJ5g2qT5kYOQRy/PC49k+KGny6l8NdcghZFdIBOS5IG2JlkYcDrhDj3x0rzy+tb/xP8PvBPiLwxD9tvPDu1JbMhS26NUySA2TzCuFHzMJARiufKFSWHjz2s5tSvtpG8E/Jy+RVRO+nYq+F9ATSfiMvhPxhoWhXxvbbzbSa3sIQoIDNnKqp2kK4OVzlRjg5PT+MfhZLez2h8J2HhqwhVWE6XGnoWZsjB3GNxjHbAx6nI24tpJ4s8SeO7rxnN4budLOjaVKLO2ngdjcSeXIEj52sxLOx+UdAF6kE9Bq2qeM/EPwkbb4fmh1u/lNnPCEEWyJnKlwjknaVwp3YI3F+FANPE4e2JpVIqmnaKkvd5VJ36baKz06gno1qeT2UqWng3XNYvdL0S+jNymnafcLpcIXziGZnHCEKIxkBkOSycDDA7Fn4YufDfi3QtO8Z6JpF1Ya2vkBbe1iV4pGwuNyBCGVmTJBIwx2kkcdt4i+GF0PhFZeHtJRJdStJ47uVUKj7TMQVf5ztGAHOCedqKKyYpPFnxD8c+F5tU8N3OjW2jt9pmnkgdVdwVZsb9vDFEUKMkZJJYDjtU8FWjOpThBQvPm0Skkorkceur10W5NpLRkXgXwboFp8QPE3hLWNLttSa2C3NnLNErlYuOGbAO4rJFxjGQ2Md/Qb34deDI9PuJF8NaaCsTEHyBkcVyvhl08a/GrVvEUV15lhocQtbTaV+YsGTIKghkJ85gc5+ZO3A9K16b7N4e1OfP+rtZX/JSa8DOV/tClL43GLl/ia1+/RvzZrT2PMvhR4G8Mat8NdJv9S0Kyububzi8sseWbEzgfoBXZn4a+CQP+RY03/vyKofB1cfCfQsf3Jf/Rr13VeSWcoPhr4LU5HhjTfxgBpx+Gngon/kWNN/78Cup6jmjtQOxyw+G/gvkjwzpnP/AE7ilb4c+DGOW8MaX+FsorqKUUCscqnw38GIwYeGdMyDnm3BH61MPh94OHA8L6Rj/rzT/CukowKAscyPh/4PDZHhfSPxsoyP5U5PAPg9OR4W0c/WyjP8xXSUlAWPIvizpmieFfCEV5o/hvQobme8jg81tMhcopVmOAVIz8gHIPBPfBHC/Di7k1bxxpmma34e0aW0vo5CEn0W2jO1VYh1KoD1jI5yMZ46Ee9eK/Cmm+MdH/szUzMIhKsySQPtdHGRkZBHQsOQevrgjA8MfCXw94T1yLWLOa/nuoVZYxcSqVQsMEgKq5OCRzkc9M4I97C4rAwwMqdSK57S+ym7te61Lpb+vPOUZc11sTeJfB3hW08Kaxcx+G9GieGymkWRbCIFCIyQc44xWD8KPCHh+9+Gej3WpaBpl1dSiVnmntI5HYea+MkjPTFdn47bZ8PvEh7/ANl3P/opqZ8P4kg+HfhtIxgHTYGP1MYJ/U14Jp1JP+EF8I9f+EW0P/wXw/8AxNJN4D8JTQywt4Z0lVkUqTHZojAEY4ZQCD7ggiuh6dqWnGTi1KLs0OxxXhn4ZeHfDumS2ctnb6mZJ3l869t43cKeFQHHQAD6nceM4G8vhjw+n3dD00duLRP8K1qWrq1Z1pupUd29WSo20Rljw5og6aNp4B/6dk/wo/4R3RR00fT/APwGT/CtMEEnjpS96zHY5zxB4N0vXtAvNMiiisXuI9i3NvCoaM5B9BkHGCMjIJGRnNT6F4R0Tw9pMOnWNjD5UY5eVFaSRu7M2OSfy7DAAFblLWvt6nsvY39297eYWV7lT7BZ9PsVv/36H+FOWytVPy20A+kYqweKKyGRLbwKciCMH2UVgeOhHH8PvEhAC/8AErueg/6ZMBXSVxXxauWtPhbr8qnloBF+DuqH+dAi/wDD5fL+HfhsY66bAfzjBrpqwvBkRg8DeH4W6x6bbKfqIlrd70Ag70Ue9JxQMWigACigDyvWvis+mfFa10FYZjpcf+jXS/ZGMrzP91kH3mUfJjA+YMxAbKGtW6+M3gy01kaeb2aWMZD3kMJeBGGeMj5m6cFVIO4c9cZXjK01mx+MnhvxDZaHe6lZx232ZzbAHaxMitk9FwJQcttB55GCR5PcfDvX7Ke40iTwzq1zqQnEcN7bPm0Kkrg8x4IIz8xdcZ5A2kV9nhcuy3FU6bm+X3FtKOru0279tPvtbQ55TnFux7bq3xj8KaPrraTM97LJFKYZ5ooP3cLhirBskMcYydoPHTPSqOn/ABNe4+Llx4eb99pE0SR2TwW7Mxk2B95PUowLfMAVwEYYXcx8q8T+Cr631XU7ez8DazBIsqi3azme5tlQKuSCYiz7vmOdy43AEDaQe50/T/FHg74h2esy+G5tRj1PTLazlWwCqLZwkCyZCjYuDGcDKoQRhhg4J5Zl9OjenrKUHZOUd/daatdLr1/zFzzb1Paa8L0PXZZU8XfFO5uLmf7MzWWl27uQEViNiyIpAKjzIuAx53tgtg17pXgng/SG1LwB41+H6TJ/bdrePKqqRtmKMgwm4g4Lw7SxAA3qfavKydU/ZVZT2vBP/A5e9+lzSpe6+ZjeL9T+I7eAbW913UoJtH1lAojWOIMu4bk3bUBG4LuGCemDg8V65rGrXHhL4PrfWyAXVrp0EUWCP3bsEjDcgg7S2cEc4xXjnjfWfFTeA9O0DV/C9zY22juqS3pifZIUUxx4bG0DB5ILBjgjA4r0PUx4t8Y6D4w8MS6J9mjt2RNMuGiaFLhY5s43O3zMyoMFRt9SuRXoYvC0Z1aU5qEbS95RslycyUXpptfztuRFvVK5z/hL4k+JG1CO41DxFpmr2i20k91YLEYJ4o0jMjMhMSK7rtxtDMDk9Bl1gn8Z/Em38K2vjVtZ0w6XcXJC2Plxhhh2GzBUMV+Qj5XLY57EiPQtC1fXfEHg+GHwS+hDRWjlvb6aAxC6CGMlmPlqSxKHAyxy56AE1h6j4J1fX/ED21l4J1DRrue8cO7OfsMKZbOD5eAAMHIcg4O1cFVHqxo4H2zvGC2buoOyTl2aSvo7pNpWTIvKx6BeXK+G/izoOvadf3MujeLlVZYi5cyOQAh2vgqoMkRHOVG8AAYWvX/SvHfiBa2mveKvCnw306fybODElzGrg+XGifIoY7mDiNZMAjB3oTnOR7FmvlM0s6VCb+JxfryptRb87aeiRvDdoKMUUYrxzQKMUUUAFFFGaACvOvje5/4VbqMQ6yzQIB6/vVP9K9Frzz4xn/ijbVdu7dqlqNv975+lAmegRoEjVR0AxT80AUEc0DCkoOc0Y5oAinghuraWCeJJYZVKSRyKCrqRggg9Qa4o/CDwL/0BB/4Fz/8AxddzjFL3rejiq9C6ozcb9m1+QnFPdFXTdNstI02DT9OgS3tIF2RxJ0A/mSTkknkkknmrdIAFGAMAdhSkZrGUnJuUndsYUmBnpRS9aQCHkc80lKBjg/hQDzQB5z8ZQz+G9GtxnFxrdrEcdcfMf6V6NxXnfxWHmDwdBu2iTxLZg4OD/F0/OvQyRkD1oEtxcen60d/akGOSBQNxBzgfSgYvBo4oxwPaigAHBxxQfzpNvpxS55oAOg4oySO1HccUntQAew470cY5NL9KTaCOeec80AJ3xzz7V5j8UXC+L/h3COjawHx9DH/jXqB+vSvNPH0CXHxN+HUTkbRc3cvzHHKrGw/UUhPY9IIUvu5yRj8P8mnZwBxnPpQM7jR+WKYwGOlOyCcelNyOn9KDnrjpQAccYpoK52jsKcBxxgenFIQMg45x6UABYY9MDnNJkdyO3NOx82c9vSm5zkjHpQA+jr7f1pOnOabn5sE/lQA7HQ57UYPr+tKaBjFAHPa5aRSeH9TXz2iQ2bEyy3UkUQ4PUg5UepHaq/hrS9P0zwnpmmtdx3y2luYw44D44bA9M8VV8eiCbwFrxkjikf7BPtGw/KRGec4PccE45xVvwPBDF8PPDqKpjQ6bA+BnqYwST+JoF1NEW6zNl7YpGdgGXDb+hz36dOeuPpVkwQbsSfMxBVM+/NS8B9yBs4PPYmiQZi5XO3BwMc/nQUMdNrCTyt8ioduAP544pQsjffIEeBx+eTnv2p6MoD4ccHnBzig8KCGGQOefb0oAdghRt+XHT0NI8hU/NsCg9+9PBBP97igH5jlB064oEY0mLfxdBtyq3WnyLJyMfunUr/6OkrZPJBPOBng96yNZcQ6hoTsF2m+MbEj+9DKB+ZxWuQByMc/lQAd87SOO/ag5zjHGOTSKVwTwDnB4xzUvU/zoAZuA4JAPpijOD/hScgepPGOlO6g4/Q0AIOOcV558XY45rPwnFIMo/iS0DD2xJmvQzgc/5Nef/FX73gxAeT4ls8f+PUCex6ARk9AcdMinZ9/yprAHIJ4/lTguCfQ0DDjNN6ZyD19aB1J5pfXjmgBenNA6c0fhzRj2oACce1KKaetKDkdMUABznHajJGPf3pcUd8d6AEyaWkx6fpS55x6UAFJjnrQc0cjGaAPMfhOFOu+PpQ2d+vTDHoNzY/nXp/X6V5h8JFDal45lxgtr84z+J/xr04A88igS2FqKaaK1t5J55UihjUvJI7BVVQMkkngADvUhGRisLxru/wCEF8QYIA/s25zkf9MmrSjD2lSMH1aQPRHlOpap8P8AUfHc/iMeNLqG3vIPIvrFLKbFwhj2FN+3hCAuRgnIJBBwVn8IeBNG1+eF9L8eahqOh6ZeCZNOVZIWhbJZOSwKnJPzqgz82CDnHBaJrFla6fpem6V4RtNY1y5B3TXUZdN/mOBHsIwRs2HdkdevGK9J+DEDW3iPxvBJBDbvFdxo0EJzHGQ83yqTztGMD2FfW18T7OlXp4eck6Vo68rVlLl/lTT1dne5gldptbkt18Fbq/lFvd+NdTuNLFyZxaTIXPLEk7i+3edzZfb1YnHOK6SD4df2f49k8R6Vrt5Y29zL595p8Y3JcSHdnJJxtJYnBUkZbaVyNvccUYzXg1M4xtRcsp6WatZWs99LeW+5qqcUV720g1KwuLK6j823uImilTJG5GGCMjkcHtXkXhDw7daho+qfDLxXYXKLYsLu2voFUoqM+RscrwWO8gnJIMinbtxXpnhvxPpfizTJL/SJHkt453gYvGUO5cc4PYgqw9mGcHIF3UtQi0nSr3Up1dobSB55FUAsVRSxAyQM4HrSoYivhebDuPvNpro4yWzX3teYNKWp594a+EP9j+I7DV9V8QTax/Z8QjtYJoMLHjhMFnbCrkkAYwcEHjm3onwvbSPA2seGT4huXXUWLiaKEReUcKDxklg20BgWwV4G3JJg0n4oyx+CpfFXiXT0tbGe8MOnR2bGSWVckYYHABG1vmJXO0/KON2x4P8AiVofjW/uLLTo7yG4hh80pcxqu5cgEgqzDgleuOoxnnHoYmeb2nOpqotXaUbJxd1sujetvRkRVPZG/oGh2PhzQ7XSNPRxbWylV8xtzMSSSSfUkk8YHPAA4rOs/B9rZePdR8WJcTNcX1slu0BxsXG0Eg9eRGnHb5uuRtr+MvH2leBvsX9qW95N9s8zy/syK2Nm3OdzD+8P1qrpvxQ0HUvCupeIlhv4bLT2CSia3+ZmONoUglSSWAxnjIJwCCeCFDHyg8RGLaqaN97vb5tfeW3G9uxw/ge+i8WfHTWNZnsJrVra1byIZ8rJEw2w5YDuR5mVOcE45wDXtmc9K8Q8IeONI1X4ua5qcAMMmq2kUFgl6REHlVQNjMu7buIGDz+eAe8+H3jS98Upqljq1glpq+lT+TdLCcxEksBt5JyCjA8kcAg84G2Y4bFzvUqU+SMFFW7R2Xrru+7Jg47J7naUUdqDgivGNQz+tBzkUyVPMjaPcy5GMqcEfSngCgAPFGf0oo7UAJnmlopM96QC5NFJ1BpRzTAM4+lHeiloA89+E774PGDjgHxNeH9I69BzmvOvhEQbDxWex8SXh/SOvRcDHT8qBLYD6igUUpoGJS80lAPtQAfWijnNHagBaQjvR1ooAXtTe/elooAM84rzv4sNmDweo6nxPZ4Hr9+vROnFeYfFRpG8TfD+3XO1tcjkIHT5WX+hNAmen5oooHIoGFBox70UAL2pKOhoHSgApe9J1HejOO1ABk0ZorP1nU4tF0W91W4DGGzgkmZVxlgozgZ7nFAGgc4oGfWs7Q9Wt9e0Sy1S03iC6iWVA4wwBHQ+9aPNAHM/EOcW/wAOfEbnodPmT/vpSP61zWsaheaN+z3Z3en3D29zHpNkiypwyhvKQ4PY4J5HI6jBrZ+KzAfC/wAQEnH+j4/8eFKnhqPxH8JrHQbid4BNptsnmoASjIqspweoyoyOMjPI6104OdOGJpzq/CpJv0vqRJN3SPAdS8Qa7pjtbv4x8Qtdm0trqNfOdY2EsaORuMufl344U5IPAHNfS/hy7udT8IaPeXE267ubGGaSTAG52RSTgcDknpXlV18A7i7ML3fi+Sd4YlijMtkWKRr0Vcy8ADOAK9i0rT4dJ0mz0+BnaG0gSCNpCCxVFCgnAAzgelevm2KoVqMYxmpy5m7qPLaNlZbK5NOLT2LYzjn9KXPNFJ15r581FzzWHoHhHRvDFzqVxpNr9nbUJVklRWOxcDhUXoq5LHH+0R0AA26K0jVnGMoRdlLdd7a6ishaKKQ9eKzGGQagvbSDUbC4srqPzLe4iaGVMkbkYEEZHI4J6VP9aXjrTTad0BkeHPDum+F9Gi0rTIfLgj5Zjy8rnq7nuxx/IDAAFR+LZfI8G63KSQE0+duOvEZraPIrnvHrhPh74kJ76XcD84mFVUqSqSc5u7e7ElYpfDC0+x/DPw7GRjdZrL/33l//AGauuxWB4GGPh94bH/ULtf8A0Utbwz1NQMXmigUnvigBaOh6Uc0f55oAO9L1pKXIoAKKTPNIQM0ALgA0H2o70UAcz8Q5BH8OfETHPOnzL+akf1qx4IGPh/4cHT/iV23/AKKWsf4sXCwfCzXnyQDCE+X1LquP1rc8IQPb+C9CgkGHi0+BGB9RGBQLqbXNLkUntR0oGLRScDjpRQAuKBSZzzS0AFFFJzQAtFIeaD70AFcF8aTj4Sa79If/AEfHXe4rgPjVx8I9bHqYP/R8dAHb2UYjsLdFAULEoAA4HFWajRdkSr2AAp/agELkUUnWloASgnC55oNBoA+QG8beK7u4up5PEuqo5Hm/JduisxYAqqhgB1JwBwB0x0+q/DF5caj4T0a9upPMubixgmlfAG52jUk4HA5J6Vz83wk8DzzyTPoMYaRi5EdxKigk54VXAA9gABXYwwxW0EcEESRQxKEjjjUKqKBgAAcAAdq97N8yw2LhGNGLTTb1UVZWWitv8zKnCUXqSUZFJRXgmoViS+EtFl8XW/ig2u3VYYmjEiMVD5G3cwH3mC5UE9jznC43MAnNFaU6s6d+R2urP0e6E0nueY/HXMvgCK2XrcajBF+eT/SvTRXnHxj+bRvDkZ6Pr9opH/fdej1mHUU0UnNL9KBmHpHhLRdD1nU9XsbXbfalKZJpXYsRnBZVz91S2WI9T6BQNyjnNGK0qVZ1Zc03d+fkJJLYD04oFFHesxgTRmjvRQAlLR3o70AHavO/jAw/4RzR4e8+t2kY+uSf6V6JXnfxVIkXwdbkf63xLZ/l83+NAmeiUc0Y4pMGgYUUuKTjpQAUUuMDFIaADNLSUvAoAQmilNNGTyDxQAufyoxRRg57UAea/FUbtX8CR88+IIDkdRgivSj04rzX4muG8U+AICeW1kSf984/xr0rjNAuod6QEntijGeMcUvWgYnI460uM46UdaP0oAOhxSYx34pfzoxQAzJ9OtOB5x+lAIPQ0ZHGOfegBTz0pBnGSMH0peoBpMZ6igAwck1574vijl+LPw8SRAwDai2GGeRCpB/MZr0E57/zrz7xTKG+MvgGMHlE1Bvzhx/SkI9CJxnPQUYB5xxR3wef6UE4/pTGGQcgHJHvTSGJGMDGc07I7c031xn1oAcD780jDIwCB9eaTI6ZOaARu5GPT3oAOCOmPXmlXAGDgnqccUvy5/CmhSCfmzznHpQAEDdnHJowcHpk96d1/wA9Kbz2HBH4UAO5Bo4pelLQBznjt9nw98QtxkabP2z/AMszSeCxu+H/AIcwT/yCrcf+QlqPx+zf8K78R/Lx/Z0/f/YOal8GH/igfDjNz/xKrfOR/wBMloF1Nx+QSRgA9zjNKeW5H05pSiOCGAO4d/SlC9CQCQMZxQMTOT2yR09aUgEjpTFXjHJxn5jinjOT8o56880AKAVHJz700jaM8nt1608+3H4U3nJHY/pQBieKWKaXAwPK6hZH/wAmIwf0rb75GMDrmsXxdj+wo+M/6fZcf9vUVbnHP+FACd+eKdkZB6U043Y3de1Ic8nt9KAHcflTeScjA9OadjuaMcUAH481558Uz/pfggeviW05/E16CRuHzCvPvij/AMf/AIHHb/hJLX+tAmegkkE9/ancDt1oIUk5GaOew/OgYAH8c0dCeaX6mgCgBBkjpj8aKWg4HWgAx/nNHGPaigjNABnimkbh3Ge4p3eigBBgnrR3paOAPSgAOaPY0c4oHU0Aea/B7DWniuTHzN4husn14WvSq81+DfOl+KP+xiuufwjr0rNAlsHfn14qC9tINRsbixuo/MtrmJoZUyRuRgQRkcjgnpU/tmjFNNp3Qzyr/hQnhX/n/wBZ+nnRf/G6830+zi8M/wDCwLjTNSubfUNIYWdkVnCu0LXHlSMQMbiAFGeilgcBtpH0L4q8QQ+FPDF7rU0DzrbKCIkIBdmYKoyegywyecDPB6V5Ho/i3QrjxrZXuofDhrGfXn8gXksrOkolAUssbIqENuXcy8kOTzuIP1+V47H16NSdW9SGnWO8WpNWbWjWjsno9jnnGKaS0OE8OT+IbHW45IPENnZSaxFMZLm41UbMmNvnmMbllcbyV3jO/wChp/g5tRsvHOi3Nxqrp/bE4inltLxJppVlI3LJsk3IWLDJbDKfmHzLXZfFHQ9L8BQWMnhvQHtJLhisuou5mj24OYdshYZYdcgZUMvzBnAr3mveA/Bl7p9xbeBrlPEEKxzy2tzdOFtWZdwBLFgWAKsPl43AnawKj21jPrNL2lGk5e0TSso30utfe0Wq77bK6M+Xldm9jZ+AFvpyWGp3K3v/ABNJZfLa1+0f8sVCkP5eefmcjcQcdBjJz2Pxg/5JbrIJ/wCeH/o+OuEvviP4E0jV4fE+jeGHudavlaSRpJVi8oFmRiQC4WQ7M8KCVfJPzEGv43+JF14l0nw//YsV/FbXzz219aQ7d0zlURoFOCWO2Tg7cfvEOCykL41TA4vEZnDGcjim0/eto46taN6aWTaRopRUHG5J4yFvFoPwpvdQh3aXBFCLt3iLxhCsBKsMHOVV+O4B4NT6z4l8Nx/HrStYg1GzNlbWL/bLuEgoZBFN/EPvttMajGT0XqMV1PgjwRf2/hi88OeK7SyvNJjkzp6yIplVWDFydpIVgXIBDEht+GK7SePg8B+GtR+NV14fh037Ppem2Immg8+R/tLkKQdxbcmPOXoT/q/9o4uhiMJJ1KU5NqEamsbWcZO/Xrra2193oJqWj72N/wAazeCPHc/ho6hrlzaWkq3MtvdCPyYZVBCshkkXCtuQEZ7KQQC6E+e63r3/AAj9r4k8GaPJ/bnhoxRPBNJN5v2YkxsXDx4G3zGxjgbtvqwappvgq48U+ENe8R2V0ljpunTzS22mu7yBQFV3G49CE2ANgliozjGa9f8Ahn4f8Pan8LoAdGhSLVIit8rOXM7xsU3FjyOVLADG0njnmt6ksNllFJylUjCSXK7e7K/MnfTVLtdXurpCV5vseP6BcWfhb4r6et/dWGtwQm2hN80+6GEsigOj5IIizgE8YXopwV9HTULfTv2kLlbeVEFzZpb3zXciIN5RCgh5GSSIRjk5L8Y5Hgv7u61D/lhZwyyf7ZjhBP8AwJtoH+8cDuak1KG6t9SnS8iSOctvZY1UId3zAps+XaQQVK/KQQRxivXqZQqsnzz1cJRelt3e9lZaeW7s355qpbofY+o61pejmP8AtLU7Ky83Pl/aZ1j34xnG4jOMj8xWPqXjfT9L8c6b4WuYnWa/gMqXDMqorEkInJySxVh9doGdxx8w6xFZ3EcN3H4ghvJ1sbYPE9tJE6uFEfkrhSreWqLliV3dsnNdPp/9iRa14H1TxBbONGfTnFxLcK0olkikmUAlVywBEQC4O1NinIHPz/8Aq1SpQ55ycnaWii078rasnZvb5+Rt7Ztn06PY15y/i7WdT+KNzpenXVna+H9DiMmp3MiiRJPlBZS/ARlOQBkY2OTuxtr0O3liuYI54JUlhlUPHIjBldSMggjggjvXjPhmznn1n4taOkeNRvfO+z20hCPIG8/awDY+U+YnPT5155FeHllGm41p1ErxSWvS8lFv5J/I0m3okTf8L35+2f8ACJ3n9j/afI+2+f8AjjGzbv287N/445r1+CeG5hjmgmSWGVQ8ckbBldSMggjggjvXzh/wm+i/8KJ/4RbfN/a3m7PK8v5dvn+dv3dNuPl9c9sc16NbeKbu20j/AIQXSIvs/i/T9IgCC6MflNIIoyyIdx3OFZiMjblST8oNelmeUxSXsaXI1KS1bs4q3vu+y11toRCp3dzZj+I+nXHxKPg6G1eRgrKbxJFKiZVLsmB2ABBOchgRt71z+q/GG6tNZ1iz03whe6jb6VK0dxcpMQE25DMwWNgq5VsEnkDPHIHl2jaN4t8IeP8AR7a20S2XXlgkkgt5ZlZZ1KygsxEm0ELuGAV+4OMk50vGXxBj8aapHo8VzDouhSyq99crG7/aJAoBdgqhnUbQEBAJwpbbwE745HhlXiqcFUp8ibfM97u8rRd3zJe6l1v2ZPtZW10Z6Jqvj7VNP8Q+GtbhuLWbwfrapCVdQhtHJG5pJRkBlyeM4wjjAK769QOc8V458TJfDz/CrRtO8PW0NzDeXMa6XFbOdwI3bmCfeduSjA87pMn5q9X0yO9i0qzj1KdJr5IEW5ljGFeQKNxHA4Jyeg+gr5/MKVNYenVjHld5Rs9G0no2u+tn1ujWDd2i39aKP84o/CvHNDzj4OEto3iNyCC2v3RII/3K9I615h8D5Hk8J6tPNw8ms3DN7khM/rXp2eKBLYBR3o7Z4oPrQMWkzRR3oAKBQKXPFABRnmg0lABj2owfp6UUtACYIGK848fjd8Qvh6mM/wCnTn8kWvRyT6V5342Bb4p/Dte3nXpI+kS0CZ6JRmg0ZAwPXigYdeKQjIxnH0paWgBOaB0pTSdTn0oAAaOtGKOtABx2ppAIKkAgjp607FJxmgBECooCgKBwABgU4DHc0UdRigDhfjFkfCjXsf3Iv/RqV1eiRmHQNOiYYKW0Sn8FFch8amx8JNbwcE+QP/I8dd6gAjUKMADgUC6jqSjr1oxQMKQ96XtRmgA4ooFFAC0Uh9KP50AHNGMdKUUUAJ2rlfiScfDXxEen+gy/yrq8VwvxhmNv8KNddepSNP8AvqVB/WgDd8GLs8DeH16bdNtgf+/S1t9c8VleF0KeEdGRhgiwgBHv5YrWzQCAj0z9KMfhRRQAA55HIozRS4oAKKKKAE70Cg8CkJx2zQAjEjpThSUoGKAPPvjWdvwk1rHcwZ/7/wAdd7HEsMSxoMKoAA9hXn/xuP8AxanVOeC8H/o5a9CVgyBlOQehHegXUfSUtJ3oGFLSHrRQAtFJ0pe1AAaSlo5oADiikFFABwa84+NDSy+DbLToAC2parbWoB6HJLD9VFekV558WebfwgB1Piay/wDalAnsehUopKWgYUUY70UAIaKWigAooooAMUUUUAFFFFAHnPxZxIng+2/jl8SWmB7Dd/iK9GrzL4nYk8ZfD63IJB1bzP8Avjaf616aOlAuoUUtFAxKKKKAA0UUDqaACjmjFFACdqXvRRigArzb4lxmbxX4AhHA/tgSf984NeknpXn3jj958Q/AEPc3dzJ/3zEDQJnoFKaBRQMMUCijrQAE4oooNAB3pO/UUY5zS0AJ3pTzRRQAmMcdqOTS0mRigDzX4gfN8Svh3FtDA3Vy2CM9Fj5r0qvO/FwEvxe+HsWfu/b34/64j/Cu/RMO7GRmDEYB6L9KBIlo6dTQfpS9qBiZ4GKB34xQKMc0AHeg/WjpR9KAA59cU08jCtinUe9ABg456UmBjgU6mE5OB2HpQApGex49K858SPu+OXguPj5LW8f84yP6V6PjkcfjXmOvNn9oXwsvZdMnP5iX/CgTPTjz/wDrpu3kjoD6U7nPOMUHrQM5Tx/40g8FeHZbv9zJfS/JZ28jH94/GTgc7VByenYZBYVHZ/Enw1L4WtNfvNTtrWKdQHhLl5EkG3fGFA3MVLDOF6EN0INVfi7ZG9+GWq7bbz5IPLmT93uaPEi7nHphC+T6Z7ZrxDxLDa6jpXhTVPst5ZaImmpYS3MVmG/0mNpC+FLKG3Md27cM5bqysB9PleV4XG4aDndPmabXblvZLz6b9fQxnOUZaH0LN4+8KW2jR6tJr1mLOT7jK+52Py5XYMtuG9cjGVzyBXPeKPitpmk+FLPWtDktdTW5uxAIjIY22rzIdpG4EDA5HHmKeQQD4adJsk8J2t7eHX4rKXU5kt7sWyNbmLyxkiMuMSsyqD823CEAsUIqex0i6v8A4d6/JpthPcWlpqUE7XZjKu8SxzA7l3Ffl3oxC5K+YSSQAR6dPh7A02pyk5JStrorXta/e++vlbqZutJ6H1FpupWmsabb6hp1wlxaTjekqDgj+hByCDyCCDzXA/EjWNXu9f0Hwb4f1F7O71JjLdTQ5WWKEHhlbIGMLISAdx2AcA4PX+Ede03xH4ctr/SbWa1shmGKKWDytgT5cKB8pXjjaSO3UEDhvFf/ABLvjx4R1O8/d2dxbPaRydd0v71duByOZo+SMfN14OPnsvoqGMmpR1gptJ66pOya623+RtN3iQar8QvF0niPU9H8JaTDq8GjxBLq5uImMjyLw5wpQbtwICqCWKkrkcDtPAPi1fGXhaDVGRI7lWMNzFHnaki4zjPYgq3fG7GSQa8zTxJL8LPHPi59W0q5nh1edrizmiyscjAs4XcwGRiYBiM7SOhzSeA/EVx8PvCvh+3vdNeZfEWoSSoUZw8Mf7mMN5YQlyeWAXqNuOvHqYvLY1MNahTV/d5WnrP3W531tpbsvLsRGdnqxutfGjxPYeLNQ0e0stG8u3vpLWJp1deFcqCzGQKOnJOB9K7/AMT/ABR0rwbfW2n6zZXpvJbZbhhZhZI1yWUgMxUnlTztHGPpXnHiHxd4Zto/E+l654NhtvEk0tygnhtkkTey4jlDybWXPytlV5++BliKy9V+HHjfWdI8OyJpU0rwaYIZPOuI1eP99KyIQ7AjEbJx26cYwOt5dgansniIKlHbVpc2l7p3tb/Mnnkr21PaviK3l/DfxEzNj/QJRnHquKt+CiP+ED8Okf8AQLt+P+2S1nfEwM3w01/EYc/Y2+Vu3qfw61o+CxjwJ4fGCD/ZluMHr/qlr4c6Opt88cdOtHvg/gaFAXj0rz/S/itpWqfEK58OrJbLY7Fjs70SHE84+8o4xg5wpzglOC29QOihhK2IU5Uo3UVd+n9fqDkluehcUdO/1rnLXx74UvdaOk22u2cl5xtVX+RycYVH+6zHcOFJPXjg1HD8QvCVzriaPb67bS30rBIwm5o3YjIAkA2EnpjPXjrxT+pYnX93LRX2e3f08xc0e5027n17UvJH9c1wfhL4lWPibxVrOiP9miaCdlsGjl3/AGuNchmBxgn5d3B+63Q7Sx7W9u4dN0+e9upClvbRNNK+CdqKCScDk8A9KWIwlbD1FSqRtJ2/Hb+u+g1JNXRi+Kka4/sWyjGTc6rAS2egizOfzEOPxrfAYZ7jPevnbTfG+tQi88Za1dPdOoLadYs7C3jnfdEhCqTtARbnIO0nZySWBrs9F+Iviy28V6RpfjDRLXTrbVgBbyxxOrb2+6D8zc5IUqcFd4JwOvo1MjxEeblafLfru0ryST1dutiFVR6zxRjjpXEfEzxfqPgvw5balp8NrLNLdrAy3Csy7Sjt/CwOcqO9YvgH4lax4h0nXdW1m0sEsdLgMp+xMRMSFLEeWzHIIHDEqMjAzzt56eV4iphfrUUuW9t9b3sNzSlynqHToeabjOeOa8Y8NfFXxfq9/YtJpGjXdpcShGt7K5RbsjO0lY2mLcfeOVA2gklR8w3PDmqa14e+KuoeFNZ1aa+s7+Jr3T5bkBpCepUbeFUBZBjAGYwVC7sHatk1ejzqclzRV7J3ulvt2316ejEqiZ6Z1OCP61538Uj/AMTLwKPXxHan9a9FJPHFedfFI41fwIM/8zFb8fjXkFs9Fxz3zRx3FBI59utGc+9IYY9KXmjGaT6UwF+lGcjnmjr0xScUALSfWgfWl60AAOelB/WlwAcij3oATkjpQfTg0tIetACHnrQO4psi7kKkkZ7qcGhQQAM5AGMnqaAPOPgyQ2k+JmAwD4hu+Pwjr0oAY/xrzX4M/wDIC8Rt6+ILo/pHXpPpQJC5paToaWgZyPxP0y91b4davZafbPcXLpGyRRjLMFkVjgdzhTwOT0GTXhnhjw/43vvGfh59S07WDbWN1Bsa4tnjjt4o2XPLAKMKgHqdoHJwK+oOtBAYYIyK9bBZq8LR9lyJu7abvo3Hle2+hnKHM73OD+LPhfVfFXg6Gz0mJJ7qG8SfymcIXUK6kAnjPzg8kcA98A8J4o+H3i7U9fTxFN4e0zU7jULaP7VYm6ZEtZVVF4IkQtkLnhiBlhzgM3K/FiWS4+Lt1bzi4uYhJbQJCkmG2tGhKxlshcliRwRkk4616h8Bp5ZPAVykkrukWoSJGrNkRrsjbA9BlmOPUk969mnUq5fgo1KU03FJtOLWlRXtdS/urZJ6b20M2lOVn/Vjj7j4YeKbPR9EhXwxoeqtHBKZ0DmGVHdwwErrKnmFRgKQcDLDBwrG1afDXxlZ+EdDukSGTVtH1OS7t9OmmDDy2MRA3bgow0ZYqDghychuD7uKOorz3xHi2kmo7t7Pre63tbVrSz8y/YxKWjS6lPotpLrFtDbai0QNxDA+9EfuAf6c46ZbGT5jqd3b+DPjyNU1GTZp+u2Ih+0yApHAw2rjdyG5iTPTaJQTwMn1vjvVLVdG03XLVLXVLKG7gSVZljmXcA6nIP8AQ+oJByCRXn4PFwo1Zucfdmmml0T7X7Oxco3Wh4zL4L+InhfTda8NeHba2vtD1JnZZTLH5saNlSpLlPmZAobggfwkHNdVoWg+MvCureGdH04pP4ct7PGolpIgvns0jSFSV8wgFl2gAA4AJHzGvSqT0rprZ1WrQcJwi73vpu7Wu9d0tmuupKppbM+RDpt5Y33ifw7Zw2l75Bk82aYKkipbOxMkYZuGxnIG47SQO9dl4bg8XarpFvf6d4d0PxHZGCO3T+0xBNJZmJdhjGShUHAcLyMODkszE42s+Cdc1v4j+KIdL06LUJre6eSTE4jEYnJZD8zLk4PTkZHOR1ueAtQ1/wAD2vjDUYlttmmLHBeWcw3F5zIY4yGU9EO8nBwRx3DL9fKt7ehOVFwlK8Wtb3cuVO9n7rctFt2fU50rPW5a1zw5aeDvhxDoF9Z2V54u1i5SSKOKIPcWsZK/KrAEtkptwCAS7Y3BST7bpXg7SNP8Kaf4fubK2v7WzUHFzCHVpOS0m1t2CSzHrxuwOK8H0P4ma9f+Mf7SuNKttW1IwTx2Sw2O+WDKOyqmwhiu7GSxZgm/BG5s6fhH4teMNV8ZW1lcXVlLBfymFIZYkjjgLH5WU5Vm29lLEsPlB3EEcOY5dmNalZyScbzk+bdvtpoklbW3UuE4J/gfQUU8VwheGVJEDMhZGBAZSVYcdwQQR2IIrhdd8IxWvjuw8YWWuJpEjNs1FZnGy5hSMsQMnGdsfI6ALvGCnzcz+z/FqQ0LU5muYTpZudqQbP3gmCqWbd2XaUGOckfw4O7D/aAi1JdZ0iW4uYX054pBawom143GzzCx/izlMHjpjAwS3lYTLpUs0lgoVbXTTdr3Vr2s9P00uXKd4czR6No+u+BvFH27xGun2cf2G5VH1O/s0iywwEdZWH+7jJDD5cgZGeg0mbw3qWpXOo6RLpN1fbVS4ubRo3l2noHZecfIMAn+H2r5a1fxjd6n4X0zw3FbQ2ulafh1jTLPJLtO52Y+rNIQBgDfjnANTnXtS8Ka+NT8P2s2h/bLGLbHJBuDIyoXZPN3ko0iMVOTx37V6tThmc01Gbi3flTd1ZW0b897JNL5awq3kfUmp6loukzwT6pfafZzMrpDJdTJGxXKlwpYg4yEyB6LntWO9l4AvrW51l7bw1cW4lP2i9aOB08wkZ3ydNxLDqc/MPWvCPGuo6l4u8TeGL6ezs5rvULGARWcUn7tiZpE2M4f+JgSeVKhtp5Uset8A6Bo2oeINc8KeI/DEdnfrBFO9vBdyNAFUghv9YxEn70fMGPykj5ctv4JZPHC4ZVZVZKSV2o22UrO2qbt32uV7TmdrF/UrjwzdfFjSHm1p9UsLaBW0vTtIhM0Vm6DPzCLJIygYBQT0DbUUbu78OfEXwz4ltYpLbUoLWeWXyVtLuVI5y+cABc/NnIxtz1x1BA8S8L6HbjxX4x1nS1Q2Ph+C8uLCVGSWNZBv8g/Nu3gBWYHnlFOfXhPs1rBZ+ZcT+ZLcW3mW627g+XIJtpWYHp8iuwA5+ZD0Jr1Z5Jh8WlSdSV4KKW2l7vVLyabd7/rmqjjrY+zp5YraCS4nlSKKJS8kkjBVRQMkkngADvWXD4u8N3M8cEHiHSZZpWCRxx3sbM7E4AADZJJ7VBpcMXinwDpya3El4uoafC9yrqAHZkVieMYOeQRjBwRjFeQv4U8Nah8YrbQdC0xF07So2n1FhMZRI687TvdgVDGNCoAOS4PTI+XwWBoVfaxrSacE3olay9Wnq9ErG8pNWt1Nr4K+JNFsPAki6lrWnWl1NfSytHcXSRtzjnBOccV6Bc+N9Fs/GMPhe5eaC+niV4pJYysUjE4CKx6sccYGM/LndxXzNptx4Xg8DXUOo6Pfvrlwxk0+7Rykax5CjOWwQGWQH5TnkZB5HoviL7VL8FfCHiOTybLVtIlj+ytJlWaMEqmxGyHYhIpORghWI44Pp/2FQj7NuTam+VPS12rqS3vG+nQzVV6nu5xxR2qrpmoRatpNnqUCusN3Ak8ayABgrqGAOCRnB9atd6+WlFxbi90dAUYFLmikAh7UHPal70lAC0nvS0dqAEyMZooAAGAKKAAmvPfGZI+LHw7x/f1D/0StehGvO/FQz8ZvAHIOEvyV9P3PX/PpQJnohI+lIACcgAn1pcDOcUtAwxRkUUn1oAOaKXr9KQYHFABz3HNHalo/CgBOfajpRS8GgBKODS0mBQB5r8dXYfDSaJf+W11BGf++s/0r0uvNfjUf+KW0mLGRNrNtGw9R8x/pXpJwMc0CF7UnbBoH1oB9qBi0nGfrR70fjQAopKDntR3oAMij615J8TvG/iHQPGOgWWmWV4tssolITBXUSSFMS4DHgEjHXLg7eEYz678cdK0fWRp0ekXk5hl8u9Z3VDCwxuVQMh2U7geQMrwxBzXrQyTGVYU50o83Om9GtLPr/XluZupFNpnqtHWvI9b+POlafLDFpmkzX++JJJGe4WJU3IrBQV35YbirDjBUjmqt58TdRvfiR4bk0KDULrR7yzH+gKqK05ZnV26nBQpjLEAeW2CFYsahkOOa5pw5VZu7a6K9vJvpe3cPaxPZq82+OWoWtt8MdRs5biJLi6aIRRM4DyBZUZto6nHGcdM16TXzF8Qv+Kk1jxrrFw8i/2XcwafbwM5YL+8KFgcjAPluduMZlPcZPLgsGsQpyk7KK+9tpRXzb3HOVrH0pZ2y2dlBaISVgiWME9cAY/pVjBIr5y2+OP+EB/4WB/wmN5/x8+Z9k859u3zdmdudn3/AODbt29/4a9qvNRutX+G1xqdhFNFeXmkNcQRwMWkSR4SyhSACWBIwQM5roxeVPDuNqiknJxdr6SVrrX1FGd+h0dFfN/gjWvEtj4m0nUPFOteIrLRZmHl3F0ZGtpmZSUVmk+UKwyd2DjqNv31g8T+Mb+bxzr6XnifXNLhgvHggh0wM8e1CUyVMyBThQTjOSSeK7/9WqrrukqiaSvdJvra2m/n26k+2Vr2PpEXtp9v+wfaYftnled9n8weZ5ecb9vXbnjPTNT5rw/xdE9no3hP4kW1zDqGo28sQ1C605GiS7Tplj/BjaYiSozvwQuAg9st5YrmCOeCVJYZVDxyIwZXUjIII4II715OMwSoU4VIu6d09LWlF6r8mti4yu7ElFFFcBYmRRgdaWigBOKOvUGiigDzf43OT8PfsijLXl9bwKPfdn/2WvSK8++KgDr4OjPIfxPZAj1Hz16D3xQJB/KgA0uKKBiHil6UcUhAPUZFAC5zRRQc9qACijmigAFAoooAOled/FRgZPBUWRlvE9mcf99f416J+FeafEndceNPh9p46PqpuT/2yCn+tAmel8UUnfpS9aBnH+I9a1bT/G/hLT7JGexv5LlbweXkYVAV+btj5j74rr+opjozFMNtAOSMdR6U8elAC54o4phRWUq3zA9Qaf2oAKO1FFABRSGlFABR3oooA858dxiX4l/DyM/8/N2/5Rqa9Grzzxfh/i78PUJHH9oHH/bEf4V6FQJbi0UtJ0oGFBpaSgAooFHWgAo+lFFABSc9zS0UAGOK888VzK3xh+H8CsCyrqDsvoDBgH9DXofavNdaiEvx+8MknmDS55B+O5f60CZ6VxR7UcUUDCijNFABRS0lAB9aOM4pCcUvWgA5o75oyKTHtQAvekpTzSGgDzbxCN/x38HLn/VWV2/5owr0nivNdUbf+0HoURHEeiyyD2yzD+lelcUCQdqWkooGGRnjrR9fxpe9IQDQAUUYweKCD1oAAAOPT1oxzmgkZxij+VAC0lBpMZ7GgBfSvM75Ym/aJ00SOVKeHy0a4B3t5sgx7cZPHpXpn4GvPNqyftCAtgmPwxkex+0//XoEz0OkyMjv/Sjv8uMGjjIJHPagZ5d468QeLG+Iek+FfDGo21i11aNP5k0asGb94SGJVsACPjA6k57YzPDPijxpY/FS28L+ItWtr9JUk80RQKAhCM4KkIpz8g9RhvXpD4+1y18M/G3Q9Xu1cwQaad2wDJLeeo/Vhnr361maJqtpr3x90rVLS8guftMUjSCCORUiZYJF2ZkVS3yqp3bRnPQV9fTw/wDsqXsU4eylJy5deb3vtW326nO372/U995JGVoP3cYNQ3FzDZ20tzcypFBGC7uxwFA6kmiCdLm2jniJKSKHXIKnBGRweRXyB0E/0rm/GfgzTvGujGyvVKTxktbXSKC8Dnv7qcDK98diAR0RwT3JHOKTA3k4IJ4JrSjWqUaiqU3aS2Ymk1ZkVlb/AGGxtrUzTXBhiWPzZ33SSYGNzHuxxkn1qwRyOB70n059KUDnJ61Dbbuxh3o4oIGeRRzSA4r4sOY/hdr7Ahf3AXn3dRW14SJPg3QySuTp8HKjAP7sdBWJ8W1D/CzXgQD+5Q4Jx0kU1ueFgP8AhDtEAPH2CAAg5/5ZigXU1+AMk8D1rwjXLWK1+MniewXSnafV9Klh04R24wZ5IFzID2BIlVnHAJbcQNxHs3iDUZdL8NapqECo01rZSzxhwdpZULDIBBxketePaZqPxT1XwrB4iTxRp0Omyh2d7iKJTCqMwLN+66ZTHGTyOK9/JVKlCpXcoqLXL7za1eq2T7GdTWyPN9D0lJdd0uyhOs/2yL5UntLe2WKSEKx3GOQvkOoGfmVQpyScLkwXVlp0OpiCwh1O4vFvjENMvbTaSgchUZkk3FzhQVCryTg8DPufwo8W674gutdsdbvY7yWwkURypD5bNksDxhRj5BjIDc/gPT9vrz6Z7V7WL4krYXESpzheyW0tNdf5VpZrs/MyjRUldM8</t>
+  </si>
+  <si>
+    <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAgGBgcGBQgHBwcJCQgKDBQNDAsLDBkSEw8UHRofHh0aHBwgJC4nICIsIxwcKDcpLDAxNDQ0Hyc5PTgyPC4zNDL/2wBDAQkJCQwLDBgNDRgyIRwhMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjL/wAARCAQ1BfEDASIAAhEBAxEB/8QAHwAAAQUBAQEBAQEAAAAAAAAAAAECAwQFBgcICQoL/8QAtRAAAgEDAwIEAwUFBAQAAAF9AQIDAAQRBRIhMUEGE1FhByJxFDKBkaEII0KxwRVS0fAkM2JyggkKFhcYGRolJicoKSo0NTY3ODk6Q0RFRkdISUpTVFVWV1hZWmNkZWZnaGlqc3R1dnd4eXqDhIWGh4iJipKTlJWWl5iZmqKjpKWmp6ipqrKztLW2t7i5usLDxMXGx8jJytLT1NXW19jZ2uHi4+Tl5ufo6erx8vP09fb3+Pn6/8QAHwEAAwEBAQEBAQEBAQAAAAAAAAECAwQFBgcICQoL/8QAtREAAgECBAQDBAcFBAQAAQJ3AAECAxEEBSExBhJBUQdhcRMiMoEIFEKRobHBCSMzUvAVYnLRChYkNOEl8RcYGRomJygpKjU2Nzg5OkNERUZHSElKU1RVVldYWVpjZGVmZ2hpanN0dXZ3eHl6goOEhYaHiImKkpOUlZaXmJmaoqOkpaanqKmqsrO0tba3uLm6wsPExcbHyMnK0tPU1dbX2Nna4uPk5ebn6Onq8vP09fb3+Pn6/9oADAMBAAIRAxEAPwD3+ko7Vy3iHxcdCvra0TSrq9lnztS3AJ4xQJtLc6miuH/4TjWmOI/BmrE/7W0f1pq+LvE7MAPBV2M9zOopXRPOjus0Vwn/AAlXjB8eX4LfnHLXij+lNPiLx4x+XwjbgehvR/hRdBzo72iuDbWPiAzDb4asFQ9zeZI/Sl+3/EZnwukaOi55LTsaLoXP5Hd5ozXAs/xOYZWHw+nsTI39RS7fia3fw8vXkLJ/jRcfM+x3uaM1wRt/ic4x9s8Ox+4ilJ/nQum/Etvva5oafS0Y/wBaLhzPsd7mjNcH/Y3xGZhu8UaUg/2NPz/M0/8AsDx6wAbxjaJx/Bpq8fmaLhzPsdzkUV5Z4gtfG2jvp5PjESC6uo7batjEpG49RxWz/wAIh4sYDPj67GPSyiGaLiU23ax3WaTPvXDf8IT4gYfvPHmrE/7EMS/0ofwLqr8HxtrXp/AD+YHWi47y7Hbk4BqPq3yDp1J71xbfD66cDzPGWulccjzlGf0qaHwFKiqG8Va5Jt6Hzl/wouF5djq54VlIU7if0qJrFVYEShR3z3rlb/4ffbJULa/rWFHX7Sea09M8GWOnZMlzfXshHL3Vwz/p0oHeXY6BSoXjywB6GoF85mZGDIg4Epbk/hUVppEFmjCNpCDyFZshfp6VWl0C3vopYrya7ljdslPPZR+hzTHqWJrfTbV1uLqRA68B5n7046xp2Ny3cUmSAAjZyaqJ4R0JRGX06KRozlWlJcj8TVxtI0/7Qk/2SISJ0Krj86A1LhfC9unUnFNW4iKBvNQhjwQeKabWBlIZdwJzyc1GlhZw27RJBGsTEsVA4yepoDUsh1/vD86a06LxkFs4wCM1VtLaJ7Qb0Q/Q5qwtpCsgcRICO+OaBajxPEykiRSB1INIJ4y20OOmRz1pBbQDdtiUZ68daj+ywOBG1uoVTkemaB6kpnhV9hlQP6Fhmke7to22vcRqfRnAqCbS7GedZ5rWF5VxhyuSMVFJoekT3Bll0+2eYfxNGCaA1LslzBFt3you44GT1qtPq2n27mKW9gjkAJKvIARxmkOkafK8cj2kRdPu5GcVHfaDp+oyB7q3ikI6ZWgNS5BcRXMIlhmSSM8hlOQRQ91bwqTJPEuBkksBTYLG2trfyIIVii/upwKqtoelsxD2UTE4Jyuc4oDUfeaxpunDdeXtvbgruBkcDI9ao23jDQbreYNTgaNer7vl/A960ZtOsrjHn28UoRdgDKDgelOSwtVhEItohEBgLsGAKBPmMqfxjoNtKY21BGdWCtsUtgkZGcCmN418PLZy3LapF5cZw3XI/wCA9a2hbQKxKxIC3BIUcgdq4nxXZ248d+EVWJF8yebd8gw2I84NJ3Jk5rU00+I3haT7mphuO0Mn+FRyfE3wpG206kxPtbSn/wBlrqBZ2wOfs8Wex2Cn/ZYM58iPP+6KNR2l3OB1/wCIPhy/8P6hZW+ozLcT27omLVxuJB+XLJgA9CfQ9R1qvqXxCso47W30/V55Fw7TXMsJjkY5G0f6hlxgt0QfdHI/i6Lxb4lg8NfYY00lr65vHZI4lIXpj2JJyygDHr+PAH4n6K//ABLn8Lac6RMSLQzJ+7bnPy+XweT2716eGw1ecItRTV3bbXp1aej+8yk2nqzWf4jRT29kF1aVHjWT7UsEDB5PmGwqXgKltoORhAWPYdJR420mTV9Mvn1m/wBsVrKsgWx5JLxkKw2HkhcMVIGU425we2t7HRtZ0qxuG0u1kt2gV4I5rdT5asoIAHIHGOnpVqXSNOuLaO2m0+1kt48bInhVlXAwMAjAwOKwdZR0tZ69F1v/AJl8sn1Odf4k+Hkx894wPQrZy/4Vzy+OtHXw3YWzi8N2ZoLmfFrJhpBMssxBxjOQ5wPoB2r0zyIgciJc/QVVj0XS4rz7ZHptml1uLGZYFD5PU7sZycn86xpVOXfun91xuMn1OJ1r4h6Lf6b5VlJd+aLiBw72ExRdsqOcjAzwOmQT0HWiz+IelWt/L9pkvbozRqfOXTJFdWBbKYC58v5spncfv5Y8V3zWlsyTI1vEUnz5qlBiTgL83rwAOewxUVnpen6dvNjY21rvxv8AJhVN2OmcDnqaaqJUnD+un+Qcsr3ucOfiFpE+qm6mtdUaG2BS3VLGRgzMBuc8cMOUA6gb8k7sC+fiTo4UMLLWDnsNPl4/SuxihihiSKKNY40UKiIMBQOAAOwp2PaspycnpsCjLucU3xM0wZK6ZrbqP4lsGxVa3+Kuk3kLy2ul63OFbyyI7Innv3xxXekDHSuF+F3zabrkuch9YuSPzA/pU6itK9rkw+JNiyh/7G1wc8j7Ecj8M01vibp6nH9ja63+7YNXb4HpRgelGo+WXc4VvifZr/zAPEH/AIAH/Gm/8LQtcjHhzxE30se/513m2jA9KNQ5Zdzg/wDhZ8Z4Xwv4iJxn/jy/+vQfib/d8J+Iz/25/wD167zA9KMD0o1Dll3OBT4lyyHA8H+Iz9LT/wCvQfiRdEfJ4L8Rk/8AXuo/rXfYHpRgelGocsu556/xK1BeF8D+ICcd4R/Qmmn4laqBn/hAvEH/AH7FeiYFGBTDll3PPB8StQ7+BfEI/wC2I/xpw+JN+SR/wgviXI9Lcf416FiigfK+55hqfxbn0i3W4v8AwZrltCzBQ8qBQSegzV0fEXVwAW8Ca8MjI/dr/jTPjIc+FbCLB+fVLYf+PV6IAKQrSvued/8ACytVPA8Ca9+MYpV+I+rjO/wHrw/3Y1P9a9ExRiiw+V9zzz/hZOp/9CJ4g59Y1/xph+JGr9R4E13/AL5Fei4owKLC5ZdzzxfiPrB/5kPXvwjX/Glb4i6yASPAWvH/AICv+NehY5pcUaj5X3PPB8Q9dKlv+Ff67x6haYfiH4iPT4e63+OK9GwKMCgOV9zzv/hYPiLP/JPtaP0ZaB8QPEhX5fh7rOfdlFeiYFJigOV9zzv/AIT7xSVyPh5qv4yrSnx54p5/4t9qf/f1a9DxRigOV9zym1+Kuv32q3emWvgm8kvLQAzxecAY89M1onx14wT73w8vz/u3Cmk8GYl+K/jyUY+T7JH+kn+FejcUCSfc82/4T3xhxj4eajn/AK7L/hTz478Y9vh5fn/t4X/CvRsUYoHyvuebnxz415x8Pbzp/wA/C0Dxv42OP+LfXY9/tC16TRimHK+55t/wmvjjOP8AhX1x7f6UtH/Ca+Ogcn4fz49rpa9IxRikHK+55sPGvjwsB/wr+bH/AF9KKU+M/H2RjwBJgjPN2tekYoxQHK+55sfGHxCPTwA3tm8j/wAaX/hLviEV48An3zex/wCNekYpeKA5X3PNh4s+IhGT4DX/AMDY/wDGqOsfEHx1oemzahf+C44LWIZeQ3SnA/A16tiuF+MZ2/C3WfdFH/jwoDlfcyrXxj8Rb21huYPBEPlSoJFdrxRkEZHGc1P/AMJN8SjwPBMI9/tsf+NdxoAx4c0wf9OkX/oIrRosCi+55v8A8JD8TWJC+DLIY7m+X/GmnXfii3TwjYLnub1eP1r0qiiwuTzPN/7X+KW3/kWNLyB/z+jn9aBrHxSPP/CMaWPY3g/xr0iiiwcnmebHVfir28N6T/4Fj/GlGrfFQ8Hw3pI9/tY/xr0ikzRYfJ5nnJ1L4qdtA0Yf9vXWgah8VCM/2HooP/X0a9H7UUWDk8zzj7b8Vi2P7J0MD1+0GgXHxXbH+g+H09jO3+Fej5oosHJ5nnW74rHgQ+Hl9zLJ/hWDH4m+Jc/jKfwyiaH9sgthcu2W8vaSB1xnv6V7FXm2mAH9oHWm7rosQx/wNaLCcbdR4h+K+4EzeHcem6T/AOJp3kfFbPNz4dx7CT/CvRaKLByeZ50bX4rEjF94cHrkS/8AxNMWy+LBHOp+Hh/wGT/4mvR6KA5PM86GnfFZuuq+Hl/7Zuf/AGWk/sr4qbcf23oGfXypP8K9HoosPkR5x/ZHxU6/29oP0ED/AOFL/YvxQI58R6KPpasa9GoosHIjzr+wPiYRz4q0ofSzNB8OfEkj/kbtO6f8+R/xr0WiiwciPOl8PfEoEE+LdN+n2I0p8NfEZs/8VjYj6WP/ANevRDRRYPZo8l8SWXxB8N+Hb7Vn8YW9wlrGZTGLEKT7DmpNF0f4h6zoVnqTeNIIftlus6ItkDtDAEDPHrXV/EkE/DnXsDn7G1RfDOS9l+H+jG8tRbbbaNIl3bi0YUAMfTPXFFhcutjK/wCES8fkDd45jB/2bEf404eEfHgP/I+Z4/58F/xr0OiixXIjzj/hD/iDj/kfVB/68VqRfCPj0E58eAjt/oC/416HRTDkR54fB/jokf8AFekev+gr/jTW8GeOHwG8fygf7Nko/rXotFKwvZo84/4QrxwRz8QJueuLJKlHg3xrjB8fy8/9OCf416Dk7sYP1paYezR53/whPjHPPxAvMf8AXogo/wCEH8YZH/Ff3gx6Wy16JRzRYPZo87/4Qnxj28f3ft/oqUjeBfFrKM/EHUN3fFugFei0UrB7NHilvp/jGT4iz+GP+E4vFSGxF3532eMk8gYx+PWuqPgXxUw+b4hal74gQVXjIi/aAlHTztE/USLXpAoFGK1OBPgXxMW48f6rjv8AuY/8Ka3gLxLJ9/4gat/wGKMf0r0GimVyI8/HgHxDtwfiBrPTskf+FIPAHiEEkeP9Z9srGf6V6D0opWDkR58PAfiQcf8ACf6tj/rlH/hUieBfEA+9491c4PZI/wDCu9oosHIjhv8AhCfEP/Q+av8A9+Yv/iaVfBfiEdfHerH/ALYxf/E13GaKYciOJ/4QrXMnPjnV8egjj/wpp8Fa9njx1qwA6fuov8K7gUUWF7NHEDwXr/OfHOrYx2ii/wAKxPFmj+IPDfhnUdVi8Z6nNJAoZVeOPHXHpXqVcl8SlDfDvW89rcn9aQpRVihZeE/EE9lDLL441Mu8YY4hiA5H0qQeC9ezz441U85/1Uf+FdTopLaJYljkm3jyf+Air9MFBNHF/wDCG64Bx431Yf8AbOL/AOJpT4R8QEceNtRA9oIun5V2dFBXIjiv+EN1/dk+OdUx6eTF/hSjwdr4dyfHGpkEcDyYuD+VdpRQHKjiB4O8Rjk+OtSJ7Zt4f8KV/B/iQtlPHGoAe9vF/hXbdqKVhezRw6+D/EijJ8b6gW558iP+WKP+ES8UGNUbxxee7C1iBP6V24paLB7NHHDwv4lUIP8AhMbg465tU5pi+FvFAmLHxpOyH+E2kfFdp3pMUWD2aOHPg/xNvD/8Jzf57j7PFj8sVh+ErbxXrM+oNP4pnhWyvHtRCbZSSE4ySfWvUiM8ZrifA/lR+IPFkKFSw1DJAJOMqOKVtSZRSkjSvvD2qXsUITxJeWsifeaKNPmP0Iqlb+FfEdu24+NLyU55EttGRiuyJxnHWjk59adiuRHPDRNW8uXd4hnMrk+WRCoC/h3qCLRNdaMRyeJpWAfJK2qgsPTP9RXUc5HP4Um0A5ziiwciMTUdI1S4SM6frctpIr7iTEJAw7DB7Vftra7W08u7uvPkIwzBNn5Yq0c5GPrQJCG2sM+4pj5UY8tjrguWlg1SHZg4jlgyAe3Q/wCc1oQm6jt0W62zyhfnMSbQT7ZNTKS05ZS20DGD0zUhG9D1XNA7WK09i02NlzNDjtGcVHNaybG8rUJYsjqcNjvnmrkUbIMFy31pWjRwQ6gg8HI60AVvKu/NBW6VkHDKyUqQziOMCfBzliRu3e3sKckrfaGQ27KD/wAtMjBqwAOMcUAUXuLqAxxmESsx5ZcgdfpU0F2JiymOWNlOCHTH69KjubaWWWCSKZ0KE5GeCD6jHNXMHb159aAILiOaVMRXBhPqFB/nUM16kDhZIJ5CMfMse78eKryWmrRSPLb38blv+Wc0XA+mDWgrlIN0u1XAywB4zQMhguDK8x82PYrbQADlfrmreD61HHJG3GU39SAaeZFDbdw3HoM0AR7JNozJznqFrNtrLVk1GSabVVktj0hFuAR+Nax44zjNOyKBWMk2bPfXNwNiTkBEl8rJC+makRNS+yFGubc3Wclgp2gfStE4JBzxUCW8aPNsTZ5hyzg8saAsUUttXAhVr62wM+btgIz9OeKpXWlatcXys+qJDZgZKRx/vGP1PQV0BVdu0jPHeopWaOBpCjMwU4RT1oCx52mmaxZ6vdTTareXMTg+SBA3A7HgYx7VrWdmbf7I8+ozMCcvuO0sffA4HtRfapBqMqRXFvqFjJkDd5/l4+g7/lWxqFpLLZRraSgFSMGdS4P4ZGaAsTbrf+5/5Boqv/Zt/wD8/wDP/wB8rRRoGp0HauJvJBP8SdPixkxQyNXbHpXCWhM/xSlJGRDZ469Mn/8AVSZnPod3RiijpTNQoxRmjNABijFFFABRRRQAUUUUAHSjNFFAHFePGYX/AIbCk5Opx8DvXaDpXF+L8SeK/CkWRn7YXxn0Qmu0HSl1Ij8TCl96SkOe1Msa2Ce+ad83PT2puBjPcU8EHkUARRnzQSeRkjjpU3bFJj04pMgNz1NADgMCjAznHNLUcjBUJIJA9KAJKYyhgQwBB6g1HBcLcJlMjBwQwwRU2cGgCIRFWypwMY29qe2fLP07U6kYblI9RQBDaOz26M6srHqG61KykrjcR7iorSHyLaOIOz7RjcxyTTmaQNhVUqOpLYx+lAkPLqGC5GT2px5BwcVEqq0omXByMZHenuCy4DbfegY10LIRvI9xTJI5HYbZSgHYDNIgFtFh5i7di5AJpD9okLDIijxww5NABBbGDOZnkJ7yHNSMdvzSNjHQCq3kxxKXMssjdwG61LvdiCFwAfunrikAfaA7dwhGOnNPIQR7VJ46cmkMmGwY+fWnK2W6fjTAUMAMbSKUE9zS84zxRjFAC4riPEZDfEjwogTJC3MmcdPlA/rXb1xWsoJfip4d5b91Z3LcdOcCkyJ7HbAd6M0UYplnmfxc0TU9YsbAadbXE2wTRs0CF2jLBdp2jnHynn/EV45pfw813Sr9ZBY37sykFGsHDMPY9ucV9X00qCQSM46V30cbGEYKUE3DZ3fe5m4N3s9yhoNrNZeH9Otbhdk0NrHHIuQdrBQCMjitGiiuKUnKTk+polYKKKOlSAUUZooAKKWkoAQn5T9K4b4VHd4ZvD66ndfj+8Ndu5xG59jXDfCUf8UdK4GN+oXTY/7amkS/iR3lLSUUygopaSgBaKSigAopaSgBaSlpKACiiigDz34uHOh6NCMZk1e1Az0+9XoQrzv4tLvs/Daf3tbtR/49XogoJW7CjNFFBQUUtJQAUUtJQAtFFFACUUUUAFHaig0Aec+BlC/E74gkdTNaf+gyV6NXm/gTP/Cz/iED08+0I/75kr0igmOwUUtJQULSUtFACUtJRQAUUtJQAUtJRQAtcL8X8/8ACr9a/wCuQ/8AQhXc1wvxgOPhfrPui/8AoQoEzqtCx/YGnYOR9li/9BFaFZvh8D/hHtLxwPskWB/wAVpUAtgooooGLSUUUAFFFGaACiiigAooooAK810vI/aA1rpg6NFn1+8telGvM9Owv7Q2rDu2hqev/TSP/GglnplLSUUFBRRRQAdKKKKACiijvQAUUUd6ACiiigDl/iKu74d68P8ApzkqbwGxfwB4ebOf+JdB/wCixR47Xf4E1xT3spf5VF8PD/xbrw76/wBnwf8AoIoJ+0dPRRR2oKClpB0ooAKKWkoAKKKO9ABRRRQAUUUHpQB5rOQvx/tuSC+iuPr+8H+Fek15xqQVfj1op28vpM3P416RQRHqFGaKBQWBoo5o60AFGaKKAClpKKACkFLRQAVzPxBj87wDra4z/orn9K6asXxbF5/hHV4z3s5f/QTQKWw7ws/m+E9JctuJtIiTnPOwVsVzXgCXz/AOhSf9OUS/kMV0tAo/CgooooKCiiigAooooAKQ8UveigAooo70AJ0FcJ4Q8uLx34wiRSCbiJzjpyld3XD6Mqw/FXxAoI/eWkEm0fiCaXUznujuaQ470vak57imaDTjP86UkdzS44xSEGgBgOCMkAH8zSspb6U44I4pmNuWGfpmgBqhkONwAPbFN8x432ueOTngYFSYdl/un2NNMSKeWwSaBCyeWI9krDBqvCbG1dkh2x47DOKeiwAnZuJ/vdcU1beGLDrhg3VmPSgBLm9eAnZbmVccFSKLbUo7llTy5kkIyUaM8e2elWhEojKgAA+lQlzny1MJbpn0oGZOr21vDqdtqD6ZLcMpwZvOAWHrztJ56ntWuZrgwh44EYn+EyY4/Ksm+u47MWllqGZkvZfLVxgKvfB9uPerZjubH5bUGaMj7ssmAvsDQIuxyTO2JICmO+4EGpNrnd8w5+7x0rNOrQecbS5QiQryEBkGO+SBVaXV3SFzp8fnpEhI35zIfQUDLDNqtsJTFa2s/PyBG8on65zWhESyq0sQWXbzjkD2zWXpGtNf24Z7S4jKj52K/Ln29a0pZniheTAcDkAAg4oAlQuV+cDPsaiaOJH3CFSzHJPH51Sg1e0vnaJBMsgGSGiYU3TtT+3GWJvLaSNiBzgn6jtQBoq5c7gV8r1PU0qIsfC8AknHXJqmkElzIy3tum1GDIyE4OOnFWkuYHkaNHVnThgD0oAeCVbBYtn1FJ5h8/ZtY4GcjpUhzyfyzVeNpERftLpvJP3RgfrQBR1ZNPnaOO83E5+TAPB9eKqXSrfaRI+n5Zm+QS52Hr69anPiG0bVjYj5lGVMo5G7+79anvin9j3IgjPyxn91GQG+ntQBzn9laj/ei/8AA9v8KKz/ALYf+gZH/wB//wD61FOxNz0Y8A1wvh4ed8RNbkzny4o0Ht7V3L/dP0rhvBahvFPiKY8kyonHTgVLJl8SO7ooopmgdqKKKACiiigAo70UUAFFFFABRRmigDh9fDTfErwzHjhEmkz+FdxiuHvx5nxb0tc/6uwlk6e+K7gUupnDqJSGnGkxTNBp3AcDP40wYB5O0/Xipen/ANemNszhh1oAFmRuNwzTfm52g8Hv0NLImY/kHIqJGIJU+YvpkgigCzkdDUSxGN8rIxU/wsc/lULQJPKG3MJAOCDkVINyQlZZO33xQA95wjAbWPOCcdKppq1s0phmIjPqSNp/GrLXVtGn724i4HJLCke3tLscoj+4oAmUqyfI+R6g5qvfXsVhaSTz7/KUEsVUnFRrarYkNawsVPBjUgD681m+I/EQ0HSLm8ms5naOMsETBz/k0Cehs2tzHc28ckQbY6BlO3HBpl1ei3IRI5JZWGQqKTx61S0i8fUdJsbm5Escs0QcoAVx9avuZywCFETI5PXFAyWKRniDMhRj/CaqyiWYkSuYUByNrYNTFlnO1WDBT8xBpsjRiQKGcYJyF96AKv2K3EolRiSeTIxzk1df7gHmYXvjrTJUV1UZOAehp4K5UjoOgoAaGcDakbDn7zc09TJnkg/hSHc5zlsemakGfakAnOc9/SnDg0cH2NGAKYAByTS0UuKAEriNQYN8YNGXB+TTJz+bD/Cu4NcbNdbviva2ZghO3S2l83HzjLkYz6UET6HZUUUUFh3paSigA6UUUUAFFFHQ0AFFHWigAooooAjnO2CQ+imuJ+Eq/wDFBwsOj3Nw4/GVq7O7/wCPOf8A3D/KuM+EIP8AwrbTCepMp/8AIhpEv4kd1RRRTKCilooASilpKAClpKWgAoopKAFpKKWgDzv4qsRF4XHGTrtrj/vqvQx0rz34pqGHhUnqNdtcf99V6EKCVuwooo70FBzRRS0AFJS0UAJS0UlAC0lLSUAFFFBoA868Dtu+Jvj8jtNaD/x2SvRa838AA/8ACyfiESePtVtj/vl69HGcnI+lBMdhaWkpaCgopKKADNFFFABS0UUAFJRRQAVwvxgH/Fr9Zx/cX/0IV3dcH8YTj4Xazz1RR/48KBM6vQht8P6aPS1i/wDQRWh2rP0P/kX9O/69Yv8A0EVoUAtgpaSloGJ3ooooAKKKKACkpaKACiiigANea2X/ACcPqP8A2AR/6Njr0qvNbPj9oa/99CH/AKMjoJZ6UKKKKChaSiigANFFFABRRRQAUlLRQACiiloAwvGS7vBmtAjP+hS/+gms74ZSCT4beHyM8WSLz7cVreKAG8J6wCM/6DN/6AaxPhUc/DLQT/07D+ZoJ+0dliiiigoKKKMUAFFFFABR3oozQAUUGigA4oopDQB5p4hkMPx38KENgSWNwjD1G1z/ADAr0yvNPFAx8bfBZ4w0F0CfpGxr0oUER3YtFFFBYUUUUAFGaKKACg0daKACgmiigA/CqGtp5mh36ActbyD/AMdNX6r3i77OdeuY2H6UCexyXwomM/w10bPVI3T8pGH9K7WuA+DZz8OLJe6zzg/9/Wrv6BQ2CiiigoWkoooAKMCiigAooooAKPeiigBO1cNBiH4y3fbz9KT8cOa7k9K4SR/L+NEMf/PXSjn8GoMqnT1O8ooooNROaPrQaKABhxxxTcEEU+kPSgBnGScmmshPJ59qkxn7wowTwelAESAAYLEZ7UySDzJAWYYHapSqggntUZXccYGM5yKBCCB9pCuUz6HOKrSQB02xjZjILIMMc9cVcGUXAzk/kBUckUc2AXOSaAOA+ImkahPpmntp9pPNPa3kckXl4/dDueevTp712UV7LFpkZnt5mkCjcZVxz71l+N7fU38Nyy6PdyRXcbK4eJ8Hbn5vrxWpZw3D2UHmXJL7ATvOc+9JEr4i3aXUU77fLMcxQEoR2+veluJ4baQFx5eR/rCvH4ntVP8As+R23Lc/PjlgxNVZtPLyKbiSQRZ5bPJH64pll263CEyWqeeG6CKXaD/SqkutalDJGo0Z3THzESgY/CpY/wCz7X97C0zEdTy2Kn0+Sa8tJHM5AJIQgDcPc9s0AT22o21xb+aGZcHlZFIYfgeaJ5reGB7mOPzDjH7kAsaZaLeMW+0NbuFOFZVOW9z6fSokjvYdzXMFrPjJDwAoQPTBzn86ALVlf299FvhkViOGXup7g042kTR7AvlqW3MF43fWqstpaXloks8Tpt+bIJVh70230eOGUOl5eNERxG0xIHvQBqDGMDtVS9s2u0SPeBHn58jJI9j2rPm8MWsknmxXV9BJ13Rzn+ta9vAbeERmWSXH8UhyaAIIoLa1WC1ht1SNFxGqp8qAfyqY4Eb7QOPbAqbrxUDKy8DDRnJbcck+woA437VB/wA/Wk/m9FWvs0H/AEKdv+n+FFFxHWS4EbfSuF8ADOq+IWByPteM5/z/AJNdxcHbbufQVxnw4Aa21i4GP3t+/PrgCpe6M5fGjuKKKKo1CiiigAo4oooASloooAKKKKACiig0AcO2JPi7HyoaPTDwepBau3rh7QBvi5f5HK6fGQfqf/rV3FJbszp7MWkpaSmaARxSEGlxRQAzdjr0NJiMx47frSkcU3yx2agCKVEOA0hU9AcYoMMDBUlYsR0yxpxQEgNmmNDz8ob8aBimzsypzFHjqTVb+z7WEiWIvnqAp6/lUghaM71GD6inZZuCSFHUACgB8eZYj5YliYf89Mn+tUdWj1GPT53toIbu5ZdqI2F/U1dLbBlHdvY9qwPF1+bPwxeTy6sbFSoCyrCHIJOOlBMtjZt5tQSyhE1tGJtgyFbgGniCS4KtdHHooFQ2Mt1/Z9tu+ZvLUliOvFWW86YYKkevpQND1kiU+QseFHB4wKaDCAQIhnpxTvIUncw2/Wn4AUBRnHQ0ARxIRgscDtzUgCjnOaME4yaeBQAuBj1o5xRxSgUAAopcUUAFFAooAK4SMmT40TA/8s9HTHPrI1d2a4WyyfjPqRP8OkQgfTzGoM57o7qigdKWg0EooooAWkoooAKKWkoAKKKKACiiloArXpxZTn0jb+Vcb8IW3fDXSz/10/8AQzXZXxC2M5PQRN/KuO+EI/4tppRxjIc/+Pmgj7R3NLSUtBYlLRRQAlLSUtABRRRQAUUUlAC0lFFAHnfxT3+b4R2dP7ets/nXogrzz4lsp1fwWjd9ajP5A16GKCVuwopaKChKKWkoAKWkooAWkoooAKKKKAFpDRQelAHnXgE5+IXj8dxewc/8AavRa87+H4/4r7x+2MZvoP8A0A16JQKOwUUUEZ/CgYUDnmiigApaSloAKKKTNAC0UmaKACuF+L6BvhfrOTjEYP8A48K7quG+L5A+F+tZ7xD/ANCFAmdToQ/4p7TR/wBOsX/oArQqhof/ACANO/69Yv8A0EVfoBbBRzRRmgYdaKKKACjrRRQAUUUUAFHNLSd6ADvXmtupH7QtyeedBz/5FSvSu9ebxHZ+0HIP72gkf+RU/wAKCZdD0iiiigoKKKMUAFFFFABRRS0AJRR3ooAKKZLNHBGZJpEjjHVnYAD8TTldWLBWBKnDAHocZwfwI/OldXsBl+JBnwxqo/6c5v8A0A1z3wjJPwt0In/niw/8iNXSeIf+Rc1P/r0l/wDQDXL/AAruraD4WaE8s0cUflMoaRgozvfjmhtJXZF7SO6opkU0c8YkhkSSM9GRgQfxFRz31pbOEnuoInIyFkkCnHrzScopXb0KurXJ6KxNfur21utINoISjXLiTzbholIEMhwxCt8vBb6qvHORDf8AiaW11K4trfTJ7lLZlWVo45mYkqHwgSNlJ2sPvOvPXAwT0RoTnbl1ur/jYXMludDRWBdeILq21eWzNhEsSOqRyTTtEbglVOIyY/LZskgLvBJU9BzU2kXGoS6xrUdxHF9mjugsbCdmZf3URChSoABB3HngkjB6kdCajzPtf8v8w5kbNFZuvSyR6NMkTtHJOyWySocGMyusYce6793bp1HWq8MA03xBbW0E1y0M9rNJIs9zJNlkeIKQXYkcO3TGc85wMKNO8b37/grjbNr60Vh65Zahd6hZG1jaS3SKXzVGoSWo3Ex7STGCWOA/GMdeemaUkV9e6da2lrBKk1pfMl5CdTlGF8tyuZ8b2B3xMBg9QCBg4uNFSinf8tN/P/ga7icjqaD7VkaGzwtdWE8LQ3ELLIVN7JdBkcYVg7gEDKuNvYqT3BOvWU48srDTueZeMty/GPwOy9xcDjr9w5/SvTK8z8d/L8UfAjLw5mnXPttr0wdBUEx3YUuaKMUFhSGloxQAUUUUAFFFFABRRRigAqOYZgkHqpqSmNgqRntQJnnnwWJ/4QaRG/gv5wB6DdXo1ecfBvI8K36N1TVLhcf8C/8Ar16PQKGwUUUUFBRRiigAppUkjDEAdfenUUAFGaKSgApaMUUABrgdV+T4xaG23/W2Eybj7c8V31cD4kwnxV8KMTt3RXKgg8n5elBnU2O9paQUtBoBpDSijFACUdKKWgBOlB60vak4oAT+tGMjB5pT1pNo7HFACFMg5qPAHoewyKlKk4zikJw3PSgDk/iKqHwJqjv5hCxZwrlO9amijOi2bjlzBGNzHJ6Cqnjkxf8ACEasJkdoxbnIXrV3w6DJ4c04kDm3jJ/Kl1M/tls7VjKM5SNhgYA5pZZo9oi2bwV4UDj8akZMNwRjGPpUMiNJwWABGePSmWVnEDCN4oCAOnOE/SoorIKxmW7hRnPLADI9hV92uBGeV9vl5AqBWYKN4iAXn7pLE+tAzHnsJLW5DQ6lIrSyY/dlmOfUgZrRnudStGEUcsNyxwFDoQSfcjilAikYvKzLg8NGvT8auhrRyJS4JXjcxxQBT1C9uorSRZrAy54AiyRWlbTLc20cqHqPyqEzB70MJFaBIixxzz/+qoP7StYpwSZU3YAQxEbs9xQBleILqSyvopoLloWAAZc8Pk9AP610drMZrdH3I2R1U5pl1YWt+uJ4VfjgnqKq6fp02nyFBdg22fki8oDH40AahppycjPbtTiAabk4J24oAzczf885/wDv6aKl81v+en/kE/40VNhEmoHFhMf9njjNcv8ADUf8U1K2Qd11KeD710urMU0u6cdoyf0rnvhsuPB1uwGN8kj/AFyxpvdEfbOvo7c0UUzQPxopKWgAooo60AFBoooAKKKKACiig0AcRpZMnxV1kknCWUIH5mu3rhvDmG+JHilvQQL1/wBmu5pIzp7BRRRTNBKKWigBDmk59qdSYoAbjIxTQCvA6elPxRQBHyDwcZowOoAB/Kn4pMZ4xQBFtVjyjA+tcb8T7QXHhB4VKgtcRABiASdw9etdxiuB+LH/ACLdmuAd+o264/7aCgip8LO3gDJaxJ90qgGByOlSctwWI/SlRQFUDoBT8GgpbDCik8tnHrTx+dGPypcUDDH4UUYpaACijtRQAUUUtACUUUUABrhNMO74y63/ALOlwD/x4mu77VwOhHzPi/4qb+5aWqfpmgznujvqKKKDQWkzRRQACiiigAxRR3ooAKKKKACiiigChrbFNC1BhyRbSH/x01zfwpTZ8M9D94M/qa6DxC23w5qZzjFpLz/wA1h/C5dvw10IY/5dgf1NBH2jr6KWkoLFopKWgBKWikoAKKWigApKKWgBKKWkoA87+Jfza34KXv8A20h/8dNeiDpXnnxH+bxB4IjH3jq4P4BTXofaglbsKKKO9BQUUUUAFFLSUAFFFFABRilpAcigAoNFBoA8+8AnPjjx6PTUIv8A0XXoIrzz4fKR408eknn+0Y//AECvQ6CY7BRRRQUFLRRQAlFLSUALRSUtACUUUUAFcJ8YUL/C7WdozhFJ+m4V3dcR8XW2/C7XPeED/wAeFAmdPoX/ACL+m+n2WL/0EVoVQ0Zduh6evpbRj/x0VfoBbBiiiigYYooooAKWikoAWkoooATFLiiigA715qy7f2gozn72iN/6MWvSu9edSAH4/Qe2hP8A+jVoJl0PRaKBRQUFFFFAB+NFAooAWkoooAWikooAz9SieS508JPJF+/YZQKf+Wb88g+mPxPtiIyvbyX9wrYjiulaUY6p5SA/lndxyduO9U9S8Q/ZtV+xQ6a93LFhgQeQSM8AA9jjPuapXOvao+YodFmg87PmEK29uAMqQBggDrg9vSvOqYikpSs3e/Z9rehzSqQTdnr8zU1KRrnwzq0rnMckM3ljHRApAIPcHG7P+1XLfCY58C+Gv+vO5/8ARy1p6jrt0+kXFs+hzW0DwtDuOQqAjaP4QO/Sq/wx05Y/hvpljexQztbvPG2V3LuWZxkZH1renWhVXLB3as+q6+Y1NSdk9Tq7R1Wa+kZgEa5AVieCdiLgH/eBH1GKqMHWTVZjMggjky8TplXHlJu3cE4x0x077ulaYtLZY44xbxCONt6KEGFb1A7Hk0SWltLMs0lvE8qY2uyAsuDkYNXKnJxS+f33/wAzRxbRw/jPxJpKTnTb+WaCeKLzYxGqSFJWUgFuoGFLDBz9/IxhWrpY9PS/3Xtve3lrDeYkliheMrL8oXdvAYjKqoyjDgAjBya4rxf8ONT1/wASzapZ3dqscoRtkruhUhAmOAcjAzz69OM16Hpdn/ZulWdh5nmfZoEh34xu2qBnHbpXp1KVGlTjOlUbk1qnbTr26PzffcmEZczbKl3opvJLkSanffZbniW0BjMZXaFKglCyggc4YckkYJqwmnCLUZLuG6njWVt80A2FJG2hdxypYHCr0IHyjjrm7RXP7WVrGtkV76zj1DT7mylLLHcRNE5Q4IDAg49+ags9LNrdvdTX1zeTMgjVrgR/u1zkhQiqBk4z67V9BV+ikpyUeVbBYypdFL/Ymj1O+hmtIGgEymN3kVtmS+9GBJKKc4Hem/2AgsraBL+7SS3uZLlbgeWXLvv3ZBQrg+Y38PpWvQKr207Wv/X9Nhyopadpw08XBN1PcyXEvmySTbASdip0VVGMIO1XaQsKXtWcpOTuxnmPxExH8RPAUjYx9slX8wK9NFeafE0BfFPgSbuNV2/mBXpY6UiI/ExaKWigsSg0UUAFFLSUAFHeiigAo70UZoAKQ0tJ1FAHnPwgb/iVa/FnOzWrj+Yr0evNvhRlJfFtu3WLW5ug9a9JoIhsGKKKKCwxRR0ooAKTvS0YoAKKKKADNFBNJjigBTXAeMwf+E/8GFev2ibJz28uu+7V578QSY/E/g2YSGM/2iUzjPVelBnV+E9CpaQdKXNBoGKPwoooAMUUUUAGKTAz70tFACUYpaKAEAwMUe1LSYoAxvFkIn8KapGwUg20nDdOlQeDCW8HaOTjJtoycfSruvxmTw7qKL1NvJj8jWX8PpXn8C6RI7BnNuu5gMZPel1M38Z0pHHSm43DsRTyMjrQUpllco27J+YD+HNPUuDiRVCdvanc4x2pGUMpznHvQMq7vl2k8MchQOaZLmQmFoY1kP3Tjr61ZCushIAOFwFAxRvI4aNQO5BpAZb2yljLEJFk4ztON2D047cVJNJc3eITaws+MhnP3astLLGP3S4Ge9DTGSMZOwpgsVwMn0GaYFUy3FvdxCSGRjwpMcvy/wDfPpUg1m3kvFt5IWTn5Xkxgn2/+vinyiWNke3llIb5iJDkY6Y9qdFfQyMFuIQkhGC2Mr9M0AaQIIBBzUUXngHzdhOeNvpSKI7aLKnEY9T0p5Y4BGSD+lADN0//AD7x/wDfz/61FL9oH91/++aKVwM7xE4j8P3zEgfuW6j2rO+H8Yi8EaYo/wCeZOcdeTVrxc5Twvft/wBMW/lTfBYK+D9M94AeaOpn9s3zRRRTNAooooAMUUd6KADFFHNLQAlAooxzQAUhpaQ0AcP4RUP438XTEDInij9Sflrua4TwEQ/iDxfLzzqeAT/uCu7pIzp/CFFLSUzQKM0UYoAKKKKAEoxS0UAJRS0UAJXA/FFRLpuixHkSatbrj15z/Su/rgPiUvmT+FoM/f1mE/lk0EVPhO9A7UuKKWgsSlopaAEooooAKKKKAClpKKAFopKWgBD0rgfC3z/FLxo3XH2Vf/IVd6elcD4N2v8AEbxy69p7Zf8AyFQZy+JHf0UUUGgUUUUAFFFGKAClpOlFAC0lFFABRRRQBkeKTjwnrBGOLGbr/wBczWX8NV2/DnQB/wBOaVf8ZnHgnXTnGNPn5/7Zmq3w+/5J/oX/AF5x/wAqCPtHS0UUUFh3paSloAKSiigBaSlpKACiiigBaSlpKAPO/iKM+K/A+Ov9qf8Ashr0SvPfHrY8b+BRjOb+Q/8AkM16FnNBK3YtJRRQULSUtJQAUUUUAFFFFAC0lFFAC0lFFAHnvw9Ibxj48P8A1Eo//RdehV518OQR4s8dg/8AQUX/ANBr0WgUdgooooGFLRSUALSUUUAFGaKKACiiigA6Vwnxhz/wq/Wcf3Fz/wB9Cu7rifi2f+LX67/1wH/oQoEzptDO7w/px9baI/8AjorQrP0QY0DTh6W0X/oIrQoBbAKKMUUDCiiigAooooAM0UUUAFFFFAB3rzmWQp8f7YYJ3aG6/T94D/SvRu9eb3HH7QFkT30STH/fwUEy6HpFLSUUFBRRRQAUtJRQAUUUUAFFBqG5uFt49xGaAOF13XtN8N6/qWr6m+2C3iQgAZLPhAAB69a85i+Olr/wkFzqs9lcSLt8m1gEmFjj4JJHdiR+laXxQ0m68TWlzFa/69ZUlVAQN+FxtySPX9K8fX4deKS2DpoA9TcR/wDxVedQrUo86lJJ8z6+ZjRqQjdNrdn0hB440nxP4QIt9RglvWjQyRBgGDblJGPpmtf4dHPhFeel9dj6f6TJXh/gzwBcaPqCapfXMazRKdsKjJJIweRx0Jr234a8eE2/6/7z/wBKJKqjUjPEtxd/dX5sXNGVa6fQ7GiikrvNwoopaAEzS0lBNAC0hopaAEooooAMUUUHpQB5n8VVxqngqQAkrrKDj6f/AFq9LXoK82+LDBJ/CEhH3dci/ka9JU8UEL4mLRRRQWFFFFABmjNHFFABRRSd6AFooIooAKKDQaAPOfhrxr/jZMrxq7HIAHUV6NXnHw6AXxZ46jHQapkfiDXo4oIhsFFHejFBYUUUUAFFFFABSdKXNFABQaSloAO1effEv5NQ8Iy7sFdYiH516DXn3xVPl23hyX+5rVuc/iaDOp8LPQMZWgfWkHNLz6UFoWjpSCloGFFFGaACiiigBKKWigAooooAp6mCdLu1wWzCwx68Gud+G0gl8A6UwAH7sjA7YYiunvF3WU6eqEfpXJfC5BH4EskH8DzIR7iVhS6mb+NHacUhBznNGMUdTTNApmOPb0xTz9M0nOfagBpHPT8qaVz64znkU8Adqayk96AIygfjnI65GKZJbh15GT2A5FTY5GQfbHNGGB3fpmgRUK/ZwREo5+9kfpUimKYeWbcrGeCSAAT/ADp7Rs43Mxz3A44pjRgryuBnOKBklsItrLCoEYbGAOKsZ5xioLbgbfmxjuOB7CpHHQDP1FAD+PWiq20/9N/zopAYvjh/L8H6m2cfuG59OKt+EwF8J6UB0+zJ/Ksv4jHb4J1D3jxitrw8u3w9pw6f6PH/ACo6mS+NmnRRRTNQooooAKKBRQAtJRRQAUdKKKAAUh6UtNY4U0AcN8OvmuvE75zv1aXP4YFd3XB/DBvOsNbuOP32rTnH413lJGdP4ULSUUmaZoLRRmjNABRRmjNABRRmjNABRRRmgArg/H4D6/4NRsYOrA8+oU13ma4LxwDJ4v8ABa/wjUHb8QtBnU+E70UtJmjNBoFFJmjIoAWijNISKAFopM0bh60ALRSbh60bl9RQK4tFNMigcsPzpPMQfxD86Auh5rz7wES3jTx05H/MQjXP0Su9aaMDl1H41554BuIU8ZeOS0qgtqCkZPbbQRJrmR6PRUAurc9J4/8AvoUG6twMmeID1LCgu6J6Kg+123/PeL/vsUG9tl+9cRD6uKA5kT0VX+3Wv/PzD/32KadRsh1u4B/20FAuZdy1RVM6pYjreW4+sooGqWJ6Xluf+2ooDmXcuUVTbVbBRk3tuB7yij+1bDGfttvj/rqKB3RcoqmdW08DP223/wC/opp1jTRwdQtR/wBtl/xoFzLuZvjgkeA/EGOv9m3H/os1H4AG3wFoQ/6c4/5VU8ba3pbeBteSPUbRnfT50VRMpJJjIA61F4E1vSovAuixyalaK6WiBgZlBBx6ZoJuuY7Sis06/o4GTqtl/wB/1/xoPiHRh11ay/8AAhP8aCuZdzSorL/4SPRP+gvY/wDf9f8AGkbxLoaDLavYj/t4T/GgOZdzVorJPifQR11iw5/6eE/xph8WeHgedb0//wACF/xoDmXc2aKxv+Er8P7tv9tWGf8Ar4X/ABpP+Et8Pk/8hqw/8CF/xoDmXc2qKxD4v8PL11qw/wC/6/41GfGnhkDnXbD/AL/rQHMu5v0Vgf8ACbeGh11yw/7/AIpP+E38L/8AQdsP+/4oDnj3Od8ebT468ChsD/TpTn/tnXoPvXkXjTxXoF1418GTW+q2kkNteSPNKkoIQbcDNd4PHfhY4/4n1h/3+FAlJXep0VFc6fHvhQddfsP+/wAKT/hP/Cf/AEMFh/3+FA+Zdzo6K5cfETwl5hX+39P/AO/wpzfELwioyfEFhj/rsKA549zpqK5sePvCbcjX7D/v8Kb/AMLC8Jf9B+w/7/CgOaPc6aiuXPxF8IKMnxBYf9/hTD8SPB+M/wDCQWX/AH9oDmXc6uiuUPxJ8HD/AJmGw/7+0H4leDQAf+EisfwloDmXc6uiuT/4WZ4NH/Mw2P8A33UbfE7wYB/yMFoeegegOZdzM+HbFvFvjvI/5ii/+gV6HXi3gPxz4c0/xF4vnu9TiijvNQEsDP8A8tFwRkV3DfFLwWvXX7X8zQKMlbc7GiuM/wCFq+Cv+g9bfr/hSf8AC1fBeAf7dg5+tA+aPc7SiuJPxa8E5wNbiP0Rv8KT/hbfgnOBrcRP+63+FAcy7nb0Vw//AAt3wQP+Y1H/AN8N/hQPi34Myf8AicJjt+7b/CgOaPc7iiuIHxZ8GlcjVf8AyC/+FN/4W34NPTU3P0gf/CgOePc7mjHOa4U/F3wcD/yEZCf+vd/8KG+Lvg4DP9oyn/t1k/woDnj3O6rhfjA+34Xaz7xgf+PCm/8AC3/B2Mi/nPp/osvP6VyvxG+JHhrXPAmq6dZzzSzyRhVzAyjOR3IoE5xPV9EH/Eh07PX7NF/6CKv15ppHxZ8J22iWEMt5OGS3RTi3c9FA7Crw+MHhM/dmvmHqLKX/AAoBTjY72iuBPxe8M4+RdSf/AHbCX/Cmn4w+GwP9Tqh/7cZP8KA54noFFcAPi94dI5g1YH0+wSf4UxvjD4cQDdb6qCfWxcf0pqLk7IOeJ6FRXnw+LugsMrYayc85Fg9N/wCFv6LkD+y9cBPA/wBAbmizDnieh0V58fi5o4IH9ka8CTgZsDz+tB+Lelj/AJgniA/SwP8AjSDnieg0cV5//wALY00jI0PxD9PsB/xpP+FsWOcL4d8RMf8Arx/+vQHPE9Brza4BP7QVmfTRZP8A0MVYPxVswSD4e8Qg+9if8a4W78ep/wALhstXbRNXVE05oBbm3/fNk5yFz0oJc0z3uivPP+FqRk/uvCniNv8AtzA/rSf8LSYE/wDFHeJMf9eq/wDxVBXtInolGa86HxSmbp4M8R/+A6/409fidO6q0fg/X5UIyJIoVKsOxB3dDTs7XD2kT0KiuB/4WRd/w+CfEZ/7YJ/8VTT8SL4FVbwVrys52xq0aZdsZwPm64BP0BoUW9g9pE9AzRmvP2+IesADb4C14k+oQf1pG+IupC1uJz4R1JRbgmZXYAphd2Ceg4IPXoRVQhKbtEPaI9BpjIr8MMj3rz+X4h63FG0kvgfVokQFnd3TaijqTz0A5qabxr4lRQYvA9/Mc4wJQD9eQKSg2uboHtEdZf6Ta3wHmwRsR/Ft+bHpmorbw7psA+a1jdv9sbv51x3/AAsLxE1tazR+CbmQXWPIC3Q+bKluMrg8AnrUh8ceLz934eXv43ij+lRPDqL96OpPPB9Dr73StPWynKWNsGEbEERLkHH0rk/gt/yTDTf+us//AKNaq114z8ZyWk6L4AukJQjc14uBx16VyXwx8T+KdP8ABsFnpvg+XULaKWXFyLoRhiWJIAI7HilGMY7Kwk4p3R7tmjNedf8ACZePCMj4dt+Opr/8TSHxb8QHBK+AEX/e1JT/AOy1RfOj0bNGa83Hif4kEceBrbPvqA/wpf8AhI/iZz/xRNl7f8TAUBz+R6PmivOG174ocFfB2nD1zqANNTX/AIoFsHwfp3/geBQHP5HpNFecf258UWGR4R0wfW/FINY+KeP+RW0n8b6gOfyPSKK83Op/Fc8jw9oY46G7JpP7T+LPbQNB+puj/jQHN5HpOaM15v8Abfi2eP7I8OL7mdz/AFpPtfxc/wCgZ4a/7/Sf40w5vIb8XDhvCJJAUa5CT+Rr0oV4B8RZPiAYdDk1u10hFTUY/s62zk7psHGc9utduknxbZB+48Mpn+88vFIlS1eh6TmkJPavOivxbPQ+GB9Gl/wpnlfF3HEvhn85f8KCubyPSc0V5s1v8W2AAuvDq+pxJ/hTja/FoDP9oeHD9I5P8KA5vI9H4oyK81+wfFtzn+1/Di/SOQ/+y09dM+KzL8+u+H1PbbA5/pQHN5Ho+aK86/sj4qHr4j0MfS0b/ClOi/FHv4n0b/wCNAcz7HolNUbVxz+NefjQ/iYcZ8VaSPX/AEE0f2H8TD/zN2l/+C+gOZ9j0LNBNefHw/8AEnbx4w07P/YO/wDr0h8PfEjt4y0//wAF/wD9egOZ9iPwKfL+IPjq3Jzm8ik/NK9FzxXhHhrR/Gw+Ifia2tPEVpDdxtE93cSWu4Skr8uF7cV3A8N/EPPzeOLQfTSwf/ZqCYPQ74EkcjmlzXCDwz49z/yPcGOv/IJX/wCOUw+GfiAXP/Fc24U+mlrx/wCPUF8z7Hf5orgf+EV8ecf8V7H/AOCpf/iqT/hFfHZGT49jB9F0tcf+hUBzPsd/QTXAHwh44P8AzUEj/uFr/wDHKD4P8bMOfiHIPppaf/F0Bd9jvs0ua8+/4QvxuEwPiJKT6nTF/wDjlL/wiPjqP7nj8N3/AHmloef++qAu+x39LmvPx4X+IA/5nuE5/wCoWvH/AI9Ug8L+Ov8AofI//BUv/wAVQHM+x3ea89+MAA8K2U+eYNTtpP8Ax7H9anPhbxyRx49XP/YKT/4quN+JPhzxVY+FGutQ8X/boY7iIiH7EIvm3AA5BPTr+FBE22tj2tDlAfUU6vPLXwx47e0ib/hO0BKA4/s1T+u6rH/CLeOt2R48jAz/ANAtT/7NQUpO2x3eeKXNcEfC3joqB/wncfXqNMX/AOKpP+EW8dDj/hPY8H10pc/+hUD5n2O+pK4U+GPHXGPHkfvnSU/+KpJPDXjzYFj8dQn1J0pQf/QjQF32O7ozXB/8I54+2/8AI623t/xLV/nmpB4b8c9T44h3Y/6BS4z/AN9UC5n2O4zS1wv/AAjfjsZ/4rmA/wDcKUf+zU4+HPHWOPHMH/gpX/4qgfM+x3FJXEDw344zk+OYh6Y0lP8A4unL4d8bhMHxrFk9/wCy14/8eoDmfY7OTlGHqK4X4Uho/Dd5bMykW+o3Ea7TnHzZ6/jTx4Z8cFMN46j5/wCoUn/xVcl4I0TxW41i303xXDBDbX8sT+ZY+YzvnluTxn2pdTOTfMtD2ejNcOvhzx2HyfHFuR6f2Sv/AMcpf+Ed8dHJPjiAH0GkqR/6FTNLvsdvSfjXFnw74424Hji2J99HX/45ULaB8QQ2V8Z2R476WBj/AMeoC77HccE9OlKc+lcKdC+IiDcPGOnsfQ6YAP8A0KnnQ/iCR/yN1hn/ALBo/wAaVw5n2O1zjnmg44OetcMuhfEPnd4wsOnH/EtByfz4qT+xfiCYwn/CVacD3b7Bk/zoC77HaMOeB+dNwepG7nuK4ptE+Iwb5PFWmFR/e0/r+tB0b4itFg+KNKB9RYH/ABphzPsdtEzbiHP0GMVIc+xrho9B8fPH+88XWIYZxt0wH6c7q0H0vxamlpFD4htXvSfnmlssr9AAf50XFzPsdN5Mf9wUVxH9i/ET/oZ9L/8AAE/40Ug5n2JPipP9n8BX8nU4C4+pFZml/FTT1021iXQ9deRYVBEdixHA9a1Pii+zwbKB/FLGP/HhXXWagWUHH8A/lQ9yLPndjiB8UFYfL4T8SEjqPsDcUg+Jty4/deC/Eb84H+hmvQdtGKZdpdzz8fEXVmbA8BeIcevk0H4ga+x/deAdaP8AvbRXfmjFAWfc4H/hNfFZ+74A1D/gVxEP60g8ZeMnHyeAbof793EP613+KXApByvuefjxX47OceBCPrfR/wCNL/wkvxAJ48DQj3OopXfUc0D5X3OCGv8AxDYf8ifZJ/v6iP6Cnf2x8Rj/AMyxpQ/7fz/hXeYFHFMXL5nCf2n8Sm6eH9FX63rf4VHPd/Ewxsy6foEYxk5nkJFd/iobn/j2kx/dNAnHTc8b+H3/AAnZ0i7k0waP5Et9MzfajIWEmeeh5FdgE+JZxmTw8PbZKf61H8IR/wAUKjYwWu5z1z/y0Nd92pIUI+6cT9m+IzY/0/QE9f3Ep/rTP7O+I3P/ABO9DGeg+xvx+tdzRTK5DhzpfxCY8+IdIQf7NiT/AFpP7F+IBBz4r08H204f413OKMUByI4RvD/j5yD/AMJlar/u6etK3hvxywYf8JwFz026bFx+ld1RQHIjgh4R8ZEEP48uAT/dsov8Kf8A8Ib4owQfHuoEH/p1h/wruqDQL2cTgR4E8Q5Jbx9q/PpHGP6U/wD4QTWyCG8d60c56LGP6V3dGKA9nE4E/D3U2zv8deIeeyShf5CuS8R+CLiHxf4a0+bxRrlyt1JJh5J8vEVXOVPava64DxQd3xR8GooyR9pY/Ty6NyZwSQ8fDWTv4x8Tn3F9j+lSH4bg8f8ACV+Jse2oH/Cu4ooL5InDf8K0tyefEviY8Y51N6D8MrMjH/CQ+JR9NTeu5ooDkicIfhdZEknxB4jJIxzqTU3/AIVTphGDrfiE/wDcRau9ooDkicGfhTo7Lh9V1+Qf7WpOaRfhLoIOftusk+v9oOK72igOSJwY+E3h4dbnV2+uoSf40v8AwqTw1kZfVDj1v5ef1ru6KA5I9jhv+FSeFSMNDet9b2X/ABpn/CoPCf8Azwvf/A6X/Gu8xR1oHyROFPwi8IdTZ3ZPqb6b/wCKrivBHw88OatqnieC8tp5IrLUTbwH7Q6naB0JB5Ne3HpXnnwuO+78YyZyW1yb+QoIcVzJFn/hUHg7tp84/wC3uX/4qnD4ReCx/wAwuU/W8mP/ALNXcjpRQXyo4f8A4VJ4L5zpT/8AgVL/APFU0/CDwWf+YVJ/4FS//FV3VGaA5UcQPhJ4KAx/ZBJ9Tcy5/wDQqX/hUvgjvo3/AJMzf/F121FAckexxP8AwqPwQAR/Yuc/9PM3/wAXSf8ACo/BH/QHP/gTN/8AFV29FAcq7HFD4TeCMY/sRSPeeX/4qlHwn8ED/mBp/wB/5f8A4qu07UUByx7HG/8ACq/BO3b/AGFDjGP9ZJn/ANCoX4VeCR/zAIT9ZHP/ALNXZUUByx7HmfjP4deEbHwVrV3a6JbxXFvZSyxuhYFWVSQevqKk8J/Djwld+FdKurrQrWW4ltY3kds/MSOvWtz4lyGP4b+IGDY/0Jx+fFafhNPL8I6Qo7WcX/oIoJ5VzbGV/wAKx8Fj/mXbM891J/rTz8NPBh/5lyw/7911dFBXKuxyY+GfgsdPDlj+KGl/4Vp4L/6Fyw/7911dFAcq7HK/8K28GYx/wjen/wDfqn/8K58G4x/wjenf9+BXT0UByrscwvw78HrnHhvTefWAGnD4feDx08NaZ/4DrXS0UByrsc3/AMID4RH/ADLel/8AgKv+FOHgPwmM48OaXz/06p/hXRUUByrsc9/wg/hXn/indM5GD/oqc/pTv+EH8Kf9C5pX/gIn+Fb9FAcq7HkvjDwx4ftPH3gqCDSLKNLi4mWSNYQFcBM8joeTXeDwV4Wzn/hHdKz/ANeif4VzHjMbvir4D4yoa7P47Vr0UUCSV2Yf/CGeGMEHw/pZB/6dE/wpv/CF+FyAP+Ed0vjp/oicfpW9RQVZGF/whXhbGP8AhHdL/wDARP8AClXwZ4Xj+74e0of9uif4VuGigLIwz4N8M5P/ABT+l8/9Oif4Uv8Awh3hrGP+Ef0v/wABE/wrboNAcqMQeE/DvT+wNNAB/wCfSP8Awp//AAinh3/oA6bx0/0RP8K2KKBcq7GQvhXw8rZXQ9OB9Rap/hSjwzoIORounj/t1T/CtaigOVdjN/4R7Rdm3+ybHb6fZ1/wo/4R/RR/zCbH/wAB1/wrSooHZHlvw60rS7rWvGSS6daP5Wrsqh4VO0bRwOPrXoQ0LSQcjTLIH/rgv+FcV8Lm3al4zYdDrcn/AKCK9FoJilYzzoelbg39m2eR0PkL/hTxpGnDGLG14/6Yr/hV2igqyKY0uw/58bb/AL9D/Cg6VYH/AJcrf/v0KuUUBZFUabZDpaQf9+xSDTbEdLO3/wC/Qq2aKAsiv9htOv2WH/vgUfY7YdLeL/vgVYoxQFkQfZLb/n3i/wC+RR9ktv8An3i/75FT0UDsRfZbf/nhF/3wK4b4uwwR/DHWWESBvLXBCj+8K76uE+Mgz8LtY/3U/wDQhQJo6XQ7W3/sDTibeIH7NFxsHHyishUfTF8WajHMZTbO8kcEscfl7hbxOOihuPu9envzWxa3qWPhWK+nVikFkJpAgySFQE49+K4OP4oRfaU1CbwuyKQsLXiyhmCEk7QSgzyrELkZIPpXdhKFWopOEbrbp69fToZykktTp44dbs4r1Lu/sY2azleF550cxuuMPxDGAg3fMSG/h6c5p6nHfRaHrFnf3U6ztp08q7hC6uEAz5bqinGGCsHQH5htPBJ6m30fTLSKaK2060hjnXbMkcCqJByMMAORyevqafZ6ZYadv+w2Nta+Zjf5ESpux0zgc9T+dSsRBO6ivuX/AAbfj8iuVjra08i3WOSVrhxnMsqqGbnvtAHtwKobFHiv96o/48f9F4/2/wB90/7Ydfw/iq/Z2Nnp8RisrWC2jLbikMYQE9M4HfgflTbzTLDUdn26xtrry87PPiV9ueuMjjoPyrCMoqTvs/6/ryKtoUdBaJdMUuyAXF5ctCSR+9DTSOpX1BT5hjqOelYupve/8JTp13Po924gvHiszG8IDxm3fdwZAdzMM/NgbUGMEkHrVtbdEgRYIlSDHkqEAEeAV+X04JHHY4pzxRyNGzorNG25CRkqcEZHocEj6E1pGuozlNLe/wCInG6sZGrWlt/bmh3X2eL7R9qaPztg37PImO3PXGecVs7R6U14o5GjZ0VmjbchIyVOCMj0OCR9CafWM58yS7L9WNIMCjFFLUDG45rzi9x/wv7SgOf+JNLn/vqvSO9ebXf/ACcDpvP/ADBpf/QqCZdD0jApcUUUFDJYo54niljWSN1KujjIYHggjuK4xdJjXwnpVl9kntY4JUXU0hs9xZhCQTsKMJR5mz5grDjIPy5Fn4ha9faB4ejuNOkSOeW4WLeyhiq4ZsgHj+HHIPU/WvKtJ+KWv6vHIY/EMUDorMIri2RWfAzgYQjP416WFpSVNS50lJ6Xb6fJ9zKTTdrHp8ukaadDggkTV3tBfGSM/wBnoxQ+Uwz5HlYWPO4cxg7zu6HcT+zLaWysJrrR45LS1vnZlSxcBomhZcrbtuZB5hUFQOSu/oc1reDtUuda8J2N/eMrXEqsHKrgEq5XOPU4ye2fSt2s6mInTm4PdNrf5dv+B5DUU1cZFIs0SSqGCuoYB1KnB9QeQfY81y10zx6XrGgi2vGnuJZo4JVtZDGwuDu3FwpVVUykHnOEJxziuspa5qdRQe3/AA6LauZmrSq+n6nbNYT3SrZs5jUECcMHHlqw53fLzgZG5fWsqxt9NOv2j6PpTWISKU3E39nvbh1+UCM7kUEliGzyR5ZHRjXUUlONXli4r8/K2wnG5yOmw/aNR0hLR9XS1tN032a+tPKjgQRNGsYYxgsw8wAfM3CsSScZ67FFFKrV9o07AlYgujttJieyH+VcF8FVI+G9qcHDXE5H/fw13t1/x6THj7h6/SuE+C7Z+G1mM5Czzgf9/WrMT+JHoWKMUUUixO+KWiigAxRiiigAoxRRQAUYFFLQAmKMUUUAeafGRS2meHMD/mNwc/g1ekqOOfSvOfjCwXSfDrYzjXLc49eHr0dTwPpTIXxMXpRRRSLCig0UAJiloooAKKKKAEpaOBRQAnOfajFLRQB5t4TOfjB414I+W2Ht/qxXpNec+GCf+Fw+MlJOTHakfTyxXo1NkQ2Cjr0oopFhijFFFABRSEZ60uaACiiigAOKKKKACuA+Mf8AyTi7OOk0J+n7wV3/AFFcN8XE8z4aaqcZ2eW35OKCZ/Czr9Px/Z9vjn90v8qtVn6NJ5ui2L4xugQ/oK0BQEdkFFFFBQYpKWigBKMUuMUdqADFFHaigAoFHaigBD0rgPhshW98VOCdp1eQAHscD/GvQD0rgfh9ITrvjGHkKmrMQPqB/hQZy+JHe0YopRyKDQKKKMUAJ7UUtFACUFQT3oxRQAAdc0mMUueOaMUAMJIPAFOUnHJyR1xQODS4ODzmgBm/2P50Um0+o/KigDhPivIRoFpF2lvYVPH+1XdwDEEY9FFcH8VSBo+mDoW1CEfUZ5rvoh+6UDpgUupnH4mPoNFGOKZoFFFFAAaMUYooAKKKKACiiigAqtftssJ29Eb+VWaoawcaNeHj/Ut16dKCZbM5T4RLj4eWZ/vSzH/yIa7quI+Ev/JNtL4I/wBZ+PztXb0kEPhQUtJRTKFpKKKAFpMUUUAFFFFABR3oozQAVwGund8YfCqf3ba6cf8AfOK7+vPdWOfjZ4dHf7Bcd+nFBE+h6HSUUUFhRRRQAUUc0UALSUZooAKWkIooAB9KKKKAEPSvOvhPh4vFU46Prs+PyX/GvRW6V5z8HR/xKfEDeutz/wAkoIfxI9HFFApaCxKKOaKACig0UAFHeiigAooooAKKKKAOO+KTBPhnrxOObYjn3Irb8MDHhfSR/wBOcX/oIrn/AItkD4X65k4zCo/8iLXR+HQV8N6WD1FpFn/vkUEfaNOig0UFi0hoooAKKRmCjJ6UtABRQKKACiiigApaTtRQB534t5+LPgdRz8t2T/3yteiDpXnXig5+MPgxeeILs/otei0EoKWkpaChKWikoAWkoooAKKKKACiiigAoxxRQRxQB538LQRc+MOn/ACHZv/QVr0SvOfhO29vFzd/7enH6LXo1BMdhaQ0UtBQlFLSUALSUUtABSUUUAFFFFACYOTzXCfGP/kl2sf7q/wDoQrvK4L4yn/i12r/RP/QhQJnSx2P9oeEFsPM8sXFgId+M7d0eM479a85j+F/iMwLZS6lYLZtIruEZmIxkZHyDJAZuMjrXqmm/8gy05z+5Tn14FWa6sPjKlBWhbvqr69yHBSWotFFFcpoFLSUUAFFFFABRRS0AJR1oooAO9ebXX/JwVh/2BpP/AEOvSe9ebX3y/H/Sjj72jy85/wBqgmXQ9JoNFFBRynjTwrceJNHWC2nSO4jmEqiUnaeCCMjp97PQ9PfNebR/BHU45/tCy6cJc7sm4lJz/wB817pRXVSxlSlBQSTS2uk7Eygm7mP4X0Z9B8N2emyyrLLCrF3QYG5mLED2GcZ74zgdK2KKKwnNzk5y3eo0rKwUUtJUDCig0UALSUUUAQXQBtJgwyNhyPwrgPgkc/De3Hpczgf99mvQZ/8AUPxn5TxXnnwRP/FuYf8Ar6n/APQzTIfxHpFFFGaRYUtIOtFABRRRQAUUZooAKWkooAKKKMUAeZ/GYhND0Bz/AA63Ac/g9ekRH5Fx6V5v8aif+Ee0IqORrcB6/wCzJXpUY/dj6UyF8THCiilpFiUUUcUAFFFFABRRRQAUUUYoAKDRRQB5v4fJHxq8WKT1trYge20V6QOleb6GSfjf4oJHSztwD+Ar0emzOHUWg0ZopGgZooo6UAFFFHWgA6UUUYoAKCce9FHNAB+lcZ8VF3fDPW+cYhBH4MK7OuS+Jab/AIb68O/2ViPrxQTLZmv4bJPhvTS2c/Zo/wD0EVrd6xPCOP8AhENJ2nI+yR8n/dFbfehhD4UGaKKKCgo70c0GgAooooAKKKKACiiigBK4HwG0Y8WeM41++NQBbjH8PH9a76vPfBDL/wAJ942RSeLyI8+6f/roM57o9DpKKO1BoLRRSc0ALRmiigAooxRQAnWjFLRigBpxg5pc5FBo9qAEy390fnRTsUUAed/FIr5OgIT9/VYR/M16EOg+led/E5x9t8MRn+LU0IIPQ4NeijkCjqZx+Ji0d6KKDQOtFFFAAKKDQKACijFHegAo70UGgA71leJGK+HNRYdRbv0PtWrWL4scp4T1VgORaSf+gmgmfwsyvhghj+G+jAgZ8knj/eNdfXKfDdNnw60Ietqh/OuroCHwoKKKKCgzRRiigAoo6UUAFFFFAC0lFFACGuA1BS/xu0Y/3NLnb9QP6135rz6ZC3xztCCfl0iRiPQbwP60Gc+nqehUtJRQaBRRiigBaSiloASiiigAo70UUAFHejNFACN0rzv4QMW0XXc/9Bq4/klehv8AdP0rz34PDPhzVpc583WLhv8A0Ef0oIfxI9EFFFFBYUUUUAFFFFABS0lFAC0UUlAC0UUlAHFfFaJf+FYa4ucDyQR9d4NdF4cyfDWlE9fscX/oArmfi++34Xa17rEOvrKtdRoQK6BpynqLaLP/AHyKCPtGjR3oooLDPFFLRQAlFFFABRRRQAUUUUALSUUGgDzrxM3/ABeTwamP+Xa6/kP8K9FrzvxIit8Z/CJzyLS6OPyr0M0EoXNFJjNLigoKM0UUAGaKKKAFpKKKACiiigAFFHWg0AedfChdp8WnOc69P/Ja9Frzj4SOWi8VAjBXXrgZ9elej5oFHYKKKKBiUtFFABRRRQAUtJRmgApaSigArg/jJz8LtY4/hX/0IV3lcF8ZTj4Xav7hP/QhQJnYaRxo1iB/z7x/+girtQWoxZwjGPkHHpxU+KAWwUYoooGLSUUtACUdaKKAFpKKKACiiigA715vqK/8X+0Yg9dHmz/30a9I715rqbf8X/0MDP8AyCJs/maZMuh6UKWkFFIoKKKbu+bGD060AOozRS0AJS0lFABRRS0AJRR3paAIp8+TJjrtOK87+CWf+FdxZ/5+5/8A0M16JLxE/wDumvOvgi2fh6gxyLufP/fVMh/Ej0miiikWFFFFAC0lFFABRRRQAUUUUAFFFHNAHmnxq/5FrSCM5GrwfyavSI/9Wv0rzr4zf8ivpn/YXts/+PV6JF/q15zxT6Ga+JklBoNFI0CigcUUAFFHeigA70UUdKACjNFFABRRQRQB5tpP/JdPEHGM2EB6+wr0mvONMwPjprgwOdNgPXmvR8U2Zw6hRRRSNAooooAKKCM0UAFFGaKACijtSUAL0rmPiIA3w71/PT7FJ/KunrnPHmD4C14EZ/0GX/0E0Ez+Fkvg6QS+DtIYdDaR/wDoIrerm/AT+Z4C0Rj3tI/5V0lNih8KCkOcHB5pc0UiwGcc0UlLQAlL2oooAKKBRQAUCjFFAAa868GHb8S/G0Q7zQv/AOO16JXnfhYlfi54xjZskpbED0G2gznuj0SloxRig0Cikpc0AFFFFABRRijFABRRRQAlA560tJQAYP8Ak0UuaKAPOfiMu/xH4QXudR4/BSa9FFecePyW8YeEEGB/pueuP4T/AI16PR1M6e7Cl70lLQaBRR2ooAM0ZpKWgAo70UdaACjNFFACVz/jhingnWWHBFrJ/KuhrmvHpx4E1o/9Oz/yoRM/hYvgJPK8BaCn/TlE35jNdJ3rC8GLt8FaIAMf6FF/6CK3aAjsgooB5ooKDNFFFABRRRQAUUUUAFFFFACV5+MP8c/9zRj+sgr0CuAhwfjlccjI0Yf+jKaMp9PU9AooopGoUUtJQAUUYooAKKKM0AGaKKKAEpaKMUAMlOImPtXn/wAG/wDkS5267tRuD/49XfTcQOT02npXCfB0f8UGrZ+9eXB/8iGn0M38aPQKD1oopGgCiiloASilpKAFoopKACiiigAooooA4D4yk/8ACr9UHq0A/wDIyV2emDbpVmpGCIEGPwFcV8aCB8M78f3pYB/5FWu4sQBZQKOgiUfpT6EL4mWaKKKRYtFJRQAUUUUAFGaKKAFpKKKADvRR3ooA8614/wDF7/C4/wCofcfzr0SvPdX5+OXh4HtpVwR9c16HQTEKKKKCgxRRRQAtJRRQAUUUUAFFFFACdKWiigDzr4TJtg8UH+9rtyf1Fei1538JgwtPEuen9u3WPzFeiigmOwlFFFBQUtJRQAUUtFACUUtFACUUGigArgfjN/yS7Vvon/oQrva4L4zDPwu1bPYJ/wChCgT2O005t+m2r4xmJT+lWs1Xstv2G32/d8tcflVigFsFFFLQMSiiigAooooAKKKKAA0UdqKAErzbUOf2gNGwOmkTZ/M16TXm9+cfH/Se+dHl/D5qaJl0PRBNGZjEHBkVQxXuAc4/kfyqWolgiSV5VQB5Mbm7nHSpaRQtJRRQAUUUZ5xQAUtJS0AJS0lFABRRRQAyTmNs9MV5x8Ef+RCb/r+nx+dejyf6th7GvO/gkQfh+MDGLyfn1+amQ/iR6PRRRSLCijpRQAUUUUALSd6M0d6ACiiigAooo7UAec/GVd/hTT/T+1bfP5mvQohiJR7V538aAT4PsyO2p2/8zXokH+qT/dFN7Ga+NklFFFI0FpKKKACgUc0CgAooooAKKKKACjNFFAHnNip/4XvqxP8A0Cofx5r0Qkgeted2jsPjxqKjodJiz/30a9Gpszh1EBJHIxS0UUjQTvS0UUAFFFFABRRRQAUUdaKADvWB43x/wg2uEgHFjN2z/Aa3+9YfjIBvBWtg9DYzf+gGhEz+FlL4dnPw+0Xkt/oy8kV1Fct8OiT8PdEJ6/ZU/lXVU3uEPhQnel6UY5opFBRRRQAUUUUAGaOaPwooAKKO9FACV5xoD4+NniuPs1pbtz7KBXpFec6UEX456+M/M2mwEj8hQRPoei9qXtRRigsKBSYpaACjNFFABRzR0ooAO1Haiko</t>
+  </si>
+  <si>
+    <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAgGBgcGBQgHBwcJCQgKDBQNDAsLDBkSEw8UHRofHh0aHBwgJC4nICIsIxwcKDcpLDAxNDQ0Hyc5PTgyPC4zNDL/2wBDAQkJCQwLDBgNDRgyIRwhMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjIyMjL/wAARCAQ1BfEDASIAAhEBAxEB/8QAHwAAAQUBAQEBAQEAAAAAAAAAAAECAwQFBgcICQoL/8QAtRAAAgEDAwIEAwUFBAQAAAF9AQIDAAQRBRIhMUEGE1FhByJxFDKBkaEII0KxwRVS0fAkM2JyggkKFhcYGRolJicoKSo0NTY3ODk6Q0RFRkdISUpTVFVWV1hZWmNkZWZnaGlqc3R1dnd4eXqDhIWGh4iJipKTlJWWl5iZmqKjpKWmp6ipqrKztLW2t7i5usLDxMXGx8jJytLT1NXW19jZ2uHi4+Tl5ufo6erx8vP09fb3+Pn6/8QAHwEAAwEBAQEBAQEBAQAAAAAAAAECAwQFBgcICQoL/8QAtREAAgECBAQDBAcFBAQAAQJ3AAECAxEEBSExBhJBUQdhcRMiMoEIFEKRobHBCSMzUvAVYnLRChYkNOEl8RcYGRomJygpKjU2Nzg5OkNERUZHSElKU1RVVldYWVpjZGVmZ2hpanN0dXZ3eHl6goOEhYaHiImKkpOUlZaXmJmaoqOkpaanqKmqsrO0tba3uLm6wsPExcbHyMnK0tPU1dbX2Nna4uPk5ebn6Onq8vP09fb3+Pn6/9oADAMBAAIRAxEAPwD3+ko7Vy3iHxcdCvra0TSrq9lnztS3AJ4xQJtLc6miuH/4TjWmOI/BmrE/7W0f1pq+LvE7MAPBV2M9zOopXRPOjus0Vwn/AAlXjB8eX4LfnHLXij+lNPiLx4x+XwjbgehvR/hRdBzo72iuDbWPiAzDb4asFQ9zeZI/Sl+3/EZnwukaOi55LTsaLoXP5Hd5ozXAs/xOYZWHw+nsTI39RS7fia3fw8vXkLJ/jRcfM+x3uaM1wRt/ic4x9s8Ox+4ilJ/nQum/Etvva5oafS0Y/wBaLhzPsd7mjNcH/Y3xGZhu8UaUg/2NPz/M0/8AsDx6wAbxjaJx/Bpq8fmaLhzPsdzkUV5Z4gtfG2jvp5PjESC6uo7batjEpG49RxWz/wAIh4sYDPj67GPSyiGaLiU23ax3WaTPvXDf8IT4gYfvPHmrE/7EMS/0ofwLqr8HxtrXp/AD+YHWi47y7Hbk4BqPq3yDp1J71xbfD66cDzPGWulccjzlGf0qaHwFKiqG8Va5Jt6Hzl/wouF5djq54VlIU7if0qJrFVYEShR3z3rlb/4ffbJULa/rWFHX7Sea09M8GWOnZMlzfXshHL3Vwz/p0oHeXY6BSoXjywB6GoF85mZGDIg4Epbk/hUVppEFmjCNpCDyFZshfp6VWl0C3vopYrya7ljdslPPZR+hzTHqWJrfTbV1uLqRA68B5n7046xp2Ny3cUmSAAjZyaqJ4R0JRGX06KRozlWlJcj8TVxtI0/7Qk/2SISJ0Krj86A1LhfC9unUnFNW4iKBvNQhjwQeKabWBlIZdwJzyc1GlhZw27RJBGsTEsVA4yepoDUsh1/vD86a06LxkFs4wCM1VtLaJ7Qb0Q/Q5qwtpCsgcRICO+OaBajxPEykiRSB1INIJ4y20OOmRz1pBbQDdtiUZ68daj+ywOBG1uoVTkemaB6kpnhV9hlQP6Fhmke7to22vcRqfRnAqCbS7GedZ5rWF5VxhyuSMVFJoekT3Bll0+2eYfxNGCaA1LslzBFt3you44GT1qtPq2n27mKW9gjkAJKvIARxmkOkafK8cj2kRdPu5GcVHfaDp+oyB7q3ikI6ZWgNS5BcRXMIlhmSSM8hlOQRQ91bwqTJPEuBkksBTYLG2trfyIIVii/upwKqtoelsxD2UTE4Jyuc4oDUfeaxpunDdeXtvbgruBkcDI9ao23jDQbreYNTgaNer7vl/A960ZtOsrjHn28UoRdgDKDgelOSwtVhEItohEBgLsGAKBPmMqfxjoNtKY21BGdWCtsUtgkZGcCmN418PLZy3LapF5cZw3XI/wCA9a2hbQKxKxIC3BIUcgdq4nxXZ248d+EVWJF8yebd8gw2I84NJ3Jk5rU00+I3haT7mphuO0Mn+FRyfE3wpG206kxPtbSn/wBlrqBZ2wOfs8Wex2Cn/ZYM58iPP+6KNR2l3POvFXjTwrrvh27sPt9yJmQvCqQypukHKg/LggnHB478EAjgZNWSy8KWtjp1/dpLO8r6jErMFPRUA4wQVzkDOc89FA9d8YeIbXw/HZ250f8AtGW+Zo1g4AYDAI6HJO4DGOefx8xi8aeF44bjSR4UtSryBpITfsZVZf8AaK7hjnjI6n1OfoMsdWNJXjdN3Wq13XVrrr6owqLXVmPa67fpoFxp8epSxWzFSIC0oLD5gyqANoU7yWBxnA607T9TCeHtU0+W6uVjmEckNuqtsaQOuWbnj5c8EYPGeVWvZ9N8K+GLzw7GtvpKiyvVjudrljJyAV+bcSCAegOOT6nN3TfCOhaR5/2LTYk89PLl8wtJuXuvzE8HuO/GelaTzekuZcrvdPZdLefk+/qCoy7nIeFvGfhvQfDdnZCa+kcLul/cSSBZDywHGAAT0H15JJOTq3irSLj4haVrksc50+3tyGMtswO4eYQQpGTgspBHevTNJ8O6ToUUkem2KQiRtznJYk9uWJOPb3PrUmqaFpetW4g1GyinRfulhhl5BO1hyM4GcHmvKhiYRxMqju4yuvPX8DTkly2ueZaf4v0mL4i6prrPMdPuLZYkkED8NiPqMZX7jdazfFviOw1bxfZ6haajeWMEdqIzdR28gkU5c/KowSDuAyOOT6V6lD4O8P2+l3Omxaci2tyytMvmPlypBGWzuwCOmcdfU0668I6De6bbWE+mxG1tf9SqllKevzAg89TzyeTk10xxtCNRTinouXpta1/W/TaxPs52tc898KfEGDSLfUItTlvL2ESh4LpLZjJIDx+8OeOAmNxyOmcAYTwl4tsbG41LWNUtNRm1K+mPzwWbyokYxhVbBIGeMZPCL6V6TB4a0a30WTSIrCMWEud8RydxPcknOemDnIwMdBWjFDHDEkUUSxxooVEQYCgcAAdhXPiMXCSn7ONnJr7l6d3qylCWl2ca3xM0wZK6ZrbqP4lsGxVa3+Kuk3kLy2ul63OFbyyI7Innv3xxXekDHSuF+F3zabrkuch9YuSPzA/pXn6jtK9rkw+JNiyh/wCxtcHPI+xHI/DNNb4m6epx/Y2ut/u2DV2+B6UYHpRqPll3OFb4n2a/8wDxB/4AH/Gm/wDC0LXIx4c8RN9LHv8AnXebaMD0o1Dll3OD/wCFnxnhfC/iInGf+PL/AOvQfib/AHfCfiM/9uf/ANeu8wPSjA9KNQ5ZdzgU+JcshwPB/iM/S0/+vQfiRdEfJ4L8Rk/9e6j+td9gelGB6Uahyy7nnr/ErUF4XwP4gJx3hH9CaafiVqoGf+EC8Qf9+xXomBRgUw5ZdzzwfErUO/gXxCP+2I/xpw+JN+SR/wAIL4lyPS3H+NehYooHyvueYan8W59It1uL/wAGa5bQswUPKgUEnoM1dHxF1cAFvAmvDIyP3a/40z4yHPhWwiwfn1S2H/j1eiACkK0r7nnf/CytVPA8Ca9+MYpV+I+rjO/wHrw/3Y1P9a9ExRiiw+V9zzz/AIWTqf8A0IniDn1jX/GmH4kav1HgTXf++RXouKMCiwuWXc88X4j6wf8AmQ9e/CNf8aVviLrIBI8Ba8f+Ar/jXoWOaXFGo+V9zzwfEPXSpb/hX+u8eoWmH4h+Ij0+Hut/jivRsCjAoDlfc87/AOFg+Is/8k+1o/RloHxA8SFfl+Hus592UV6JgUmKA5X3PO/+E+8Ulcj4ear+Mq0p8eeKef8Ai32p/wDf1a9DxRigOV9zym1+Kuv32q3emWvgm8kvLQAzxecAY89M1onx14wT73w8vz/u3Cmk8GYl+K/jyUY+T7JH+kn+FejcUCSfc82/4T3xhxj4eajn/rsv+FPPjvxj2+Hl+f8At4X/AAr0bFGKB8r7nm58c+NecfD286f8/C0Dxv42OP8Ai312Pf7Qtek0Yphyvuebf8Jr44zj/hX1x7f6UtH/AAmvjoHJ+H8+Pa6WvSMUYpByvuebDxr48LAf8K/mx/19KKU+M/H2RjwBJgjPN2tekYoxQHK+55sfGHxCPTwA3tm8j/xpf+Eu+IRXjwCffN7H/jXpGKXigOV9zzYeLPiIRk+A1/8AA2P/ABqjrHxB8daHps2oX/guOC1iGXkN0pwPwNerYrhfjGdvwt1n3RR/48KA5X3Mq18Y/EW9tYbmDwRD5UqCRXa8UZBGRxnNT/8ACTfEo8DwTCPf7bH/AI13GgDHhzTB/wBOkX/oIrRosCi+55v/AMJD8TWJC+DLIY7m+X/GmnXfii3TwjYLnub1eP1r0qiiwuTzPN/7X+KW3/kWNLyB/wA/o5/Wgax8Ujz/AMIxpY9jeD/GvSKKLByeZ5sdV+Kvbw3pP/gWP8aUat8VDwfDekj3+1j/ABr0ikzRYfJ5nnJ1L4qdtA0Yf9vXWgah8VCM/wBh6KD/ANfRr0ftRRYOTzPOPtvxWLY/snQwPX7QaBcfFdsf6D4fT2M7f4V6PmiiwcnmedbviseBD4eX3Msn+FYMfib4lz+Mp/DKJof2yC2Fy7Zby9pIHXGe/pXsVebaYAf2gdabuuixDH/A1osJxt1HiH4r7gTN4dx6bpP/AImneR8Vs83Ph3HsJP8ACvRaKLByeZ50bX4rEjF94cHrkS//ABNMWy+LBHOp+Hh/wGT/AOJr0eigOTzPOhp3xWbrqvh5f+2bn/2Wk/sr4qbcf23oGfXypP8ACvR6KLD5Eecf2R8VOv8Ab2g/QQP/AIUv9i/FAjnxHoo+lqxr0aiiwciPOv7A+JhHPirSh9LM0Hw58SSP+Ru07p/z5H/GvRaKLByI86Xw98SgQT4t036fYjSnw18Rmz/xWNiPpY//AF69ENFFg9mjyXxJZfEHw34dvtWfxhb3CWsZlMYsQpPsOak0XR/iHrOhWepN40gh+2W6zoi2QO0MAQM8etdX8SQT8OdewOfsbVF8M5L2X4f6Mby1Fttto0iXduLRhQAx9M9cUWFy62Mr/hEvH5A3eOYwf9mxH+NOHhHx4D/yPmeP+fBf8a9DoosVyI84/wCEP+IOP+R9UH/rxWpF8I+PQTnx4CO3+gL/AI16HRTDkR54fB/jokf8V6R6/wCgr/jTW8GeOHwG8fygf7Nko/rXotFKwvZo84/4QrxwRz8QJueuLJKlHg3xrjB8fy8/9OCf416Dk7sYP1paYezR53/whPjHPPxAvMf9eiCj/hB/GGR/xX94MelsteiUc0WD2aPO/wDhCfGPbx/d+3+ipSN4F8Wsoz8QdQ3d8W6AV6LRSsHs0eKW+n+MZPiLP4Y/4Ti8VIbEXfnfZ4yTyBjH49a6o+BfFTD5viFqXviBBVeMiL9oCUdPO0T9RItekCgUYrU4E+BfExbjx/quO/7mP/Cmt4C8Syff+IGrf8BijH9K9BoplciPPx4B8Q7cH4gaz07JH/hSDwB4hBJHj/WfbKxn+leg9KKVg5EefDwH4kHH/Cf6tj/rlH/hUieBfEA+9491c4PZI/8ACu9oosHIjhv+EJ8Q/wDQ+av/AN+Yv/iaVfBfiEdfHerH/tjF/wDE13GaKYciOJ/4QrXMnPjnV8egjj/wpp8Fa9njx1qwA6fuov8ACu4FFFhezRxA8F6/znxzq2Mdoov8KxPFmj+IPDfhnUdVi8Z6nNJAoZVeOPHXHpXqVcl8SlDfDvW89rcn9aQpRVihZeE/EE9lDLL441Mu8YY4hiA5H0qQeC9ezz441U85/wBVH/hXU6KS2iWJY5Jt48n/AICKv0wUE0cX/wAIbrgHHjfVh/2zi/8AiaU+EfEBHHjbUQPaCLp+VdnRQVyI4r/hDdf3ZPjnVMenkxf4Uo8Ha+HcnxxqZBHA8mLg/lXaUUByo4geDvEY5PjrUie2beH/AApX8H+JC2U8cagB728X+Fdt2opWF7NHDr4P8SKMnxvqBbnnyI/5Yo/4RLxQY1RvHF57sLWIE/pXbilosHs0ccPC/iVQg/4TG4OOubVOaYvhbxQJix8aTsh/hNpHxXad6TFFg9mjhz4P8Tbw/wDwnN/nuPs8WPyxWH4StvFesz6g0/imeFbK8e1EJtlJITjJJ9a9SIzxmuJ8D+VH4g8WQoVLDUMkAk4yo4pW1JlFKSNK+8PapexQhPEl5ayJ95oo0+Y/QiqVv4V8R27bj40vJTnkS20ZGK7InGcdaOTn1p2K5Ec8NE1by5d3iGcyuT5ZEKgL+HeoItE11oxHJ4mlYB8kraqCw9M/1FdRzkc/hSbQDnOKLByIxNR0jVLhIzp+ty2kivuJMQkDDsMHtV+2trtbTy7u68+QjDME2flirRzkY+tAkIbawz7imPlRjy2OuC5aWDVIdmDiOWDIB7dD/nNaEJuo7dFuts8oX5zEm0E+2TUyktOWUttAxg9M1IRvQ9VzQO1itPYtNjZczQ47RnFRzWsmxvK1CWLI6nDY755q5FGyDBct9aVo0cEOoIPByOtAFbyrvzQVulZBwyslKkM4jjAnwc5Ykbt3t7CnJK32hkNuyg/8tMjBqwAOMcUAUXuLqAxxmESsx5ZcgdfpU0F2JiymOWNlOCHTH69KjubaWWWCSKZ0KE5GeCD6jHNXMHb159aAILiOaVMRXBhPqFB/nUM16kDhZIJ5CMfMse78eKryWmrRSPLb38blv+Wc0XA+mDWgrlIN0u1XAywB4zQMhguDK8x82PYrbQADlfrmreD61HHJG3GU39SAaeZFDbdw3HoM0AR7JNozJznqFrNtrLVk1GSabVVktj0hFuAR+Nax44zjNOyKBWMk2bPfXNwNiTkBEl8rJC+makRNS+yFGubc3Wclgp2gfStE4JBzxUCW8aPNsTZ5hyzg8saAsUUttXAhVr62wM+btgIz9OeKpXWlatcXys+qJDZgZKRx/vGP1PQV0BVdu0jPHeopWaOBpCjMwU4RT1oCx52mmaxZ6vdTTareXMTg+SBA3A7HgYx7VrWdmbf7I8+ozMCcvuO0sffA4HtRfapBqMqRXFvqFjJkDd5/l4+g7/lWxqFpLLZRraSgFSMGdS4P4ZGaAsTbrf8Auf8AkGiq/wDZt/8A8/8AP/3ytFGganQdq4m8kE/xJ0+LGTFDI1dselcJaEz/ABSlJGRDZ469Mn/9VJmc+h3dGKKOlM1CjFGaM0AGKMUUUAFFFFABRRRQAdKM0UUAcV48Zhf+GwpOTqcfA712g6Vxfi/EnivwpFkZ+2F8Z9EJrtB0pdSI/EwpfekpDntTLGtgnvmnfNz09qbgYz3FPBB5FAEUZ80EnkZI46VN2xSY9OKTIDc9TQA4DAowM5xzS1HIwVCSCQPSgCSmMoYEMAQeoNRwXC3CZTIwcEMMEVNnBoAiERVsqcDGNvantnyz9O1OpGG5SPUUAQ2js9ujOrKx6hutSspK43Ee4qK0h8i2jiDs+0Y3Mck05mkDYVVKjqS2MfpQJDy6hguRk9qceQcHFRKqtKJlwcjGR3p7gsuA233oGNdCyEbyPcUySOR2G2UoB2AzSIBbRYeYu3YuQCaQ/aJCwyIo8cMOTQAQWxgzmZ5Ce8hzUjHb80jYx0Aqt5McSlzLLI3cButS73YghcAH7p64pAH2gO3cIRjpzTyEEe1SeOnJpDJhsGPn1pytlun40wFDADG0ilBPc0vOM8UYxQAuK4jxGQ3xI8KIEyQtzJnHT5QP6129cVrKCX4qeHeW/dWdy3HTnApMiex2wHejNFGKZZ5n8XNE1PWLGwGnW1xNsE0bNAhdoywXado5x8p5/wARXjml/DzXdKv1kFjfuzKQUawcMw9j25xX1fTSoJBIzjpXfRxsYRgpQTcNnd97mbg3ez3KGg2s1l4f061uF2TQ2scci5B2sFAIyOK0aKK4pScpOT6miVgooo6VIBRRmigAopaSgBCflP0rhvhUd3hm8Prqd1+P7w127nEbn2NcN8JR/wAUdK4GN+oXTY/7amkS/iR3lLSUUygopaSgBaKSigAopaSgBaSlpKACiiigDz34uHOh6NCMZk1e1Az0+9XoQrzv4tLvs/Daf3tbtR/49XogoJW7CjNFFBQUUtJQAUUtJQAtFFFACUUUUAFHaig0Aec+BlC/E74gkdTNaf8AoMlejV5v4Ez/AMLP+IQPTz7Qj/vmSvSKCY7BRS0lBQtJS0UAJS0lFABRS0lABS0lFAC1wvxfz/wq/Wv+uQ/9CFdzXC/GA4+F+s+6L/6EKBM6rQsf2Bp2DkfZYv8A0EVoVm+HwP8AhHtLxwPskWB/wAVpUAtgooooGLSUUUAFFFGaACiiigAooooAK810vI/aA1rpg6NFn1+8telGvM9Owv7Q2rDu2hqev/TSP/GglnplLSUUFBRRRQAdKKKKACiijvQAUUUd6ACiiigDl/iKu74d68P+nOSpvAbF/AHh5s5/4l0H/osUeO13+BNcU97KX+VRfDw/8W68O+v9nwf+gign7R09FFHagoKWkHSigAopaSgAooo70AFFFFABRRQelAHms5C/H+25IL6K4+v7wf4V6TXnGpBV+PWinby+kzc/jXpFBEeoUZooFBYGijmjrQAUZoooAKWkooAKQUtFABXM/EGPzvAOtrjP+iuf0rpqxfFsXn+EdXjPezl/9BNApbDvCz+b4T0ly24m0iJOc87BWxXNeAJfP8A6FJ/05RL+QxXS0Cj8KCiiigoKKKKACiiigApDxS96KACiijvQAnQVwnhDy4vHfjCJFIJuInOOnKV3dcPoyrD8VfECgj95aQSbR+IJpdTOe6O5pDjvS9qTnuKZoNOM/wA6UkdzS44xSEGgBgOCMkAH8zSspb6U44I4pmNuWGfpmgBqhkONwAPbFN8x432ueOTngYFSYdl/un2NNMSKeWwSaBCyeWI9krDBqvCbG1dkh2x47DOKeiwAnZuJ/vdcU1beGLDrhg3VmPSgBLm9eAnZbmVccFSKLbUo7llTy5kkIyUaM8e2elWhEojKgAA+lQlzny1MJbpn0oGZOr21vDqdtqD6ZLcMpwZvOAWHrztJ56ntWuZrgwh44EYn+EyY4/Ksm+u47MWllqGZkvZfLVxgKvfB9uPerZjubH5bUGaMj7ssmAvsDQIuxyTO2JICmO+4EGpNrnd8w5+7x0rNOrQecbS5QiQryEBkGO+SBVaXV3SFzp8fnpEhI35zIfQUDLDNqtsJTFa2s/PyBG8on65zWhESyq0sQWXbzjkD2zWXpGtNf24Z7S4jKj52K/Ln29a0pZniheTAcDkAAg4oAlQuV+cDPsaiaOJH3CFSzHJPH51Sg1e0vnaJBMsgGSGiYU3TtT+3GWJvLaSNiBzgn6jtQBoq5c7gV8r1PU0qIsfC8AknHXJqmkElzIy3tum1GDIyE4OOnFWkuYHkaNHVnThgD0oAeCVbBYtn1FJ5h8/ZtY4GcjpUhzyfyzVeNpERftLpvJP3RgfrQBR1ZNPnaOO83E5+TAPB9eKqXSrfaRI+n5Zm+QS52Hr69anPiG0bVjYj5lGVMo5G7+79anvin9j3IgjPyxn91GQG+ntQBzn9laj/AHov/A9v8KKz/th/6Bkf/f8A/wDrUU7E3PRjwDXC+Hh53xE1uTOfLijQe3tXcv8AdP0rhvBahvFPiKY8kyonHTgVLJl8SO7ooopmgdqKKKACiiigAo70UUAFFFFABRRmigDh9fDTfErwzHjhEmkz+FdxiuHvx5nxb0tc/wCrsJZOnviu4FLqZw6iUhpxpMUzQadwHAz+NMGAeTtP14qXp/8AXpjbM4YdaABZkbjcM035udoPB79DSyJmP5ByKiRiCVPmL6ZIIoAs5HQ1EsRjfKyMVP8ACxz+VQtAk8obcwkA4IORUg3JCVlk7ffFAD3nCMBtY84Jx0qmmrWzSmGYiM+pI2n8astdW0afvbiLgcksKR7e0uxyiP7igCZSrJ8j5HqDmq99exWFpJPPv8pQSxVScVGtqtiQ1rCxU8GNSAPrzWb4j8RDQdIubyazmdo4ywRMHP8Ak0Cehs2tzHc28ckQbY6BlO3HBpl1ei3IRI5JZWGQqKTx61S0i8fUdJsbm5Escs0QcoAVx9avuZywCFETI5PXFAyWKRniDMhRj/CaqyiWYkSuYUByNrYNTFlnO1WDBT8xBpsjRiQKGcYJyF96AKv2K3EolRiSeTIxzk1df7gHmYXvjrTJUV1UZOAehp4K5UjoOgoAaGcDakbDn7zc09TJnkg/hSHc5zlsemakGfakAnOc9/SnDg0cH2NGAKYAByTS0UuKAEriNQYN8YNGXB+TTJz+bD/Cu4NcbNdbviva2ZghO3S2l83HzjLkYz6UET6HZUUUUFh3paSigA6UUUUAFFFHQ0AFFHWigAooooAjnO2CQ+imuJ+Eq/8AFBwsOj3Nw4/GVq7O7/485/8AcP8AKuM+EIP/AArbTCepMp/8iGkS/iR3VFFFMoKKWigBKKWkoAKWkpaACiikoAWkopaAPO/iqxEXhccZOu2uP++q9DHSvPfimoYeFSeo121x/wB9V6EKCVuwooo70FBzRRS0AFJS0UAJS0UlAC0lLSUAFFFBoA868Dtu+Jvj8jtNaD/x2SvRa838AA/8LJ+IRJ4+1W2P++Xr0cZycj6UEx2FpaSloKCikooAM0UUUAFLRRQAUlFFABXC/GAf8Wv1nH9xf/QhXd1wfxhOPhdrPPVFH/jwoEzq9CG3w/po9LWL/wBBFaHas/Q/+Rf07/r1i/8AQRWhQC2ClpKWgYneiiigAooooAKSlooAKKKKAA15rZf8nD6j/wBgEf8Ao2OvSq81s+P2hr/30If+jI6CWelCiiigoWkoooADRRRQAUUUUAFJS0UAAoopaAMLxku7wZrQIz/oUv8A6CazvhlIJPht4fIzxZIvPtxWt4oAbwnrAIz/AKDN/wCgGsT4VHPwy0E/9Ow/maCftHZYooooKCiijFABRRRQAUd6KM0AFFBooAOKKKQ0AeaeIZDD8d/ChDYEljcIw9Rtc/zAr0yvNPFAx8bfBZ4w0F0CfpGxr0oUER3YtFFFBYUUUUAFGaKKACg0daKACgmiigA/CqGtp5mh36ActbyD/wAdNX6r3i77OdeuY2H6UCexyXwomM/w10bPVI3T8pGH9K7WuA+DZz8OLJe6zzg/9/Wrv6BQ2CiiigoWkoooAKMCiigAooooAKPeiigBO1cNBiH4y3fbz9KT8cOa7k9K4SR/L+NEMf8Az10o5/BqDKp09TvKKKKDUTmj60GigAYcccU3BBFPpD0oAZxknJprITyefapMZ+8KME8HpQBEgAGCxGe1Mkg8yQFmGB2qUqoIJ7VGV3HGBjOcigQggfaQrlM+hziq0kAdNsY2YyCyDDHPXFXBlFwM5P5AVHJFHNgFzkmgDgPiJpGoT6Zp7afaTzT2t5HJF5eP3Q7nnr06e9dlFeyxaZGZ7eZpAo3GVcc+9Zfje31N/Dcsuj3ckV3GyuHifB25+b68VqWcNw9lB5lyS+wE7znPvSRK+It2l1FO+3yzHMUBKEdvr3pbieG2kBceXkf6wrx+J7VT/s+R23Lc/PjlgxNVZtPLyKbiSQRZ5bPJH64pll263CEyWqeeG6CKXaD/AEqpLrWpQyRqNGd0x8xEoGPwqWP+z7X97C0zEdTy2Kn0+Sa8tJHM5AJIQgDcPc9s0AT22o21xb+aGZcHlZFIYfgeaJ5reGB7mOPzDjH7kAsaZaLeMW+0NbuFOFZVOW9z6fSokjvYdzXMFrPjJDwAoQPTBzn86ALVlf299FvhkViOGXup7g042kTR7AvlqW3MF43fWqstpaXloks8Tpt+bIJVh70230eOGUOl5eNERxG0xIHvQBqDGMDtVS9s2u0SPeBHn58jJI9j2rPm8MWsknmxXV9BJ13Rzn+ta9vAbeERmWSXH8UhyaAIIoLa1WC1ht1SNFxGqp8qAfyqY4Eb7QOPbAqbrxUDKy8DDRnJbcck+woA437VB/z9aT+b0Va+zQf9Cnb/AKf4UUXEdZLgRt9K4XwAM6r4hYHI+14zn/P+TXcXB227n0FcZ8OAGttYuBj97fvz64AqXujOXxo7iiiiqNQooooAKOKKKAEpaKKACiiigAoooNAHDtiT4ux8qGj0w8HqQWrt64e0Ab4uX+RyunxkH6n/AOtXcUluzOnsxaSlpKZoBHFIQaXFFADN2OvQ0mIzHjt+tKRxTfLHZqAIpUQ4DSFT0BxigwwMFSVixHTLGnFASA2aY0PPyhvxoGKbOzKnMUeOpNVv7PtYSJYi+eoCnr+VSCFozvUYPqKdlm4JIUdQAKAHx5liPliWJh/z0yf61R1aPUY9Pne2ghu7ll2ojYX9TV0tsGUd29j2rA8XX5s/DF5PLqxsVKgLKsIcgk46UEy2Nm3m1BLKETW0Ym2DIVuAaeIJLgq10ceigVDYy3X9n2275m8tSWI68VZbzphgqR6+lA0PWSJT5Cx4UcHjApoMIBAiGenFO8hSdzDb9afgBQFGcdDQBHEhGCxwO3NSAKOc5owTjJp4FAC4GPWjnFHFKBQACilxRQAUUCigArhIyZPjRMD/AMs9HTHPrI1d2a4WyyfjPqRP8OkQgfTzGoM57o7qigdKWg0EooooAWkoooAKKWkoAKKKKACiiloArXpxZTn0jb+Vcb8IW3fDXSz/ANdP/QzXZXxC2M5PQRN/KuO+EI/4tppRxjIc/wDj5oI+0dzS0lLQWJS0UUAJS0lLQAUUUUAFFFJQAtJRRQB538U9/m+EdnT+3rbP516IK88+JbKdX8Fo3fWoz+QNehiglbsKKWigoSilpKAClpKKAFpKKKACiiigBaQ0UHpQB514BOfiF4/HcXsHP/AGr0WvO/h+P+K+8ftjGb6D/wBANeiUCjsFFFBGfwoGFA55oooAKWkpaACiikzQAtFJmigArhfi+gb4X6zk4xGD/wCPCu6rhvi+QPhfrWe8Q/8AQhQJnU6EP+Ke00f9OsX/AKAK0KoaH/yANO/69Yv/AEEVfoBbBRzRRmgYdaKKKACjrRRQAUUUUAFHNLSd6ADvXmtupH7QtyeedBz/AORUr0rvXm8R2ftByD+9oJH/AJFT/CgmXQ9IooooKCiijFABRRRQAUUUtACUUd6KACiqepalb6VafaLjeVLBQqDJJP8A+o/lUdjrVnqFx5EJkEoiWUq6FcA//rHtyMZrN1qanyN6k88U+W+pF4kGfDGqj/pzm/8AQDXPfCMk/C3Qif8Aniw/8iNXSeIf+Rc1P/r0l/8AQDXK/C+7gtfhJpFzIcRRW7k9Mn524Ge56VbaSuxN2ldneUVh2XivT768jtkSdHkOFaQKBn069+lat7eRWFnJdTkiOMZO0ZJ7AD8azhXpzi5xlogjUjJXT0JJJY4VDSuqKWCgscDJIAH1JIA9zT68h+JWutq9nZpbMyWaSZeKSMBjJg4bcCcjG4Y4/HIw7xR478S6NeLowuLZLq1SPz7qKIEyuUDHAbIA+YduSueAdo9TC4H63ShUoTT5r/K1v8yPbx17HrlMeWONo1d1VpG2oCcFjgnA9TgE/QGvHdV+JXiSTTrGWCFbESqxacW3yyMrMCELlgVAKZ77s9qg1LWdY8SR+E7lpbaO++1PBDIuD+9DRYkcDIXkr8u3sTyGAHRHJ62jqNJO/wCCf+QOsuh7ZVK81jTNPlEV7qNpbSFdwSadUJHTOCenB/KrUQkESCVleQKN7Iu0E9yBk4Htk/WvL9J0Cy8XeL/FkusebK1vP5ERRtmwZdQeOpURqBnI65Brjw1CFRSlUdoxXTfV2LlJqyR6jFLHPCksbrJG6hkdDlWB5BB7is+XxDokErxS6xp8ciMVdHuUBUjggjPBrmPhRcyz+D3jkfckF08cYwBtUhWx78sx/GuT1vwJqcmoa1rwk0+WyiuZ7jY0zHzFUlmX5RweqkZByD7GuingqXt50qs7W28yXN8qaR6xeaxpmnyiK91G0tpCu4JNOqEjpnBPTg/lVi3uoLy3W4tJ4p4XztkicMpwcHBHHUV5Vq2gXPj+TTNS0dbS0txYCNoJZMGErI6gYUH5T8204xhD06V03w7uoo7C+0MWkUF1pc5iuHhJKTsSw35POfkOc+gxgcCa2ChTo88ZXkt126fmEZtyt0MbxluX4x+B2XuLgcdfuHP6V6ZXmfjv5fij4EZeHM0659ttemDoK84qO7ClzRRigsKQ0tGKACiiigAooooAKKKMUAFRzDMEg9VNSUxsFSM9qBM88+CxP/CDSI38F/OAPQbq9Grzj4N5HhW/RuqapcLj/gX/ANevR6BQ2CiiigoKKMUUAFNKkkYYgDr706igAozRSUAFLRiigANcDqvyfGLQ22/62wmTcfbniu+rgfEmE+KvhRidu6K5UEHk/L0oM6mx3tLSCloNANIaUUYoASjpRS0AJ0oPWl7UnFACf1oxkYPNKetJtHY4oAQpkHNR4A9D2GRUpUnGcUhOG56UAcn8RVQ+BNUd/MIWLOFcp3rU0UZ0WzccuYIxuY5PQVU8cmL/AIQjVhMjtGLc5C9au+HQZPDmnEgc28ZP5Uupn9stnasZRnKRsMDAHNLLNHtEWzeCvCgcfjUjJhuCMYx9KhkRpOCwAIzx6Uyys4gYRvFAQB05wn6VFFZBWMy3cKM55YAZHsKvu1wIzyvt8vIFQKzBRvEQC8/dJYn1oGY89hJa3IaHUpFaWTH7ssxz6kDNaM9zqVowijlhuWOAodCCT7kcUoEUjF5WZcHho16fjV0NaORKXBK8bmOKAKeoXt1FaSLNYGXPAEWSK0raZbm2jlQ9R+VQmYPehhIrQJEWOOef/wBVQf2laxTgkypuwAhiI3Z7igDK8QXUllfRTQXLQsAAy54fJ6Af1ro7WYzW6PuRsjqpzTLqwtb9cTwq/HBPUVV0/TptPkKC7Bts/JF5QGPxoA1DTTk5Ge3anEA03JwTtxQBm5m/55z/APf00VL5rf8APT/yCf8AGipsIk1A4sJj/s8cZrl/hqP+KalbIO66lPB966XVmKaXdOO0ZP6Vz3w2XHg63YDG+SR/rljTe6I+2dfR25oopmgfjRSUtABRRR1oAKDRRQAUUUUAFFFBoA4jSyZPirrJJOEsoQPzNdvXDeHMN8SPFLeggXr/ALNdzSRnT2CiiimaCUUtFACHNJz7U6kxQA3GRimgFeB09KfiigCPkHg4zRgdQAD+VPxSYzxigCLarHlGB9a434n2guPCDwqVBa4iADEAk7h69a7jFcD8WP8AkW7NcA79Rt1x/wBtBQRU+FnbwBktYk+6VQDA5HSpOW4LEfpSooCqB0Ap+DQUthhRSeWzj1p4/OjH5UuKBhj8KKMUtABRR2ooAKKKWgBKKKKAA1wmmHd8Zdb/ANnS4B/48TXd9q4HQj5nxf8AFTf3LS1T9M0Gc90d9RRRQaC0maKKAAUUUUAGKKO9FABRRRQAUUUUAUNbYpoWoMOSLaQ/+Omub+FKbPhnofvBn9TXQeIW2+HNTOcYtJef+AGsP4XLt+GuhDH/AC7A/qaCPtHX0UtJQWLRSUtACUtFJQAUUtFABSUUtACUUtJQB538S/m1vwUvf+2kP/jpr0QdK88+I/zeIPBEY+8dXB/AKa9D7UErdhRRR3oKCiiigAopaSgAooooAKMUtIDkUAFBooNAHn3gE58cePR6ahF/6Lr0EV558PlI8aePSTz/AGjH/wCgV6HQTHYKKKKCgpaKKAEopaSgBaKSloASiiigArhPjChf4XaztGcIpP03Cu7riPi6234Xa57wgf8AjwoEzp9C/wCRf030+yxf+gitCqGjLt0PT19LaMf+Oir9ALYMUUUUDDFFFFABS0UlAC0lFFACYpcUUUAHevNWXb+0FGc/e0Rv/Ri16V3rzqQA/H6D20J//Rq0Ey6HotFAooKCiiigA/GigUUALSUUUALRSUUAcr42tkNnb3WX8xZPLA3fLggnp68f54rOn0111rUrSzeXzILVGiO9txK+We3U8cDpnGMYGNbWdai+3nTTpTXxjKuRnv14AB7EfmR0qjeateymZrfQri1vbhAnnqGL4B5x8vpxn6egrw8SqMqspX+5Pomn0t2OGqoOTf6PzGSXU+t2mqX8oKQQ6dJEFBYAuUy3GcHv+G2sbwUc/ArTv+uf/tc1prfXVj4bn0+XR5kSSN0edgVGXyMn5fcDr2FT/C2za2+G+nWNzskaEzwSY5VsTOD16iurDONWhKnf3mtdH1/yKp2nFxvq/wBRuozx3Ft4eis54zdoEVSHBEbYQfMMHvj8jwaueKL231HRSbOUTCC5USFP4eGGfpnv0Nblnoem2FwJ7a1CSgEBizNjPpknFTW+mWVokyQW0aJMSZFxkNntz29ulJYSs4yjJr3t9+isrfqV7GbTTe55N4yXTV8jTbjxD9oEa70MamTyjggLgEgA8dDkdcdM1bjQ7+aW0vkvb9b6dRi7JYm4GF2lTwfTnJz8vfk7PiX4XXupa495pdxaxWzhWWOaR1KkLtI4B3Dvz69OAa9DsdIt7XTtNtZlSd7CJEjlZccqoXOO3TOPp6V7M6csNhaawlZqW7WjSulfeN7eTb6MzWHk2+hyX/Cup4rLT007xFqNhJBCySfMSCWIZtoVwE56gEg4XqQSXJ8MraPQILGPU50vre5a5ivUXGxjtBAUHphF75BGc44ru6K3/tDE/wA3nsv8vP0Ov2cexV021lsdNt7We7lvJYkCtPKBuc+px/8AXPqSea5PXPh3HqWq3Ooafqs+myXastykaZSQEAEYBXg4JOc5JrtqKxpYmrSm5wdm/T8thuKasziW+HUKWuhQ2uotbtpkrTPKsCl5nZlJb0BGzAyG4wDnHNe8+G9w1xerp3iK5sLC6dnayjjPljcPmGFdQR2xjpgc4rvqBWyzDErXm/BdXft3F7OPY4a6+G8Ub2r6Fq1zpMkUHkSPECWmGd2WIKnJPXtwoAGK2vC/heLw1b3JN1LeXl0++4uZMgyHJxxk+p5ySSTz0A3iwpe1Z1MZXqQ5Jyuv667jUIp3SPMfiJiP4ieApGxj7ZKv5gV6aK80+JoC+KfAk3cart/MCvSx0rmFH4mLRS0UFiUGiigAopaSgAo70UUAFHeijNABSGlpOooA85+EDf8AEq1+LOdmtXH8xXo9ebfCjKS+LbdusWtzdB616TQRDYMUUUUFhiijpRQAUneloxQAUUUUAGaKCaTHFACmuA8Zg/8ACf8Agwr1+0TZOe3l133avPfiCTH4n8GzCQxn+0SmcZ6r0oM6vwnoVLSDpS5oNAxR+FFFABiiiigAxSYGfelooASjFLRQAgGBij2paTFAGN4shE/hTVI2CkG2k4bp0qDwYS3g7RycZNtGTj6Vd1+MyeHdRRept5Mfkay/h9K8/gXSJHYM5t13MBjJ70upm/jOlI46U3G4diKeRkdaClMsrlG3ZPzAfw5p6lwcSKoTt7U7nGO1IyhlOc496BlXd8u0nhjkKBzTJcyEwtDGsh+6cdfWrIV1kJABwuAoGKN5HDRqB3INIDLe2UsZYhIsnGdpxuwenHbipJpLm7xCbWFnxkM5+7VlpZYx+6XAz3oaYyRjJ2FMFiuBk+gzTAqmW4t7uISQyMeFJjl+X/vn0qQazbyXi28kLJz8ryYwT7f/AF8U+USxsj28spDfMRIcjHTHtTor6GRgtxCEkIwWxlfpmgDSBBAIOaii88A+bsJzxt9KRRHbRZU4jHqelPLHAIyQf0oAZun/AOfeP/v5/wDWopftA/uv/wB80UrgZ3iJxH4fvmJA/ct1HtWd8P4xF4I0xR/zzJzjryateLnKeF79v+mLfypvgsFfB+me8APNHUz+2b5ooopmgUUUUAGKKO9FABiijmloASgUUY5oAKQ0tIaAOH8IqH8b+LpiBkTxR+pPy13NcJ4CIfxB4vl551PAJ/3BXd0kZ0/hCilpKZoFGaKMUAFFFFACUYpaKAEopaKAErgfiiol03RYjyJNWt1x685/pXf1wHxKXzJ/C0Gfv6zCfyyaCKnwnegdqXFFLQWJS0UtACUUUUAFFFFABS0lFAC0UlLQAh6VwPhb5/il40brj7Kv/kKu9PSuB8G7X+I3jl17T2y/+QqDOXxI7+iiig0CiiigAoooxQAUtJ0ooAWkoooAKKKKAMjxSceE9YIxxYzdf+uZrL+Gq7fhzoA/6c0q/wCMzjwTrpzjGnz8/wDbM1W+H3/JP9C/684/5UEfaOlooooLDvS0lLQAUlFFAC0lLSUAFFFFAC0lLSUAed/EUZ8V+B8df7U/9kNeiV5749bHjfwKMZzfyH/yGa9CzmglbsWkoooKFpKWkoAKKKKACiiigBaSiigBaSiigDz34ekN4x8eH/qJR/8AouvQq86+HII8WeOwf+gov/oNei0CjsFFFFAwpaKSgBaSiigAozRRQAUUUUAHSuE+MOf+FX6zj+4uf++hXd1xPxbP/Fr9d/64D/0IUCZ02hnd4f04+ttEf/HRWhWfogxoGnD0tov/AEEVoUAtgFFGKKBhRRRQAUUUUAGaKKKACiiigA715zLIU+P9sME7tDdfp+8B/pXo3evN7jj9oCyJ76JJj/v4KCZdD0ilpKKCgooooAKWkooAKKKKACig1Dc3C28e4jNAHC67r2m+G9f1LV9TfbBbxIQAMlnwgAA9etecxfHS1/4SC51WeyuJF2+TawCTCxx8EkjuxI/StL4oaTdeJrS5itf9esqSqgIG/C425JHr+lePr8OvFJbB00AepuI//iq86hWpR51KST5n18zGjUhG6bW7PpCDxxpPifwgRb6jBLetGhkiDAMG3KSMfTNa/wAOjnwivPS+ux9P9Jkrw/wZ4AuNH1BNUvrmNZolO2FRkkkYPI46E17b8NePCbf9f95/6USVVGpGeJbi7+6vzYuaMq10+h2NFFJXebhRRS0AJmlpKCaAFpDRS0AJRRRQAYoooPSgDzP4qrjVPBUgBJXWUHH0/wDrV6WvQV5t8WGCT+EJCPu65F/I16Sp4oIXxMWiiigsKKKKADNGaOKKACiik70ALRQRRQAUUGg0Aec/DXjX/GyZXjV2OQAOor0avOPh0Avizx1GOg1TI/EGvRxQRDYKKO9GKCwooooAKKKKACk6UuaKACg0lLQAdq8++Jfyah4Rl3YK6xEPzr0GvPviqfLtvDkv9zWrc5/E0GdT4WegYytA+tIOaXn0oLQtHSkFLQMKKKM0AFFFFACUUtFABRRRQBT1ME6XdrgtmFhj14Nc78NpBL4B0pgAP3ZGB2wxFdPeLusp09UI/SuS+FyCPwJZIP4HmQj3ErCl1M38aO04pCDnOaMYo6mmaBTMce3pinn6ZpOc+1ADSOen5U0rn1xnPIp4A7U1lJ70ARlA/HOR1yMUyS3DryMnsByKmxyMg+2OaMMDu/TNAioV+zgiJRz97I/SpFMUw8s25WM8EkAAn+dPaNnG5mOe4HHFMaMFeVwM5xQMkthFtZYVAjDYwBxVjPOMVBbcDb82MdxwPYVI46AZ+ooAfx60VW2n/pv+dFIDF8cP5fg/U2zj9w3PpxVvwmAvhPSgOn2ZP5Vl/EY7fBOoe8eMVteHl2+HtOHT/R4/5UdTJfGzTooopmoUUUUAFFAooAWkoooAKOlFFAAKQ9KWmscKaAOG+HXzXXid8536tLn8MCu7rg/hg3nWGt3HH77Vpzj8a7ykjOn8KFpKKTNM0FoozRmgAoozRmgAoozRmgAooozQAVwfj8B9f8Go2MHVgefUKa7zNcF44Bk8X+C1/hGoO34haDOp8J3opaTNGaDQKKTNGRQAtFGaQkUALRSZo3D1oAWik3D1o3L6igVxaKaZFA5YfnSeYg/iH50BdDzXn3gIlvGnjpyP+YhGufold600YHLqPxrzzwDcQp4y8clpVBbUFIye22giTXMj0eioBdW56Tx/99Cg3VuBkzxAepYUF3RPRUH2u2/57xf99ig3tsv3riIfVxQHMieiq/261/5+Yf8AvsU06jZDrdwD/toKBcy7lqiqZ1SxHW8tx9ZRQNUsT0vLc/8AbUUBzLuXKKptqtgoyb23A95RR/athjP223x/11FA7ouUVTOraeBn7bb/APf0U06xpo4OoWo/7bL/AI0C5l3M3xwSPAfiDHX+zbj/ANFmo/AA2+AtCH/TnH/KqnjbW9LbwNryR6jaM76fOiqJlJJMZAHWovAmt6VF4F0WOTUrRXS0QMDMoIOPTNBN1zHaUVmnX9HAydVsv+/6/wCNB8Q6MOurWX/gQn+NBXMu5pUVl/8ACR6J/wBBex/7/r/jSN4l0NBltXsR/wBvCf40BzLuatFZJ8T6COusWHP/AE8J/jTD4s8PA863p/8A4EL/AI0BzLubNFY3/CV+H923+2rDP/Xwv+NJ/wAJb4fJ/wCQ1Yf+BC/40BzLubVFYh8X+Hl661Yf9/1/xqM+NPDIHOu2H/f9aA5l3N+isD/hNvDQ665Yf9/xSf8ACb+F/wDoO2H/AH/FAc8e5zvjzafHXgUNgf6dKc/9s69B968i8aeK9AuvGvgya31W0khtryR5pUlBCDbgZrvB478LHH/E+sP+/wAKBKSu9ToqK50+PfCg66/Yf9/hSf8ACf8AhP8A6GCw/wC/woHzLudHRXLj4ieEvMK/2/p//f4U5viF4RUZPiCwx/12FAc8e501Fc2PH3hNuRr9h/3+FN/4WF4S/wCg/Yf9/hQHNHudNRXLn4i+EFGT4gsP+/wph+JHg/Gf+Egsv+/tAcy7nV0Vyh+JPg4f8zDYf9/aD8SvBoAP/CRWP4S0BzLudXRXJ/8ACzPBo/5mGx/77qNvid4MA/5GC0PPQPQHMu5mfDti3i3x3kf8xRf/AECvQ68W8B+OfDmn+IvF893qcUUd5qAlgZ/+Wi4IyK7hvil4LXrr9r+ZoFGStudjRXGf8LV8Ff8AQetv1/wpP+Fq+C8A/wBuwc/WgfNHudpRXEn4teCc4GtxH6I3+FJ/wtvwTnA1uIn/AHW/woDmXc7eiuH/AOFu+CB/zGo/++G/woHxb8GZP/E4THb923+FAc0e53FFcQPiz4NK5Gq/+QX/AMKb/wALb8Gnpqbn6QP/AIUBzx7nc0Y5zXCn4u+Dgf8AkIyE/wDXu/8AhQ3xd8HAZ/tGU/8AbrJ/hQHPHud1XC/GB9vwu1n3jA/8eFN/4W/4OxkX859P9Fl5/SuV+I3xI8Na54E1XTrOeaWeSMKuYGUZyO5FAnOJ6vog/wCJDp2ev2aL/wBBFX6800j4s+E7bRLCGW8nDJbopxbueigdhV0fGDwmfuzXrD1FlL/hQCnGx31FcCfi94Zx8i6k/wDu2Ev+FN/4XB4bH/LHVD/24yf4UBzxPQKK4AfF7w6RzBqwPp9gk/wpB8XdAI4tNXJ9rCT/AAoDniegUV5//wALc0LnFhrWe/8AoD00fF3Rj00rXen/AD4NQHPE9Corz/8A4W3pHbRtf/8AAA/40h+Lelj/AJgniA/SwP8AjQHPE9Bo4rz/AP4WxppGRofiH6fYD/jSf8LYsc4Xw74iY/8AXj/9egOeJ6DXm1wCf2grM+miyf8AoYqwfirZgkHw94hB97E/41wt349T/hcNlq7aJq6omnNALc2/75snOQuelBLmme90V55/wtSMn914U8Rt/wBuYH9aT/haTAn/AIo7xJj/AK9V/wDiqCvaRPRKM15vJ8WTDEZZvCPiCKMYy8kKKoyccktiqtv8YgInNzoF5K6ZZmtGRkVN2FzuYEHkD0J+uBtDD1JwdSKul+ovaxPUqK8yX4x2jK7R+HdWZUG5yDD8oyBk/PwMkD8RTV+McUqSGLw3qLbF3MzSRbVGQMsQxIGSBnB601ha17cj+4PaxPT80ZrzKw+Kd/ewhbfwlqF9PGAJntHQpk9wCcgHB6+/JxmjUPibrMIjgTwle2d1OdsBvcEOcjICqcseR6dfwLWGqut7C3vB7WNrnptMZFfhhke9eYQ/EfxJbX/2C/8ADEk95KAYYLZTG5GCScOTkcdvQ9ezNX+JfiOx8jf4abTd+7H2/wCfzMY+7tYYxnnPqKtYKq6yoq13qtdGvUXtY2ueiX+k2t8B5sEbEfxbfmx6ZqK28O6bAPmtY3b/AGxu/nXncfxU1yPTDcz6DFLG7mNLyOTbEj7chWUksTxnqOCOnWrD/EDxbp93FBqPhuN5bgbbeFC0DSNkdGYkHr068j8SWVT95tLS/bW29u9he1g+h317pWnrZTlLG2DCNiCIlyDj6VyfwW/5Jhpv/XWf/wBGtVa68Z+M5LSdF8AXSEoRua8XA469K5L4Y+J/FOn+DYLPTfB8uoW0UsuLkXQjDEsSQAR2PFcUYxjsrAnFO6Pds0Zrzr/hMvHhGR8O2/HU1/8AiaQ+LfiA4JXwAi/72pKf/ZaovnR6NmjNebjxP8SCOPA1tn31Af4Uv/CR/Ezn/iibL2/4mAoDn8j0fNFecNr3xQ4K+DtOHrnUAaamv/FAtg+D9O/8DwKA5/I9Jorzj+3PiiwyPCOmD634pBrHxTx/yK2k/jfUBz+R6RRXm51P4rnkeHtDHHQ3ZNJ/afxZ7aBoP1N0f8aA5vI9JzRmvN/tvxbPH9keHF9zO5/rSfa/i5/0DPDX/f6T/GmHN5Dfi4cN4RJICjXISfyNelCvAPiLJ8QDDocmt2ukIqajH9nW2cndNg4znt1rt0k+LbIP3HhlM/3nl4pEqWr0PSc0hJ7V50V+LZ6HwwPo0v8AhTPK+LuOJfDP5y/4UFc3kek5orzZrf4tsABdeHV9TiT/AApxtfi0Bn+0PDh+kcn+FAc3kej8UZFea/YPi25z/a/hxfpHIf8A2WnrpnxWZfn13w+p7bYHP9KA5vI9HzRXnX9kfFQ9fEehj6Wjf4Up0X4o9/E+jf8AgEaA5n2PRKao2rjn8a8/Gh/Ew4z4q0kev+gmj+w/iYf+Zu0v/wAF9Acz7HoWaCa8+Ph/4k7ePGGnZ/7B3/16Q+HviR28Zaf/AOC//wCvQHM+xH4FPl/EHx1bk5zeRSfmlei54rwjw1o/jYfEPxNbWniK0hu42ie7uJLXcJSV+XC9uK7geG/iHn5vHFoPppYP/s1BMHod8CSORzS5rhB4Z8e5/wCR7gx1/wCQSv8A8cph8M/EAuf+K5twp9NLXj/x6gvmfY7/ADRXA/8ACK+POP8AivY//BUv/wAVSf8ACK+OyMnx7GD6Lpa4/wDQqA5n2O/oJrgD4Q8cH/moJH/cLX/45QfB/jZhz8Q5B9NLT/4ugLvsd9mlzXn3/CF+NwmB8RJSfU6Yv/xyl/4RHx1H9zx+G7/vNLQ8/wDfVAXfY7+lzXn48L/EAf8AM9wnP/ULXj/x6pB4X8df9D5H/wCCpf8A4qgOZ9ju81578YAB4Vsp88wanbSf+PY/rU58LeOSOPHq5/7BSf8AxVcb8SfDniqx8KNdah4v+3Qx3EREP2IRfNuAByCenX8KCJttbHtaHKA+op1eeWvhjx29pE3/AAnaAlAcf2ap/XdVj/hFvHW7I8eRgZ/6Ban/ANmoKUnbY7vPFLmuCPhbx0VA/wCE7j69Rpi//FUn/CLeOhx/wnseD66Uuf8A0KgfM+x31JXCnwx464x48j986Sn/AMVSSeGvHmwLH46hPqTpSg/+hGgLvsd3RmuD/wCEc8fbf+R1tvb/AIlq/wA81IPDfjnqfHEO7H/QKXGf++qBcz7HcZpa4X/hG/HYz/xXMB/7hSj/ANmpx8OeOsceOYP/AAUr/wDFUD5n2O4pK4geG/HGcnxzEPTGkp/8XTl8O+NwmD41iye/9lrx/wCPUBzPsdnJyjD1FcL8KQ0fhu8tmZSLfUbiNdpzj5s9fxp48M+OCmG8dR8/9QpP/iq5LwRonitxrFvpviuGCG2v5Yn8yx8xnfPLcnjPtS6mcm+ZaHs9Ga4dfDnjsPk+OLcj0/slf/jlL/wjvjo5J8cQA+g0lSP/AEKmaXfY7ek/GuLPh3xxtwPHFsT76Ov/AMcqFtA+IIbK+M7I8d9LAx/49QF32O44J6dKU59K4U6F8REG4eMdPY+h0wAf+hU86H8QSP8AkbrDP/YNH+NK4cz7Ha5xzzQccHPWuGXQviHzu8YWHTj/AIloOT+fFSf2L8QTGE/4SrTge7fYMn+dAXfY7RhzwPzpuD1I3c9xXFNonxGDfJ4q0wqP72n9f1oOjfEVosHxRpQPqLA/40w5n2O2iZtxDn6DGKkOfY1w0eg+Pnj/AHni6xDDONumA/TndWg+l+LU0tIofENq96T880tllfoAD/Oi4uZ9jpvJj/uCiuI/sX4if9DPpf8A4An/ABopBzPsSfFSf7P4Cv5OpwFx9SKzNL+KmnrptrEuh668iwqCI7FiOB61qfFF9ng2UD+KWMf+PCuus1AsoOP4B/Kh7kWfO7HED4oKw+Xwn4kJHUfYG4pB8Tblx+68F+I35wP9DNeg7aMUy7S7nn4+IurM2B4C8Q49fJoPxA19j+68A60f97aK780YoCz7nA/8Jr4rP3fAGof8CuIh/WkHjLxk4+TwDdD/AH7uIf1rv8UuBSDlfc8/Hivx2c48CEfW+j/xpf8AhJfiATx4GhHudRSu+o5oHyvucENf+IbD/kT7JP8Af1Ef0FO/tj4jH/mWNKH/AG/n/Cu8wKOKYuXzOE/tP4lN08P6Kv1vW/wqOe7+JhjZl0/QIxjJzPISK7/FQ3P/AB7SY/umgTjpueN/D7/hOzpF3Jpg0fyJb6Zm+1GQsJM89DyK7AJ8SzjMnh4e2yU/1qP4Qj/ihUbGC13Oeuf+Whrvu1JChH3Tifs3xGbH+n6Anr+4lP8AWmf2d8Ruf+J3oYz0H2N+P1ruaKZXIcOdL+ITHnxDpCD/AGbEn+tJ/YvxAIOfFeng+2nD/Gu5xRigORHCN4f8fOQf+EytV/3dPWlbw345YMP+E4C56bdNi4/Su6ooDkRwQ8I+MiCH8eXAJ/u2UX+FP/4Q3xRgg+PdQIP/AE6w/wCFd1QaBezicCPAniHJLePtX59I4x/Sn/8ACCa2QQ3jvWjnPRYx/Su7oxQHs4nAn4e6m2d/jrxDz2SUL/IVyXiPwRcQ+L/DWnzeKNcuVupJMPJPl4iq5yp7V7XXAeKDu+KPg1FGSPtLH6eXRuTOCSHj4ayd/GPic+4vsf0qQ/DcHj/hK/E2PbUD/hXcUUF8kThv+FaW5PPiXxMeMc6m9B+GVmRj/hIfEo+mpvXc0UByROEPwusiST4g8RkkY51Jqb/wqnTCMHW/EJ/7iLV3tFAckTgz8KdHZcPquvyD/a1JzSL8JdBBz9t1kn1/tBxXe0UByRODHwm8PDrc6u311CT/ABpf+FSeGsjL6ocet/Lz+td3RQHJHscN/wAKk8KkYaG9b63sv+NM/wCFQeE/+eF7/wCB0v8AjXeYo60D5InCn4ReEOps7sn1N9N/8VXFeCPh54c1bVPE8F5bTyRWWom3gP2h1O0DoSDya9uPSvPPhcd934xkzktrk38hQQ4rmSLP/CoPB3bT5x/29y//ABVOHwi8Fj/mFyn63kx/9mruR0ooL5UcP/wqTwXznSn/APAqX/4qmn4QeCz/AMwqT/wKl/8Aiq7qjNAcqOIHwk8FAY/sgk+puZc/+hUv/CpfBHfRv/Jmb/4uu2ooDkj2OJ/4VH4IAI/sXOf+nmb/AOLpP+FR+CP+gOf/AAJm/wDiq7eigOVdjih8JvBGMf2IpHvPL/8AFUo+E/ggf8wNP+/8v/xVdp2ooDlj2ON/4VX4J27f7ChxjH+skz/6FQvwq8Ej/mAQn6yOf/Zq7KigOWPY8z8Z/DrwjY+Ctau7XRLeK4t7KWWN0LAqyqSD19RUnhP4ceErvwrpV1daFay3EtrG8jtn5iR161ufEuQx/DfxAwbH+hOPz4rT8Jp5fhHSFHazi/8AQRQTyrm2Mr/hWPgsf8y7ZnnupP8AWnn4aeDD/wAy5Yf9+66uigrlXY5MfDPwWOnhyx/FDS/8K08F/wDQuWH/AH7rq6KA5V2OV/4Vt4Mxj/hG9P8A+/VP/wCFc+DcY/4RvTv+/Arp6KA5V2OYX4d+D1zjw3pvPrADTh8PvB46eGtM/wDAda6WigOVdjm/+EB8Ij/mW9L/APAVf8KcPAfhMZx4c0vn/p1T/CuiooDlXY57/hB/CvP/ABTumcjB/wBFTn9Kd/wg/hT/AKFzSv8AwET/AArfooDlXY8l8YeGPD9p4+8FQQaRZRpcXEyyRrCArgJnkdDya7weCvC2c/8ACO6Vn/r0T/CuY8Zjd8VfAfGVDXZ/HateiigSSuzD/wCEM8MYIPh/SyD/ANOif4U3/hC/C5AH/CO6Xx0/0ROP0reooKsjC/4QrwtjH/CO6X/4CJ/hSr4M8Lx/d8PaUP8At0T/AArcNFAWRhnwb4Zyf+Kf0vn/AKdE/wAKX/hDvDWMf8I/pf8A4CJ/hW3QaA5UYg8J+Hen9gaaAD/z6R/4U/8A4RTw7/0AdN46f6In+FbFFAuVdjIXwr4eVsroenA+otU/wpR4Z0EHI0XTx/26p/hWtRQHKuxm/wDCPaLs2/2TY7fT7Ov+FH/CP6KP+YTY/wDgOv8AhWlRQOyPLfh1pWl3WteMkl060fytXZVDwqdo2jgcfWvQhoWkg5GmWQP/AFwX/CuK+FzbtS8ZsOh1uT/0EV6LQTFKxnnQ9K3Bv7Ns8jofIX/CnjSNOGMWNrx/0xX/AAq7RQVZFMaXYf8APjbf9+h/hQdKsD/y5W//AH6FXKKAsiqNNsh0tIP+/YpBptiOlnb/APfoVbNFAWRX+w2nX7LD/wB8Cj7HbDpbxf8AfAqxRigLIg+yW3/PvF/3yKPslt/z7xf98ip6KB2Ivstv/wA8Iv8AvgVw3xdhgj+GOssIkDeWuCFH94V31cJ8ZBn4Xax/up/6EKBNHS6Ha2/9gacTbxA/ZouNg4+UVoi3hHSGMf8AARVbR2LaLYswwTbxk/8AfIqdLmB7mW3SRTLEql1zyoOcfyNALYkEMY/gX8qPJj/uL+VPooGN8pP7i/lR5ajoo/KnUUAJsX0H5UbR6D8qWigBNo9KNo9KWigAwKMUUtADcc15xe4/4X9pQHP/ABJpc/8AfVekd682u/8Ak4HTef8AmDS/+hUEy6HpGBS4oooKGSxRzxPFLGskbqVdHGQwPBBHcV4Jb28k/gfUbCKwn+3WV+tzdN5OCkQRkwx65Vt3ynoCT0DY9R+IWvX2geHo7jTpEjnluFi3soYquGbIB4/hxyD1P1ryrSfilr+rxyGPxDFA6KzCK4tkVnwM4GEIz+Nezl7lRp810uZq121qvRPuYVFzO3YjsNOtZ49VktDq91aQ2JaR4oVj2ybgVEg3sDHkBjg5+XOMKTVjw3Yx3evTWukpPfGWwuUDTQ+UY2aJ1B4cgAkquWOPn6Zwa9h8Hapc614Tsb+8ZWuJVYOVXAJVyucepxk9s+lbtbVs3nGU6bjrqt/l2X6CjRTs7nCfDHUbY6M+ii0ngvrJma6Lw7QWLt1P94AAYbB44yAcHxHtruKXQ9btrZrmPTLkyzRoDnHyvkkA4X92ck9Miu7pa8362lifrCjvfS/fc15Pd5TyaHX/APhIPHEniWxs5RZaNp0juJjtMmEfAyAQpJc4GTwpPtV3UvGNhf2Wi6xq3hxZ9NdplJKmRopRwANyqrKRz15IPQx8+mUlavG0nJP2eysvee1n+rv+BPs33PGIFsNWuPE2rwaLcnw8LVdkEKLHtnAQBgBkAr87FhnCscj5sGLwrYy+I/G9jcC91LULay2yzXN0oVoypLIvLvwWA4zk5bgYzXtlFavNXyyjGO6stb20t2389PPYXsdb3ILo7bSYnsh/lXBfBVSPhvanBw1xOR/38Nd7df8AHpMePuHr9K4T4Ltn4bWYzkLPOB/39avJLfxI9CxRiiikWJ3xS0UUAGKMUUUAFGKKKACjAopaAExRiiigDzT4yKW0zw5gf8xuDn8Gr0lRxz6V5z8YWC6T4dbGca5bnHrw9ejqeB9KZC+Ji9KKKKRYUUGigBMUtFFABRRRQAlLRwKKAE5z7UYpaKAPNvCZz8YPGvBHy2w9v9WK9JrznwwT/wALh8ZKScmO1I+nlivRqbIhsFHXpRRSLDFGKKKACikIz1pc0AFFFFAAcUUUUAFcB8Y/+ScXZx0mhP0/eCu/6iuG+LieZ8NNVOM7PLb8nFBM/hZ1+n4/s+3xz+6X+VWqz9Gk83RbF8Y3QIf0FaAoCOyCiiigoMUlLRQAlGKXGKO1ABiijtRQAUCjtRQAh6VwHw2Qre+KnBO06vIAD2OB/jXoB6VwPw+kJ13xjDyFTVmIH1A/woM5fEjvaMUUo5FBoFFFGKAE9qKWigBKCoJ70YooAAOuaTGKXPHNGKAGEkHgCnKTjk5I64oHBpcHB5zQAzf7H86KTafUflRQBwnxXkI0C0i7S3sKnj/aru4BiCMeiiuD+KpA0fTB0LahCPqM8130Q/dKB0wKXUzj8TH0GijHFM0CiiigANGKMUUAFFFFABRRRQAVWv22WE7eiN/KrNUNYONGvDx/qW69OlBMtmcp8Ilx8PLM/wB6WY/+RDXdVxHwl/5JtpfBH+s/H52rt6SCHwoKWkoplC0lFFAC0mKKKACiiigAo70UZoAK4DXTu+MPhVP7ttdOP++cV39ee6sc/Gzw6O/2C479OKCJ9D0OkoooLCiiigAoo5ooAWkozRQAUtIRRQAD6UUUUAIeledfCfDxeKpx0fXZ8fkv+Neit0rzn4Oj/iU+IG9dbn/klBD+JHo4ooFLQWJRRzRQAUUGigAo70UUAFFFFABRRRQBx3xSYJ8M9eJxzbEc+5FbfhgY8L6SP+nOL/0EVz/xbIHwv1zJxmFR/wCRFro/DoK+G9LB6i0iz/3yKCPtGnRQaKCxaQ0UUAFFIzBRk9KWgAooFFABRRRQAUtJ2ooA878W8/FnwOo5+W7J/wC+Vr0QdK868UHPxh8GLzxBdn9Fr0WglBS0lLQUJS0UlAC0lFFABRRRQAUUUUAFGOKKCOKAPO/haCLnxh0/5Ds3/oK16JXnPwnbe3i5u/8Ab04/Ra9GoJjsLSGiloKEopaSgBaSiloAKSiigAooooATByea4T4x/wDJLtY/3V/9CFd5XBfGU/8AFrtX+if+hCgTOv0hf+JLZL2+zx/+gim2+lRW+pXV6ru0tzs3gnj5Rgf59zU2m/8AIMtOc/uU59eBVmgFsLRRRQMKWkooAKKKKACiiloASjrRRQAd682uv+TgrD/sDSf+h16T3rza++X4/wClHH3tHl5z/tUEy6HpNBoooKOU8aeFbjxJo6wW06R3EcwlUSk7TwQRkdPvZ6Hp75rzaP4I6nHP9oWXThLndk3EpOf++a90orqpYypSgoJJpbXSdiZQTdzH8L6M+g+G7PTZZVllhVi7oMDczFiB7DOM98ZwOlbFFFYTm5yc5bvUaVlYKKWkqBhRQaKAFpKKKAILoA2kwYZGw5H4VwHwSOfhvbj0uZwP++zXoM/+ofjPynivPPgif+Lcw/8AX1P/AOhmmQ/iPSKKKM0iwpaQdaKACiiigAoozRQAUtJRQAUUUYoA8z+MxCaHoDn+HW4Dn8Hr0iI/IuPSvN/jUT/wj2hFRyNbgPX/AGZK9KjH7sfSmQviY4UUUtIsSiijigAooooAKKKKACiijFABQaKKAPN/D5I+NXixSettbED22ivSB0rzfQyT8b/FBI6WduAfwFej02Zw6i0GjNFI0DNFFHSgAooo60AHSiijFABQTj3oo5oAP0rjPiou74Z63zjEII/BhXZ1yXxLTf8ADfXh3+ysR9eKCZbM1/DZJ8N6aWzn7NH/AOgitbvWJ4Rx/wAIhpO05H2SPk/7orb70MIfCgzRRRQUFHejmg0AFFFFABRRRQAUUUUAJXA+A2jHizxnGv3xqALcY/h4/rXfV574IZf+E+8bIpPF5EefdP8A9dBnPdHodJRR2oNBaKKTmgBaM0UUAFFGKKAE60YpaMUANOMHNLnIoNHtQAmW/uj86KdiigDzv4pFfJ0BCfv6rCP5mvQh0H0rzv4nOPtvhiM/xamhBB6HBr0UcgUdTOPxMWjvRRQaB1ooooABRQaBQAUUYo70AFHeig0AHesrxIxXw5qLDqLd+h9q1axfFjlPCeqsByLST/0E0Ez+FmV8MEMfw30YEDPkk8f7xrr65T4bps+HWhD1tUP511dAQ+FBRRRQUGaKMUUAFFHSigAooooAWkoooAQ1wGoKX+N2jH+5pc7fqB/Wu/NefTIW+OdoQT8ukSMR6DeB/Wgzn09T0KlpKKDQKKMUUALSUUtACUUUUAFHeiigAo70ZooARuled/CBi2i67n/oNXH8kr0N/un6V578Hhnw5q0uc+brFw3/AKCP6UEP4keiCiiigsKKKKACiiigApaSigBaKKSgBaKKSgDivitEv/CsNcXOB5II+u8Gui8OZPhrSiev2OL/ANAFcz8X32/C7WvdYh19ZVrqNCBXQNOU9RbRZ/75FBH2jRo70UUFhniilooASiiigAooooAKKKKAFpKKDQB514mb/i8ng1Mf8u11/If4V6LXnfiRFb4z+ETnkWl0cflXoZoJQuaKTGaXFBQUZoooAM0UUUALSUUUAFFFFAAKKOtBoA86+FC7T4tOc516f+S16LXnHwkctF4qBGCuvXAz69K9HzQKOwUUUUDEpaKKACiiigApaSjNABS0lFABXB/GTn4Xaxx/Cv8A6EK7yuC+Mpx8LtX9wn/oQoEzsNI40axA/wCfeP8A9BFXagtRizhGMfIOPTip8UAtgoxRRQMWkopaAEo60UUALSUUUAFFFFAB3rzfUV/4v9oxB66PNn/vo16R3rzXU2/4v/oYGf8AkETZ/M0yZdD0oUtIKKRQUUU3d82MHp1oAdRmiloASlpKKACiiloASijvS0ART58mTHXacV538Es/8K7iz/z9z/8AoZr0SXiJ/wDdNedfBFs/D1BjkXc+f++qZD+JHpNFFFIsKKKKAFpKKKACiiigAooooAKKKOaAPNPjV/yLWkEZyNXg/k1ekR/6tfpXnXxm/wCRX0z/ALC9tn/x6vRIv9WvOeKfQzXxMkoNBopGgUUDiigAoo70UAHeiijpQAUZoooAKKKCKAPNtJ/5Lp4g4xmwgPX2Fek15xpmB8dNcGBzpsB6816PimzOHUKKKKRoFFFFABRQRmigAoozRQAUUdqSgBelcx8RAG+Hev56fYpP5V09c548wfAWvAjP+gy/+gmgmfwsl8HSCXwdpDDobSP/ANBFb1c34CfzPAWiMe9pH/KukpsUPhQUhzg4PNLmikWAzjmikpaAEpe1FFABRQKKACgUYooADXnXgw7fiX42iHeaF/8Ax2vRK878LEr8XPGMbNklLYgeg20Gc90eiUtGKMUGgUUlLmgAooooAKKMUYoAKKKKAEoHPWlpKADB/wAmilzRQB5z8Rl3+I/CC9zqPH4KTXoorzjx+S3jDwggwP8ATc9cfwn/ABr0ejqZ092FL3pKWg0CijtRQAZozSUtABR3oo60AFGaKKAErn/HDFPBOssOCLWT+VdDXNePTjwJrR/6dn/lQiZ/CxfASeV4C0FP+nKJvzGa6TvWF4MXb4K0QAY/0KL/ANBFbtAR2QUUA80UFBmiiigAooooAKKKKACiiigBK8/GH+Of+5ox/WQV6BXAQ4PxyuORkaMP/RlNGU+nqegUUUUjUKKWkoAKKMUUAFFFGaADNFFFACUtFGKAGSnETH2rz/4N/wDIlzt13ajcH/x6u+m4gcnptPSuE+Do/wCKDVs/evLg/wDkQ0+hm/jR6BQetFFI0AUUUtACUUtJQAtFFJQAUUUUAFFFFAHAfGUn/hV+qD1aAf8AkZK7PTBt0qzUjBECDH4CuK+NBA+Gd+P70sA/8irXcWIAsoFHQRKP0p9CF8TLNFFFIsWikooAKKKKACjNFFAC0lFFAB3oo70UAeda8f8Ai9/hcf8AUPuP516JXnur8/HLw8D20q4I+ua9DoJiFFFFBQYooooAWkoooAKKKKACiiigBOlLRRQB518Jk2weKD/e125P6ivRa87+EwYWniXPT+3brH5ivRRQTHYSiiigoKWkooAKKWigBKKWigBKKDRQAVwPxm/5Jdq30T/0IV3tcF8Zhn4XatnsE/8AQhQJ7Haac2/TbV8YzEp/SrWar2W37Db7fu+WuPyqxQC2CiiloGJRRRQAUUUUAFFFFAAaKO1FACV5tqHP7QGjYHTSJs/ma9Jrze/OPj/pPfOjy/h81NEy6HogmjMxiDgyKoYr3AOcfyP5VLUSwRJK8qoA8mNzdzjpUtIoWkoooAKKKM84oAKWkpaAEpaSigAooooAZJzG2emK84+CP/IhN/1/T4/OvR5P9Ww9jXnfwSIPw/GBjF5Pz6/NTIfxI9HooopFhRR0ooAKKKKAFpO9GaO9ABRRRQAUUUdqAPOfjKu/wpp/p/atvn8zXoUQxEo9q87+NAJ8H2ZHbU7f+Zr0SD/VJ/uim9jNfGySiiikaC0lFFABQKOaBQAUUUUAFFFFABRmiigDzmxU/wDC99WJ/wCgVD+PNeiEkD1rzu0dh8e</t>
   </si>
 </sst>
 </file>
@@ -518,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -561,25 +609,25 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F2">
         <v>207</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -587,25 +635,25 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F3">
         <v>207</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -613,25 +661,25 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F4">
         <v>207</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H4" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -639,25 +687,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F5">
         <v>152</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -665,25 +713,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F6">
         <v>207</v>
       </c>
       <c r="G6" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H6" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -697,22 +745,22 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>207</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I7">
         <v>5</v>
@@ -726,22 +774,22 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F8">
         <v>69</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I8">
         <v>11</v>
@@ -750,7 +798,7 @@
         <v>58</v>
       </c>
       <c r="K8" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -758,22 +806,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F9">
         <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I9">
         <v>11</v>
@@ -782,7 +830,7 @@
         <v>58</v>
       </c>
       <c r="K9" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -790,22 +838,22 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F10">
         <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I10">
         <v>11</v>
@@ -814,7 +862,7 @@
         <v>58</v>
       </c>
       <c r="K10" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -822,22 +870,22 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F11">
         <v>69</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I11">
         <v>11</v>
@@ -846,7 +894,7 @@
         <v>58</v>
       </c>
       <c r="K11" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -854,22 +902,22 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F12">
         <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I12">
         <v>11</v>
@@ -878,7 +926,7 @@
         <v>58</v>
       </c>
       <c r="K12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -886,22 +934,22 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F13">
         <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I13">
         <v>11</v>
@@ -910,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="K13" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -918,22 +966,22 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F14">
         <v>69</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I14">
         <v>11</v>
@@ -942,7 +990,7 @@
         <v>58</v>
       </c>
       <c r="K14" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -950,22 +998,22 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F15">
         <v>207</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I15">
         <v>5</v>
@@ -974,7 +1022,7 @@
         <v>202</v>
       </c>
       <c r="K15" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -982,22 +1030,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F16">
         <v>207</v>
       </c>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1006,7 +1054,7 @@
         <v>202</v>
       </c>
       <c r="K16" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1014,22 +1062,22 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F17">
         <v>207</v>
       </c>
       <c r="G17" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I17">
         <v>5</v>
@@ -1038,7 +1086,7 @@
         <v>202</v>
       </c>
       <c r="K17" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1046,22 +1094,22 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F18">
         <v>207</v>
       </c>
       <c r="G18" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -1070,7 +1118,147 @@
         <v>202</v>
       </c>
       <c r="K18" t="s">
-        <v>48</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19">
+        <v>109</v>
+      </c>
+      <c r="G19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19">
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <v>102</v>
+      </c>
+      <c r="K19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20">
+        <v>115</v>
+      </c>
+      <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20">
+        <v>8</v>
+      </c>
+      <c r="J20">
+        <v>107</v>
+      </c>
+      <c r="K20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21">
+        <v>115</v>
+      </c>
+      <c r="G21" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21">
+        <v>8</v>
+      </c>
+      <c r="J21">
+        <v>107</v>
+      </c>
+      <c r="K21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22">
+        <v>91</v>
+      </c>
+      <c r="G22" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22">
+        <v>6</v>
+      </c>
+      <c r="J22">
+        <v>85</v>
+      </c>
+      <c r="K22" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
